--- a/Pathways/HMBA48h_vs_HMBA24h/ORA/ORA_output_HMBA48h_vs_HMBA24h.xlsx
+++ b/Pathways/HMBA48h_vs_HMBA24h/ORA/ORA_output_HMBA48h_vs_HMBA24h.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3026" uniqueCount="3026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3031" uniqueCount="3031">
   <si>
     <t xml:space="preserve">ONTOLOGY</t>
   </si>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">355/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Trim10/Mturn/Cited2/Fech/Tfrc/Sox6/Cnot4/Slc11a2/Fos/Bpgm/Klf1/Rhd/Fasn/Ubash3b/Actn1/Gba/Dnase2a/Junb/Vps33a/Fbxw7/Tmem14c/Cib1/Pknox1/Rara/Gnas/Rb1/Gfi1b/Asxl2/Smap1/Sirt1/Kat6a/Abi1/Psen1/Ctnnb1/Tcf3/Wdr1/Ldb1/Pabpc4/Hcls1/Lyar/Prkca/Flna/Srf/Prmt1/Stat5a/Lmo2/Stat5b/Ptpn6/Gata2/Lrrk1/Zfp36l1/Snx10/Fli1/Nrros/Gab2/Cbfb/Il4/Csf1/Fes/Tgfb1/Spi1/Tyrobp/Myb/Cdk6/Jak3</t>
+    <t xml:space="preserve">Alas2/Car2/Fam210b/Jak3/Slc4a1/Myb/Abcb10/Tgfb1/Cdk6/Slc11a2/Fech/Tal1/Dmtn/Ank1/Epb42/Trim10/Cbfb/Spi1/Gab2/Klf1/Cited2/Rhag/Actn1/Fli1/Cnot4/Stat5b/Ptpn6/Fasn/Pabpc4/Gnas/Lrrk1/Tmem14c/Flna/Mturn/Fbxw7/Gba/Nrros/Ldb1/Dnase2a/Rhd/Tyrobp/Stat5a/Il4/Gata2/Lmo2/Prmt1/Srf/Fes/Zfp36l1/Csf1/Snx10/Pknox1/Ctnnb1/Vps33a/Wdr1/Rb1/Tfrc/Hcls1/Sox6/Smap1/Cib1/Prkca/Tcf3/Ubash3b/Psen1/Sirt1/Bpgm/Fos/Junb/Rara/Lyar/Kat6a/Gfi1b/Abi1/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045321</t>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">769/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr1/Pld2/Mink1/Egr3/Wnk4/St3gal1/Cd47/Snca/Prdx2/Tfrc/Grn/Prnp/Tsc1/Adam10/Aplf/Lamp1/Ldlr/D6Wsu163e/Prex1/Hs1bp3/Anxa3/Ticam1/Zbtb7b/Gba/Hdac5/Fzd5/Atp7a/Ap3d1/Shb/Pknox1/Bax/Rara/Fcho1/Rnf168/Nck1/Bid/Tusc2/Swap70/Fnip1/Phf10/Gpr89/Psen1/Ctnnb1/Elf4/Tcf3/Was/Nedd4/Phb2/Ifngr1/Fkbp1a/Impdh2/Hspd1/Ap1g1/Cd320/Shld2/Srf/Irf2bp2/Stat5a/Samsn1/Fkbp1b/Vsir/Itgb2/Smarcd1/Fzd7/Cst7/Zbtb32/Pik3cd/Trp53/Stat5b/Fcgr3/Ptpn6/Il27ra/Sema4a/Kat2a/Gata2/Plcg2/Traf3ip2/Unc13d/Vav1/Zfp36l1/Psmb10/Cplx2/Cd37/Gab2/Nr1d1/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Wdfy4/Prr7/Pik3r6/Cd48/Il4/Ywhaz/Fes/Cxcr4/Lgals9/Dock2/Spn/Mmp14/Selplg/Lcp2/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Tyrobp/Hdac7/Btk/Ptprc/Myb/Cdk6/Coro1a/Cmtm7/Jak3/Apbb1ip/Lgals1/Dpp4/P2rx7/Tbc1d10c/Il1rl1/Cd84/Nfam1/Syk/Lcp1</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Hdac7/Btk/Egr1/Cmtm7/Dock2/Jak3/Laptm5/Nfam1/Snca/Wdfy4/Il1rl1/Syk/Slc4a1/Myb/Ptprc/Wnk4/Mink1/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Ywhaz/Cdk6/Grn/Spn/Apbb1ip/Tsc1/St3gal1/Lamp1/Cd44/Cd47/Dock8/Cd84/Ripor2/Cbfb/Spi1/Gab2/Tbc1d10c/Vav1/P2rx7/Lcp1/Plcg2/Lgals9/Cxcr4/Kat2a/Stat5b/Prex1/Adam10/Pld2/Ldlr/Hs1bp3/Ptpn6/Dpp4/Unc13d/Cd48/Gba/Irf2bp2/Ap1g1/Smarcd1/Trp53/Aplf/Lcp2/Egr3/Zbtb7b/Selplg/D6Wsu163e/Ticam1/Tyrobp/Pik3cd/Stat5a/Fzd5/Il4/Gata2/Lgals7/Mmp14/Fzd7/Sema4a/Cd37/Pik3r6/Srf/Fes/Zfp36l1/Pknox1/Ctnnb1/Impdh2/Ap3d1/Il27ra/Hdac5/Prr7/Rnf168/Nr1d1/Havcr2/Nedd4/Fcgr3/Anxa3/Tfrc/Cplx2/Itgb2/Tcf3/Psmb10/Atp7a/Swap70/Vsir/Psen1/Bid/Tusc2/Fkbp1a/Traf3ip2/Samsn1/Hspd1/Ifngr1/Fnip1/Rara/Bax/Cd320/Elf4/Phb2/Zbtb32/Shld2/Fkbp1b/Nck1/Cst7/Gpr89/Fcho1/Shb/Phf10/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002262</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">179/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Ampd3/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Trim10/Cited2/Fech/Sox6/Slc11a2/Bpgm/Klf1/Rhd/Dnase2a/Tmem14c/Pknox1/Bax/Bcl2l11/Rb1/Gfi1b/Smap1/Tcf3/Gpi1/Ldb1/Hcls1/Lyar/Mthfd1/Srf/Prmt1/Stat5a/Lmo2/Pik3cd/Stat5b/Gata2/Traf3ip2/Zfp36l1/Pde4b/Csf1/Cd44/Spi1/Cdk6/Jak3</t>
+    <t xml:space="preserve">Alas2/Fam210b/Ampd3/Jak3/Slc4a1/Abcb10/Cdk6/Slc11a2/Fech/Tal1/Dmtn/Ank1/Cd44/Epb42/Trim10/Spi1/Klf1/Cited2/Rhag/Stat5b/Tmem14c/Ldb1/Dnase2a/Rhd/Pik3cd/Stat5a/Gata2/Lmo2/Prmt1/Srf/Zfp36l1/Csf1/Pknox1/Rb1/Mthfd1/Hcls1/Sox6/Smap1/Bcl2l11/Tcf3/Pde4b/Bpgm/Traf3ip2/Bax/Lyar/Gfi1b/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006779</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">31/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Spta1/Slc6a9/Ank1/Abcb10/Sptb/Abcb6/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Snx3/Pgrmc1/Cox10/Rsad1</t>
+    <t xml:space="preserve">Alas2/Spta1/Sptb/Abcb6/Slc6a9/Abcb10/Slc11a2/Fech/Ank1/Urod/Hmbs/Tmem14c/Rsad1/Cox10/Pgrmc1/Alad/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033014</t>
@@ -127,7 +127,7 @@
     <t xml:space="preserve">636/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr1/Mink1/Egr3/St3gal1/Cd47/Prdx2/Tfrc/Prnp/Tsc1/Aplf/Lamp1/Prex1/Hs1bp3/Ticam1/Zbtb7b/Gba/Hdac5/Fzd5/Atp7a/Ap3d1/Shb/Pknox1/Bax/Rara/Fcho1/Rnf168/Nck1/Bid/Tusc2/Swap70/Fnip1/Phf10/Gpr89/Psen1/Ctnnb1/Elf4/Tcf3/Was/Nedd4/Phb2/Fkbp1a/Impdh2/Hspd1/Ap1g1/Cd320/Shld2/Srf/Irf2bp2/Stat5a/Samsn1/Fkbp1b/Vsir/Itgb2/Smarcd1/Fzd7/Zbtb32/Pik3cd/Trp53/Stat5b/Ptpn6/Il27ra/Sema4a/Kat2a/Plcg2/Traf3ip2/Unc13d/Vav1/Zfp36l1/Psmb10/Cd37/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Wdfy4/Prr7/Pik3r6/Cd48/Il4/Cxcr4/Lgals9/Dock2/Spn/Mmp14/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Tyrobp/Hdac7/Btk/Ptprc/Myb/Cdk6/Coro1a/Cmtm7/Jak3/Apbb1ip/Lgals1/Dpp4/P2rx7/Tbc1d10c/Cd84/Nfam1/Syk/Lcp1</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Hdac7/Btk/Egr1/Cmtm7/Dock2/Jak3/Laptm5/Nfam1/Wdfy4/Syk/Slc4a1/Myb/Ptprc/Mink1/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Cdk6/Spn/Apbb1ip/Tsc1/St3gal1/Lamp1/Cd44/Cd47/Dock8/Cd84/Ripor2/Cbfb/Spi1/Tbc1d10c/Vav1/P2rx7/Lcp1/Plcg2/Lgals9/Cxcr4/Kat2a/Stat5b/Prex1/Hs1bp3/Ptpn6/Dpp4/Unc13d/Cd48/Gba/Irf2bp2/Ap1g1/Smarcd1/Trp53/Aplf/Egr3/Zbtb7b/Ticam1/Tyrobp/Pik3cd/Stat5a/Fzd5/Il4/Lgals7/Mmp14/Fzd7/Sema4a/Cd37/Pik3r6/Srf/Zfp36l1/Pknox1/Ctnnb1/Impdh2/Ap3d1/Il27ra/Hdac5/Prr7/Rnf168/Havcr2/Nedd4/Tfrc/Itgb2/Tcf3/Psmb10/Atp7a/Swap70/Vsir/Psen1/Bid/Tusc2/Fkbp1a/Traf3ip2/Samsn1/Hspd1/Fnip1/Rara/Bax/Cd320/Elf4/Phb2/Zbtb32/Shld2/Fkbp1b/Nck1/Gpr89/Fcho1/Shb/Phf10/Was</t>
   </si>
   <si>
     <t xml:space="preserve">CC</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">524/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Atp6v0d1/Trp53inp2/Ctns/Abcb6/H2-T23/Wdr81/Mfsd1/Pip4p1/Ctsd/Slc36a1/Dpp7/Grn/Mcoln1/Tpp1/Rubcnl/Rragc/Atp6v1c1/Clcn7/Glmp/Neu1/Vps26a/Atp6v1e1/Serpinb1a/Atg9a/Slc11a2/Vps11/Fnip2/Lamp1/Ldlr/Cltc/Atp6v0a1/Map1lc3b/Uvrag/Lamtor1/Gba/Trp53inp1/Zfyve26/Atp6ap2/Dnase2a/Clcn3/Vps33a/Tmem199/Atp6v1a/Ftl1/Atp6v1b2/Hexa/Flcn/Lamtor3/Chmp3/C9orf72/Gabarap/Atp6v0b/Vps35/Ctsa/Lrrc8a/Rmc1/Pip4k2c/Atp6v1g1/Nbr1/Arl8b/Slc39a8/Snx2/Snap29/Fnip1/Clec16a/Sh3glb1/Psen1/Got1/Man2b1/Ubqln4/Ifitm2/Hsp90ab1/Shkbp1/Itm2c/Tmem97/Gla/Ap1g1/Anxa11/Dtx3l/Pcsk9/Srgn/Arsk/Cst7/Abca2/Cyb561/Prdx6/Gusb/Unc13d/Man2b2/Ankrd27/Cxcr4/Apoe/Laptm5/Mst1r/Unc93b1</t>
+    <t xml:space="preserve">Atp6v0d1/Ctsd/Laptm5/Mfsd1/Tpp1/Abcb6/Vps26a/Rragc/Cltc/Mst1/Slc11a2/Ctns/Grn/Atp6v1c1/Atp6v1e1/Ankrd27/Trp53inp2/Lamp1/Pip4p1/Dpp7/Glmp/Fnip2/Man2b2/Mcoln1/Abca2/Slc36a1/Vps11/Wdr81/Cxcr4/Unc93b1/Clcn7/Apoe/Map1lc3b/Mst1r/Ldlr/Atp6ap2/Serpinb1a/Unc13d/Gusb/Atg9a/Uvrag/Atp6v1b2/Gba/Neu1/Ap1g1/Atp6v1a/Prdx6/Clcn3/Gabarap/Atp6v0a1/Dnase2a/H2-T23/Cyb561/Trp53inp1/Ctsa/Zfyve26/Atp6v0b/Lamtor3/Lamtor1/Anxa11/Vps33a/Vps35/Lrrc8a/Sh3glb1/Ubqln4/Chmp3/Srgn/Man2b1/Dtx3l/Arl8b/Hsp90ab1/Tmem199/Rubcnl/Flcn/Ftl1/Gla/Psen1/Hexa/Snx2/Rmc1/C9orf72/Ifitm2/Fnip1/Pcsk9/Itm2c/Arsk/Got1/Slc39a8/Tmem97/Nbr1/Atp6v1g1/Cst7/Clec16a/Shkbp1/Snap29/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042110</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">444/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr1/Mink1/Egr3/Cd47/Prdx2/Tfrc/Prnp/Tsc1/Prex1/Hs1bp3/Zbtb7b/Gba/Fzd5/Atp7a/Ap3d1/Shb/Pknox1/Bax/Rara/Fcho1/Nck1/Bid/Phf10/Gpr89/Psen1/Ctnnb1/Elf4/Tcf3/Was/Nedd4/Fkbp1a/Hspd1/Srf/Stat5a/Fkbp1b/Vsir/Itgb2/Smarcd1/Fzd7/Zbtb32/Trp53/Stat5b/Ptpn6/Il27ra/Sema4a/Kat2a/Traf3ip2/Vav1/Zfp36l1/Psmb10/Cd37/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Wdfy4/Prr7/Pik3r6/Cd48/Il4/Cxcr4/Lgals9/Dock2/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Ptprc/Myb/Cdk6/Coro1a/Jak3/Apbb1ip/Lgals1/Dpp4/P2rx7/Cd84/Syk/Lcp1</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Egr1/Dock2/Jak3/Laptm5/Wdfy4/Syk/Slc4a1/Myb/Ptprc/Mink1/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Cdk6/Spn/Apbb1ip/Tsc1/Cd44/Cd47/Dock8/Cd84/Ripor2/Cbfb/Spi1/Vav1/P2rx7/Lcp1/Lgals9/Cxcr4/Kat2a/Stat5b/Prex1/Hs1bp3/Ptpn6/Dpp4/Cd48/Gba/Smarcd1/Trp53/Egr3/Zbtb7b/Stat5a/Fzd5/Il4/Lgals7/Fzd7/Sema4a/Cd37/Pik3r6/Srf/Zfp36l1/Pknox1/Ctnnb1/Ap3d1/Il27ra/Prr7/Havcr2/Nedd4/Tfrc/Itgb2/Tcf3/Psmb10/Atp7a/Vsir/Psen1/Bid/Fkbp1a/Traf3ip2/Hspd1/Rara/Bax/Elf4/Zbtb32/Fkbp1b/Nck1/Gpr89/Fcho1/Shb/Phf10/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002684</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">705/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Cd36/Pld2/Appl2/Btnl10/Car2/Egr3/Cd47/H2-T23/Tfrc/Prnp/Adam10/Ermap/Lamp1/Fos/D6Wsu163e/Ticam1/Zbtb7b/Mospd2/Trim56/Fzd5/Tbk1/Usp9x/Ap3d1/Shb/Elf1/Bax/Rara/Fcho1/Nck1/Rnf185/Gnas/Hexim1/Swap70/Rb1/Gfi1b/Asxl2/Sirt1/Mia3/Fbxo38/Phf10/Nras/Psen1/Nono/Tcf3/Phb2/Ddx21/Gpi1/Pde4d/Rbck1/Dgkz/Matr3/Hspd1/Ap1g1/Cd320/Shld2/Hcls1/Prkca/Stat5a/Vsir/Itgb2/Smarcd1/Lpxn/Pik3cd/Trp53/Stat5b/Fcgr3/Ptpn6/Il27ra/Xrcc5/Gata2/Plcg2/Unc13d/Vav1/Zfp36l1/Ano6/Ubash3a/Cadm1/Pde4b/Cd37/Fut4/Gab2/Plvap/Rac1/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Il4/Csf1/Fes/Lgals9/Spn/Mmp14/Lcp2/Tgfb1/Ccdc88b/Cd44/Laptm5/Fyb/Spi1/Tyrobp/Btk/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Myo1g/Rftn1/P2rx7/Il1rl1/Cd84/Nfam1/Syk</t>
+    <t xml:space="preserve">Car2/Lgals1/Spta1/Btk/Jak3/Laptm5/Nfam1/Myo1g/Appl2/Il1rl1/Rftn1/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ano6/Prnp/Btnl10/Ccdc88b/Rac2/Tgfb1/Spn/Ermap/Fyb/Lamp1/Cd44/Rac1/Cd47/Dock8/Cd84/Ripor2/Cbfb/Spi1/Gab2/Vav1/P2rx7/Plcg2/Lgals9/Stat5b/Cd36/Adam10/Pld2/Ptpn6/Dpp4/Xrcc5/Gnas/Unc13d/Tbk1/Ap1g1/Smarcd1/Trp53/Usp9x/Lcp2/Egr3/Zbtb7b/Ubash3a/H2-T23/D6Wsu163e/Trim56/Fut4/Ticam1/Tyrobp/Elf1/Pik3cd/Stat5a/Fzd5/Il4/Gata2/Dgkz/Mmp14/Cd37/Pik3r6/Fes/Zfp36l1/Csf1/Nono/Ap3d1/Il27ra/Rb1/Mospd2/Rbck1/Havcr2/Matr3/Fcgr3/Plvap/Tfrc/Hcls1/Hexim1/Itgb2/Prkca/Tcf3/Pde4b/Swap70/Cadm1/Vsir/Psen1/Fbxo38/Sirt1/Fos/Hspd1/Rara/Bax/Nras/Rnf185/Cd320/Phb2/Gfi1b/Shld2/Asxl2/Ddx21/Nck1/Mia3/Fcho1/Shb/Pde4d/Phf10/Gpi1/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034101</t>
@@ -190,7 +190,7 @@
     <t xml:space="preserve">143/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Ampd3/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Trim10/Cited2/Fech/Sox6/Slc11a2/Bpgm/Klf1/Rhd/Dnase2a/Tmem14c/Pknox1/Rb1/Gfi1b/Smap1/Tcf3/Gpi1/Ldb1/Hcls1/Lyar/Srf/Prmt1/Stat5a/Lmo2/Stat5b/Gata2/Zfp36l1/Spi1/Cdk6/Jak3</t>
+    <t xml:space="preserve">Alas2/Fam210b/Ampd3/Jak3/Slc4a1/Abcb10/Cdk6/Slc11a2/Fech/Tal1/Dmtn/Ank1/Epb42/Trim10/Spi1/Klf1/Cited2/Rhag/Stat5b/Tmem14c/Ldb1/Dnase2a/Rhd/Stat5a/Gata2/Lmo2/Prmt1/Srf/Zfp36l1/Pknox1/Rb1/Hcls1/Sox6/Smap1/Tcf3/Bpgm/Lyar/Gfi1b/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005769</t>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">291/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Slc30a10/Abcb6/Neurl1b/H2-T23/Wdr81/Tfrc/Washc2/Clcn5/Snx8/Washc5/Vps26a/Pheta2/Als2/Picalm/Slc11a2/Vps11/Ptpn23/Ldlr/Uvrag/Numb/Pikfyve/Rab22a/Wdfy1/Zfyve26/Igf2r/Fzd5/Trak2/Clcn3/Vps33a/Dnajc13/Atp7a/Ap3d1/Chmp3/Tom1/Ehd1/Nipa1/Vps35/Gripap1/Siah1b/Washc4/Sh3glb1/Snx3/Psen1/Hspd1/Ap1g1/Snx5/Dtx3l/Ehd3/Pcsk9/Ankrd13b/Plpp2/Tmem230/Cmtm6/Ankrd27/Rac1/Rcc2/Havcr2/Cxcr4/Apoe/Coro1a/Rin3</t>
+    <t xml:space="preserve">Atp6v0d1/Picalm/Coro1a/Abcb6/Vps26a/Slc30a10/Slc11a2/Washc5/Washc2/Ankrd27/Rac1/Rcc2/Ptpn23/Rin3/Pheta2/Vps11/Wdr81/Snx8/Cxcr4/Als2/Clcn5/Apoe/Igf2r/Ldlr/Pikfyve/Cmtm6/Wdfy1/Uvrag/Dnajc13/Ehd1/Rab22a/Ap1g1/Clcn3/Numb/H2-T23/Neurl1b/Ankrd13b/Fzd5/Zfyve26/Ap3d1/Vps33a/Vps35/Sh3glb1/Havcr2/Chmp3/Tfrc/Trak2/Snx5/Dtx3l/Ehd3/Atp7a/Tmem230/Washc4/Plpp2/Psen1/Nipa1/Hspd1/Pcsk9/Gripap1/Siah1b/Tom1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030218</t>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">133/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Trim10/Cited2/Fech/Sox6/Slc11a2/Bpgm/Klf1/Rhd/Dnase2a/Tmem14c/Pknox1/Rb1/Gfi1b/Smap1/Tcf3/Ldb1/Hcls1/Lyar/Srf/Prmt1/Stat5a/Lmo2/Stat5b/Gata2/Zfp36l1/Spi1/Cdk6/Jak3</t>
+    <t xml:space="preserve">Alas2/Fam210b/Jak3/Slc4a1/Abcb10/Cdk6/Slc11a2/Fech/Tal1/Dmtn/Ank1/Epb42/Trim10/Spi1/Klf1/Cited2/Rhag/Stat5b/Tmem14c/Ldb1/Dnase2a/Rhd/Stat5a/Gata2/Lmo2/Prmt1/Srf/Zfp36l1/Pknox1/Rb1/Hcls1/Sox6/Smap1/Tcf3/Bpgm/Lyar/Gfi1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0061515</t>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">84/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Cited2/Sox6/Slc11a2/Bpgm/Klf1/Rhd/Fbxw7/Abi1/Pabpc4/Lyar/Flna/Srf/Ptpn6/Lrrk1/Fli1/Nrros/Tyrobp/Myb</t>
+    <t xml:space="preserve">Alas2/Fam210b/Slc4a1/Myb/Abcb10/Slc11a2/Tal1/Dmtn/Ank1/Epb42/Klf1/Cited2/Rhag/Fli1/Ptpn6/Pabpc4/Lrrk1/Flna/Fbxw7/Nrros/Rhd/Tyrobp/Srf/Sox6/Bpgm/Lyar/Abi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043112</t>
@@ -250,7 +250,7 @@
     <t xml:space="preserve">65/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Agtr1a/Optn/Pheta2/Als2/Ache/Ldlr/Mylip/Snx25/Uvrag/Lamtor1/Arfgef2/Sh3glb1/Psen1/Nedd4/Dtx3l/Ehd3/Pcsk9/Abca2/Fut8/Apoe/Tgfb1/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Snca/Tgfb1/Pheta2/Abca2/Snx25/Optn/Als2/Arfgef2/Apoe/Ldlr/Ache/Uvrag/Fut8/Agtr1a/Lamtor1/Mylip/Sh3glb1/Nedd4/Dtx3l/Ehd3/Psen1/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006778</t>
@@ -265,7 +265,7 @@
     <t xml:space="preserve">42/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Spta1/Slc6a9/Ank1/Abcb10/Sptb/Abcb6/Hebp1/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Snx3/Pgrmc1/Cox10/Rsad1</t>
+    <t xml:space="preserve">Alas2/Spta1/Sptb/Abcb6/Slc6a9/Abcb10/Slc11a2/Fech/Ank1/Urod/Hebp1/Hmbs/Tmem14c/Rsad1/Cox10/Pgrmc1/Alad/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">MF</t>
@@ -283,7 +283,7 @@
     <t xml:space="preserve">370/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Arhgap23/Itsn1/Kalrn/Agfg2/Ranbp10/Als2/Gdpgp1/Asap3/Fgd6/Prex1/Arhgap12/Lamtor1/Rab3ip/Rgl1/Arrb1/Arfgef2/Smcr8/Rabep1/Tbc1d24/Dennd2c/Arhgef12/Arhgap15/Gpsm2/Flcn/Plekhg2/Lamtor3/Elmod2/C9orf72/Myo9a/Acap3/Rabgap1/Arhgap35/Smap1/Arhgef11/Itsn2/Fnip1/Usp6nl/Iqgap1/Gopc/Rcc1/Dennd4b/Syngap1/Eef1b2/Arhgap9/Arhgef1/Dennd1c/Vav1/Rangrf/Ankrd27/Rgs2/Arhgef6/Gmip/Rgl2/Rcc2/Dock8/Arhgdig/Rgs1/Rgs14/Arhgef2/Dock2/Adap1/Rgs18/Arhgap27/Arhgef18/Elmo1/Tbc1d10c/Arap3/Arhgdib/Rin3</t>
+    <t xml:space="preserve">Rab3il1/Arap3/Dock2/Arhgef2/Arhgap23/Ankrd27/Arhgef1/Dock8/Arhgap27/Itsn1/Rcc2/Elmo1/Tbc1d10c/Vav1/Rin3/Agfg2/Arhgdib/Als2/Arfgef2/Rgl2/Rabep1/Prex1/Tbc1d24/Arhgef18/Kalrn/Gmip/Rgs18/Arhgef6/Arhgdig/Adap1/Rgs14/Rabgap1/Rangrf/Rab3ip/Arhgef12/Rgs2/Fgd6/Lamtor3/Dennd4b/Lamtor1/Gdpgp1/Rgs1/Smcr8/Eef1b2/Arhgap12/Arrb1/Dennd2c/Gpsm2/Plekhg2/Asap3/Rgl1/Smap1/Arhgap9/Flcn/Arhgef11/Ranbp10/Rcc1/C9orf72/Iqgap1/Dennd1c/Fnip1/Syngap1/Arhgap15/Arhgap35/Elmod2/Acap3/Myo9a/Gopc/Usp6nl/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060589</t>
@@ -304,7 +304,7 @@
     <t xml:space="preserve">446/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Ctns/Abcb6/H2-T23/Wdr81/Mfsd1/Pip4p1/Ctsd/Slc36a1/Dpp7/Grn/Mcoln1/Tpp1/Rragc/Clcn7/Glmp/Neu1/Vps26a/Serpinb1a/Slc11a2/Vps11/Fnip2/Lamp1/Ldlr/Cltc/Map1lc3b/Uvrag/Lamtor1/Gba/Zfyve26/Atp6ap2/Dnase2a/Clcn3/Vps33a/Atp6v1a/Ftl1/Hexa/Flcn/Lamtor3/Chmp3/C9orf72/Gabarap/Vps35/Ctsa/Lrrc8a/Rmc1/Atp6v1g1/Nbr1/Arl8b/Slc39a8/Snx2/Fnip1/Clec16a/Psen1/Got1/Man2b1/Ifitm2/Hsp90ab1/Shkbp1/Itm2c/Tmem97/Gla/Ap1g1/Anxa11/Dtx3l/Pcsk9/Srgn/Arsk/Cst7/Abca2/Cyb561/Prdx6/Gusb/Unc13d/Man2b2/Ankrd27/Cxcr4/Apoe/Laptm5/Unc93b1</t>
+    <t xml:space="preserve">Atp6v0d1/Ctsd/Laptm5/Mfsd1/Tpp1/Abcb6/Vps26a/Rragc/Cltc/Slc11a2/Ctns/Grn/Ankrd27/Lamp1/Pip4p1/Dpp7/Glmp/Fnip2/Man2b2/Mcoln1/Abca2/Slc36a1/Vps11/Wdr81/Cxcr4/Unc93b1/Clcn7/Apoe/Map1lc3b/Ldlr/Atp6ap2/Serpinb1a/Unc13d/Gusb/Uvrag/Gba/Neu1/Ap1g1/Atp6v1a/Prdx6/Clcn3/Gabarap/Dnase2a/H2-T23/Cyb561/Ctsa/Zfyve26/Lamtor3/Lamtor1/Anxa11/Vps33a/Vps35/Lrrc8a/Chmp3/Srgn/Man2b1/Dtx3l/Arl8b/Hsp90ab1/Flcn/Ftl1/Gla/Psen1/Hexa/Snx2/Rmc1/C9orf72/Ifitm2/Fnip1/Pcsk9/Itm2c/Arsk/Got1/Slc39a8/Tmem97/Nbr1/Atp6v1g1/Cst7/Clec16a/Shkbp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005764</t>
@@ -325,7 +325,7 @@
     <t xml:space="preserve">235/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/St3gal1/Tfrc/Grn/Tsc1/Aplf/Lamp1/D6Wsu163e/Anxa3/Ticam1/Zbtb7b/Atp7a/Shb/Rara/Rnf168/Swap70/Psen1/Hspd1/Ap1g1/Shld2/Itgb2/Trp53/Ptpn6/Il27ra/Sema4a/Gata2/Plcg2/Unc13d/Cplx2/Gab2/Rac2/Havcr2/Il4/Ywhaz/Fes/Lgals9/Dock2/Spn/Tgfb1/Spi1/Tyrobp/Ptprc/Myb/Coro1a/Jak3/Apbb1ip/Lgals1/Cd84/Syk/Lcp1</t>
+    <t xml:space="preserve">Lgals1/Dock2/Jak3/Syk/Myb/Ptprc/Coro1a/Rac2/Tgfb1/Ywhaz/Grn/Spn/Apbb1ip/Tsc1/St3gal1/Lamp1/Cd84/Spi1/Gab2/Lcp1/Plcg2/Lgals9/Pld2/Ptpn6/Unc13d/Ap1g1/Trp53/Aplf/Zbtb7b/D6Wsu163e/Ticam1/Tyrobp/Il4/Gata2/Sema4a/Fes/Il27ra/Rnf168/Havcr2/Anxa3/Tfrc/Cplx2/Itgb2/Atp7a/Swap70/Psen1/Hspd1/Rara/Shld2/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048872</t>
@@ -337,7 +337,7 @@
     <t xml:space="preserve">319/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Spta1/Ampd3/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Trim10/Prdx2/Cited2/Fech/Sox6/Slc11a2/Bpgm/Klf1/Rhd/Gba/Gigyf2/Dnase2a/Tmem14c/Lpcat3/Mtch2/Pknox1/Bax/Bcl2l11/Rb1/Tsc22d3/Zfp251/Gfi1b/Smap1/Ubap2l/Tcf3/Gpi1/Ldb1/Hcls1/Lyar/Mthfd1/Srf/Prmt1/Stat5a/Lmo2/Pik3cd/Stat5b/Gata2/Traf3ip2/Zfp36l1/Pmaip1/Pde4b/Rac1/Csf1/Tgfb1/Cd44/Spi1/Myb/Cdk6/Coro1a/Jak3/P2rx7</t>
+    <t xml:space="preserve">Alas2/Prdx2/Spta1/Fam210b/Ampd3/Jak3/Slc4a1/Myb/Coro1a/Abcb10/Tgfb1/Cdk6/Slc11a2/Fech/Tal1/Dmtn/Ank1/Cd44/Rac1/Epb42/Gigyf2/Trim10/Spi1/Klf1/Cited2/Rhag/P2rx7/Stat5b/Tmem14c/Mtch2/Pmaip1/Gba/Ldb1/Dnase2a/Rhd/Pik3cd/Stat5a/Gata2/Lmo2/Prmt1/Srf/Zfp36l1/Csf1/Pknox1/Rb1/Mthfd1/Hcls1/Lpcat3/Sox6/Smap1/Bcl2l11/Tcf3/Pde4b/Bpgm/Traf3ip2/Bax/Lyar/Gfi1b/Zfp251/Tsc22d3/Ubap2l/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002263</t>
@@ -361,7 +361,7 @@
     <t xml:space="preserve">51/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Spta1/Slc6a9/Ank1/Abcb10/Sptb/Abcb6/Hebp1/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Snx3/Pgrmc1/Mmachc/Cox10/Rsad1</t>
+    <t xml:space="preserve">Alas2/Spta1/Sptb/Abcb6/Slc6a9/Abcb10/Slc11a2/Fech/Ank1/Urod/Hebp1/Hmbs/Tmem14c/Rsad1/Cox10/Pgrmc1/Alad/Mmachc/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048821</t>
@@ -370,7 +370,7 @@
     <t xml:space="preserve">erythrocyte development</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Ank1/Fam210b/Epb42/Abcb10/Tal1/Rhag/Dmtn/Cited2/Sox6/Slc11a2/Bpgm/Klf1/Rhd/Lyar/Srf</t>
+    <t xml:space="preserve">Alas2/Fam210b/Slc4a1/Abcb10/Slc11a2/Tal1/Dmtn/Ank1/Epb42/Klf1/Cited2/Rhag/Rhd/Srf/Sox6/Bpgm/Lyar</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002521</t>
@@ -385,7 +385,7 @@
     <t xml:space="preserve">512/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Car2/Mink1/Egr3/St3gal1/Tal1/Prdx2/Cited2/Tfrc/Tsc1/Fos/Prex1/Hs1bp3/Fasn/Zbtb7b/Ubash3b/Gba/Hdac5/Fzd5/Junb/Fbxw7/Atp7a/Ap3d1/Shb/Pknox1/Bax/Rara/Gnas/Tusc2/Rb1/Gfi1b/Asxl2/Sirt1/Fnip1/Phf10/Gpr89/Psen1/Ctnnb1/Tcf3/Hcls1/Prkca/Srf/Irf2bp2/Stat5a/Vsir/Smarcd1/Fzd7/Trp53/Stat5b/Ptpn6/Sema4a/Kat2a/Gata2/Plcg2/Lrrk1/Traf3ip2/Vav1/Zfp36l1/Snx10/Nrros/Gab2/Cbfb/Prr7/Pik3r6/Il4/Csf1/Fes/Lgals9/Dock2/Spn/Mmp14/Tgfb1/Cd44/Laptm5/Spi1/Tyrobp/Hdac7/Btk/Ptprc/Myb/Cdk6/Cmtm7/Jak3/Lgals1/Dpp4/Nfam1/Syk</t>
+    <t xml:space="preserve">Car2/Prdx2/Lgals1/Hdac7/Btk/Egr1/Cmtm7/Dock2/Jak3/Laptm5/Nfam1/Syk/Myb/Ptprc/Mink1/Tgfb1/Cdk6/Spn/Tal1/Tsc1/St3gal1/Cd44/Cbfb/Spi1/Gab2/Cited2/Vav1/Plcg2/Lgals9/Kat2a/Stat5b/Prex1/Hs1bp3/Ptpn6/Dpp4/Fasn/Gnas/Lrrk1/Fbxw7/Gba/Irf2bp2/Smarcd1/Trp53/Nrros/Egr3/Zbtb7b/Tyrobp/Stat5a/Fzd5/Il4/Gata2/Mmp14/Fzd7/Sema4a/Pik3r6/Srf/Fes/Zfp36l1/Csf1/Snx10/Pknox1/Ctnnb1/Ap3d1/Hdac5/Prr7/Rb1/Tfrc/Hcls1/Prkca/Tcf3/Ubash3b/Atp7a/Vsir/Psen1/Tusc2/Sirt1/Fos/Junb/Traf3ip2/Fnip1/Rara/Bax/Gfi1b/Asxl2/Gpr89/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042098</t>
@@ -400,7 +400,7 @@
     <t xml:space="preserve">187/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Prdx2/Tfrc/Prnp/Zbtb7b/Bax/Nck1/Bid/Ctnnb1/Elf4/Fkbp1a/Stat5a/Fkbp1b/Vsir/Itgb2/Zbtb32/Trp53/Stat5b/Ptpn6/Il27ra/Psmb10/Cd37/Ripor2/Dock8/Rac2/Havcr2/Il4/Cxcr4/Lgals9/Dock2/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Ptprc/Coro1a/Jak3/P2rx7/Syk</t>
+    <t xml:space="preserve">Prdx2/Spta1/Dock2/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Dock8/Ripor2/P2rx7/Lgals9/Cxcr4/Stat5b/Ptpn6/Trp53/Zbtb7b/Stat5a/Il4/Lgals7/Cd37/Ctnnb1/Il27ra/Havcr2/Tfrc/Itgb2/Psmb10/Vsir/Bid/Fkbp1a/Bax/Elf4/Zbtb32/Fkbp1b/Nck1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032943</t>
@@ -415,7 +415,7 @@
     <t xml:space="preserve">256/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Prdx2/Tfrc/Prnp/Ticam1/Zbtb7b/Tbk1/Shb/Bax/Nck1/Bid/Ctnnb1/Elf4/Tcf3/Fkbp1a/Impdh2/Hspd1/Cd320/Stat5a/Fkbp1b/Vsir/Itgb2/Zbtb32/Trp53/Stat5b/Ptpn6/Il27ra/Psmb10/Cd37/Ripor2/Dock8/Rac2/Havcr2/Il4/Csf1/Cxcr4/Lgals9/Dock2/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Tyrobp/Btk/Ptprc/Coro1a/Jak3/P2rx7/Syk</t>
+    <t xml:space="preserve">Prdx2/Spta1/Btk/Dock2/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Dock8/Ripor2/P2rx7/Lgals9/Cxcr4/Stat5b/Ptpn6/Tbk1/Trp53/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Lgals7/Cd37/Csf1/Ctnnb1/Impdh2/Il27ra/Havcr2/Tfrc/Itgb2/Tcf3/Psmb10/Vsir/Bid/Fkbp1a/Hspd1/Bax/Cd320/Elf4/Zbtb32/Fkbp1b/Nck1/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902533</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">765/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Mink1/Map3k1/Ptp4a3/Ctns/S100a4/Slc30a10/Mturn/Prdx2/Itsn1/Pip4p1/Tfrc/Glrx/Hipk2/Rragc/Gab1/Traf4/Nupr1/Ticam1/Lamtor1/Mlst8/Arrb1/Epor/Fzd5/Smcr8/Map3k12/Ppard/Akap12/Fbxw7/Hmgcr/Flcn/Usp9x/Cib1/Lamtor3/Mtch2/Stk25/Bax/Dvl2/Glipr2/Rara/Birc5/Nck1/Bcl2l11/Garem1/Rictor/Gnas/Bid/Hexim1/Rap1b/Mcl1/Siah1b/Avpi1/Cpne1/Sirt1/Bnip2/Taok1/Fnip1/Clec16a/Sh3glb1/Usp15/Rack1/Psen1/Rps20/Iqgap1/Dnajc27/Serinc3/Ctnnb1/Nedd4/Ppp3r1/Phb2/Ddx21/Maged1/Cbl/Rbck1/Hsp90ab1/Dhx33/Ndst1/Igf1r/Hcls1/Prkca/Traf3/Prmt1/Pik3r5/Map4k1/Tcf7l2/Akap5/Oasl1/Pik3cd/Trp53/Irak1/Vangl2/Ptpn6/Pdcd4/Plcg2/Lrrk1/Traf3ip2/Spred2/Pmaip1/Npr2/Rgl2/Havcr2/Pik3r6/Csf1/Cxcr4/Dock2/Apoe/Tgfb1/Cd44/Laptm5/Mst1r/Spi1/Ptprc/P2rx7/Cd84/Igfbp4/Syk/Eng</t>
+    <t xml:space="preserve">Prdx2/Dock2/Map3k1/Laptm5/Syk/Ptprc/Mink1/Rragc/Igfbp4/Tgfb1/Slc30a10/Ctns/Cd44/Pip4p1/Cd84/Itsn1/Gab1/Spi1/Eng/P2rx7/Plcg2/Cxcr4/Glrx/Rgl2/Apoe/Mst1r/Cd36/Pld2/Ptpn6/Hipk2/Gnas/Lrrk1/Mtch2/Irak1/S100a4/Mturn/Traf4/Pmaip1/Fbxw7/Mlst8/Stk25/Ptp4a3/Trp53/Usp9x/Spred2/Epor/Traf3/Ticam1/Pik3cd/Fzd5/Npr2/Map4k1/Prmt1/Pik3r6/Maged1/Csf1/Lamtor3/Lamtor1/Ctnnb1/Ppard/Smcr8/Rbck1/Sh3glb1/Havcr2/Arrb1/Vangl2/Mcl1/Nedd4/Dvl2/Tfrc/Hcls1/Hmgcr/Hexim1/Ndst1/Cib1/Bcl2l11/Prkca/Usp15/Hsp90ab1/Dhx33/Flcn/Birc5/Pdcd4/Rap1b/Psen1/Bid/Cpne1/Sirt1/Taok1/Iqgap1/Garem1/Ppp3r1/Traf3ip2/Fnip1/Rara/Bax/Nupr1/Serinc3/Avpi1/Map3k12/Phb2/Akap12/Siah1b/Bnip2/Ddx21/Igf1r/Nck1/Tcf7l2/Cbl/Oasl1/Rack1/Clec16a/Rps20/Akap5/Dnajc27/Pik3r5/Glipr2/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007033</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">182/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Ctsd/Grn/Tpp1/Washc5/Atg9a/Vps11/Nupr1/Map1lc3b/Pikfyve/Rab43/Lamtor1/Gba/Trp53inp1/Zfyve26/Atp6ap2/Vps33a/Smcr8/Tmem199/Cln8/Hexa/Tmem41b/Chmp3/Atg2b/C9orf72/Gabarap/Vps35/Mtmr3/Atg4d/Trappc8/Pacs2/Pip4k2c/Arl8b/Sh3glb1/Psen1/Pik3c2b/Ulk2/Aktip/Laptm5/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Ctsd/Laptm5/Coro1a/Tpp1/Grn/Washc5/Trp53inp2/P2rx7/Vps11/Map1lc3b/Pikfyve/Atp6ap2/Atg9a/Gba/Rab43/Pacs2/Atg2b/Gabarap/Trp53inp1/Mtmr3/Zfyve26/Lamtor1/Vps33a/Tmem41b/Smcr8/Vps35/Aktip/Trappc8/Sh3glb1/Chmp3/Arl8b/Tmem199/Psen1/Hexa/Ulk2/C9orf72/Nupr1/Cln8/Atg4d/Pip4k2c/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050776</t>
@@ -460,7 +460,7 @@
     <t xml:space="preserve">669/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Btnl10/Cd47/H2-T23/Tfrc/Grn/Prnp/Serpinb1a/Aplf/Ermap/Lamp1/D6Wsu163e/Ticam1/Zbtb7b/Wdfy1/Trim56/Fzd5/Dnase2a/Smcr8/Tbk1/Usp9x/Shb/Elf1/Bax/C9orf72/Rara/Fcho1/Rnf185/Hexim1/Sirt1/Fbxo38/Usp15/Nras/Otud4/Psen1/Nono/Was/Cnot7/Phb2/Pde4d/Rbck1/Dgkz/Matr3/Hspd1/Ap1g1/Shld2/Lyar/Traf3/Ifih1/Stat5a/Samsn1/Vsir/Itgb2/Lpxn/Oasl1/Stat5b/Irak1/Fcgr3/Ptpn6/Il27ra/Xrcc5/Gata2/Plcg2/Unc13d/Vav1/Ubash3a/Cadm1/Pde4b/Cd37/Serpinb9/Gab2/Nr1d1/Rac2/Havcr2/Pik3r6/Cd48/Il4/Ptprs/Fes/Rnf125/Lgals9/Spn/Apoe/Lcp2/Tgfb1/Cd44/Laptm5/Fyb/Spi1/Tyrobp/Adcy7/Unc93b1/Btk/Ptprc/Myb/Jak3/Dpp4/Myo1g/Rftn1/P2rx7/Il1rl1/Cd84/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Jak3/Adcy7/Laptm5/Nfam1/Myo1g/Appl2/Il1rl1/Rftn1/Syk/Myb/Ptprs/Ptprc/Prnp/Btnl10/Rac2/Tgfb1/Grn/Spn/Ermap/Fyb/Lamp1/Cd44/Cd47/Cd84/Spi1/Gab2/Vav1/P2rx7/Plcg2/Lgals9/Unc93b1/Apoe/Stat5b/Cd36/Pld2/Rnf125/Ptpn6/Dpp4/Xrcc5/Wdfy1/Serpinb1a/Unc13d/Cd48/Irak1/Tbk1/Ap1g1/Aplf/Usp9x/Lcp2/Zbtb7b/Ubash3a/Dnase2a/H2-T23/D6Wsu163e/Trim56/Traf3/Ticam1/Tyrobp/Elf1/Stat5a/Fzd5/Il4/Gata2/Dgkz/Cd37/Pik3r6/Fes/Nono/Il27ra/Smcr8/Nr1d1/Rbck1/Havcr2/Otud4/Matr3/Fcgr3/Serpinb9/Tfrc/Hexim1/Itgb2/Usp15/Pde4b/Cadm1/Vsir/Psen1/Ifih1/Fbxo38/Sirt1/C9orf72/Samsn1/Hspd1/Rara/Bax/Nras/Rnf185/Lyar/Phb2/Shld2/Cnot7/Oasl1/Fcho1/Shb/Pde4d/Lpxn/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0015629</t>
@@ -475,7 +475,7 @@
     <t xml:space="preserve">418/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Cgn/Tmod1/Map3k1/Add2/Dmtn/Sptb/Specc1/Neurl1b/Snca/Itsn1/Mylpf/Epb41/Tsc1/H1f0/Vps11/Micall2/Samd14/Actn1/Rab22a/Stk38l/Myo6/Wasl/Ppp1r9b/Rara/Nckap1/Dyrk1a/Gabarap/Myo9a/Sorbs1/Swap70/Twf1/Arhgap35/Vcl/Daam1/Cttn/Acaca/Cdc42bpa/Iqgap1/Actr2/Was/Dctn6/Flii/Wdr1/Tnni3/Parvg/Myh10/Wipf1/Hcls1/Sptan1/Flna/Cap1/Lpxn/Sh3pxd2b/Arpc2/Pdxp/Dapk1/Vangl2/Pdlim2/Npm3/Rac1/Rac2/Capg/Fermt3/Arhgef2/Fyb/Mst1r/Vill/Coro1a/Myo1g/Lcp1</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Map3k1/Snca/Myo1g/Arhgef2/Vill/Coro1a/Tmod1/Rac2/Tsc1/Dmtn/Fyb/Rac1/Cgn/Capg/Itsn1/Fermt3/Cap1/Actn1/Micall2/Lcp1/Npm3/Vps11/Arpc2/Mst1r/Dyrk1a/Specc1/Flna/Samd14/H1f0/Stk38l/Rab22a/Epb41/Sh3pxd2b/Myo6/Gabarap/Pdxp/Neurl1b/Myh10/Wasl/Ppp1r9b/Nckap1/Wdr1/Dapk1/Flii/Twf1/Vangl2/Hcls1/Mylpf/Wipf1/Sptan1/Acaca/Swap70/Pdlim2/Actr2/Tnni3/Iqgap1/Rara/Parvg/Cdc42bpa/Sorbs1/Arhgap35/Cttn/Myo9a/Vcl/Dctn6/Daam1/Lpxn/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009156</t>
@@ -490,7 +490,7 @@
     <t xml:space="preserve">32/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Prps1/Impdh2/Aprt/Adsl/Umps/Cad/Adssl1/Atic/Pfas/Gmpr/Gart/Uprt</t>
+    <t xml:space="preserve">Ampd3/Uprt/Gart/Pfas/Atic/Cad/Umps/Adssl1/Adsl/Gmpr/Impdh2/Prps1/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046651</t>
@@ -502,7 +502,7 @@
     <t xml:space="preserve">250/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Prdx2/Tfrc/Prnp/Ticam1/Zbtb7b/Shb/Bax/Nck1/Bid/Ctnnb1/Elf4/Tcf3/Fkbp1a/Impdh2/Hspd1/Cd320/Stat5a/Fkbp1b/Vsir/Itgb2/Zbtb32/Trp53/Stat5b/Ptpn6/Il27ra/Psmb10/Cd37/Ripor2/Dock8/Rac2/Havcr2/Il4/Cxcr4/Lgals9/Dock2/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Tyrobp/Btk/Ptprc/Coro1a/Jak3/P2rx7/Syk</t>
+    <t xml:space="preserve">Prdx2/Spta1/Btk/Dock2/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Dock8/Ripor2/P2rx7/Lgals9/Cxcr4/Stat5b/Ptpn6/Trp53/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Lgals7/Cd37/Ctnnb1/Impdh2/Il27ra/Havcr2/Tfrc/Itgb2/Tcf3/Psmb10/Vsir/Bid/Fkbp1a/Hspd1/Bax/Cd320/Elf4/Zbtb32/Fkbp1b/Nck1/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016236</t>
@@ -517,7 +517,7 @@
     <t xml:space="preserve">236/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Scoc/Wdr81/Optn/Ctsd/Mcoln1/Rubcnl/Tsc1/Atg9a/Yod1/Nupr1/Sesn1/Atp6v0a1/Map1lc3b/Uvrag/Pikfyve/Rab43/Gba/Trp53inp1/Zfyve26/Vps33a/Retreg2/Smcr8/Tbk1/Tmem41b/Atg2b/C9orf72/Sesn3/Gabarap/Mtmr3/Atg4d/Trappc8/Pacs2/Pip4k2c/Nbr1/Arl8b/Sirt1/Snap29/Clec16a/Sh3glb1/Vps4b/Psen1/Ubqln4/Phb2/Pik3c2b/Ulk2/Trp53/Il4</t>
+    <t xml:space="preserve">Ctsd/Tsc1/Trp53inp2/Scoc/Mcoln1/Wdr81/Optn/Map1lc3b/Yod1/Pikfyve/Sesn1/Atg9a/Uvrag/Tbk1/Gba/Rab43/Pacs2/Atg2b/Trp53/Gabarap/Atp6v0a1/Retreg2/Trp53inp1/Mtmr3/Il4/Zfyve26/Vps33a/Tmem41b/Smcr8/Trappc8/Sh3glb1/Ubqln4/Arl8b/Rubcnl/Psen1/Sesn3/Ulk2/Sirt1/C9orf72/Nupr1/Phb2/Nbr1/Vps4b/Clec16a/Snap29/Atg4d/Pip4k2c/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019725</t>
@@ -532,7 +532,7 @@
     <t xml:space="preserve">635/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Mink1/Wnk4/Atp6v0d1/Rhag/Slc30a10/Abcb6/Snca/Prdx2/Map1a/Tfrc/Grn/Mcoln1/Prnp/Abcg1/Dmpk/Ankrd9/Serpinb1a/Slc11a2/Atp6v0a1/Kel/Ubash3b/Micu1/Arrb1/Atp6ap2/Clcn3/Vps33a/Slc30a9/Tmem199/Ppard/Atp2b1/Fbxw7/Smdt1/Grina/Atp6v1a/Ftl1/Hmgcr/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Ccdc186/Xpr1/Birc5/Mafg/Slc12a7/Aco1/Lrrc8a/Pacs2/Atp6v1g1/Cdk16/Slc39a8/Sirt1/Taok1/Rack1/Gpr89/Psen1/Nucks1/Lrp5/Pde4d/Selenot/Fkbp1a/Pdzd8/Tnni3/Ube2s/Igf1r/Prkca/Prdx4/P2rx1/Flna/Srf/Fkbp1b/Tcf7l2/Abca2/Tfr2/Trp53/Frrs1/Cyb561/Abcb8/Slc4a8/Prdx6/Ptpn6/Atp1b2/Plcg2/Atp1a3/Snx10/Hk2/Ano6/Pim3/Rac1/Nr1d1/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Prdx2/Atp6v0d1/Snca/Slc4a1/Ptprc/Wnk4/Mink1/Coro1a/Ano6/Abcb6/Prnp/Tgfb1/Slc30a10/Slc11a2/Grn/Abcg1/Rac1/Gsto1/Rhag/P2rx7/Mcoln1/Slc30a9/Abca2/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Pim3/Serpinb1a/Flna/Xpr1/Fbxw7/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Map1a/Atp6v1a/Abcb8/Prdx6/Clcn3/Atp6v0a1/Tfr2/Cyb561/Smdt1/Xk/Ankrd9/Aco1/Srf/Snx10/Ap3d1/Vps33a/Selenot/Ppard/Kel/Nr1d1/Lrrc8a/Dmpk/Arrb1/Slc4a8/Atp1b2/Tfrc/Hmgcr/Ube2s/Lrp5/Nucks1/Prkca/Ubash3b/Cdk16/Prdx4/Tmem199/Atp1a3/Atp7a/Hk2/Birc5/Ftl1/Psen1/Sirt1/Fkbp1a/Taok1/Tnni3/Grina/Slc12a7/Bax/Slc39a8/Fkbp1b/Igf1r/Tcf7l2/Ccdc186/Atp6v1g1/P2rx1/Gpr89/Rack1/Mafg/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005085</t>
@@ -544,7 +544,7 @@
     <t xml:space="preserve">177/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Itsn1/Kalrn/Ranbp10/Als2/Gdpgp1/Fgd6/Prex1/Lamtor1/Rab3ip/Rgl1/Arfgef2/Smcr8/Dennd2c/Arhgef12/Flcn/Plekhg2/Lamtor3/C9orf72/Arhgef11/Itsn2/Fnip1/Rcc1/Dennd4b/Eef1b2/Arhgef1/Dennd1c/Vav1/Rangrf/Ankrd27/Arhgef6/Rgl2/Rcc2/Dock8/Arhgef2/Dock2/Arhgef18/Elmo1/Rin3</t>
+    <t xml:space="preserve">Rab3il1/Dock2/Arhgef2/Ankrd27/Arhgef1/Dock8/Itsn1/Rcc2/Elmo1/Vav1/Rin3/Als2/Arfgef2/Rgl2/Prex1/Arhgef18/Kalrn/Arhgef6/Rangrf/Rab3ip/Arhgef12/Fgd6/Lamtor3/Dennd4b/Lamtor1/Gdpgp1/Smcr8/Eef1b2/Dennd2c/Plekhg2/Rgl1/Flcn/Arhgef11/Ranbp10/Rcc1/C9orf72/Dennd1c/Fnip1/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002252</t>
@@ -559,7 +559,7 @@
     <t xml:space="preserve">509/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/St3gal1/Cd47/Prdx2/H2-T23/Tfrc/Grn/Tsc1/Atg9a/Aplf/Lamp1/D6Wsu163e/Anxa3/Ticam1/Zbtb7b/Gba/Fzd5/Atp7a/Shb/Rara/Rnf168/Tusc2/Swap70/Arl8b/Sirt1/Fbxo38/Psen1/Was/Phb2/Ddx21/Gpi1/Wdr1/Hspd1/Ap1g1/Shld2/Stat5a/Vsir/Itgb2/Trp53/Stat5b/Fcgr3/Ptpn6/Il27ra/Sema4a/Gata2/Plcg2/Traf3ip2/Unc13d/Vav1/Cplx2/Cadm1/Cd37/Serpinb9/Gab2/Rac2/Havcr2/Pik3r6/Il4/Ywhaz/Fes/Lgals9/Dock2/Spn/Tgfb1/Laptm5/Spi1/Tyrobp/Unc93b1/Btk/Ptprc/Myb/Coro1a/Jak3/Apbb1ip/Lgals1/Dpp4/Myo1g/Rftn1/P2rx7/Cd84/Syk/Lcp1</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Btk/Dock2/Jak3/Laptm5/Myo1g/Appl2/Rftn1/Syk/Myb/Ptprc/Coro1a/Rac2/Tgfb1/Ywhaz/Grn/Spn/Apbb1ip/Tsc1/St3gal1/Lamp1/Cd47/Cd84/Spi1/Gab2/Vav1/P2rx7/Lcp1/Plcg2/Lgals9/Unc93b1/Stat5b/Cd36/Pld2/Ptpn6/Dpp4/Unc13d/Atg9a/Gba/Ap1g1/Trp53/Aplf/Zbtb7b/H2-T23/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Fzd5/Il4/Gata2/Sema4a/Cd37/Pik3r6/Fes/Wdr1/Il27ra/Rnf168/Havcr2/Fcgr3/Serpinb9/Anxa3/Tfrc/Cplx2/Itgb2/Arl8b/Atp7a/Swap70/Cadm1/Vsir/Psen1/Tusc2/Fbxo38/Sirt1/Traf3ip2/Hspd1/Rara/Phb2/Shld2/Ddx21/Shb/Gpi1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009124</t>
@@ -571,7 +571,7 @@
     <t xml:space="preserve">16/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Prps1/Dut/Impdh2/Aprt/Adsl/Umps/Cad/Adssl1/Atic/Pfas/Gmpr/Gart/Uprt/Dctd</t>
+    <t xml:space="preserve">Ampd3/Uprt/Dctd/Gart/Pfas/Atic/Cad/Umps/Adssl1/Adsl/Gmpr/Impdh2/Dut/Prps1/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070661</t>
@@ -586,7 +586,7 @@
     <t xml:space="preserve">282/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Prdx2/Tfrc/Prnp/Ticam1/Zbtb7b/Gba/Junb/Tbk1/Shb/Bax/Nck1/Bid/Ctnnb1/Elf4/Tcf3/Fkbp1a/Impdh2/Hspd1/Cd320/Stat5a/Fkbp1b/Vsir/Itgb2/Zbtb32/Trp53/Stat5b/Ptpn6/Il27ra/Psmb10/Cd37/Ripor2/Dock8/Rac2/Havcr2/Il4/Csf1/Cxcr4/Lgals9/Dock2/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Tyrobp/Btk/Ptprc/Coro1a/Jak3/P2rx7/Syk</t>
+    <t xml:space="preserve">Prdx2/Spta1/Btk/Dock2/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Dock8/Ripor2/P2rx7/Lgals9/Cxcr4/Stat5b/Ptpn6/Tbk1/Gba/Trp53/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Lgals7/Cd37/Csf1/Ctnnb1/Impdh2/Il27ra/Havcr2/Tfrc/Itgb2/Tcf3/Psmb10/Vsir/Bid/Fkbp1a/Junb/Hspd1/Bax/Cd320/Elf4/Zbtb32/Fkbp1b/Nck1/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002703</t>
@@ -601,7 +601,7 @@
     <t xml:space="preserve">216/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/H2-T23/Tfrc/Aplf/Lamp1/D6Wsu163e/Ticam1/Fzd5/Fbxo38/Was/Ddx21/Hspd1/Ap1g1/Shld2/Stat5a/Vsir/Itgb2/Stat5b/Fcgr3/Ptpn6/Il27ra/Gata2/Plcg2/Unc13d/Vav1/Cadm1/Serpinb9/Gab2/Rac2/Havcr2/Pik3r6/Il4/Fes/Lgals9/Spn/Tgfb1/Spi1/Tyrobp/Ptprc/Jak3/Dpp4/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Jak3/Syk/Ptprc/Rac2/Tgfb1/Spn/Lamp1/Cd84/Spi1/Gab2/Vav1/P2rx7/Plcg2/Lgals9/Stat5b/Pld2/Ptpn6/Dpp4/Unc13d/Ap1g1/Aplf/H2-T23/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Fzd5/Il4/Gata2/Pik3r6/Fes/Il27ra/Havcr2/Fcgr3/Serpinb9/Tfrc/Itgb2/Cadm1/Vsir/Fbxo38/Hspd1/Shld2/Ddx21/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009123</t>
@@ -613,7 +613,7 @@
     <t xml:space="preserve">59/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Prps1/Dut/Impdh2/Guk1/Aprt/Adsl/Nt5m/Umps/Cad/Adssl1/Atic/Ak4/Pfas/Gmpr/Gart/Uprt/Dctd</t>
+    <t xml:space="preserve">Ampd3/Uprt/Dctd/Gart/Pfas/Atic/Cad/Umps/Adssl1/Adsl/Gmpr/Impdh2/Dut/Guk1/Prps1/Ak4/Aprt/Adss/Nt5m</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045597</t>
@@ -628,7 +628,7 @@
     <t xml:space="preserve">755/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Car2/Egr3/Dpf3/Egr2/Fam210b/Abcb10/Tal1/Dmtn/Mturn/Zhx3/Sox6/Kalrn/Arntl/Nedd9/Ache/Picalm/Fos/Prex1/Numb/Pim1/Zbtb7b/Junb/Tbc1d24/Socs2/Fbxo5/Cib1/Mtch2/Ap3d1/Shb/Stk25/Dag1/Pias2/Cdkl5/Glipr2/Plag1/Rara/Suco/Golga4/Gnas/Rb1/Ncoa1/Lamc1/Gfi1b/Asxl2/Smap1/Cpne1/Sirt1/Bnip2/Sav1/Sh3glb1/Phf10/Nap1l1/Rpl4/Parp1/Actr2/Ctnnb1/Tcf3/Zfp219/Prpf19/Pa2g4/Lrp5/Hsp90ab1/Pwp1/Stau2/Jade2/Cul7/Hcls1/Prkca/Megf8/Flna/Srf/Prmt1/Stat5a/Vsir/Smarcd1/Sh3pxd2b/Tcf7l2/Dnmt3b/Akap5/Arpc2/Stat5b/Xrcc5/Kat2a/Gata2/Unc13d/Zfp36l1/Ankrd27/Clic1/Rac1/Plxnc1/Cbfb/Ripor2/Vim/Mmd/Pik3r6/Il4/Csf1/Tenm4/Fes/Rgs14/Cxcr4/Lgals9/Arhgef2/Mmp14/Apoe/Tgfb1/Gdf3/Tyrobp/Ptprc/Myb/Syk/Eng</t>
+    <t xml:space="preserve">Car2/Fam210b/Syk/Picalm/Arhgef2/Myb/Ptprc/Abcb10/Tgfb1/Ankrd27/Tal1/Dmtn/Dpf3/Rac1/Ripor2/Cbfb/Clic1/Eng/Zhx3/Lgals9/Vim/Cxcr4/Kat2a/Arpc2/Apoe/Stat5b/Cd36/Prex1/Tbc1d24/Mmd/Xrcc5/Kalrn/Gnas/Ache/Megf8/Unc13d/Flna/Mtch2/Mturn/Dnmt3b/Arntl/Stk25/Rgs14/Gdf3/Tenm4/Sh3pxd2b/Smarcd1/Dag1/Egr3/Zbtb7b/Numb/Nedd9/Pias2/Egr2/Socs2/Tyrobp/Stat5a/Il4/Gata2/Cul7/Mmp14/Prmt1/Pik3r6/Srf/Fes/Zfp36l1/Csf1/Ctnnb1/Ap3d1/Rb1/Sh3glb1/Suco/Fbxo5/Hcls1/Plxnc1/Pwp1/Lrp5/Sox6/Smap1/Cib1/Prkca/Prpf19/Tcf3/Hsp90ab1/Plag1/Lamc1/Vsir/Cpne1/Sirt1/Actr2/Fos/Junb/Ncoa1/Sav1/Golga4/Rara/Cdkl5/Rpl4/Stau2/Gfi1b/Bnip2/Asxl2/Zfp219/Parp1/Tcf7l2/Jade2/Nap1l1/Pim1/Akap5/Shb/Pa2g4/Phf10/Glipr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008047</t>
@@ -640,7 +640,7 @@
     <t xml:space="preserve">432/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Arhgap23/Tal1/Itsn1/Agfg2/Als2/Asap3/Psme4/Nupr1/Pim1/Arhgap12/Mlst8/Arrb1/Ppp2r5a/Map3k12/Rabep1/Ppard/Tbc1d24/Fbxw7/Arhgef12/Arhgap15/Mob3c/Ccnt1/Flcn/Lamtor3/Elmod2/Ppp2r5b/Myo9a/Acap3/Rabgap1/Rictor/Stradb/Gnas/Dbf4/Arhgap35/Smap1/Taok1/Abi1/Rack1/Usp6nl/Iqgap1/Tcf3/Ncf2/Syngap1/Cwf19l1/Psme1/Dtx3l/Arhgap9/Vsir/Prkag2/Sh3pxd2b/Arhgef1/Ankrd27/Rgs2/Mob3b/Gmip/Alox5ap/Arhgdig/Rgs1/Rgs14/Lgals9/Dock2/Apoe/Tgfb1/Cd44/Adap1/Rgs18/Btk/Arhgap27/P2rx7/Tbc1d10c/Arap3/Arhgdib/Rin3</t>
+    <t xml:space="preserve">Arap3/Btk/Dock2/Psme4/Tgfb1/Arhgap23/Ankrd27/Tal1/Arhgef1/Cd44/Arhgap27/Itsn1/Ppp2r5a/Tbc1d10c/P2rx7/Rin3/Agfg2/Alox5ap/Lgals9/Arhgdib/Als2/Apoe/Rabep1/Tbc1d24/Gnas/Gmip/Rgs18/Fbxw7/Arhgdig/Mlst8/Adap1/Rgs14/Sh3pxd2b/Mob3b/Rabgap1/Arhgef12/Rgs2/Prkag2/Ccnt1/Lamtor3/Ppard/Rgs1/Arhgap12/Arrb1/Psme1/Asap3/Cwf19l1/Dtx3l/Smap1/Arhgap9/Tcf3/Flcn/Ncf2/Vsir/Taok1/Iqgap1/Nupr1/Stradb/Syngap1/Map3k12/Arhgap15/Abi1/Arhgap35/Mob3c/Dbf4/Ppp2r5b/Rack1/Elmod2/Pim1/Acap3/Myo9a/Usp6nl/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006783</t>
@@ -655,7 +655,7 @@
     <t xml:space="preserve">26/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Slc6a9/Abcb10/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Snx3/Pgrmc1/Cox10</t>
+    <t xml:space="preserve">Alas2/Slc6a9/Abcb10/Slc11a2/Fech/Urod/Hmbs/Tmem14c/Cox10/Pgrmc1/Alad/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045785</t>
@@ -670,7 +670,7 @@
     <t xml:space="preserve">395/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Cd36/Pld2/Egr3/Dmtn/Cd47/Cited2/Tfrc/Nedd9/Tsc1/Ptpn23/Prex1/Zbtb7b/Flcn/Cib1/Ap3d1/Shb/Dag1/Rara/Fcho1/Nck1/Lamc1/Phf10/Iqgap1/Kifap3/Pde4d/Ptpru/Mfsd2b/Ldb1/Hspd1/Prkca/Flna/Stat5a/Vsir/Plekha2/Itgb2/Smarcd1/Arpc2/Stat5b/Irak1/Ptpn6/Il27ra/Unc13d/Vav1/Fut4/Itga5/Rac1/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Csf1/Lgals9/Spn/Tgfb1/Ccdc88b/Cd44/Ptprc/Myb/Cdk6/Coro1a/Jak3/Apbb1ip/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Cdk6/Spn/Apbb1ip/Tsc1/Dmtn/Cd44/Rac1/Cd47/Dock8/Cbfb/Ptpn23/Cited2/Vav1/Lgals9/Arpc2/Stat5b/Cd36/Prex1/Pld2/Ptpn6/Dpp4/Itga5/Unc13d/Flna/Irak1/Smarcd1/Dag1/Egr3/Zbtb7b/Ldb1/Nedd9/Fut4/Stat5a/Il4/Pik3r6/Csf1/Ap3d1/Il27ra/Havcr2/Tfrc/Cib1/Itgb2/Prkca/Lamc1/Flcn/Vsir/Plekha2/Iqgap1/Hspd1/Rara/Ptpru/Nck1/Kifap3/Fcho1/Shb/Mfsd2b/Pde4d/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042168</t>
@@ -682,7 +682,7 @@
     <t xml:space="preserve">35/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Slc6a9/Abcb10/Abcb6/Hebp1/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Snx3/Pgrmc1/Cox10</t>
+    <t xml:space="preserve">Alas2/Abcb6/Slc6a9/Abcb10/Slc11a2/Fech/Urod/Hebp1/Hmbs/Tmem14c/Cox10/Pgrmc1/Alad/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005774</t>
@@ -694,7 +694,7 @@
     <t xml:space="preserve">218/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Ctns/Abcb6/H2-T23/Wdr81/Pip4p1/Ctsd/Grn/Mcoln1/Rubcnl/Atp6v1c1/Clcn7/Atp6v1e1/Slc11a2/Lamp1/Atp6v0a1/Map1lc3b/Uvrag/Lamtor1/Gba/Atp6ap2/Clcn3/Tmem199/Atp6v1a/Atp6v1b2/Flcn/Lamtor3/Chmp3/Gabarap/Atp6v0b/Lrrc8a/Atp6v1g1/Arl8b/Slc39a8/Fnip1/Clec16a/Sh3glb1/Psen1/Ifitm2/Hsp90ab1/Ap1g1/Abca2/Cyb561/Laptm5</t>
+    <t xml:space="preserve">Atp6v0d1/Ctsd/Laptm5/Abcb6/Slc11a2/Ctns/Grn/Atp6v1c1/Atp6v1e1/Lamp1/Pip4p1/Mcoln1/Abca2/Wdr81/Clcn7/Map1lc3b/Atp6ap2/Uvrag/Atp6v1b2/Gba/Ap1g1/Atp6v1a/Clcn3/Gabarap/Atp6v0a1/H2-T23/Cyb561/Atp6v0b/Lamtor3/Lamtor1/Lrrc8a/Sh3glb1/Chmp3/Arl8b/Hsp90ab1/Tmem199/Rubcnl/Flcn/Psen1/Ifitm2/Fnip1/Slc39a8/Atp6v1g1/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006914</t>
@@ -709,7 +709,7 @@
     <t xml:space="preserve">420/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Scoc/Snca/Wdr81/Optn/Ctsd/Mcoln1/Rubcnl/Rragc/Tsc1/Atg9a/Vps11/Yod1/Tollip/Nupr1/Sesn1/Cltc/Atp6v0a1/Map1lc3b/Ticam1/Uvrag/Pikfyve/Rab43/Gba/Trp53inp1/Mlst8/Zfyve26/Vps33a/Retreg2/Smcr8/Tbk1/Fbxw7/Flcn/Tmem41b/Atg2b/C9orf72/Sesn3/Gabarap/Rnf185/Bcl2l11/Ctsa/Mtmr3/Bid/Atg4d/Trappc8/Pacs2/Mcl1/Rmc1/Pip4k2c/Nbr1/Arl8b/Cttn/Sirt1/Snap29/Clec16a/Sh3glb1/Vps4b/Psen1/Gopc/Ubqln4/Phb2/Pik3c2b/Eif4g2/Ulk2/Trp53/Dapk1/Mtmr9/Hk2/Wdfy4/Il4/Cd84</t>
+    <t xml:space="preserve">Ctsd/Snca/Wdfy4/Rragc/Cltc/Tsc1/Trp53inp2/Cd84/Scoc/Tollip/Mcoln1/Vps11/Wdr81/Optn/Map1lc3b/Yod1/Mtmr9/Pikfyve/Sesn1/Atg9a/Uvrag/Fbxw7/Tbk1/Gba/Mlst8/Rab43/Pacs2/Atg2b/Trp53/Gabarap/Atp6v0a1/Retreg2/Ticam1/Trp53inp1/Mtmr3/Il4/Ctsa/Zfyve26/Vps33a/Tmem41b/Smcr8/Dapk1/Trappc8/Sh3glb1/Mcl1/Ubqln4/Bcl2l11/Arl8b/Hk2/Rubcnl/Flcn/Psen1/Bid/Sesn3/Rmc1/Ulk2/Sirt1/C9orf72/Eif4g2/Nupr1/Rnf185/Phb2/Nbr1/Vps4b/Cttn/Clec16a/Snap29/Gopc/Atg4d/Pip4k2c/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0061919</t>
@@ -730,7 +730,7 @@
     <t xml:space="preserve">331/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Sema4b/Washc5/Tsc1/Picalm/Kel/Rab22a/Dpysl2/Ssh2/Mlst8/Clcn3/Cln8/Atp7a/Plekhg2/Xk/Chmp3/Dip2b/Cdkl5/Nckap1/Golga4/Nck1/Slc12a7/Rictor/Lrrc8a/Swap70/Twf1/Arhgap35/Cttn/Ap2m1/Rpl4/Was/Flii/Wdr1/Hsp90ab1/Wdr36/Ulk2/Hcls1/Sptan1/Megf8/Srf/Arpc2/Pdxp/Abcb8/Hp1bp3/Sema4a/Ano6/Rac1/Capg/Ptprs/Apoe/Vill/Coro1a/P2rx7/Rin3</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Picalm/Vill/Ptprs/Coro1a/Ano6/Tmod1/Washc5/Tsc1/Dmtn/Rac1/Capg/Hp1bp3/P2rx7/Rin3/Arpc2/Apoe/Megf8/Dip2b/Mlst8/Rab22a/Ssh2/Abcb8/Clcn3/Dpysl2/Pdxp/Sema4b/Xk/Sema4a/Srf/Nckap1/Wdr1/Kel/Lrrc8a/Flii/Twf1/Chmp3/Plekhg2/Hcls1/Sptan1/Hsp90ab1/Atp7a/Swap70/Ap2m1/Ulk2/Slc12a7/Golga4/Cdkl5/Rpl4/Wdr36/Arhgap35/Nck1/Cttn/Cln8/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009161</t>
@@ -742,7 +742,7 @@
     <t xml:space="preserve">46/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Prps1/Impdh2/Guk1/Aprt/Adsl/Umps/Cad/Adssl1/Atic/Ak4/Pfas/Gmpr/Gart/Uprt</t>
+    <t xml:space="preserve">Ampd3/Uprt/Gart/Pfas/Atic/Cad/Umps/Adssl1/Adsl/Gmpr/Impdh2/Guk1/Prps1/Ak4/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019207</t>
@@ -754,7 +754,7 @@
     <t xml:space="preserve">208/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Inka2/Prkar2b/Itsn1/Wdr81/Als2/Pim1/Mlst8/Smcr8/Map3k12/Cdkn2c/Socs2/Mob3c/Ccnt1/Cib1/Lamtor3/Rara/Nck1/Rictor/Stradb/Hexim1/Dbf4/Taok1/Abi1/Qars/Rack1/Iqgap1/Parp1/Tcf3/Elp3/Hsp90ab1/Pik3r5/Prkag2/Ccng1/Spred2/Mob3b/Rac2/Pik3r6/Lgals9/Trib2/Tgfb1/P2rx7</t>
+    <t xml:space="preserve">Prkar2b/Rac2/Tgfb1/Tal1/Trib2/Itsn1/P2rx7/Wdr81/Lgals9/Als2/Ccng1/Mlst8/Inka2/Mob3b/Cdkn2c/Spred2/Socs2/Prkag2/Ccnt1/Pik3r6/Lamtor3/Smcr8/Hexim1/Cib1/Tcf3/Hsp90ab1/Taok1/Iqgap1/Rara/Stradb/Map3k12/Abi1/Mob3c/Nck1/Parp1/Dbf4/Qars/Rack1/Pim1/Pik3r5/Elp3/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055086</t>
@@ -769,7 +769,7 @@
     <t xml:space="preserve">513/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Uap1l1/Aldh1l2/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Oard1/Fasn/Mlst8/Gnpda1/Atp6v1a/Nmnat3/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Adal/Gcdh/Enpp5/Acaca/Ndufa10/Psen1/Cs/Parp1/Ncf2/B3galnt2/Gpi1/Adss/Prps1/Dlat/Dut/Entpd6/Impdh2/Guk1/Pdha1/Mtap/Aprt/Nudt14/Adsl/Mthfd1/Nt5m/Idh2/Umps/Macrod1/Suclg2/Prkag2/Dpagt1/Fut8/Trp53/Qprt/Cad/Khk/Adssl1/Acsl5/H6pd/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Kcnab2/Pgm2/Uprt/Il4/Tgfb1/Nme4/Dctd/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Uprt/Kcnab2/Pfkfb2/Nme4/Dctd/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Uap1l1/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Cad/Pkm/Trp53/Fut8/Atp6v1a/Umps/Idh2/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/Gnpda1/Pgm2/Dpagt1/H6pd/Oard1/Gmpr/Impdh2/Dut/Aldh1l2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Prps1/Eno3/Dlat/Qprt/Acaca/Atp7a/Adal/Hk2/Flcn/Ncf2/Psen1/B3galnt2/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Mtap/Adss/Parp1/Enpp5/Macrod1/Pmvk/Nudt14/Nmnat3/Nt5m/Gpi1/Entpd6</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002443</t>
@@ -781,7 +781,7 @@
     <t xml:space="preserve">334/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/H2-T23/Tfrc/Aplf/Lamp1/D6Wsu163e/Anxa3/Ticam1/Gba/Fzd5/Rnf168/Tusc2/Swap70/Arl8b/Fbxo38/Was/Ddx21/Wdr1/Hspd1/Ap1g1/Shld2/Stat5a/Vsir/Itgb2/Stat5b/Fcgr3/Ptpn6/Il27ra/Gata2/Plcg2/Traf3ip2/Unc13d/Vav1/Cplx2/Cadm1/Serpinb9/Gab2/Rac2/Havcr2/Pik3r6/Il4/Ywhaz/Fes/Lgals9/Spn/Tgfb1/Spi1/Tyrobp/Unc93b1/Btk/Ptprc/Coro1a/Jak3/Dpp4/Myo1g/Rftn1/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Btk/Jak3/Myo1g/Rftn1/Syk/Ptprc/Coro1a/Rac2/Tgfb1/Ywhaz/Spn/Lamp1/Cd84/Spi1/Gab2/Vav1/P2rx7/Plcg2/Lgals9/Unc93b1/Stat5b/Pld2/Ptpn6/Dpp4/Unc13d/Gba/Ap1g1/Aplf/H2-T23/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Fzd5/Il4/Gata2/Pik3r6/Fes/Wdr1/Il27ra/Rnf168/Havcr2/Fcgr3/Serpinb9/Anxa3/Tfrc/Cplx2/Itgb2/Arl8b/Swap70/Cadm1/Vsir/Tusc2/Fbxo38/Traf3ip2/Hspd1/Shld2/Ddx21/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055080</t>
@@ -796,7 +796,7 @@
     <t xml:space="preserve">475/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Wnk4/Ank1/Epb42/Atp6v0d1/Rhag/Slc30a10/Abcb6/Cnnm2/Snca/Fech/Agtr1a/Tfrc/Grn/Mcoln1/Prnp/Dmpk/Ankrd9/Picalm/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Atp6ap2/Vps33a/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Cnnm4/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Mafg/Slc12a7/Aco1/Gnas/Pacs2/Atp6v1g1/Slc39a8/Gpr89/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Mllt6/Prkca/P2rx1/Flna/Snx5/Fkbp1b/Tfr2/Trp53/Frrs1/Cyb561/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Snx10/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Atp6v0d1/Snca/Picalm/Slc4a1/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Cnnm2/Tgfb1/Slc30a10/Slc11a2/Grn/Fech/Ank1/Gsto1/Epb42/Rhag/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Gnas/Flna/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Atp6v1a/Atp6v0a1/Tfr2/Agtr1a/Cyb561/Rhd/Smdt1/Xk/Mllt6/Cnnm4/Ankrd9/Aco1/Snx10/Ap3d1/Vps33a/Kel/Dmpk/Slc4a8/Atp1b2/Tfrc/Snx5/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Slc12a7/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Gpr89/Mafg/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098771</t>
@@ -811,7 +811,7 @@
     <t xml:space="preserve">484/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Wnk4/Ank1/Epb42/Atp6v0d1/Rhag/Slc30a10/Abcb6/Cnnm2/Snca/Fech/Agtr1a/Tfrc/Grn/Mcoln1/Prnp/Dmpk/Ankrd9/Picalm/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Atp6ap2/Vps33a/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Cnnm4/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Xpr1/Mafg/Slc12a7/Aco1/Gnas/Pacs2/Atp6v1g1/Slc39a8/Gpr89/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Mllt6/Prkca/P2rx1/Flna/Snx5/Fkbp1b/Tfr2/Trp53/Frrs1/Cyb561/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Snx10/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Atp6v0d1/Snca/Picalm/Slc4a1/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Cnnm2/Tgfb1/Slc30a10/Slc11a2/Grn/Fech/Ank1/Gsto1/Epb42/Rhag/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Gnas/Flna/Xpr1/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Atp6v1a/Atp6v0a1/Tfr2/Agtr1a/Cyb561/Rhd/Smdt1/Xk/Mllt6/Cnnm4/Ankrd9/Aco1/Snx10/Ap3d1/Vps33a/Kel/Dmpk/Slc4a8/Atp1b2/Tfrc/Snx5/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Slc12a7/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Gpr89/Mafg/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033176</t>
@@ -826,7 +826,7 @@
     <t xml:space="preserve">24/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Atp6v1c1/Atp6v1e1/Atp6v0a1/Atp6ap2/Tmem199/Atp6v1a/Atp6v1b2/Atp6v0b/Atp6v1g1</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Atp6v1c1/Atp6v1e1/Atp6ap2/Atp6v1b2/Atp6v1a/Atp6v0a1/Atp6v0b/Tmem199/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046984</t>
@@ -841,7 +841,7 @@
     <t xml:space="preserve">7/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Slc25a37/Abcb10/Fech/Ldb1/Prmt1</t>
+    <t xml:space="preserve">Slc6a9/Abcb10/Fech/Slc25a37/Ldb1/Prmt1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050801</t>
@@ -856,7 +856,7 @@
     <t xml:space="preserve">493/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Wnk4/Ank1/Epb42/Atp6v0d1/Rhag/Slc30a10/Abcb6/Cnnm2/Snca/Fech/Agtr1a/Tfrc/Grn/Mcoln1/Prnp/Dmpk/Ankrd9/Picalm/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Atp6ap2/Vps33a/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Cnnm4/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Xpr1/Mafg/Slc12a7/Aco1/Gnas/Pacs2/Atp6v1g1/Slc39a8/Gls/Gpr89/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Mllt6/Prkca/P2rx1/Flna/Snx5/Fkbp1b/Tfr2/Trp53/Frrs1/Cyb561/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Snx10/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Atp6v0d1/Snca/Picalm/Slc4a1/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Cnnm2/Tgfb1/Slc30a10/Slc11a2/Grn/Fech/Ank1/Gsto1/Epb42/Rhag/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Gnas/Flna/Xpr1/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Atp6v1a/Atp6v0a1/Tfr2/Agtr1a/Cyb561/Rhd/Smdt1/Xk/Mllt6/Cnnm4/Ankrd9/Aco1/Snx10/Ap3d1/Vps33a/Kel/Dmpk/Slc4a8/Atp1b2/Tfrc/Snx5/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Slc12a7/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Gpr89/Mafg/Gls/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051402</t>
@@ -871,7 +871,7 @@
     <t xml:space="preserve">262/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cpeb4/Btg2/Slc30a10/Snca/Prdx2/Trim2/Itsn1/Agtr1a/Optn/Grn/Prnp/Hipk2/Nupr1/Gba/Arrb1/Epor/Map3k12/Fbxw7/Cln8/Atp7a/Usp53/Bax/Birc5/Bcl2l11/Mcl1/Rb1/Siah1b/Sirt1/Psen1/Parp1/Nono/Ctnnb1/Ncf2/Gpi1/Hsp90ab1/Set/Pigt/Lancl1/Syngap1/Hspd1/Pcsk9/Trp53/Il27ra/Pmaip1/Casp7/Apoe/Tyrobp/Coro1a</t>
+    <t xml:space="preserve">Prdx2/Egr1/Snca/Btg2/Trim2/Coro1a/Prnp/Casp7/Slc30a10/Grn/Cpeb4/Itsn1/Optn/Apoe/Hipk2/Pmaip1/Fbxw7/Gba/Trp53/Epor/Agtr1a/Tyrobp/Nono/Ctnnb1/Il27ra/Rb1/Arrb1/Mcl1/Usp53/Pigt/Bcl2l11/Hsp90ab1/Atp7a/Birc5/Ncf2/Lancl1/Psen1/Set/Sirt1/Hspd1/Pcsk9/Bax/Nupr1/Syngap1/Map3k12/Siah1b/Parp1/Cln8/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043254</t>
@@ -883,7 +883,7 @@
     <t xml:space="preserve">360/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Cd36/Tmod1/Map3k1/Add2/Tal1/Dmtn/Sptb/Snca/Tfrc/Fnip2/Ticam1/Slf2/Mapre3/Ssh2/Gba/Mlst8/Epn1/1810058I24Rik/Plekhg2/Bax/Ppp2r5b/Nckap1/Dyrk1a/Camsap2/Vps35/Nck1/Bcl2l11/Rictor/Bid/Rap1b/Twf1/Togaram1/Cttn/Fnip1/Sh3glb1/Rack1/Parp1/Flii/Ncln/Dut/Dhx33/Hcls1/Sptan1/Slain2/Sar1b/Unc13a/Arpc2/Trp53/Plcg2/Rangrf/Ankrd27/Rac1/Capg/Fes/Arhgef2/Apoe/Tgfb1/Vill/Coro1a/Syk/Lcp1</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Snca/Syk/Arhgef2/Vill/Coro1a/Tmod1/Tgfb1/Ankrd27/Tal1/Dmtn/Rac1/Capg/Fnip2/Lcp1/Plcg2/Slf2/Arpc2/Epn1/Apoe/Cd36/Dyrk1a/Gba/Mlst8/Trp53/Ssh2/Ticam1/Rangrf/1810058I24Rik/Fes/Nckap1/Slain2/Vps35/Dut/Flii/Sh3glb1/Twf1/Togaram1/Camsap2/Tfrc/Plekhg2/Hcls1/Sptan1/Sar1b/Bcl2l11/Dhx33/Mapre3/Rap1b/Bid/Fnip1/Bax/Ncln/Unc13a/Nck1/Parp1/Ppp2r5b/Cttn/Rack1/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097435</t>
@@ -898,7 +898,7 @@
     <t xml:space="preserve">624/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Cd36/Mid1ip1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Snca/Map1a/Washc2/Nedd9/Washc5/Tsc1/Asap3/Ldlr/Micall2/Samd14/Rhof/Actn1/Arhgap12/Mybpc3/Mapre3/Ssh2/Mlst8/Arrb1/Myo6/Wasl/Fbxo5/Atp7a/Plekhg2/Cib1/Ppp1r9b/Bax/C9orf72/Nckap1/Ttbk2/Dyrk1a/Camsap2/Nck1/Sorbs1/Rictor/Bid/Swap70/Rb1/Twf1/Togaram1/Washc4/Arhgap35/Cttn/Taok1/Mia3/Abi1/Psen1/Actr2/Was/Colgalt1/Flii/Wdr1/Hsp90ab1/Myh10/Wipf1/Crtap/Hcls1/Plod3/Ift172/Sptan1/Slain2/Flna/Srf/Sh3pxd2b/Arpc2/Pdxp/Rangrf/Des/Rac1/Rac2/Col11a2/Capg/Vim/Fes/Arhgef2/Ltbp4/Apoe/Col5a1/Ccdc88b/Vill/Coro1a/Arhgef18/Myo1g/Elmo1/Lcp1</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Map3k1/Snca/Myo1g/Arhgef2/Vill/Mid1ip1/Coro1a/Tmod1/Ccdc88b/Rac2/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Elmo1/Actn1/Micall2/Lcp1/Vim/Arpc2/Apoe/Cd36/Ldlr/Arhgef18/Ltbp4/Col5a1/Dyrk1a/Flna/Des/Samd14/Mlst8/Sh3pxd2b/Map1a/Ssh2/Myo6/Nedd9/Pdxp/Col11a2/Rangrf/Myh10/Wasl/Ppp1r9b/Srf/Fes/Nckap1/Slain2/Wdr1/Plod3/Rb1/Flii/Ift172/Arhgap12/Arrb1/Twf1/Togaram1/Camsap2/Fbxo5/Plekhg2/Hcls1/Asap3/Wipf1/Sptan1/Cib1/Hsp90ab1/Atp7a/Swap70/Ttbk2/Washc4/Mapre3/Psen1/Bid/C9orf72/Actr2/Taok1/Bax/Rhof/Crtap/Sorbs1/Abi1/Arhgap35/Nck1/Mia3/Cttn/Colgalt1/Rictor/Mybpc3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042541</t>
@@ -913,7 +913,7 @@
     <t xml:space="preserve">13/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Slc6a9/Slc25a37/Abcb10/Fech/Snx3/Ldb1/Prmt1</t>
+    <t xml:space="preserve">Alas2/Slc6a9/Abcb10/Fech/Slc25a37/Ldb1/Prmt1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005884</t>
@@ -925,7 +925,7 @@
     <t xml:space="preserve">112/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Fhdc1/Tmod1/Map3k1/Dmtn/Specc1/Tsc1/Vps11/Actn1/Myo6/Wasl/Nckap1/Dyrk1a/Myo9a/Twf1/Vcl/Cttn/Was/Wipf1/Hcls1/Flna/Arpc2/Pdlim2/Rac1/Rac2/Coro1a/Lcp1</t>
+    <t xml:space="preserve">Fhdc1/Cobl/Map3k1/Coro1a/Tmod1/Rac2/Tsc1/Dmtn/Rac1/Actn1/Lcp1/Vps11/Arpc2/Dyrk1a/Specc1/Flna/Myo6/Wasl/Nckap1/Twf1/Hcls1/Wipf1/Pdlim2/Cttn/Myo9a/Vcl/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010872</t>
@@ -940,7 +940,7 @@
     <t xml:space="preserve">10/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Scd1/Abcg1/Stard4/Lamtor1/Abca2/Apoe</t>
+    <t xml:space="preserve">Abcg1/Stard4/Abca2/Apoe/Agtr1a/Scd1/Lamtor1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002274</t>
@@ -952,7 +952,7 @@
     <t xml:space="preserve">193/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Wnk4/Snca/Grn/Adam10/Ldlr/D6Wsu163e/Anxa3/Ticam1/Psen1/Ifngr1/Hspd1/Itgb2/Cst7/Fcgr3/Ptpn6/Gata2/Plcg2/Traf3ip2/Unc13d/Cplx2/Cd37/Gab2/Nr1d1/Rac2/Havcr2/Cd48/Il4/Ywhaz/Fes/Lgals9/Dock2/Lcp2/Tgfb1/Spi1/Tyrobp/Il1rl1/Cd84/Syk</t>
+    <t xml:space="preserve">Dock2/Snca/Il1rl1/Syk/Wnk4/Rac2/Tgfb1/Ywhaz/Grn/Cd84/Spi1/Gab2/Plcg2/Lgals9/Adam10/Pld2/Ldlr/Ptpn6/Unc13d/Cd48/Lcp2/D6Wsu163e/Ticam1/Tyrobp/Il4/Gata2/Cd37/Fes/Nr1d1/Havcr2/Fcgr3/Anxa3/Cplx2/Itgb2/Psen1/Traf3ip2/Hspd1/Ifngr1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043244</t>
@@ -967,7 +967,7 @@
     <t xml:space="preserve">119/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Gba/Smcr8/Cib1/Ttbk2/Camsap2/Swap70/Twf1/Taok1/Clec16a/Scaf4/Ubqln4/Flii/Wdr1/Igf1r/Sptan1/Arpc2/Pdxp/Ogfod1/Capg/Arhgef2/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Arpc2/Gba/Map1a/Pdxp/Ogfod1/Wdr1/Smcr8/Flii/Twf1/Camsap2/Ubqln4/Sptan1/Cib1/Swap70/Ttbk2/Taok1/Scaf4/Igf1r/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002275</t>
@@ -982,7 +982,7 @@
     <t xml:space="preserve">82/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Grn/D6Wsu163e/Anxa3/Ticam1/Itgb2/Ptpn6/Gata2/Plcg2/Unc13d/Cplx2/Gab2/Rac2/Havcr2/Il4/Ywhaz/Fes/Dock2/Spi1/Tyrobp/Cd84/Syk</t>
+    <t xml:space="preserve">Dock2/Syk/Rac2/Ywhaz/Grn/Cd84/Spi1/Gab2/Plcg2/Pld2/Ptpn6/Unc13d/D6Wsu163e/Ticam1/Tyrobp/Il4/Gata2/Fes/Havcr2/Anxa3/Cplx2/Itgb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043299</t>
@@ -991,7 +991,7 @@
     <t xml:space="preserve">leukocyte degranulation</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Lamp1/D6Wsu163e/Anxa3/Ap1g1/Itgb2/Gata2/Unc13d/Cplx2/Gab2/Rac2/Il4/Ywhaz/Fes/Lgals9/Spi1/Coro1a/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Coro1a/Rac2/Ywhaz/Lamp1/Cd84/Spi1/Gab2/Lgals9/Pld2/Unc13d/Ap1g1/D6Wsu163e/Il4/Gata2/Fes/Anxa3/Cplx2/Itgb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046985</t>
@@ -1006,7 +1006,7 @@
     <t xml:space="preserve">5/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Slc25a37/Abcb10/Ldb1/Prmt1</t>
+    <t xml:space="preserve">Slc6a9/Abcb10/Slc25a37/Ldb1/Prmt1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030098</t>
@@ -1018,7 +1018,7 @@
     <t xml:space="preserve">365/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Mink1/Egr3/St3gal1/Prdx2/Tsc1/Prex1/Hs1bp3/Zbtb7b/Gba/Hdac5/Fzd5/Atp7a/Ap3d1/Shb/Pknox1/Bax/Rara/Tusc2/Fnip1/Phf10/Gpr89/Ctnnb1/Tcf3/Srf/Irf2bp2/Stat5a/Vsir/Smarcd1/Fzd7/Trp53/Stat5b/Ptpn6/Sema4a/Kat2a/Plcg2/Traf3ip2/Vav1/Zfp36l1/Cbfb/Prr7/Pik3r6/Il4/Lgals9/Dock2/Spn/Mmp14/Tgfb1/Cd44/Laptm5/Spi1/Hdac7/Btk/Ptprc/Myb/Cdk6/Cmtm7/Jak3/Lgals1/Dpp4/Nfam1/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Hdac7/Btk/Egr1/Cmtm7/Dock2/Jak3/Laptm5/Nfam1/Syk/Myb/Ptprc/Mink1/Tgfb1/Cdk6/Spn/Tsc1/St3gal1/Cd44/Cbfb/Spi1/Vav1/Plcg2/Lgals9/Kat2a/Stat5b/Prex1/Hs1bp3/Ptpn6/Dpp4/Gba/Irf2bp2/Smarcd1/Trp53/Egr3/Zbtb7b/Stat5a/Fzd5/Il4/Mmp14/Fzd7/Sema4a/Pik3r6/Srf/Zfp36l1/Pknox1/Ctnnb1/Ap3d1/Hdac5/Prr7/Tcf3/Atp7a/Vsir/Tusc2/Traf3ip2/Fnip1/Rara/Bax/Gpr89/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045087</t>
@@ -1033,7 +1033,7 @@
     <t xml:space="preserve">557/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Irgm2/Trim10/Cd47/Snca/Optn/Grn/Herc6/Traf4/Serpinb1a/Atg9a/Lamp1/Isg20/Tollip/Ticam1/Rab43/Trim56/Tbk1/1810058I24Rik/Rnf185/Serinc5/Hexim1/Ankhd1/Arl8b/Rps6kb1/Usp15/Otud4/Actr2/Serinc3/Nono/Elf4/Was/Trim28/Cnot7/Phb2/Ifitm2/Ddx21/Trim35/Matr3/Ap1g1/Lyar/Traf3/Sp100/Dtx3l/Polr3e/Ifih1/Stat5a/Oasl1/Pik3cd/Trp53/Stat5b/Dapk1/Irak1/Fau/Ptpn6/Xrcc5/Plcg2/Unc13d/Vav1/Apobec3/Cadm1/Serpinb9/Havcr2/Capg/Vim/Irf5/Pik3r6/Il4/Csf1/Pla2g1b/Fes/Lgals9/Arhgef2/Apoe/Mst1r/Spi1/Tyrobp/Unc93b1/Btk/Coro1a/Jak3/Dpp4/Sla/Cd84/Syk/Oas2</t>
+    <t xml:space="preserve">Btk/Jak3/Snca/Appl2/Syk/Arhgef2/Coro1a/Grn/Sla/Oas2/Lamp1/Cd47/Capg/Cd84/Trim10/Spi1/Fau/Vav1/Tollip/Plcg2/Lgals9/Vim/Optn/Unc93b1/Apoe/Stat5b/Mst1r/Ptpn6/Dpp4/Xrcc5/Herc6/Irgm2/Serpinb1a/Unc13d/Irak1/Atg9a/Traf4/Tbk1/Apobec3/Rab43/Ap1g1/Trp53/Irf5/Trim56/Traf3/Ticam1/Tyrobp/Pik3cd/1810058I24Rik/Stat5a/Il4/Pla2g1b/Pik3r6/Fes/Csf1/Isg20/Polr3e/Nono/Dapk1/Havcr2/Ankhd1/Otud4/Matr3/Serpinb9/Hexim1/Dtx3l/Arl8b/Usp15/Trim28/Cadm1/Ifih1/Serinc5/Actr2/Ifitm2/Serinc3/Rnf185/Trim35/Lyar/Elf4/Phb2/Ddx21/Cnot7/Oasl1/Sp100/Rps6kb1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043242</t>
@@ -1045,7 +1045,7 @@
     <t xml:space="preserve">83/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Cib1/Ttbk2/Camsap2/Swap70/Twf1/Taok1/Clec16a/Scaf4/Ubqln4/Flii/Sptan1/Arpc2/Capg/Arhgef2/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Arpc2/Map1a/Flii/Twf1/Camsap2/Ubqln4/Sptan1/Cib1/Swap70/Ttbk2/Taok1/Scaf4/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030155</t>
@@ -1060,7 +1060,7 @@
     <t xml:space="preserve">623/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Cd36/Pld2/Mink1/Egr3/Dmtn/Cd47/Prdx2/Cited2/Tfrc/Prnp/Nedd9/Tsc1/Adam10/Ptpn23/Prex1/Zbtb7b/Ubash3b/Serpini1/Flcn/Cib1/Ap3d1/Shb/Dag1/Rara/Fcho1/Nck1/Swap70/Lamc1/Vcl/Mia3/Phf10/Iqgap1/Kifap3/Gtpbp4/Pde4d/Ptpru/Mfsd2b/Ldb1/Hspd1/Prkca/Flna/Srf/Stat5a/Vsir/Plekha2/Itgb2/Smarcd1/Fzd7/Lpxn/Arpc2/Stat5b/Irak1/Ptpn6/Il27ra/Unc13d/Vav1/Zdhhc21/Cd37/Fut4/Itga5/Rac1/Rcc2/Plxnc1/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Fermt3/Il4/Csf1/Fes/Cxcr4/Lgals9/Spn/Mmp14/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Ptprc/Myb/Cdk6/Coro1a/Jak3/Apbb1ip/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Jak3/Laptm5/Syk/Slc4a1/Myb/Ptprc/Mink1/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Cdk6/Spn/Apbb1ip/Tsc1/Dmtn/Cd44/Rac1/Cd47/Dock8/Ripor2/Rcc2/Cbfb/Ptpn23/Spi1/Fermt3/Cited2/Vav1/Lgals9/Zdhhc21/Cxcr4/Arpc2/Stat5b/Cd36/Prex1/Adam10/Pld2/Ptpn6/Dpp4/Itga5/Unc13d/Flna/Irak1/Smarcd1/Dag1/Egr3/Zbtb7b/Ldb1/Nedd9/Fut4/Stat5a/Il4/Lgals7/Mmp14/Fzd7/Cd37/Pik3r6/Srf/Fes/Csf1/Ap3d1/Il27ra/Havcr2/Tfrc/Plxnc1/Cib1/Itgb2/Prkca/Ubash3b/Swap70/Lamc1/Flcn/Vsir/Plekha2/Iqgap1/Hspd1/Rara/Serpini1/Gtpbp4/Ptpru/Nck1/Mia3/Kifap3/Fcho1/Shb/Vcl/Mfsd2b/Pde4d/Phf10/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016471</t>
@@ -1075,7 +1075,7 @@
     <t xml:space="preserve">21/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp6v0a1/Atp6ap2/Tmem199/Atp6v1a/Atp6v1b2/Atp6v0b/Atp6v1g1</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp6ap2/Atp6v1b2/Atp6v1a/Atp6v0a1/Atp6v0b/Tmem199/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002697</t>
@@ -1090,7 +1090,7 @@
     <t xml:space="preserve">335/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Cd47/H2-T23/Tfrc/Grn/Atg9a/Aplf/Lamp1/D6Wsu163e/Ticam1/Zbtb7b/Fzd5/Shb/Rara/Sirt1/Fbxo38/Was/Phb2/Ddx21/Gpi1/Hspd1/Ap1g1/Shld2/Stat5a/Vsir/Itgb2/Stat5b/Fcgr3/Ptpn6/Il27ra/Gata2/Plcg2/Unc13d/Vav1/Cadm1/Cd37/Serpinb9/Gab2/Rac2/Havcr2/Pik3r6/Il4/Fes/Lgals9/Spn/Tgfb1/Laptm5/Spi1/Tyrobp/Ptprc/Myb/Jak3/Dpp4/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Jak3/Laptm5/Appl2/Syk/Myb/Ptprc/Rac2/Tgfb1/Grn/Spn/Lamp1/Cd47/Cd84/Spi1/Gab2/Vav1/P2rx7/Plcg2/Lgals9/Stat5b/Cd36/Pld2/Ptpn6/Dpp4/Unc13d/Atg9a/Ap1g1/Aplf/Zbtb7b/H2-T23/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Fzd5/Il4/Gata2/Cd37/Pik3r6/Fes/Il27ra/Havcr2/Fcgr3/Serpinb9/Tfrc/Itgb2/Cadm1/Vsir/Fbxo38/Sirt1/Hspd1/Rara/Phb2/Shld2/Ddx21/Shb/Gpi1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006909</t>
@@ -1105,7 +1105,7 @@
     <t xml:space="preserve">188/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Cd47/Washc5/Ldlr/Anxa3/Pikfyve/Arhgap12/Icam5/Clcn3/Rara/4933434E20Rik/Tusc2/Arl8b/Snx3/Rack1/Ncf2/Lyar/Anxa11/Itgb2/Fcgr3/Gata2/Plcg2/Unc13d/Vav1/Ano6/Rac1/Rac2/Dock2/Tgfb1/Mst1r/Tyrobp/Ptprc/Coro1a/Myo1g/Elmo1/P2rx7/Syk</t>
+    <t xml:space="preserve">Dock2/Myo1g/Appl2/Syk/Ptprc/Coro1a/Ano6/Rac2/Tgfb1/Washc5/Rac1/Cd47/Elmo1/Vav1/P2rx7/Plcg2/Mst1r/Cd36/Ldlr/Pikfyve/Unc13d/Clcn3/Tyrobp/Gata2/4933434E20Rik/Anxa11/Arhgap12/Fcgr3/Anxa3/Itgb2/Arl8b/Ncf2/Tusc2/Icam5/Rara/Lyar/Rack1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098542</t>
@@ -1120,7 +1120,7 @@
     <t xml:space="preserve">758/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Irgm2/Trim10/Cd47/Snca/Scd1/Optn/Grn/Herc6/Ddit4/Traf4/Serpinb1a/Atg9a/Lamp1/Isg20/Tollip/Bpgm/Anxa3/Ticam1/Rab43/Trim56/Tbk1/1810058I24Rik/Elmod2/Rnf185/Serinc5/Tusc2/Hexim1/Irf2/Ankhd1/Arl8b/Rps6kb1/Ppm1b/Usp15/Nras/Otud4/Actr2/Serinc3/Nono/Elf4/Was/Trim28/Cnot7/Phb2/Ifitm2/Ddx21/Trim35/Ifngr1/Rbck1/Mov10/Matr3/Ap1g1/Lyar/Traf3/Sp100/Exosc5/Dtx3l/Polr3e/Ifih1/Stat5a/Oasl1/Pik3cd/Trp53/Stat5b/Dapk1/Irak1/Fau/Ptpn6/Il27ra/Xrcc5/Plcg2/Traf3ip2/Unc13d/Vav1/Apobec3/Pmaip1/Cadm1/Cd37/Serpinb9/Havcr2/Capg/Vim/Irf5/Pik3r6/Il4/Csf1/Pla2g1b/Fes/Rnf125/Lgals9/Arhgef2/Spn/Apoe/Tgfb1/Ccdc88b/Mst1r/Spi1/Tyrobp/Unc93b1/Btk/Ptprc/Coro1a/Jak3/Dpp4/Sla/P2rx7/Cd84/Syk/Oas2</t>
+    <t xml:space="preserve">Btk/Jak3/Snca/Appl2/Syk/Arhgef2/Ptprc/Coro1a/Ccdc88b/Tgfb1/Grn/Spn/Sla/Oas2/Lamp1/Cd47/Capg/Cd84/Trim10/Spi1/Fau/Vav1/Tollip/P2rx7/Plcg2/Lgals9/Vim/Ddit4/Optn/Unc93b1/Apoe/Stat5b/Mst1r/Cd36/Rnf125/Ptpn6/Dpp4/Xrcc5/Herc6/Irgm2/Serpinb1a/Unc13d/Irak1/Atg9a/Traf4/Pmaip1/Tbk1/Apobec3/Rab43/Ap1g1/Trp53/Irf5/Trim56/Traf3/Ticam1/Tyrobp/Scd1/Pik3cd/1810058I24Rik/Stat5a/Il4/Pla2g1b/Cd37/Pik3r6/Fes/Csf1/Isg20/Polr3e/Nono/Il27ra/Dapk1/Rbck1/Havcr2/Ankhd1/Otud4/Matr3/Serpinb9/Anxa3/Hexim1/Mov10/Dtx3l/Arl8b/Usp15/Trim28/Cadm1/Ifih1/Serinc5/Tusc2/Exosc5/Bpgm/Actr2/Ifitm2/Traf3ip2/Ifngr1/Serinc3/Nras/Rnf185/Trim35/Lyar/Elf4/Phb2/Irf2/Ddx21/Cnot7/Oasl1/Elmod2/Sp100/Rps6kb1/Ppm1b/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902903</t>
@@ -1135,7 +1135,7 @@
     <t xml:space="preserve">328/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Snca/Map1a/Washc2/Washc5/Tsc1/Asap3/Ldlr/Mapre3/Ssh2/Mlst8/Wasl/Plekhg2/Cib1/C9orf72/Nckap1/Ttbk2/Dyrk1a/Camsap2/Nck1/Rictor/Swap70/Rb1/Twf1/Togaram1/Washc4/Arhgap35/Cttn/Taok1/Psen1/Was/Colgalt1/Flii/Wdr1/Hcls1/Sptan1/Slain2/Flna/Sh3pxd2b/Arpc2/Pdxp/Rangrf/Rac1/Capg/Fes/Arhgef2/Apoe/Vill/Coro1a/Arhgef18</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Snca/Arhgef2/Vill/Mid1ip1/Coro1a/Tmod1/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Arpc2/Apoe/Ldlr/Arhgef18/Dyrk1a/Flna/Mlst8/Sh3pxd2b/Map1a/Ssh2/Pdxp/Rangrf/Wasl/Fes/Nckap1/Slain2/Wdr1/Rb1/Flii/Twf1/Togaram1/Camsap2/Plekhg2/Hcls1/Asap3/Sptan1/Cib1/Swap70/Ttbk2/Washc4/Mapre3/Psen1/C9orf72/Taok1/Arhgap35/Nck1/Cttn/Colgalt1/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010008</t>
@@ -1150,7 +1150,7 @@
     <t xml:space="preserve">246/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Abcb6/H2-T23/Wdr81/Pip4p1/Ctsd/Tfrc/Washc2/Ubap1/Snx8/Washc5/Vps26a/Atg9a/Slc11a2/Lamp1/Ldlr/Pikfyve/Lamtor1/Atp6ap2/Igf2r/Clcn3/Dnajc13/Atp7a/Lamtor3/Ap3d1/Chmp3/Ehd1/Rap2b/Vps35/Gripap1/Rmc1/Washc4/Snx2/Clec16a/Snx3/Vps4b/Ifitm2/Snx5/Ehd3/Rap2c/Fzd7/Abca2/Cmtm6/Snx10/Rac1/Rcc2</t>
+    <t xml:space="preserve">Ctsd/Appl2/Abcb6/Vps26a/Slc11a2/Washc5/Washc2/Lamp1/Pip4p1/Rac1/Rcc2/Abca2/Wdr81/Snx8/Ubap1/Igf2r/Ldlr/Pikfyve/Cmtm6/Atp6ap2/Atg9a/Dnajc13/Rap2b/Ehd1/Clcn3/H2-T23/Rap2c/Fzd7/Lamtor3/Snx10/Lamtor1/Ap3d1/Vps35/Chmp3/Tfrc/Snx5/Ehd3/Atp7a/Washc4/Snx2/Rmc1/Ifitm2/Gripap1/Vps4b/Clec16a/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055082</t>
@@ -1162,7 +1162,7 @@
     <t xml:space="preserve">552/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Wnk4/Atp6v0d1/Rhag/Slc30a10/Abcb6/Snca/Tfrc/Grn/Mcoln1/Prnp/Abcg1/Dmpk/Ankrd9/Slc11a2/Atp6v0a1/Kel/Ubash3b/Micu1/Arrb1/Atp6ap2/Vps33a/Slc30a9/Tmem199/Ppard/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Hmgcr/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Ccdc186/Xpr1/Birc5/Mafg/Slc12a7/Aco1/Pacs2/Atp6v1g1/Cdk16/Slc39a8/Sirt1/Rack1/Gpr89/Psen1/Nucks1/Lrp5/Pde4d/Selenot/Fkbp1a/Pdzd8/Tnni3/Igf1r/Prkca/P2rx1/Flna/Fkbp1b/Tcf7l2/Abca2/Tfr2/Trp53/Frrs1/Cyb561/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Hk2/Pim3/Rac1/Nr1d1/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Atp6v0d1/Snca/Slc4a1/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Tgfb1/Slc30a10/Slc11a2/Grn/Abcg1/Rac1/Gsto1/Rhag/P2rx7/Mcoln1/Slc30a9/Abca2/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Pim3/Flna/Xpr1/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Atp6v1a/Atp6v0a1/Tfr2/Cyb561/Smdt1/Xk/Ankrd9/Aco1/Ap3d1/Vps33a/Selenot/Ppard/Kel/Nr1d1/Dmpk/Arrb1/Slc4a8/Atp1b2/Tfrc/Hmgcr/Lrp5/Nucks1/Prkca/Ubash3b/Cdk16/Tmem199/Atp1a3/Atp7a/Hk2/Birc5/Ftl1/Psen1/Sirt1/Fkbp1a/Tnni3/Grina/Slc12a7/Bax/Slc39a8/Fkbp1b/Igf1r/Tcf7l2/Ccdc186/Atp6v1g1/P2rx1/Gpr89/Rack1/Mafg/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070997</t>
@@ -1177,7 +1177,7 @@
     <t xml:space="preserve">353/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cpeb4/Btg2/Slc30a10/Snca/Prdx2/Trim2/Itsn1/Agtr1a/Optn/Grn/Prnp/Hipk2/Ddit4/Ache/Tsc1/Picalm/Fos/Nupr1/Gba/Arrb1/Epor/Map3k12/Tbc1d24/Fbxw7/Cln8/Atp7a/Usp53/Bax/Birc5/Vps35/Bcl2l11/Elk1/Mcl1/Rb1/Siah1b/Sirt1/Rack1/Psen1/Parp1/Nono/Ctnnb1/Ncf2/Gpi1/Cbl/Hsp90ab1/Set/Pigt/Lancl1/Syngap1/Hspd1/Pcsk9/Trp53/Il27ra/Pmaip1/Casp7/Csf1/Apoe/Tyrobp/Coro1a</t>
+    <t xml:space="preserve">Prdx2/Egr1/Snca/Btg2/Picalm/Trim2/Coro1a/Prnp/Casp7/Slc30a10/Grn/Tsc1/Cpeb4/Itsn1/Ddit4/Optn/Apoe/Tbc1d24/Hipk2/Ache/Pmaip1/Fbxw7/Gba/Trp53/Epor/Agtr1a/Tyrobp/Csf1/Nono/Ctnnb1/Il27ra/Vps35/Rb1/Arrb1/Mcl1/Usp53/Pigt/Bcl2l11/Hsp90ab1/Atp7a/Birc5/Ncf2/Lancl1/Elk1/Psen1/Set/Sirt1/Fos/Hspd1/Pcsk9/Bax/Nupr1/Syngap1/Map3k12/Siah1b/Parp1/Cbl/Rack1/Cln8/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055076</t>
@@ -1192,7 +1192,7 @@
     <t xml:space="preserve">109/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Ank1/Epb42/Atp6v0d1/Rhag/Slc30a10/Abcb6/Fech/Tfrc/Prnp/Ankrd9/Picalm/Slc11a2/Rhd/Slc30a9/Tmem199/Atp6v1a/Ftl1/Atp7a/Ap3d1/Aco1/Atp6v1g1/Slc39a8/Tfr2/Frrs1/Cyb561</t>
+    <t xml:space="preserve">Alas2/Atp6v0d1/Picalm/Abcb6/Prnp/Slc30a10/Slc11a2/Fech/Ank1/Epb42/Rhag/Slc30a9/Frrs1/Atp6v1a/Tfr2/Cyb561/Rhd/Ankrd9/Aco1/Ap3d1/Tfrc/Tmem199/Atp7a/Ftl1/Slc39a8/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043300</t>
@@ -1207,7 +1207,7 @@
     <t xml:space="preserve">45/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Lamp1/D6Wsu163e/Ap1g1/Itgb2/Gata2/Unc13d/Gab2/Rac2/Il4/Fes/Lgals9/Spi1/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Lamp1/Cd84/Spi1/Gab2/Lgals9/Pld2/Unc13d/Ap1g1/D6Wsu163e/Il4/Gata2/Fes/Itgb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0090066</t>
@@ -1219,7 +1219,7 @@
     <t xml:space="preserve">433/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Agtr1a/Sema4b/Washc5/Tsc1/Picalm/Kel/Rab22a/Dpysl2/Ssh2/Mlst8/Clcn3/Ppard/Atp2b1/Cln8/Hmgcr/Atp7a/Plekhg2/Xk/Chmp3/Dip2b/Cdkl5/Nckap1/Golga4/Nck1/Slc12a7/Rictor/Lrrc8a/Swap70/Twf1/Arhgap35/Cttn/Sirt1/Ap2m1/Rpl4/Was/Flii/Wdr1/Hsp90ab1/Wdr36/Ulk2/Hcls1/Plod3/Sptan1/Megf8/P2rx1/Srf/Faah/Arpc2/Pdxp/Scpep1/Abcb8/Hp1bp3/Sema4a/Ano6/Zdhhc21/Rgs2/Rac1/Capg/Ptprs/Apoe/Vill/Coro1a/P2rx7/Rin3</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Picalm/Vill/Ptprs/Coro1a/Ano6/Tmod1/Washc5/Tsc1/Dmtn/Rac1/Capg/Hp1bp3/P2rx7/Rin3/Zdhhc21/Arpc2/Atp2b1/Apoe/Megf8/Dip2b/Mlst8/Rab22a/Ssh2/Abcb8/Clcn3/Dpysl2/Pdxp/Sema4b/Agtr1a/Xk/Scpep1/Rgs2/Sema4a/Srf/Nckap1/Wdr1/Ppard/Kel/Plod3/Lrrc8a/Flii/Faah/Twf1/Chmp3/Plekhg2/Hcls1/Hmgcr/Sptan1/Hsp90ab1/Atp7a/Swap70/Ap2m1/Ulk2/Sirt1/Slc12a7/Golga4/Cdkl5/Rpl4/Wdr36/Arhgap35/Nck1/Cttn/P2rx1/Cln8/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050865</t>
@@ -1234,7 +1234,7 @@
     <t xml:space="preserve">522/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Pld2/Egr3/Dmtn/Cd47/Snca/Prdx2/Tfrc/Grn/Prnp/Aplf/Lamp1/Ldlr/D6Wsu163e/Ticam1/Zbtb7b/Ubash3b/Ap3d1/Shb/Rara/Fcho1/Nck1/Bid/Phf10/Ctnnb1/Tcf3/Mfsd2b/Hspd1/Ap1g1/Cd320/Shld2/Prkca/Flna/Stat5a/Samsn1/Vsir/Itgb2/Smarcd1/Cst7/Stat5b/Ptpn6/Il27ra/Kat2a/Gata2/Unc13d/Zfp36l1/Cd37/Gab2/Nr1d1/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Il4/Fes/Lgals9/Spn/Mmp14/Apoe/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Tyrobp/Btk/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Tbc1d10c/Il1rl1/Cd84/Nfam1/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Btk/Jak3/Laptm5/Nfam1/Snca/Il1rl1/Syk/Slc4a1/Myb/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Grn/Spn/Dmtn/Lamp1/Cd44/Cd47/Dock8/Cd84/Ripor2/Cbfb/Spi1/Gab2/Tbc1d10c/Lgals9/Kat2a/Apoe/Stat5b/Pld2/Ldlr/Ptpn6/Dpp4/Unc13d/Flna/Ap1g1/Smarcd1/Aplf/Egr3/Zbtb7b/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Il4/Gata2/Lgals7/Mmp14/Cd37/Pik3r6/Fes/Zfp36l1/Ctnnb1/Ap3d1/Il27ra/Nr1d1/Havcr2/Tfrc/Itgb2/Prkca/Tcf3/Ubash3b/Vsir/Bid/Samsn1/Hspd1/Rara/Cd320/Shld2/Nck1/Cst7/Fcho1/Shb/Mfsd2b/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032880</t>
@@ -1246,7 +1246,7 @@
     <t xml:space="preserve">790/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Sh3tc2/Ptp4a3/Trp53inp2/Rph3al/Dmtn/Dnajb2/Map1a/Ctsd/Tfrc/Insig1/Glrx/Prnp/Kalrn/Pfkfb2/Abcg1/Arntl/Epb41/Rhbdf1/Picalm/Adam10/Ptpn23/Yod1/Cltc/Numb/Arrb1/Ppp2r5a/Ppard/Wasl/Fbxw7/Gpsm2/Hmgcr/Flcn/Cib1/Ppp1r9b/Wapl/Dag1/C9orf72/Nckap1/Uhmk1/Ttbk2/Rnf168/Birc5/Vps35/Gripap1/Otud7b/Sorbs1/Brca1/Swap70/Rb1/Exoc1/Stom/Cdk16/Vcl/Sirt1/Ap2m1/Sh3glb1/Snx3/Rack1/Psen1/Iqgap1/Parp1/Dnajc27/Ctnnb1/Trim28/Ipo5/Cct6a/Ergic3/Gopc/Lrp5/Tm7sf3/Cct2/Maged1/Lztfl1/Pgrmc1/Hsp90ab1/Polr1a/Myh10/Wipf1/Hcls1/Sp100/Sar1b/Idh2/Flna/Dtx3l/Ier3ip1/Ptpn9/Fkbp1b/Tcf7l2/Abca2/Ripor1/Akap5/Arpc2/Hadh/Pmaip1/Rangrf/Tmem231/Pim3/Rac1/Nr1d1/Ripor2/Lypla1/Kcnab2/Mmd/Arhgdig/Mmp14/Apoe/Tgfb1/Sytl4/Spi1/Tyrobp/P2rx7/Lcp1</t>
+    <t xml:space="preserve">Sh3tc2/Ctsd/Picalm/Prnp/Tgfb1/Cltc/Rph3al/Abcg1/Dmtn/Trp53inp2/Rac1/Lypla1/Ripor2/Kcnab2/Pfkfb2/Ptpn23/Spi1/Ppp2r5a/P2rx7/Abca2/Lcp1/Ripor1/Wapl/Glrx/Arpc2/Apoe/Cd36/Adam10/Yod1/Mmd/Insig1/Pim3/Kalrn/Hadh/Flna/Pmaip1/Fbxw7/Arntl/Arhgdig/Ptp4a3/Epb41/Map1a/Dag1/Numb/Idh2/Rangrf/Tyrobp/Sytl4/Myh10/Mmp14/Wasl/Ppp1r9b/Ptpn9/Maged1/Ctnnb1/Dnajb2/Nckap1/Tmem231/Ppard/Rnf168/Vps35/Rb1/Nr1d1/Uhmk1/Sh3glb1/Rhbdf1/Arrb1/Gpsm2/Tfrc/Cct2/Hcls1/Hmgcr/Wipf1/Polr1a/Otud7b/Dtx3l/Lrp5/Sar1b/Ergic3/Cib1/Cdk16/Hsp90ab1/Swap70/Trim28/Ttbk2/Ap2m1/Ier3ip1/Flcn/Birc5/Exoc1/Psen1/Sirt1/C9orf72/Iqgap1/Pgrmc1/Tm7sf3/Brca1/Lztfl1/Sorbs1/Gripap1/Fkbp1b/Ipo5/Cct6a/Parp1/Tcf7l2/Stom/Rack1/Akap5/Sp100/Snx3/Dnajc27/Vcl/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903131</t>
@@ -1261,7 +1261,7 @@
     <t xml:space="preserve">403/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Mink1/Egr3/St3gal1/Prdx2/Tsc1/Prex1/Hs1bp3/Fasn/Zbtb7b/Gba/Hdac5/Fzd5/Atp7a/Ap3d1/Shb/Pknox1/Bax/Rara/Tusc2/Fnip1/Phf10/Gpr89/Psen1/Ctnnb1/Tcf3/Srf/Irf2bp2/Stat5a/Vsir/Smarcd1/Fzd7/Trp53/Stat5b/Ptpn6/Sema4a/Kat2a/Plcg2/Traf3ip2/Vav1/Zfp36l1/Cbfb/Prr7/Pik3r6/Il4/Csf1/Fes/Lgals9/Dock2/Spn/Mmp14/Tgfb1/Cd44/Laptm5/Spi1/Hdac7/Btk/Ptprc/Myb/Cdk6/Cmtm7/Jak3/Lgals1/Dpp4/Nfam1/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Hdac7/Btk/Egr1/Cmtm7/Dock2/Jak3/Laptm5/Nfam1/Syk/Myb/Ptprc/Mink1/Tgfb1/Cdk6/Spn/Tsc1/St3gal1/Cd44/Cbfb/Spi1/Vav1/Plcg2/Lgals9/Kat2a/Stat5b/Prex1/Hs1bp3/Ptpn6/Dpp4/Fasn/Gba/Irf2bp2/Smarcd1/Trp53/Egr3/Zbtb7b/Stat5a/Fzd5/Il4/Mmp14/Fzd7/Sema4a/Pik3r6/Srf/Fes/Zfp36l1/Csf1/Pknox1/Ctnnb1/Ap3d1/Hdac5/Prr7/Tcf3/Atp7a/Vsir/Psen1/Tusc2/Traf3ip2/Fnip1/Rara/Bax/Gpr89/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002699</t>
@@ -1270,7 +1270,7 @@
     <t xml:space="preserve">positive regulation of immune effector process</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/H2-T23/Tfrc/Lamp1/D6Wsu163e/Ticam1/Fzd5/Shb/Rara/Sirt1/Fbxo38/Phb2/Ddx21/Gpi1/Hspd1/Ap1g1/Shld2/Stat5a/Itgb2/Stat5b/Fcgr3/Ptpn6/Gata2/Plcg2/Unc13d/Vav1/Cadm1/Cd37/Gab2/Rac2/Il4/Fes/Tgfb1/Laptm5/Spi1/Tyrobp/Ptprc/Myb/Dpp4/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Laptm5/Appl2/Syk/Myb/Ptprc/Rac2/Tgfb1/Lamp1/Cd84/Spi1/Gab2/Vav1/P2rx7/Plcg2/Stat5b/Cd36/Pld2/Ptpn6/Dpp4/Unc13d/Ap1g1/H2-T23/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Fzd5/Il4/Gata2/Cd37/Fes/Fcgr3/Tfrc/Itgb2/Cadm1/Fbxo38/Sirt1/Hspd1/Rara/Phb2/Shld2/Ddx21/Shb/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001817</t>
@@ -1285,7 +1285,7 @@
     <t xml:space="preserve">581/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Appl2/Btnl10/Cd47/Agtr1a/Optn/Prnp/Serpinb1a/Atg9a/Ermap/Ticam1/Zbtb7b/Gba/Arrb1/Arfgef2/Trim56/Atp6ap2/Fzd5/Sars/Akap12/Tbk1/Atp2b1/1810058I24Rik/Kpna6/Elf1/Rara/Otud7b/Brca1/Tusc2/Arnt/Sirt1/Ppm1b/Nras/Psen1/Iqgap1/Parp1/Ddx21/Pde4d/Ifngr1/Hsp90ab1/Dhx33/Hspd1/Traf3/Ifih1/Stat5a/Vsir/Srgn/Zbtb32/Stat5b/Irak1/Fcgr3/Ptpn6/Il27ra/Kat2a/Pdcd4/Plcg2/Ubash3a/Cadm1/Pde4b/Rac1/Havcr2/Irf5/Il4/Ptprs/Rnf125/Lgals9/Arhgef2/Spn/Trib2/Lgals7/Tgfb1/Ccdc88b/Laptm5/Tyrobp/Hdac7/Adcy7/Unc93b1/Btk/Ptprc/Jak3/Rftn1/P2rx7/Il1rl1/Cd84/Nfam1/Syk/Oas2</t>
+    <t xml:space="preserve">Hdac7/Btk/Egr1/Jak3/Adcy7/Laptm5/Nfam1/Appl2/Il1rl1/Rftn1/Syk/Arhgef2/Ptprs/Ptprc/Prnp/Btnl10/Ccdc88b/Tgfb1/Spn/Ermap/Oas2/Rac1/Cd47/Trib2/Cd84/P2rx7/Plcg2/Lgals9/Optn/Kat2a/Arfgef2/Unc93b1/Atp2b1/Stat5b/Cd36/Rnf125/Atp6ap2/Ptpn6/Arnt/Serpinb1a/Irak1/Atg9a/Tbk1/Gba/Zbtb7b/Ubash3a/Irf5/Kpna6/Trim56/Sars/Traf3/Agtr1a/Ticam1/Tyrobp/Elf1/1810058I24Rik/Stat5a/Fzd5/Il4/Lgals7/Il27ra/Havcr2/Arrb1/Fcgr3/Srgn/Otud7b/Pde4b/Hsp90ab1/Cadm1/Dhx33/Pdcd4/Vsir/Psen1/Ifih1/Tusc2/Sirt1/Iqgap1/Hspd1/Ifngr1/Rara/Nras/Brca1/Akap12/Zbtb32/Ddx21/Parp1/Ppm1b/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009168</t>
@@ -1297,7 +1297,7 @@
     <t xml:space="preserve">22/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Impdh2/Aprt/Adsl/Adssl1/Atic/Pfas/Gmpr/Gart</t>
+    <t xml:space="preserve">Ampd3/Gart/Pfas/Atic/Adssl1/Adsl/Gmpr/Impdh2/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045639</t>
@@ -1309,7 +1309,7 @@
     <t xml:space="preserve">86/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Fam210b/Abcb10/Tal1/Mturn/Fos/Gnas/Rb1/Gfi1b/Asxl2/Smap1/Hcls1/Prkca/Prmt1/Stat5a/Stat5b/Gata2/Zfp36l1/Csf1/Fes/Tgfb1/Tyrobp</t>
+    <t xml:space="preserve">Car2/Fam210b/Abcb10/Tgfb1/Tal1/Stat5b/Gnas/Mturn/Tyrobp/Stat5a/Gata2/Prmt1/Fes/Zfp36l1/Csf1/Rb1/Hcls1/Smap1/Prkca/Fos/Gfi1b/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008154</t>
@@ -1324,7 +1324,7 @@
     <t xml:space="preserve">165/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Washc5/Micall2/Ssh2/Mlst8/Wasl/Plekhg2/Nckap1/Nck1/Rictor/Swap70/Twf1/Arhgap35/Cttn/Abi1/Was/Flii/Wdr1/Wipf1/Hcls1/Sptan1/Arpc2/Pdxp/Rac1/Capg/Vill/Coro1a</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Map3k1/Vill/Coro1a/Tmod1/Washc5/Dmtn/Rac1/Capg/Micall2/Arpc2/Mlst8/Ssh2/Pdxp/Wasl/Nckap1/Wdr1/Flii/Twf1/Plekhg2/Hcls1/Wipf1/Sptan1/Swap70/Abi1/Arhgap35/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002694</t>
@@ -1336,7 +1336,7 @@
     <t xml:space="preserve">478/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Pld2/Egr3/Cd47/Snca/Prdx2/Tfrc/Grn/Prnp/Aplf/Lamp1/Ldlr/D6Wsu163e/Ticam1/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Bid/Phf10/Ctnnb1/Tcf3/Hspd1/Ap1g1/Cd320/Shld2/Stat5a/Samsn1/Vsir/Itgb2/Smarcd1/Cst7/Stat5b/Ptpn6/Il27ra/Kat2a/Gata2/Unc13d/Zfp36l1/Cd37/Gab2/Nr1d1/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Il4/Fes/Lgals9/Spn/Mmp14/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Tyrobp/Btk/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Tbc1d10c/Il1rl1/Cd84/Nfam1/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Btk/Jak3/Laptm5/Nfam1/Snca/Il1rl1/Syk/Slc4a1/Myb/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Grn/Spn/Lamp1/Cd44/Cd47/Dock8/Cd84/Ripor2/Cbfb/Spi1/Gab2/Tbc1d10c/Lgals9/Kat2a/Stat5b/Pld2/Ldlr/Ptpn6/Dpp4/Unc13d/Ap1g1/Smarcd1/Aplf/Egr3/Zbtb7b/D6Wsu163e/Ticam1/Tyrobp/Stat5a/Il4/Gata2/Lgals7/Mmp14/Cd37/Pik3r6/Fes/Zfp36l1/Ctnnb1/Ap3d1/Il27ra/Nr1d1/Havcr2/Tfrc/Itgb2/Tcf3/Vsir/Bid/Samsn1/Hspd1/Rara/Cd320/Shld2/Nck1/Cst7/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044208</t>
@@ -1348,7 +1348,7 @@
     <t xml:space="preserve">8/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Adss/Adsl/Adssl1/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">Gart/Pfas/Atic/Adssl1/Adsl/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0022409</t>
@@ -1360,7 +1360,7 @@
     <t xml:space="preserve">45/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Dmtn/Cd47/Cited2/Tfrc/Ptpn23/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Phf10/Kifap3/Pde4d/Ptpru/Mfsd2b/Hspd1/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Irak1/Il27ra/Fut4/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Tgfb1/Ccdc88b/Cd44/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Spn/Dmtn/Cd44/Cd47/Dock8/Cbfb/Ptpn23/Cited2/Lgals9/Stat5b/Dpp4/Irak1/Smarcd1/Egr3/Zbtb7b/Fut4/Stat5a/Il4/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Vsir/Hspd1/Rara/Ptpru/Nck1/Kifap3/Fcho1/Shb/Mfsd2b/Pde4d/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006753</t>
@@ -1372,7 +1372,7 @@
     <t xml:space="preserve">464/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Aldh1l2/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Fasn/Mlst8/Atp6v1a/Nmnat3/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Adal/Gcdh/Enpp5/Acaca/Ndufa10/Psen1/Cs/Parp1/Ncf2/Gpi1/Adss/Prps1/Dlat/Dut/Entpd6/Impdh2/Guk1/Pdha1/Aprt/Nudt14/Adsl/Mthfd1/Nt5m/Idh2/Umps/Suclg2/Prkag2/Trp53/Qprt/Cad/Khk/Adssl1/Acsl5/H6pd/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Kcnab2/Uprt/Il4/Tgfb1/Nme4/Dctd/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Uprt/Kcnab2/Pfkfb2/Nme4/Dctd/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Cad/Pkm/Trp53/Atp6v1a/Umps/Idh2/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/H6pd/Gmpr/Impdh2/Dut/Aldh1l2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Prps1/Eno3/Dlat/Qprt/Acaca/Atp7a/Adal/Hk2/Flcn/Ncf2/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Adss/Parp1/Enpp5/Pmvk/Nudt14/Nmnat3/Nt5m/Gpi1/Entpd6</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046148</t>
@@ -1381,7 +1381,7 @@
     <t xml:space="preserve">pigment biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Slc6a9/Ctns/Abcb10/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Atp7a/Snx3/Pgrmc1/Cox10</t>
+    <t xml:space="preserve">Alas2/Slc6a9/Abcb10/Slc11a2/Ctns/Fech/Urod/Hmbs/Tmem14c/Cox10/Atp7a/Pgrmc1/Alad/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001816</t>
@@ -1393,7 +1393,7 @@
     <t xml:space="preserve">638/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Appl2/Btnl10/Cd47/Agtr1a/Optn/Prnp/Serpinb1a/Atg9a/Ermap/Ticam1/Zbtb7b/Gba/Arrb1/Arfgef2/Trim56/Atp6ap2/Fzd5/Sars/Akap12/Tbk1/Atp2b1/1810058I24Rik/Kpna6/Ap3d1/Elf1/Rara/Ash1l/Usp25/Otud7b/Brca1/Tusc2/Arnt/Sirt1/Ppm1b/Nras/Psen1/Iqgap1/Parp1/Ddx21/Pde4d/Ifngr1/Hsp90ab1/Dhx33/Hspd1/Traf3/Ifih1/Stat5a/Vsir/Srgn/Zbtb32/Stat5b/Irak1/Fcgr3/Ptpn6/Il27ra/Kat2a/Pdcd4/Plcg2/Traf3ip2/Ubash3a/Cadm1/Pde4b/Nrros/Rac1/Havcr2/Irf5/Il4/Ptprs/Rnf125/Lgals9/Arhgef2/Spn/Trib2/Lcp2/Lgals7/Tgfb1/Ccdc88b/Laptm5/Tyrobp/Hdac7/Adcy7/Unc93b1/Btk/Ptprc/Jak3/Rftn1/P2rx7/Il1rl1/Cd84/Nfam1/Syk/Oas2</t>
+    <t xml:space="preserve">Hdac7/Btk/Egr1/Jak3/Adcy7/Laptm5/Nfam1/Appl2/Il1rl1/Rftn1/Syk/Arhgef2/Ptprs/Ptprc/Prnp/Btnl10/Ccdc88b/Tgfb1/Spn/Ermap/Oas2/Rac1/Cd47/Trib2/Cd84/P2rx7/Plcg2/Lgals9/Optn/Kat2a/Arfgef2/Unc93b1/Atp2b1/Stat5b/Cd36/Rnf125/Atp6ap2/Ptpn6/Arnt/Serpinb1a/Irak1/Atg9a/Tbk1/Gba/Nrros/Lcp2/Zbtb7b/Ubash3a/Irf5/Kpna6/Trim56/Sars/Traf3/Agtr1a/Ticam1/Tyrobp/Elf1/1810058I24Rik/Stat5a/Fzd5/Il4/Lgals7/Ap3d1/Il27ra/Havcr2/Arrb1/Fcgr3/Srgn/Otud7b/Pde4b/Hsp90ab1/Usp25/Cadm1/Dhx33/Pdcd4/Vsir/Psen1/Ifih1/Tusc2/Sirt1/Ash1l/Iqgap1/Traf3ip2/Hspd1/Ifngr1/Rara/Nras/Brca1/Akap12/Zbtb32/Ddx21/Parp1/Ppm1b/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901137</t>
@@ -1405,7 +1405,7 @@
     <t xml:space="preserve">514/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/St3gal1/Extl3/Snca/Uap1l1/St3gal6/St3gal5/Pkm/Cltc/St3gal2/Trak2/Gnpda1/Hexa/Flcn/Atp7a/Adal/Gcdh/Man1c1/Ago2/Sord/Slc39a8/Ndufa10/Psen1/Parp1/Ctnnb1/Alg11/Dpy19l3/B3galnt2/Adss/Prps1/Dlat/Itm2c/Dut/Pigt/Ndst1/St6galnac4/Impdh2/Guk1/Pdha1/Tyw1/Mtap/Aprt/Plod3/Adsl/Mthfd1/Alg5/Umps/Ugcg/Gk/Pomt1/Tcf7l2/Abca2/Dpagt1/Galnt7/Fut8/Cad/Vangl2/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/B4galnt1/Gmpr/Pgap2/Gart/Npr2/Fut4/Rft1/Pgm2/Uprt/Il4/Xxylt1/Tgfb1/Nme4/Dctd/Adcy7/Jak3</t>
+    <t xml:space="preserve">Ampd3/Jak3/Adcy7/Snca/Extl3/Tgfb1/Cltc/St3gal5/St3gal1/Uprt/Nme4/Xxylt1/Dctd/Gart/Abca2/Pfas/Acsl5/Ugcg/Uap1l1/Pdha1/Atic/Pgap2/Cad/Pkm/Fut8/Rft1/Umps/Fut4/Galnt7/Il4/Gk/Adssl1/Npr2/Adsl/Gnpda1/Alg5/Pgm2/Dpagt1/Gmpr/Ctnnb1/Impdh2/Plod3/Pomt1/Dut/Vangl2/Mthfd1/B4galnt1/Papss2/Guk1/Prps1/Ndst1/Alg11/Trak2/Dlat/St3gal6/Pigt/Atp7a/Adal/Flcn/Tyw1/Psen1/Hexa/B3galnt2/St3gal2/Gcdh/Ak4/Ndufa10/Man1c1/Aprt/Mtap/Itm2c/St6galnac4/Slc39a8/Ago2/Adss/Dpy19l3/Parp1/Tcf7l2/Sord</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002886</t>
@@ -1417,7 +1417,7 @@
     <t xml:space="preserve">53/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Ticam1/Ddx21/Itgb2/Fcgr3/Gata2/Unc13d/Gab2/Rac2/Il4/Fes/Spi1/Tyrobp/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Cd84/Spi1/Gab2/Pld2/Unc13d/D6Wsu163e/Ticam1/Tyrobp/Il4/Gata2/Fes/Fcgr3/Itgb2/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007159</t>
@@ -1432,7 +1432,7 @@
     <t xml:space="preserve">308/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Add2/Cd47/Prdx2/Tfrc/Prnp/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Slc39a8/Mia3/Phf10/Hspd1/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Irak1/Ptpn6/Il27ra/Zdhhc21/Cd37/Fut4/Itga5/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Fermt3/Il4/Lgals9/Spn/Selplg/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Add2/Jak3/Laptm5/Syk/Slc4a1/Myb/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Cd47/Dock8/Ripor2/Cbfb/Fermt3/Lgals9/Zdhhc21/Stat5b/Ptpn6/Dpp4/Itga5/Irak1/Smarcd1/Egr3/Zbtb7b/Selplg/Fut4/Stat5a/Il4/Lgals7/Cd37/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Vsir/Hspd1/Rara/Slc39a8/Nck1/Mia3/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006898</t>
@@ -1441,7 +1441,7 @@
     <t xml:space="preserve">receptor-mediated endocytosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Snca/Itsn1/Bmp2k/Tfrc/Ache/Picalm/Ldlr/Cltc/Numb/Pikfyve/Arrb1/Myo6/Wasl/Dnajc13/Fcho1/Smap1/Cttn/Itsn2/Ap2m1/Nedd4/Ppp3r1/Cbl/Atad1/Ap1g1/Prkca/Pcsk9/Itgb2/Cap1/Ankrd13b/Abca2/Akap5/Tfr2/Plcg2/Il4/Apoe/Cd44/Arhgap27/Syk/Rin3</t>
+    <t xml:space="preserve">Snca/Syk/Picalm/Cltc/Cd44/Arhgap27/Itsn1/Bmp2k/Cap1/Rin3/Abca2/Plcg2/Apoe/Cd36/Pld2/Ldlr/Pikfyve/Ache/Dnajc13/Ap1g1/Myo6/Numb/Tfr2/Ankrd13b/Il4/Atad1/Wasl/Arrb1/Nedd4/Tfrc/Smap1/Itgb2/Prkca/Ap2m1/Ppp3r1/Pcsk9/Cbl/Cttn/Akap5/Fcho1/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031267</t>
@@ -1453,7 +1453,7 @@
     <t xml:space="preserve">255/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Rph3al/Optn/Ranbp10/Als2/Picalm/Micall2/Gga2/Yipf2/Hace1/Atp7a/Cib1/Dvl2/Ccdc186/C9orf72/Cdkl5/Ehd1/Nckap1/Pkn2/Birc5/Exoc8/Golga4/Rabgap1/Ipo9/Vcl/Daam1/Usp6nl/Iqgap1/Was/Ipo5/Ncf2/Tnpo1/Rcc1/Ap1g1/Flna/Xpo5/Unc13d/Rangrf/Ankrd27/Rac1/Rcc2/Arhgef2/Dock2/Sytl4/Arhgdib/Rin3</t>
+    <t xml:space="preserve">Dock2/Appl2/Picalm/Arhgef2/Rph3al/Ankrd27/Rac1/Gga2/Rcc2/Rin3/Micall2/Arhgdib/Optn/Als2/Xpo5/Unc13d/Flna/Ehd1/Ap1g1/Pkn2/Hace1/Rabgap1/Rangrf/Tnpo1/Ipo9/Yipf2/Sytl4/Nckap1/Dvl2/Exoc8/Cib1/Atp7a/Birc5/Ncf2/Ranbp10/Rcc1/C9orf72/Iqgap1/Golga4/Cdkl5/Ipo5/Ccdc186/Vcl/Usp6nl/Daam1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0020027</t>
@@ -1468,7 +1468,7 @@
     <t xml:space="preserve">19/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Slc6a9/Epb42/Slc25a37/Abcb10/Fech/Snx3/Ldb1/Prmt1</t>
+    <t xml:space="preserve">Alas2/Slc6a9/Abcb10/Fech/Epb42/Slc25a37/Ldb1/Prmt1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070161</t>
@@ -1480,7 +1480,7 @@
     <t xml:space="preserve">508/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cldn13/Cgn/Wnk4/Mpp2/Nedd9/Gab1/Dcaf6/Traf4/Asap3/Ubn1/Micall2/Frmd6/Pikfyve/Actn1/Fzd5/Tle2/Flcn/Usp53/Dag1/Mpp1/Pkn2/Rap2b/Nck1/Ash1l/Ddx6/Sorbs1/Rap1b/Irf2/Twf1/Vcl/Cttn/Sav1/Cdc42bpa/Iqgap1/Ctnnb1/Was/Wdr1/Cbl/Ptpru/Parvg/Sptan1/Prkca/Flna/Focad/Itgb2/Rap2c/Lpxn/Lin7c/Arpc2/Pdxp/Vangl2/Ptpn6/Pdlim2/Vapa/Vav1/Rangrf/Cadm1/Arhgef6/Vamp5/Des/Tjp3/Itga5/Fermt3/Fes/Cxcr4/Arhgef2/Lcp2/Def6/Plxdc1/Ptprc/Coro1a/Dpp4/Sla/P2rx7/Il1rl1/Lcp1/Cd53</t>
+    <t xml:space="preserve">Cldn13/Il1rl1/Arhgef2/Slc4a1/Ptprc/Wnk4/Coro1a/Sla/Ubn1/Cgn/Def6/Gab1/Fermt3/Vav1/Actn1/Cd53/P2rx7/Micall2/Vapa/Lcp1/Mpp2/Cxcr4/Vamp5/Arpc2/Lin7c/Pikfyve/Ptpn6/Dpp4/Itga5/Flna/Frmd6/Des/Traf4/Arhgef6/Rap2b/Dag1/Lcp2/Plxdc1/Dcaf6/Nedd9/Ddx6/Pdxp/Pkn2/Rangrf/Fzd5/Rap2c/Fes/Focad/Ctnnb1/Wdr1/Tjp3/Twf1/Vangl2/Asap3/Sptan1/Mpp1/Usp53/Itgb2/Prkca/Cadm1/Flcn/Rap1b/Pdlim2/Ash1l/Iqgap1/Sav1/Parvg/Cdc42bpa/Irf2/Sorbs1/Ptpru/Nck1/Cbl/Cttn/Tle2/Vcl/Lpxn/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043523</t>
@@ -1495,7 +1495,7 @@
     <t xml:space="preserve">234/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cpeb4/Btg2/Slc30a10/Snca/Prdx2/Trim2/Itsn1/Optn/Grn/Prnp/Hipk2/Nupr1/Gba/Arrb1/Epor/Map3k12/Fbxw7/Cln8/Atp7a/Bax/Birc5/Bcl2l11/Mcl1/Sirt1/Psen1/Parp1/Nono/Ctnnb1/Ncf2/Gpi1/Hsp90ab1/Set/Lancl1/Syngap1/Hspd1/Pcsk9/Trp53/Il27ra/Pmaip1/Apoe/Tyrobp/Coro1a</t>
+    <t xml:space="preserve">Prdx2/Egr1/Snca/Btg2/Trim2/Coro1a/Prnp/Slc30a10/Grn/Cpeb4/Itsn1/Optn/Apoe/Hipk2/Pmaip1/Fbxw7/Gba/Trp53/Epor/Tyrobp/Nono/Ctnnb1/Il27ra/Arrb1/Mcl1/Bcl2l11/Hsp90ab1/Atp7a/Birc5/Ncf2/Lancl1/Psen1/Set/Sirt1/Hspd1/Pcsk9/Bax/Nupr1/Syngap1/Map3k12/Parp1/Cln8/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010942</t>
@@ -1507,7 +1507,7 @@
     <t xml:space="preserve">567/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Aldh1a1/Map3k1/Snca/Optn/Ctsd/Grn/Prnp/Dusp6/Ddit4/Picalm/Adam10/Atg9a/Fos/Nupr1/Trp53inp1/Arrb1/Pea15a/Igf2r/Rbm5/Akap12/Fbxw7/Dcun1d3/Hmgcr/Flcn/Mtch2/Bax/Nck1/Bcl2l11/Ccar1/Bid/Elk1/Mcl1/Ncoa1/Siah1b/Sirt1/Sav1/Fnip1/Sh3glb1/Celf1/Rack1/Psen1/Parp1/Serinc3/Ctnnb1/Ncf2/Trim35/Maged1/Scp2/Rbck1/Itm2c/Rrp1b/Hspd1/Rps6ka2/Calhm2/Tnfrsf26/Pcsk9/Mybbp1a/Tcf7l2/Pik3cd/Trp53/Dapk1/Ppp2r1a/Pdcd4/Pmaip1/Ano6/Zfas1/Casp7/Prodh/Irf5/Prr7/Tfap4/Pla2g1b/Phlda2/Apoe/Tgfb1/Cd44/Laptm5/Tyrobp/Ptprc/Jak3/Lgals1/P2rx7/Syk</t>
+    <t xml:space="preserve">Lgals1/Egr1/Map3k1/Jak3/Ctsd/Laptm5/Aldh1a1/Snca/Syk/Picalm/Ptprc/Ano6/Prnp/Tgfb1/Casp7/Grn/Cd44/Ppp2r1a/P2rx7/Ddit4/Optn/Apoe/Cd36/Adam10/Igf2r/Mtch2/Tfap4/Atg9a/Pmaip1/Prodh/Fbxw7/Trp53/Phlda2/Rbm5/Irf5/Zfas1/Dusp6/Trp53inp1/Tyrobp/Pik3cd/Pla2g1b/Maged1/Pea15a/Ctnnb1/Mybbp1a/Prr7/Dapk1/Rbck1/Sh3glb1/Arrb1/Mcl1/Celf1/Ccar1/Hmgcr/Bcl2l11/Rps6ka2/Flcn/Pdcd4/Ncf2/Elk1/Psen1/Bid/Sirt1/Fos/Ncoa1/Sav1/Hspd1/Fnip1/Pcsk9/Bax/Nupr1/Scp2/Serinc3/Trim35/Itm2c/Dcun1d3/Akap12/Siah1b/Calhm2/Nck1/Parp1/Tcf7l2/Tnfrsf26/Rack1/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055072</t>
@@ -1519,7 +1519,7 @@
     <t xml:space="preserve">71/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Ank1/Epb42/Atp6v0d1/Rhag/Fech/Tfrc/Picalm/Slc11a2/Rhd/Tmem199/Atp6v1a/Ftl1/Aco1/Atp6v1g1/Slc39a8/Tfr2/Frrs1/Cyb561</t>
+    <t xml:space="preserve">Alas2/Atp6v0d1/Picalm/Slc11a2/Fech/Ank1/Epb42/Rhag/Frrs1/Atp6v1a/Tfr2/Cyb561/Rhd/Aco1/Tfrc/Tmem199/Ftl1/Slc39a8/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042113</t>
@@ -1528,7 +1528,7 @@
     <t xml:space="preserve">B cell activation</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Tfrc/Aplf/Ticam1/Hdac5/Shb/Bax/Rnf168/Swap70/Fnip1/Tcf3/Phb2/Hspd1/Cd320/Shld2/Irf2bp2/Stat5a/Samsn1/Pik3cd/Trp53/Stat5b/Ptpn6/Il27ra/Plcg2/Traf3ip2/Zfp36l1/Il4/Mmp14/Tgfb1/Laptm5/Spi1/Tyrobp/Hdac7/Btk/Ptprc/Myb/Cmtm7/Jak3/Lgals1/Dpp4/Tbc1d10c/Nfam1/Syk</t>
+    <t xml:space="preserve">Lgals1/Hdac7/Btk/Cmtm7/Jak3/Laptm5/Nfam1/Syk/Myb/Ptprc/Tgfb1/St3gal1/Spi1/Tbc1d10c/Plcg2/Stat5b/Ptpn6/Dpp4/Irf2bp2/Trp53/Aplf/Ticam1/Tyrobp/Pik3cd/Stat5a/Il4/Mmp14/Zfp36l1/Il27ra/Hdac5/Rnf168/Tfrc/Tcf3/Swap70/Traf3ip2/Samsn1/Hspd1/Fnip1/Bax/Cd320/Phb2/Shld2/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009167</t>
@@ -1540,7 +1540,7 @@
     <t xml:space="preserve">33/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Impdh2/Guk1/Aprt/Adsl/Adssl1/Atic/Ak4/Pfas/Gmpr/Gart</t>
+    <t xml:space="preserve">Ampd3/Gart/Pfas/Atic/Adssl1/Adsl/Gmpr/Impdh2/Guk1/Ak4/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002285</t>
@@ -1555,7 +1555,7 @@
     <t xml:space="preserve">163/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Tfrc/Tsc1/Aplf/Lamp1/Zbtb7b/Atp7a/Shb/Rara/Rnf168/Swap70/Psen1/Hspd1/Ap1g1/Shld2/Trp53/Il27ra/Sema4a/Plcg2/Unc13d/Havcr2/Il4/Lgals9/Spn/Tgfb1/Spi1/Ptprc/Myb/Coro1a/Jak3/Apbb1ip/Lgals1/Lcp1</t>
+    <t xml:space="preserve">Lgals1/Jak3/Myb/Ptprc/Coro1a/Tgfb1/Spn/Apbb1ip/Tsc1/St3gal1/Lamp1/Spi1/Lcp1/Plcg2/Lgals9/Unc13d/Ap1g1/Trp53/Aplf/Zbtb7b/Il4/Sema4a/Il27ra/Rnf168/Havcr2/Tfrc/Atp7a/Swap70/Psen1/Hspd1/Rara/Shld2/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051020</t>
@@ -1567,7 +1567,7 @@
     <t xml:space="preserve">288/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Rph3al/Optn/Rragc/Ranbp10/Als2/Picalm/Micall2/Gga2/Yipf2/Lamtor1/Rab3ip/Hace1/Atp7a/Cib1/Dvl2/Ccdc186/C9orf72/Cdkl5/Ehd1/Nckap1/Pkn2/Birc5/Exoc8/Golga4/Rabgap1/Ipo9/Vcl/Daam1/Usp6nl/Iqgap1/Was/Ipo5/Ncf2/Tnpo1/Rcc1/Ap1g1/Flna/Xpo5/Unc13d/Rangrf/Ankrd27/Rac1/Rcc2/Arhgef2/Dock2/Sytl4/Lcp1/Arhgdib/Rin3</t>
+    <t xml:space="preserve">Dock2/Appl2/Picalm/Arhgef2/Rragc/Rph3al/Ankrd27/Rac1/Gga2/Rcc2/Rin3/Micall2/Lcp1/Arhgdib/Optn/Als2/Xpo5/Unc13d/Flna/Ehd1/Ap1g1/Pkn2/Hace1/Rabgap1/Rangrf/Tnpo1/Rab3ip/Ipo9/Yipf2/Sytl4/Lamtor1/Nckap1/Dvl2/Exoc8/Cib1/Atp7a/Birc5/Ncf2/Ranbp10/Rcc1/C9orf72/Iqgap1/Golga4/Cdkl5/Ipo5/Ccdc186/Vcl/Usp6nl/Daam1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002444</t>
@@ -1579,7 +1579,7 @@
     <t xml:space="preserve">90/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Anxa3/Ticam1/Tusc2/Ddx21/Wdr1/Itgb2/Fcgr3/Gata2/Traf3ip2/Unc13d/Cplx2/Gab2/Rac2/Il4/Ywhaz/Fes/Spi1/Tyrobp/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Ywhaz/Cd84/Spi1/Gab2/Pld2/Unc13d/D6Wsu163e/Ticam1/Tyrobp/Il4/Gata2/Fes/Wdr1/Fcgr3/Anxa3/Cplx2/Itgb2/Tusc2/Traf3ip2/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050778</t>
@@ -1591,7 +1591,7 @@
     <t xml:space="preserve">414/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Appl2/Btnl10/Cd47/H2-T23/Tfrc/Prnp/Ermap/Lamp1/Trim56/Fzd5/Tbk1/Usp9x/Shb/Elf1/Bax/Rara/Fcho1/Rnf185/Hexim1/Sirt1/Fbxo38/Nras/Psen1/Nono/Pde4d/Rbck1/Dgkz/Matr3/Hspd1/Ap1g1/Shld2/Stat5a/Itgb2/Lpxn/Stat5b/Fcgr3/Ptpn6/Il27ra/Xrcc5/Gata2/Plcg2/Vav1/Ubash3a/Cadm1/Pde4b/Gab2/Havcr2/Il4/Lgals9/Lcp2/Tgfb1/Cd44/Laptm5/Fyb/Spi1/Tyrobp/Btk/Ptprc/Myb/Dpp4/Myo1g/Rftn1/P2rx7/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Laptm5/Nfam1/Myo1g/Appl2/Rftn1/Syk/Myb/Ptprc/Prnp/Btnl10/Tgfb1/Ermap/Fyb/Lamp1/Cd44/Cd47/Spi1/Gab2/Vav1/P2rx7/Plcg2/Lgals9/Stat5b/Pld2/Ptpn6/Dpp4/Xrcc5/Tbk1/Ap1g1/Usp9x/Lcp2/Ubash3a/H2-T23/Trim56/Tyrobp/Elf1/Stat5a/Fzd5/Il4/Gata2/Dgkz/Nono/Il27ra/Rbck1/Havcr2/Matr3/Fcgr3/Tfrc/Hexim1/Itgb2/Pde4b/Cadm1/Psen1/Fbxo38/Sirt1/Hspd1/Rara/Bax/Nras/Rnf185/Shld2/Fcho1/Shb/Pde4d/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0022603</t>
@@ -1603,7 +1603,7 @@
     <t xml:space="preserve">781/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Spta1/Cd36/Epb42/Strip2/Dmtn/Cited2/Ddhd1/Agtr1a/Tfrc/Sema4b/Grn/Kalrn/Hipk2/Nedd9/Epb41/Ache/Gab1/Picalm/Adam10/Pkm/Prex1/Anxa3/Numb/Rhof/Kel/Epn1/Trak2/Sars/Tbc1d24/Foxo4/Arhgap15/Kif13b/Flcn/Xk/Cib1/Mtch2/Stk25/Dag1/Pias2/Dip2b/Dvl2/Cdkl5/Brwd3/Golga4/Vps35/Myo9a/Ago2/Brca1/Gna13/Arhgap35/Sirt1/Itsn2/Sh3glb1/Nras/Psen1/Rpl4/Actr2/Ctnnb1/Nedd4/Phb2/Maged1/Wdr1/Pdzd8/Stau2/Myh10/Mov10/Syngap1/Ulk2/Cul7/Prkca/Megf8/Sp100/Flna/Srf/Adck1/Gtf2i/Itgb2/Unc13a/Akap5/Pik3cd/Arpc2/Vangl2/Sema4a/Gata2/Unc13d/Sh3d19/Hk2/Ankrd27/Ago4/Itga5/Rac1/Rcc2/Plxnc1/Rac2/Vim/Pik3r6/Csf1/Ptprs/Tenm4/Fes/Cxcr4/Apoe/Tgfb1/Cd44/Vash2/Coro1a/Arhgef18/Arap3/Eng</t>
+    <t xml:space="preserve">Spta1/Arap3/Cldn13/Picalm/Ptprs/Coro1a/Rac2/Tgfb1/Grn/Ankrd27/Dmtn/Cd44/Rac1/Strip2/Vash2/Epb42/Rcc2/Gab1/Cited2/Eng/Vim/Cxcr4/Arpc2/Epn1/Apoe/Cd36/Prex1/Adam10/Tbc1d24/Arhgef18/Ddhd1/Itga5/Kalrn/Hipk2/Ache/Gtf2i/Megf8/Unc13d/Flna/Mtch2/Dip2b/Ago4/Stk25/Tenm4/Epb41/Pkm/Pdzd8/Dag1/Numb/Nedd9/Pias2/Sars/Sema4b/Agtr1a/Xk/Pik3cd/Myh10/Gata2/Cul7/Sh3d19/Sema4a/Gna13/Pik3r6/Srf/Fes/Maged1/Csf1/Ctnnb1/Wdr1/Kel/Vps35/Sh3glb1/Vangl2/Nedd4/Dvl2/Anxa3/Tfrc/Plxnc1/Mov10/Trak2/Cib1/Itgb2/Prkca/Hk2/Flcn/Psen1/Kif13b/Ulk2/Sirt1/Adck1/Actr2/Golga4/Cdkl5/Rpl4/Nras/Rhof/Stau2/Brwd3/Brca1/Syngap1/Phb2/Foxo4/Ago2/Arhgap15/Arhgap35/Unc13a/Akap5/Myo9a/Sp100/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901879</t>
@@ -1615,7 +1615,7 @@
     <t xml:space="preserve">21/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Cib1/Ttbk2/Camsap2/Swap70/Twf1/Taok1/Flii/Wdr1/Sptan1/Arpc2/Pdxp/Capg/Arhgef2/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Arpc2/Map1a/Pdxp/Wdr1/Flii/Twf1/Camsap2/Sptan1/Cib1/Swap70/Ttbk2/Taok1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030863</t>
@@ -1630,7 +1630,7 @@
     <t xml:space="preserve">103/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cobl/Spta1/Tmod1/Gypc/Ank1/Epb42/Dmtn/Sptb/Epb41/Actn1/Wasl/Ppp1r9b/Mpp1/Cttn/Iqgap1/Actr2/Wdr1/Hcls1/Sptan1/Flna/Cap1/Pdlim2/Coro1a</t>
+    <t xml:space="preserve">Spta1/Cobl/Sptb/Gypc/Slc4a1/Coro1a/Tmod1/Dmtn/Ank1/Epb42/Cap1/Actn1/Flna/Epb41/Wasl/Ppp1r9b/Wdr1/Hcls1/Sptan1/Mpp1/Pdlim2/Actr2/Iqgap1/Cttn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009127</t>
@@ -1651,7 +1651,7 @@
     <t xml:space="preserve">731/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Aldh1a1/Appl2/Fads3/Amdhd2/Mid1ip1/Mgst3/Renbp/Snca/Prkar2b/Scd1/Insig1/Aldh1l2/Pfkfb2/Eno3/Scd2/Urod/Cyb5a/Ddit4/Pkm/Pycr1/Nupr1/Acox1/Stard4/Bpgm/Hagh/Pcx/Fasn/Mlst8/Gnpda1/Sars/Ppard/Atp7a/Mtch2/Gcdh/Aco1/Sord/Aldh4a1/Brca1/Slc39a8/Mpst/Sirt1/Adipor2/Acaca/Qars/Gls/Pycr2/Sgpl1/Psen1/Cs/Vars2/Etfb/Got1/Got2/Farsb/Idh3g/Gpi1/Scp2/Adss/Dlat/Ppa2/Idh3a/Enoph1/Pdha1/Mtap/Plod3/Ilvbl/Tars2/Mthfd1/Acsf2/Idh2/Stat5a/Gk/Prkag2/Faah/Mthfd1l/Hadh/Trp53/Qprt/Stat5b/Cad/Khk/Adssl1/Acsl5/Atic/Thap4/Pfas/Papss2/Sdsl/Hk2/Gart/Nudt19/Alox5ap/Nr1d1/Lypla1/Prodh/Acsbg1/Gsto1/Pla2g1b/Kyat3/Ces2g/P2rx7/Syk</t>
+    <t xml:space="preserve">Ces2g/Prkar2b/Fads3/Aldh1a1/Snca/Appl2/Mgst3/Syk/Slc4a1/Mid1ip1/Kyat3/Renbp/Gsto1/Lypla1/Urod/Amdhd2/Pfkfb2/Gart/P2rx7/Stard4/Pfas/Alox5ap/Acsl5/Nudt19/Ddit4/Cyb5a/Stat5b/Cd36/Thap4/Insig1/Khk/Fasn/Hadh/Sdsl/Pdha1/Tars2/Pcx/Mtch2/Atic/Hagh/Prodh/Acox1/Mlst8/Cad/Pkm/Trp53/Sars/Idh2/Scd1/Stat5a/Gk/Adssl1/Prkag2/Pla2g1b/Acsbg1/Gnpda1/Aco1/Ppard/Plod3/Aldh1l2/Nr1d1/Faah/Idh3a/Cs/Mthfd1/Got2/Papss2/Mthfd1l/Scd2/Eno3/Dlat/Qprt/Acaca/Atp7a/Adipor2/Hk2/Psen1/Gcdh/Sirt1/Bpgm/Aldh4a1/Idh3g/Acsf2/Pycr1/Nupr1/Scp2/Brca1/Mtap/Got1/Farsb/Enoph1/Etfb/Slc39a8/Vars2/Adss/Mpst/Ilvbl/Qars/Sgpl1/Sord/Pycr2/Ppa2/Gls/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0022604</t>
@@ -1663,7 +1663,7 @@
     <t xml:space="preserve">290/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Spta1/Epb42/Strip2/Dmtn/Kalrn/Nedd9/Epb41/Ache/Picalm/Prex1/Numb/Rhof/Tbc1d24/Arhgap15/Cib1/Pias2/Cdkl5/Brwd3/Myo9a/Gna13/Arhgap35/Itsn2/Sh3glb1/Actr2/Wdr1/Pdzd8/Stau2/Myh10/Mov10/Cul7/Flna/Unc13a/Akap5/Arpc2/Sema4a/Unc13d/Sh3d19/Ankrd27/Ago4/Rac1/Rcc2/Plxnc1/Rac2/Fes/Cxcr4/Cd44/Coro1a/Arhgef18/Arap3</t>
+    <t xml:space="preserve">Spta1/Arap3/Cldn13/Picalm/Coro1a/Rac2/Ankrd27/Dmtn/Cd44/Rac1/Strip2/Epb42/Rcc2/Cxcr4/Arpc2/Prex1/Tbc1d24/Arhgef18/Kalrn/Ache/Unc13d/Flna/Ago4/Epb41/Pdzd8/Numb/Nedd9/Pias2/Myh10/Cul7/Sh3d19/Sema4a/Gna13/Fes/Wdr1/Sh3glb1/Plxnc1/Mov10/Cib1/Actr2/Cdkl5/Rhof/Stau2/Brwd3/Arhgap15/Arhgap35/Unc13a/Akap5/Myo9a/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0022407</t>
@@ -1678,7 +1678,7 @@
     <t xml:space="preserve">376/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Mink1/Egr3/Dmtn/Cd47/Prdx2/Cited2/Tfrc/Prnp/Ptpn23/Zbtb7b/Ubash3b/Ap3d1/Shb/Rara/Fcho1/Nck1/Swap70/Mia3/Phf10/Kifap3/Gtpbp4/Pde4d/Ptpru/Mfsd2b/Hspd1/Prkca/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Irak1/Ptpn6/Il27ra/Zdhhc21/Cd37/Fut4/Cbfb/Ripor2/Dock8/Havcr2/Pik3r6/Fermt3/Il4/Lgals9/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Jak3/Laptm5/Syk/Slc4a1/Myb/Ptprc/Mink1/Coro1a/Prnp/Ccdc88b/Tgfb1/Spn/Dmtn/Cd44/Cd47/Dock8/Ripor2/Cbfb/Ptpn23/Spi1/Fermt3/Cited2/Lgals9/Zdhhc21/Stat5b/Ptpn6/Dpp4/Irak1/Smarcd1/Egr3/Zbtb7b/Fut4/Stat5a/Il4/Lgals7/Cd37/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Prkca/Ubash3b/Swap70/Vsir/Hspd1/Rara/Gtpbp4/Ptpru/Nck1/Mia3/Kifap3/Fcho1/Shb/Mfsd2b/Pde4d/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042440</t>
@@ -1690,7 +1690,7 @@
     <t xml:space="preserve">55/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Slc6a9/Ctns/Abcb10/Abcb6/Hebp1/Fech/Hmbs/Urod/Slc11a2/Alad/Tmem14c/Atp7a/Snx3/Pgrmc1/Cox10</t>
+    <t xml:space="preserve">Alas2/Abcb6/Slc6a9/Abcb10/Slc11a2/Ctns/Fech/Urod/Hebp1/Hmbs/Tmem14c/Cox10/Atp7a/Pgrmc1/Alad/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046040</t>
@@ -1702,7 +1702,7 @@
     <t xml:space="preserve">20/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Aprt/Adsl/Adssl1/Atic/Pfas/Gmpr/Gart</t>
+    <t xml:space="preserve">Ampd3/Gart/Pfas/Atic/Adssl1/Adsl/Gmpr/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009117</t>
@@ -1714,7 +1714,7 @@
     <t xml:space="preserve">458/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Aldh1l2/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Fasn/Mlst8/Atp6v1a/Nmnat3/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Adal/Gcdh/Enpp5/Acaca/Ndufa10/Psen1/Cs/Parp1/Ncf2/Gpi1/Adss/Prps1/Dlat/Dut/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Nt5m/Idh2/Umps/Suclg2/Prkag2/Trp53/Qprt/Cad/Khk/Adssl1/Acsl5/H6pd/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Kcnab2/Uprt/Il4/Tgfb1/Nme4/Dctd/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Uprt/Kcnab2/Pfkfb2/Nme4/Dctd/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Cad/Pkm/Trp53/Atp6v1a/Umps/Idh2/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/H6pd/Gmpr/Impdh2/Dut/Aldh1l2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Prps1/Eno3/Dlat/Qprt/Acaca/Atp7a/Adal/Hk2/Flcn/Ncf2/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Adss/Parp1/Enpp5/Pmvk/Nmnat3/Nt5m/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001881</t>
@@ -1726,7 +1726,7 @@
     <t xml:space="preserve">34/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Agtr1a/Optn/Pheta2/Als2/Ache/Ldlr/Lamtor1/Arfgef2/Psen1/Ehd3/Pcsk9</t>
+    <t xml:space="preserve">Snca/Pheta2/Optn/Als2/Arfgef2/Ldlr/Ache/Agtr1a/Lamtor1/Ehd3/Psen1/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901880</t>
@@ -1738,7 +1738,7 @@
     <t xml:space="preserve">73/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Cib1/Ttbk2/Camsap2/Swap70/Twf1/Taok1/Flii/Sptan1/Arpc2/Capg/Arhgef2/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Arpc2/Map1a/Flii/Twf1/Camsap2/Sptan1/Cib1/Swap70/Ttbk2/Taok1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019887</t>
@@ -1753,7 +1753,7 @@
     <t xml:space="preserve">180/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Inka2/Prkar2b/Als2/Pim1/Mlst8/Smcr8/Map3k12/Cdkn2c/Mob3c/Ccnt1/Cib1/Nck1/Rictor/Stradb/Hexim1/Dbf4/Taok1/Abi1/Qars/Rack1/Iqgap1/Parp1/Tcf3/Elp3/Hsp90ab1/Prkag2/Ccng1/Spred2/Mob3b/Rac2/Lgals9/Trib2/Tgfb1/P2rx7</t>
+    <t xml:space="preserve">Prkar2b/Rac2/Tgfb1/Tal1/Trib2/P2rx7/Lgals9/Als2/Ccng1/Mlst8/Inka2/Mob3b/Cdkn2c/Spred2/Prkag2/Ccnt1/Smcr8/Hexim1/Cib1/Tcf3/Hsp90ab1/Taok1/Iqgap1/Stradb/Map3k12/Abi1/Mob3c/Nck1/Parp1/Dbf4/Qars/Rack1/Pim1/Elp3/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006873</t>
@@ -1768,7 +1768,7 @@
     <t xml:space="preserve">410/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Wnk4/Atp6v0d1/Rhag/Slc30a10/Abcb6/Snca/Tfrc/Grn/Mcoln1/Prnp/Dmpk/Ankrd9/Slc11a2/Atp6v0a1/Kel/Ubash3b/Micu1/Atp6ap2/Vps33a/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Xpr1/Mafg/Aco1/Pacs2/Atp6v1g1/Slc39a8/Gpr89/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Prkca/P2rx1/Flna/Fkbp1b/Tfr2/Trp53/Frrs1/Cyb561/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Atp6v0d1/Snca/Slc4a1/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Tgfb1/Slc30a10/Slc11a2/Grn/Gsto1/Rhag/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Flna/Xpr1/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Atp6v1a/Atp6v0a1/Tfr2/Cyb561/Smdt1/Xk/Ankrd9/Aco1/Ap3d1/Vps33a/Kel/Dmpk/Slc4a8/Atp1b2/Tfrc/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Gpr89/Mafg/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030003</t>
@@ -1780,7 +1780,7 @@
     <t xml:space="preserve">63/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Alas2/Car2/Wnk4/Atp6v0d1/Slc30a10/Abcb6/Snca/Tfrc/Grn/Mcoln1/Prnp/Dmpk/Ankrd9/Slc11a2/Atp6v0a1/Kel/Ubash3b/Micu1/Atp6ap2/Vps33a/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Atp6v1b2/Atp7a/Xk/Ap3d1/Bax/Mafg/Aco1/Pacs2/Atp6v1g1/Slc39a8/Gpr89/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Prkca/P2rx1/Flna/Fkbp1b/Tfr2/Trp53/Frrs1/Cyb561/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Car2/Atp6v0d1/Snca/Slc4a1/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Tgfb1/Slc30a10/Slc11a2/Grn/Gsto1/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Atp6ap2/Ptpn6/Micu1/Flna/Frrs1/Atp6v1b2/Pacs2/Pdzd8/Trp53/Atp6v1a/Atp6v0a1/Tfr2/Cyb561/Smdt1/Xk/Ankrd9/Aco1/Ap3d1/Vps33a/Kel/Dmpk/Slc4a8/Atp1b2/Tfrc/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Gpr89/Mafg/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901214</t>
@@ -1792,7 +1792,7 @@
     <t xml:space="preserve">316/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cpeb4/Btg2/Slc30a10/Snca/Prdx2/Trim2/Itsn1/Optn/Grn/Prnp/Hipk2/Ddit4/Tsc1/Picalm/Fos/Nupr1/Gba/Arrb1/Epor/Map3k12/Tbc1d24/Fbxw7/Cln8/Atp7a/Bax/Birc5/Vps35/Bcl2l11/Elk1/Mcl1/Sirt1/Rack1/Psen1/Parp1/Nono/Ctnnb1/Ncf2/Gpi1/Cbl/Hsp90ab1/Set/Lancl1/Syngap1/Hspd1/Pcsk9/Trp53/Il27ra/Pmaip1/Csf1/Apoe/Tyrobp/Coro1a</t>
+    <t xml:space="preserve">Prdx2/Egr1/Snca/Btg2/Picalm/Trim2/Coro1a/Prnp/Slc30a10/Grn/Tsc1/Cpeb4/Itsn1/Ddit4/Optn/Apoe/Tbc1d24/Hipk2/Pmaip1/Fbxw7/Gba/Trp53/Epor/Tyrobp/Csf1/Nono/Ctnnb1/Il27ra/Vps35/Arrb1/Mcl1/Bcl2l11/Hsp90ab1/Atp7a/Birc5/Ncf2/Lancl1/Elk1/Psen1/Set/Sirt1/Fos/Hspd1/Pcsk9/Bax/Nupr1/Syngap1/Map3k12/Parp1/Cbl/Rack1/Cln8/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048193</t>
@@ -1801,7 +1801,7 @@
     <t xml:space="preserve">Golgi vesicle transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Ank1/Optn/Insig1/Trappc2l/Snx8/Lamp1/Gga2/Uvrag/Arfgef2/Rabep1/Rnf139/Ccdc93/Ap3d1/Vps29/Exoc8/Golga4/Trappc8/Exoc1/Cog4/Snx2/Ergic2/Mia3/Uso1/Snx3/Rack1/Mia2/Ergic3/Gopc/Copg2/Use1/Ap1g1/Lman1/Tmed5/Sar1b/Ier3ip1/Ehd3/Kif1c/Tmed3/Vapa/Rangrf/Ergic1/Vamp5/Lypla1/Bcap29/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Ank1/Lamp1/Gga2/Lypla1/Bcap29/Vapa/Snx8/Optn/Arfgef2/Vamp5/Ergic1/Rabep1/Insig1/Lman1/Tmed3/Uvrag/Kif1c/Ap1g1/Rnf139/Rangrf/Trappc2l/Ap3d1/Copg2/Trappc8/Vps29/Ccdc93/Exoc8/Mia2/Sar1b/Ergic3/Ehd3/Ier3ip1/Exoc1/Tmed5/Snx2/Golga4/Cog4/Mia3/Use1/Ergic2/Rack1/Snx3/Gopc/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055065</t>
@@ -1813,7 +1813,7 @@
     <t xml:space="preserve">412/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Wnk4/Ank1/Epb42/Atp6v0d1/Rhag/Slc30a10/Abcb6/Cnnm2/Snca/Fech/Tfrc/Mcoln1/Prnp/Dmpk/Ankrd9/Picalm/Slc11a2/Rhd/Kel/Ubash3b/Micu1/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Cnnm4/Atp7a/Xk/Ap3d1/Bax/Slc12a7/Aco1/Gnas/Pacs2/Atp6v1g1/Slc39a8/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Mllt6/Prkca/P2rx1/Flna/Snx5/Fkbp1b/Tfr2/Frrs1/Cyb561/Ptpn6/Atp1b2/Plcg2/Atp1a3/Snx10/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Atp6v0d1/Snca/Picalm/Ptprc/Wnk4/Coro1a/Abcb6/Prnp/Cnnm2/Tgfb1/Slc30a10/Slc11a2/Fech/Ank1/Gsto1/Epb42/Rhag/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Ptpn6/Micu1/Gnas/Flna/Frrs1/Pacs2/Pdzd8/Atp6v1a/Tfr2/Cyb561/Rhd/Smdt1/Xk/Mllt6/Cnnm4/Ankrd9/Aco1/Snx10/Ap3d1/Kel/Dmpk/Atp1b2/Tfrc/Snx5/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Slc12a7/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043436</t>
@@ -1828,7 +1828,7 @@
     <t xml:space="preserve">723/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Aldh1a1/Appl2/Fads3/Amdhd2/Mid1ip1/Mgst3/Renbp/Snca/Prkar2b/Scd1/Insig1/Aldh1l2/Pfkfb2/Eno3/Scd2/Urod/Cyb5a/Ddit4/Pkm/Pycr1/Nupr1/Acox1/Stard4/Bpgm/Hagh/Pcx/Fasn/Mlst8/Gnpda1/Sars/Ppard/Atp7a/Mtch2/Gcdh/Aco1/Sord/Aldh4a1/Brca1/Slc39a8/Mpst/Sirt1/Adipor2/Acaca/Qars/Gls/Pycr2/Sgpl1/Psen1/Cs/Vars2/Etfb/Got1/Got2/Farsb/Idh3g/Gpi1/Scp2/Adss/Dlat/Ppa2/Idh3a/Enoph1/Pdha1/Mtap/Plod3/Ilvbl/Tars2/Mthfd1/Acsf2/Idh2/Gk/Prkag2/Faah/Mthfd1l/Hadh/Trp53/Qprt/Cad/Khk/Adssl1/Acsl5/Atic/Thap4/Pfas/Papss2/Sdsl/Hk2/Gart/Nudt19/Alox5ap/Nr1d1/Lypla1/Prodh/Acsbg1/Gsto1/Pla2g1b/Kyat3/Ces2g/P2rx7/Syk</t>
+    <t xml:space="preserve">Ces2g/Prkar2b/Fads3/Aldh1a1/Snca/Appl2/Mgst3/Syk/Slc4a1/Mid1ip1/Kyat3/Renbp/Gsto1/Lypla1/Urod/Amdhd2/Pfkfb2/Gart/P2rx7/Stard4/Pfas/Alox5ap/Acsl5/Nudt19/Ddit4/Cyb5a/Cd36/Thap4/Insig1/Khk/Fasn/Hadh/Sdsl/Pdha1/Tars2/Pcx/Mtch2/Atic/Hagh/Prodh/Acox1/Mlst8/Cad/Pkm/Trp53/Sars/Idh2/Scd1/Gk/Adssl1/Prkag2/Pla2g1b/Acsbg1/Gnpda1/Aco1/Ppard/Plod3/Aldh1l2/Nr1d1/Faah/Idh3a/Cs/Mthfd1/Got2/Papss2/Mthfd1l/Scd2/Eno3/Dlat/Qprt/Acaca/Atp7a/Adipor2/Hk2/Psen1/Gcdh/Sirt1/Bpgm/Aldh4a1/Idh3g/Acsf2/Pycr1/Nupr1/Scp2/Brca1/Mtap/Got1/Farsb/Enoph1/Etfb/Slc39a8/Vars2/Adss/Mpst/Ilvbl/Qars/Sgpl1/Sord/Pycr2/Ppa2/Gls/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032801</t>
@@ -1840,7 +1840,7 @@
     <t xml:space="preserve">30/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mylip/Snx25/Uvrag/Sh3glb1/Nedd4/Dtx3l/Pcsk9/Abca2/Apoe/Tgfb1/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Tgfb1/Abca2/Snx25/Apoe/Uvrag/Mylip/Sh3glb1/Nedd4/Dtx3l/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007015</t>
@@ -1852,7 +1852,7 @@
     <t xml:space="preserve">374/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Washc2/Nedd9/Washc5/Tsc1/Asap3/Micall2/Samd14/Rhof/Actn1/Arhgap12/Ssh2/Mlst8/Arrb1/Myo6/Wasl/Plekhg2/Ppp1r9b/C9orf72/Nckap1/Nck1/Sorbs1/Rictor/Swap70/Twf1/Washc4/Arhgap35/Cttn/Abi1/Actr2/Was/Flii/Wdr1/Myh10/Wipf1/Hcls1/Sptan1/Flna/Srf/Sh3pxd2b/Arpc2/Pdxp/Rac1/Rac2/Capg/Arhgef2/Vill/Coro1a/Arhgef18/Myo1g/Elmo1/Lcp1</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Map3k1/Myo1g/Arhgef2/Vill/Coro1a/Tmod1/Rac2/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Elmo1/Actn1/Micall2/Lcp1/Arpc2/Arhgef18/Flna/Samd14/Mlst8/Sh3pxd2b/Ssh2/Myo6/Nedd9/Pdxp/Myh10/Wasl/Ppp1r9b/Srf/Nckap1/Wdr1/Flii/Arhgap12/Arrb1/Twf1/Plekhg2/Hcls1/Asap3/Wipf1/Sptan1/Swap70/Washc4/C9orf72/Actr2/Rhof/Sorbs1/Abi1/Arhgap35/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032418</t>
@@ -1864,7 +1864,7 @@
     <t xml:space="preserve">75/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Pip4p1/D6Wsu163e/Lamtor1/Vps33a/Flcn/Arl8b/Def8/Gata2/Unc13d/Cplx2/Gab2/Rac2/Il4/Ywhaz/Fes/Sytl4/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Ywhaz/Pip4p1/Cd84/Gab2/Pld2/Unc13d/D6Wsu163e/Sytl4/Il4/Gata2/Fes/Lamtor1/Vps33a/Def8/Cplx2/Arl8b/Flcn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990849</t>
@@ -1882,7 +1882,7 @@
     <t xml:space="preserve">107/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Ctsd/Atg9a/Nupr1/Map1lc3b/Pikfyve/Rab43/Gba/Trp53inp1/Zfyve26/Smcr8/Tmem41b/Atg2b/C9orf72/Gabarap/Mtmr3/Atg4d/Trappc8/Pacs2/Pip4k2c/Sh3glb1/Psen1/Pik3c2b/Ulk2</t>
+    <t xml:space="preserve">Ctsd/Trp53inp2/Map1lc3b/Pikfyve/Atg9a/Gba/Rab43/Pacs2/Atg2b/Gabarap/Trp53inp1/Mtmr3/Zfyve26/Tmem41b/Smcr8/Trappc8/Sh3glb1/Psen1/Ulk2/C9orf72/Nupr1/Atg4d/Pip4k2c/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043101</t>
@@ -1891,7 +1891,7 @@
     <t xml:space="preserve">purine-containing compound salvage</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Impdh2/Mtap/Aprt/Adsl/Adssl1/Gmpr/Pgm2</t>
+    <t xml:space="preserve">Ampd3/Adssl1/Adsl/Pgm2/Gmpr/Impdh2/Aprt/Mtap/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044325</t>
@@ -1906,7 +1906,7 @@
     <t xml:space="preserve">114/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ank1/Scn10a/Mpp2/Prnp/Actn1/Arrb1/Epn1/Grina/Cib1/Ppp1r9b/Pacs2/Homer1/Ap2m1/Ctnnb1/Gopc/Pde4d/Fkbp1a/Hsp90ab1/Flna/Fkbp1b/Zfas1/Rangrf/Pde4b/Kcnab2/Ywhaz</t>
+    <t xml:space="preserve">Prnp/Ywhaz/Ank1/Kcnab2/Actn1/Mpp2/Epn1/Flna/Scn10a/Pacs2/Zfas1/Rangrf/Ppp1r9b/Ctnnb1/Arrb1/Cib1/Pde4b/Hsp90ab1/Ap2m1/Fkbp1a/Grina/Homer1/Fkbp1b/Gopc/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060627</t>
@@ -1918,7 +1918,7 @@
     <t xml:space="preserve">498/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Rph3al/Cd47/Snca/Itsn1/Bmp2k/Glrx/Picalm/Vps11/Lamp1/Ptpn23/D6Wsu163e/Numb/Arrb1/Syn1/Myo6/Smcr8/Rnf139/Wasl/Dnajc13/C9orf72/Ehd1/Gripap1/Rap1b/Smap1/Snap29/Ap2m1/Sh3glb1/Snx3/Vps4b/Rack1/Nedd4/Ppp3r1/Gopc/Cbl/Atad1/Use1/Ap1g1/Lyar/Prkca/P2rx1/Sar1b/Pcsk9/Itgb2/Ankrd13b/Abca2/Akap5/Tfr2/Slc4a8/Fcgr3/Gata2/Plcg2/Unc13d/Ano6/Cplx2/Ankrd27/Gab2/Lypla1/Rac2/Il4/Fes/Lgals9/Dock2/Apoe/Tgfb1/Sytl4/Spi1/Ptprc/Coro1a/P2rx7/Cd84/Syk/Rin3</t>
+    <t xml:space="preserve">Dock2/Snca/Appl2/Syk/Picalm/Ptprc/Coro1a/Ano6/Rac2/Tgfb1/Rph3al/Ankrd27/Lamp1/Cd47/Cd84/Lypla1/Itsn1/Ptpn23/Bmp2k/Spi1/Gab2/P2rx7/Rin3/Abca2/Vps11/Plcg2/Lgals9/Glrx/Apoe/Cd36/Pld2/Unc13d/Dnajc13/Ehd1/Ap1g1/Myo6/Rnf139/Numb/Tfr2/D6Wsu163e/Ankrd13b/Sytl4/Il4/Gata2/Atad1/Wasl/Fes/Smcr8/Sh3glb1/Arrb1/Nedd4/Fcgr3/Slc4a8/Sar1b/Smap1/Cplx2/Itgb2/Prkca/Ap2m1/Rap1b/C9orf72/Ppp3r1/Pcsk9/Lyar/Gripap1/Vps4b/Cbl/P2rx1/Use1/Rack1/Akap5/Snx3/Snap29/Syn1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030334</t>
@@ -1933,7 +1933,7 @@
     <t xml:space="preserve">752/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Egr1/Pld2/Appl2/Mink1/Mst1/Map3k1/Dmtn/Cd47/Cited2/Sema4b/Grn/Nedd9/Gab1/Adam10/Ptpn23/Anxa3/Numb/Ssh2/Trp53inp1/Hdac5/Mospd2/Ppard/Akap12/Tbc1d24/Wasl/Fbxw7/Hace1/Foxo4/Fbxo5/Flcn/Atp7a/Cib1/Dag1/Glipr2/Mpp1/Ttbk2/Rap2b/Nck1/Ago2/Ccar1/Swap70/Gna13/Vcl/Sirt1/Rps6kb1/Adipor2/Mia3/Rack1/Iqgap1/Elp3/Gpi1/Gtpbp4/Pde4d/Ptpru/Ldb1/Igf1r/Prkca/Sp100/Idh2/Flna/Srf/Stat5a/Vsir/Rap2c/Ripor1/Pik3cd/Arpc2/Trp53/Il27ra/Sema4a/Atp1b2/Gata2/Plcg2/Ano6/Fut4/Gab2/Plvap/Itga5/Rac1/Rcc2/Plxnc1/Ripor2/Dock8/Rac2/Vim/Fermt3/Il4/Csf1/Phlda2/Cxcr4/Lgals9/Arhgef2/Spn/Mmp14/Apoe/Tgfb1/Spi1/Hdac7/Ptprc/Coro1a/Dpp4/Arhgdib/Eng/Rin3</t>
+    <t xml:space="preserve">Hdac7/Egr1/Map3k1/Cldn13/Appl2/Arhgef2/Ptprc/Mink1/Coro1a/Ano6/Rac2/Tgfb1/Mst1/Grn/Spn/Dmtn/Rac1/Cd47/Dock8/Ripor2/Rcc2/Ptpn23/Gab1/Spi1/Gab2/Fermt3/Cited2/Eng/Rin3/Ripor1/Plcg2/Lgals9/Vim/Arhgdib/Cxcr4/Arpc2/Apoe/Adam10/Pld2/Tbc1d24/Dpp4/Itga5/Flna/Fbxw7/Rap2b/Trp53/Ssh2/Phlda2/Dag1/Ldb1/Numb/Nedd9/Hace1/Sema4b/Idh2/Fut4/Trp53inp1/Pik3cd/Stat5a/Il4/Gata2/Rap2c/Mmp14/Wasl/Sema4a/Gna13/Srf/Csf1/Il27ra/Ppard/Hdac5/Mospd2/Plvap/Fbxo5/Atp1b2/Ccar1/Anxa3/Plxnc1/Mpp1/Cib1/Prkca/Atp7a/Swap70/Adipor2/Ttbk2/Flcn/Vsir/Sirt1/Iqgap1/Foxo4/Ago2/Gtpbp4/Akap12/Ptpru/Igf1r/Nck1/Mia3/Rack1/Sp100/Vcl/Rps6kb1/Elp3/Pde4d/Glipr2/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006897</t>
@@ -1945,7 +1945,7 @@
     <t xml:space="preserve">457/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Neurl1b/Cd47/Snca/Itsn1/Bmp2k/Tfrc/Grn/Clcn5/Ache/Picalm/Ldlr/Cltc/Numb/Pikfyve/Rab22a/Arhgap12/Dpysl2/Arrb1/Epn1/Clcn3/Myo6/Rabep1/Tbc1d24/Wasl/Dnajc13/Ap3d1/C9orf72/Ehd1/Fcho1/Smap1/Cttn/Snx2/Itsn2/Ap2m1/Nedd4/Ppp3r1/Lrp5/Cbl/Atad1/Ap1g1/Prkca/Snx5/Ehd3/Pcsk9/Itgb2/Cap1/Ankrd13b/Abca2/Akap5/Tfr2/Mtmr9/Fcgr3/Dennd1c/Gata2/Plcg2/Snx10/Ano6/Rac1/Rac2/Il4/Dock2/Apoe/Cd44/Arhgap27/Elmo1/Syk/Rin3</t>
+    <t xml:space="preserve">Dock2/Snca/Appl2/Syk/Picalm/Ano6/Rac2/Cltc/Grn/Cd44/Rac1/Cd47/Arhgap27/Itsn1/Elmo1/Bmp2k/Cap1/Rin3/Abca2/Plcg2/Epn1/Clcn5/Apoe/Rabep1/Cd36/Pld2/Tbc1d24/Ldlr/Mtmr9/Pikfyve/Ache/Dnajc13/Ehd1/Rab22a/Ap1g1/Myo6/Clcn3/Dpysl2/Numb/Tfr2/Neurl1b/Ankrd13b/Il4/Gata2/Atad1/Wasl/Snx10/Ap3d1/Arhgap12/Arrb1/Nedd4/Fcgr3/Tfrc/Snx5/Lrp5/Smap1/Itgb2/Prkca/Ehd3/Ap2m1/Snx2/C9orf72/Ppp3r1/Dennd1c/Pcsk9/Cbl/Cttn/Akap5/Fcho1/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019693</t>
@@ -1957,7 +1957,7 @@
     <t xml:space="preserve">368/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Fasn/Mlst8/Atp6v1a/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Gcdh/Acaca/Ndufa10/Psen1/Cs/Parp1/Gpi1/Adss/Prps1/Dlat/Impdh2/Guk1/Pdha1/Aprt/Nudt14/Adsl/Mthfd1/Umps/Suclg2/Prkag2/Cad/Khk/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Uprt/Il4/Tgfb1/Nme4/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Uprt/Pfkfb2/Nme4/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Cad/Pkm/Atp6v1a/Umps/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/Gmpr/Impdh2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Prps1/Eno3/Dlat/Acaca/Atp7a/Hk2/Flcn/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Adss/Parp1/Pmvk/Nudt14/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034433</t>
@@ -1987,7 +1987,7 @@
     <t xml:space="preserve">52/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Arl8b/Ap1g1/Stat5a/Stat5b/Ptpn6/Unc13d/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9/Coro1a/Dpp4</t>
+    <t xml:space="preserve">Coro1a/Lamp1/Vav1/Lgals9/Stat5b/Ptpn6/Dpp4/Unc13d/Ap1g1/Stat5a/Pik3r6/Havcr2/Serpinb9/Arl8b/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048568</t>
@@ -2002,7 +2002,7 @@
     <t xml:space="preserve">337/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Aldh1a1/Nfe2/Tal1/Cited2/Insig1/Hipk2/Gab1/Zfat/Klf1/Stil/Epn1/Fzd5/Junb/Plcd3/Myo6/Ggnbp2/Dvl2/Rara/Nckap1/Kdm2a/Ttbk2/Gnas/Tnrc6c/Ncoa1/Arnt/Asxl2/Kat6a/Psen1/Ctnnb1/Trim28/Ndst1/Ldb1/Ift172/Megf8/Tshz1/Srf/Lmo2/Tcf7l2/Mthfd1l/Trp53/Vangl2/Pcgf2/Gata2/Zfp36l1/Pbx4/Rac1/Ripor2/Phlda2/Mmp14/Tgfb1/Gdf3/Vash2/Myb/Eng</t>
+    <t xml:space="preserve">Cobl/Aldh1a1/Myb/Tgfb1/Tal1/Nfe2/Rac1/Vash2/Ripor2/Gab1/Klf1/Cited2/Eng/Epn1/Insig1/Hipk2/Gnas/Arnt/Megf8/Gdf3/Kdm2a/Trp53/Phlda2/Myo6/Ldb1/Pcgf2/Fzd5/Stil/Gata2/Tshz1/Lmo2/Mmp14/Srf/Ggnbp2/Zfp36l1/Ctnnb1/Nckap1/Zfat/Pbx4/Ift172/Vangl2/Dvl2/Mthfd1l/Ndst1/Trim28/Ttbk2/Psen1/Junb/Ncoa1/Rara/Kat6a/Plcd3/Asxl2/Tnrc6c/Tcf7l2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008289</t>
@@ -2017,7 +2017,7 @@
     <t xml:space="preserve">634/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Apol11a/Apol11b/Cd36/Pld2/Appl2/Map3k1/Snca/Insig1/Mcoln1/Tpp1/Washc2/Rubcnl/Snx8/Epb41/Picalm/Plek2/Pcyt1b/Prex1/Acox1/Hs1bp3/Snx25/Stard4/Map1lc3b/Anxa3/Nrgn/Wdfy1/Zfyve26/Grk5/Igf2r/Epn1/Fzd5/Ppard/Cln8/Sgk3/Tex2/Chmp3/Atg2b/Bax/Ttpal/Rara/Gcdh/Exoc8/Syt14/Twf1/Exoc1/Lamc1/Arhgap35/Cpne1/Snx2/Ap2m1/Sh3glb1/Snx3/Iqgap1/Got2/Phb2/Flii/Scp2/Esyt1/Pgrmc1/Pdzd8/Hspd1/Anxa11/Snx5/Paqr8/Arhgap9/Ehd3/Plekha2/Fzd7/Faah/Sh3pxd2b/Unc13a/Dennd1c/Snx10/Gab2/Alox5ap/Pitpnm2/Plcb2/Capg/Prr7/Fes/Phlda2/Apoe/Nme4/Fyb/Sytl4/Adap1/Vill/Btk/Myo1g/P2rx7/Arap3</t>
+    <t xml:space="preserve">Apol11b/Apol11a/Arap3/Btk/Map3k1/Snca/Myo1g/Appl2/Picalm/Vill/Tpp1/Washc2/Fyb/Capg/Nme4/Gab2/Pitpnm2/Plcb2/P2rx7/Mcoln1/Stard4/Snx25/Alox5ap/Snx8/Epn1/Apoe/Map1lc3b/Cd36/Prex1/Igf2r/Pld2/Hs1bp3/Insig1/Wdfy1/Acox1/Adap1/Epb41/Sh3pxd2b/Atg2b/Pdzd8/Phlda2/Sytl4/Fzd5/Pcyt1b/Fzd7/Tex2/Zfyve26/Fes/Snx10/Grk5/Anxa11/Ppard/Prr7/Flii/Sh3glb1/Faah/Twf1/Got2/Esyt1/Chmp3/Anxa3/Nrgn/Exoc8/Snx5/Arhgap9/Ehd3/Lamc1/Ap2m1/Rubcnl/Exoc1/Plekha2/Cpne1/Snx2/Gcdh/Plek2/Ttpal/Iqgap1/Pgrmc1/Hspd1/Dennd1c/Rara/Bax/Scp2/Phb2/Sgk3/Syt14/Arhgap35/Unc13a/Paqr8/Cln8/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007040</t>
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">76/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Tpp1/Washc5/Pikfyve/Lamtor1/Gba/Zfyve26/Atp6ap2/Vps33a/Tmem199/Cln8/Hexa/Chmp3/Vps35/Arl8b/Aktip/Laptm5/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Laptm5/Coro1a/Tpp1/Grn/Washc5/P2rx7/Pikfyve/Atp6ap2/Gba/Zfyve26/Lamtor1/Vps33a/Vps35/Aktip/Chmp3/Arl8b/Tmem199/Hexa/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0080171</t>
@@ -2047,7 +2047,7 @@
     <t xml:space="preserve">185/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pheta2/Picalm/Cltc/Gga2/Numb/Nrgn/Syn1/Igf2r/Epn1/Myo6/Tmem199/Atp7a/Dvl2/Fcho1/Gnas/Ergic2/Ap2m1/Uso1/Snx3/Actr1a/Ergic3/Gopc/Copg2/Use1/Hspd1/Ap1g1/Lman1/Tmed5/Sar1b/Ier3ip1/Pcsk9/Tmed3/Vangl2/Unc13d/Ergic1</t>
+    <t xml:space="preserve">Picalm/Cltc/Gga2/Pheta2/Epn1/Ergic1/Igf2r/Gnas/Unc13d/Lman1/Tmed3/Ap1g1/Myo6/Numb/Copg2/Vangl2/Dvl2/Nrgn/Sar1b/Ergic3/Actr1a/Tmem199/Atp7a/Ap2m1/Ier3ip1/Tmed5/Hspd1/Pcsk9/Use1/Ergic2/Fcho1/Snx3/Syn1/Gopc/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009126</t>
@@ -2068,7 +2068,7 @@
     <t xml:space="preserve">109/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Aldh1a1/Pld2/Appl2/Fads3/Mid1ip1/St3gal1/Snca/Prkar2b/Agtr1a/Pip4p1/Scd1/Serac1/Gpcpd1/Insig1/Aldh1l2/St3gal6/Abcg1/Scd2/Neu1/Cyb5a/Mvd/Pcyt1b/Ldlr/Acox1/Stard4/Pcx/Uvrag/Lss/Fasn/St3gal2/Pikfyve/Lamtor1/Gba/Isyna1/Ppard/Socs2/Abhd15/Cln8/Hmgcr/Hexa/Lpcat3/Pmvk/Bax/Gcdh/Serinc5/Ip6k1/Mtmr3/Brca1/Pip4k2c/Sirt1/Adipor2/Acaca/Sh3glb1/Mtmr12/Pi4ka/Tbl1xr1/Sgpl1/Serinc3/Etfb/Cers5/Alg11/Phb2/Ttc7b/Scp2/Pik3c2b/Abhd16a/Dgkz/Pigt/St6galnac4/Gla/Ilvbl/Acsf2/P2rx1/Mboat7/Pcsk9/Ugcg/Gk/Prkag2/Faah/Plpp2/Pla2g12a/Tcf7l2/Abca2/Agk/Pik3cd/Dpagt1/Hadh/Mtmr9/Prdx6/Acsl5/Plcg2/Vapa/B4galnt1/Pgap2/Retsat/Fut4/Rft1/Nudt19/Alox5ap/Plcb2/Lypla1/Acsbg1/Pla2g1b/Lpcat2/Apoe/Sptssa/Ces2g/P2rx7</t>
+    <t xml:space="preserve">Ces2g/Prkar2b/Fads3/Aldh1a1/Snca/Appl2/Mid1ip1/Sptssa/Abcg1/St3gal1/Pip4p1/Lypla1/Plcb2/Serac1/P2rx7/Stard4/Abca2/Alox5ap/Vapa/Plcg2/Acsl5/Nudt19/Cyb5a/Apoe/Cd36/Ugcg/Pld2/Ldlr/Mtmr9/Pikfyve/Insig1/Retsat/Fasn/Hadh/Pcx/Isyna1/Uvrag/Pgap2/Acox1/Gba/Neu1/Prdx6/Rft1/Agk/Agtr1a/Socs2/Fut4/Mtmr3/Scd1/Mvd/Lpcat2/Pik3cd/Pla2g12a/Pcyt1b/Gk/Prkag2/Dgkz/Pla2g1b/Acsbg1/Dpagt1/Mboat7/Lamtor1/Ppard/Aldh1l2/Lss/Sh3glb1/Faah/Gpcpd1/B4galnt1/Hmgcr/Scd2/Alg11/Lpcat3/St3gal6/Pigt/Acaca/Adipor2/Abhd16a/Gla/Plpp2/Hexa/Serinc5/St3gal2/Gcdh/Sirt1/Ip6k1/Acsf2/Pcsk9/Bax/Scp2/Serinc3/Mtmr12/Ttc7b/Brca1/St6galnac4/Cers5/Phb2/Etfb/Abhd15/Tbl1xr1/Tcf7l2/P2rx1/Ilvbl/Pmvk/Sgpl1/Cln8/Pip4k2c/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030217</t>
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">268/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Mink1/Egr3/Prdx2/Tsc1/Prex1/Hs1bp3/Zbtb7b/Gba/Fzd5/Atp7a/Ap3d1/Shb/Pknox1/Rara/Phf10/Gpr89/Ctnnb1/Tcf3/Srf/Stat5a/Vsir/Smarcd1/Fzd7/Trp53/Stat5b/Sema4a/Kat2a/Traf3ip2/Vav1/Zfp36l1/Cbfb/Prr7/Pik3r6/Il4/Lgals9/Dock2/Spn/Tgfb1/Cd44/Spi1/Ptprc/Myb/Cdk6/Jak3/Syk</t>
+    <t xml:space="preserve">Prdx2/Egr1/Dock2/Jak3/Syk/Myb/Ptprc/Mink1/Tgfb1/Cdk6/Spn/Tsc1/Cd44/Cbfb/Spi1/Vav1/Lgals9/Kat2a/Stat5b/Prex1/Hs1bp3/Gba/Smarcd1/Trp53/Egr3/Zbtb7b/Stat5a/Fzd5/Il4/Fzd7/Sema4a/Pik3r6/Srf/Zfp36l1/Pknox1/Ctnnb1/Ap3d1/Prr7/Tcf3/Atp7a/Vsir/Traf3ip2/Rara/Gpr89/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904375</t>
@@ -2092,7 +2092,7 @@
     <t xml:space="preserve">122/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Kalrn/Epb41/Picalm/Adam10/Cltc/Numb/Ppp2r5a/Gpsm2/Cib1/Ppp1r9b/Dag1/Gripap1/Sorbs1/Ap2m1/Rack1/Gopc/Lztfl1/Pgrmc1/Ptpn9/Abca2/Akap5/Rangrf/Lypla1/Mmp14/Tgfb1</t>
+    <t xml:space="preserve">Picalm/Prnp/Tgfb1/Cltc/Lypla1/Ppp2r5a/Abca2/Adam10/Kalrn/Epb41/Dag1/Numb/Rangrf/Mmp14/Ppp1r9b/Ptpn9/Gpsm2/Cib1/Ap2m1/Pgrmc1/Lztfl1/Sorbs1/Gripap1/Rack1/Akap5/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031344</t>
@@ -2104,7 +2104,7 @@
     <t xml:space="preserve">610/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Dmtn/Sema4b/Grn/Prnp/Kalrn/Neu1/Washc5/Ache/Tsc1/Picalm/Adam10/Plek2/Mylip/Numb/Kel/Dpysl2/Rab3ip/Epor/Trak2/Tbc1d24/Wasl/Serpini1/Kif13b/Atp7a/Xk/Cib1/Stk25/Pias2/Dip2b/Ppp2r5b/Cdkl5/Ehd1/Nckap1/Ttbk2/Camsap2/Golga4/Vps35/Nck1/Myo9a/Acap3/Tapt1/Twf1/Arhgap35/Cttn/Homer1/Sirt1/Fbxo38/Sh3glb1/Snx3/Psen1/Iqgap1/Rpl4/Actr2/Was/Nedd4/Itm2c/Stau2/Def8/Mov10/Syngap1/Ulk2/Cul7/Igf1r/Megf8/Flna/Srf/Ptpn9/Fkbp1b/Akap5/Arpc2/Sema4a/Atp1b2/Kat2a/Ankrd27/Rgs2/Rac1/Rcc2/Plxnc1/Ripor2/Rac2/Vim/Ptprs/Fes/Apoe/Cd44/Lgals1/P2rx7</t>
+    <t xml:space="preserve">Lgals1/Cobl/Picalm/Ptprs/Prnp/Rac2/Grn/Washc5/Ankrd27/Tsc1/Dmtn/Cd44/Rac1/Ripor2/Rcc2/P2rx7/Vim/Kat2a/Arpc2/Apoe/Adam10/Tbc1d24/Kalrn/Ache/Megf8/Flna/Dip2b/Ehd1/Neu1/Stk25/Dpysl2/Epor/Numb/Pias2/Sema4b/Rab3ip/Xk/Tapt1/Rgs2/Cul7/Wasl/Sema4a/Srf/Fes/Ptpn9/Mylip/Nckap1/Kel/Vps35/Sh3glb1/Twf1/Nedd4/Camsap2/Atp1b2/Plxnc1/Mov10/Trak2/Def8/Cib1/Atp7a/Ttbk2/Psen1/Kif13b/Ulk2/Plek2/Fbxo38/Sirt1/Actr2/Iqgap1/Golga4/Cdkl5/Rpl4/Serpini1/Stau2/Syngap1/Itm2c/Homer1/Arhgap35/Fkbp1b/Igf1r/Nck1/Ppp2r5b/Cttn/Akap5/Acap3/Myo9a/Snx3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045646</t>
@@ -2116,7 +2116,7 @@
     <t xml:space="preserve">47/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Fam210b/Abcb10/Tal1/Gfi1b/Smap1/Ldb1/Prmt1/Stat5a/Lmo2/Stat5b/Gata2/Zfp36l1/Spi1/Cdk6</t>
+    <t xml:space="preserve">Fam210b/Abcb10/Cdk6/Tal1/Spi1/Stat5b/Ldb1/Stat5a/Gata2/Lmo2/Prmt1/Zfp36l1/Smap1/Gfi1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019752</t>
@@ -2128,7 +2128,7 @@
     <t xml:space="preserve">714/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Aldh1a1/Appl2/Fads3/Amdhd2/Mid1ip1/Mgst3/Renbp/Snca/Prkar2b/Scd1/Insig1/Aldh1l2/Pfkfb2/Eno3/Scd2/Urod/Cyb5a/Ddit4/Pkm/Pycr1/Nupr1/Acox1/Stard4/Bpgm/Hagh/Pcx/Fasn/Mlst8/Gnpda1/Sars/Ppard/Atp7a/Mtch2/Gcdh/Aco1/Sord/Aldh4a1/Brca1/Slc39a8/Mpst/Sirt1/Adipor2/Acaca/Qars/Gls/Pycr2/Sgpl1/Psen1/Cs/Vars2/Etfb/Got1/Got2/Farsb/Idh3g/Gpi1/Scp2/Adss/Dlat/Idh3a/Enoph1/Pdha1/Mtap/Plod3/Ilvbl/Tars2/Mthfd1/Acsf2/Idh2/Gk/Prkag2/Faah/Mthfd1l/Hadh/Trp53/Qprt/Cad/Khk/Adssl1/Acsl5/Atic/Thap4/Pfas/Sdsl/Hk2/Gart/Nudt19/Alox5ap/Nr1d1/Lypla1/Prodh/Acsbg1/Gsto1/Pla2g1b/Kyat3/Ces2g/P2rx7/Syk</t>
+    <t xml:space="preserve">Ces2g/Prkar2b/Fads3/Aldh1a1/Snca/Appl2/Mgst3/Syk/Slc4a1/Mid1ip1/Kyat3/Renbp/Gsto1/Lypla1/Urod/Amdhd2/Pfkfb2/Gart/P2rx7/Stard4/Pfas/Alox5ap/Acsl5/Nudt19/Ddit4/Cyb5a/Cd36/Thap4/Insig1/Khk/Fasn/Hadh/Sdsl/Pdha1/Tars2/Pcx/Mtch2/Atic/Hagh/Prodh/Acox1/Mlst8/Cad/Pkm/Trp53/Sars/Idh2/Scd1/Gk/Adssl1/Prkag2/Pla2g1b/Acsbg1/Gnpda1/Aco1/Ppard/Plod3/Aldh1l2/Nr1d1/Faah/Idh3a/Cs/Mthfd1/Got2/Mthfd1l/Scd2/Eno3/Dlat/Qprt/Acaca/Atp7a/Adipor2/Hk2/Psen1/Gcdh/Sirt1/Bpgm/Aldh4a1/Idh3g/Acsf2/Pycr1/Nupr1/Scp2/Brca1/Mtap/Got1/Farsb/Enoph1/Etfb/Slc39a8/Vars2/Adss/Mpst/Ilvbl/Qars/Sgpl1/Sord/Pycr2/Gls/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0000904</t>
@@ -2143,7 +2143,7 @@
     <t xml:space="preserve">620/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Cgn/Mink1/Map3k1/Egr2/Tal1/Dmtn/Map1a/Sema4b/Kalrn/Nedd9/Als2/Ache/Picalm/Adam10/Slc11a2/Micall2/Prex1/Frmd6/Numb/Kel/Actn1/Dpysl2/Trak2/Vps33a/Tbc1d24/Wasl/Megf9/Kif13b/Hexa/Atp7a/Xk/Usp9x/Cib1/Stk25/Dag1/Pias2/Dip2b/C9orf72/Cdkl5/Golga4/Atrnl1/Rb1/Lamc1/Arhgap35/Vcl/Cttn/Sh3glb1/Abi1/Psen1/Rpl4/Actr2/Ctnnb1/Nedd4/Wdr1/Hsp90ab1/Wdr36/Stau2/Parvg/Myh10/Syngap1/Ulk2/Cul7/Igf1r/Plod3/Prkca/Megf8/Flna/Srf/Fzd7/Lpxn/Akap5/Arpc2/Vangl2/Ptpn6/Sema4a/Unc13d/Ankrd27/Rac1/Rcc2/Plxnc1/Ripor2/Rac2/Vim/Fermt3/Ptprs/Cxcr4/Apoe/Spi1</t>
+    <t xml:space="preserve">Cobl/Map3k1/Picalm/Ptprs/Mink1/Rac2/Slc11a2/Ankrd27/Tal1/Dmtn/Rac1/Cgn/Ripor2/Rcc2/Spi1/Fermt3/Actn1/Micall2/Vim/Cxcr4/Als2/Arpc2/Apoe/Prex1/Adam10/Tbc1d24/Ptpn6/Kalrn/Ache/Megf8/Unc13d/Flna/Frmd6/Dip2b/Stk25/Map1a/Usp9x/Dag1/Dpysl2/Numb/Nedd9/Pias2/Sema4b/Egr2/Xk/Myh10/Cul7/Fzd7/Wasl/Sema4a/Srf/Ctnnb1/Megf9/Vps33a/Wdr1/Kel/Plod3/Rb1/Sh3glb1/Vangl2/Nedd4/Plxnc1/Trak2/Cib1/Prkca/Hsp90ab1/Atp7a/Lamc1/Psen1/Hexa/Kif13b/Ulk2/C9orf72/Actr2/Golga4/Cdkl5/Parvg/Rpl4/Stau2/Syngap1/Wdr36/Abi1/Arhgap35/Igf1r/Cttn/Akap5/Atrnl1/Vcl/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0012506</t>
@@ -2155,7 +2155,7 @@
     <t xml:space="preserve">519/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Appl2/Rph3al/Abcb6/Snca/H2-T23/Wdr81/Pip4p1/Ctsd/Tfrc/Washc2/Ubap1/Snx8/Washc5/Vps26a/Atg9a/Slc11a2/Lamp1/Ldlr/Cltc/Atp6v0a1/Anxa3/Nrgn/Pikfyve/Actn1/Lamtor1/Syn1/Atp6ap2/Igf2r/Epn1/Clcn3/Myo6/Tmem199/Atp2b1/Dnajc13/Atp7a/Lamtor3/Ap3d1/Chmp3/Ehd1/Rap2b/Vps35/Nck1/Gripap1/Rmc1/Washc4/Snx2/Ap2m1/Clec16a/Uso1/Pi4ka/Snx3/Vps4b/Gpr89/Was/Sec61a1/Ifitm2/Copg2/Ap1g1/Sar1b/Snx5/Ehd3/Rap2c/Fzd7/Lin7c/Abca2/Mfsd10/Unc13a/Tmed3/Cyb561/Cmtm6/Snx10/Vamp5/Rac1/Rcc2/Ptprs/Sytl4</t>
+    <t xml:space="preserve">Ctsd/Snca/Appl2/Ptprs/Abcb6/Slc6a9/Vps26a/Cltc/Rph3al/Slc11a2/Washc5/Washc2/Lamp1/Pip4p1/Rac1/Rcc2/Actn1/Abca2/Wdr81/Snx8/Ubap1/Vamp5/Epn1/Atp2b1/Lin7c/Igf2r/Ldlr/Pikfyve/Cmtm6/Atp6ap2/Tmed3/Atg9a/Dnajc13/Rap2b/Ehd1/Ap1g1/Mfsd10/Myo6/Clcn3/Atp6v0a1/H2-T23/Cyb561/Sytl4/Rap2c/Fzd7/Lamtor3/Snx10/Lamtor1/Ap3d1/Vps35/Copg2/Chmp3/Anxa3/Tfrc/Nrgn/Snx5/Sar1b/Tmem199/Ehd3/Atp7a/Ap2m1/Washc4/Snx2/Rmc1/Sec61a1/Ifitm2/Gripap1/Unc13a/Nck1/Vps4b/Gpr89/Clec16a/Snx3/Syn1/Pi4ka/Uso1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0035091</t>
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">231/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Appl2/Washc2/Rubcnl/Snx8/Epb41/Picalm/Plek2/Hs1bp3/Snx25/Nrgn/Wdfy1/Zfyve26/Sgk3/Chmp3/Atg2b/Ttpal/Exoc8/Twf1/Exoc1/Snx2/Snx3/Iqgap1/Flii/Esyt1/Snx5/Arhgap9/Fzd7/Sh3pxd2b/Dennd1c/Snx10/Gab2/Pitpnm2/Capg/Fes/Phlda2/Adap1/Vill/Btk/Myo1g/Arap3</t>
+    <t xml:space="preserve">Arap3/Btk/Myo1g/Appl2/Picalm/Vill/Washc2/Capg/Gab2/Pitpnm2/Snx25/Snx8/Pld2/Hs1bp3/Wdfy1/Adap1/Epb41/Sh3pxd2b/Atg2b/Phlda2/Fzd7/Zfyve26/Fes/Snx10/Flii/Twf1/Esyt1/Chmp3/Nrgn/Exoc8/Snx5/Arhgap9/Rubcnl/Exoc1/Snx2/Plek2/Ttpal/Iqgap1/Dennd1c/Sgk3/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016482</t>
@@ -2182,7 +2182,7 @@
     <t xml:space="preserve">144/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Wdr81/Washc2/Snx8/Vps26a/Pheta2/Vps11/Lamp1/Ptpn23/Cltc/Pikfyve/Dnajc13/Vps29/Vps35/Arl8b/Snx2/Sh3glb1/Snx3/Actr2/Ap1g1/Flna/Snx5/Ehd3/Kif1c/Aktip/Vps53/Ankrd27/Laptm5/Coro1a/Tbc1d10c</t>
+    <t xml:space="preserve">Laptm5/Coro1a/Vps26a/Cltc/Washc2/Ankrd27/Lamp1/Ptpn23/Tbc1d10c/Vps53/Pheta2/Vps11/Wdr81/Snx8/Pikfyve/Flna/Dnajc13/Kif1c/Ap1g1/Vps35/Aktip/Sh3glb1/Vps29/Snx5/Arl8b/Ehd3/Snx2/Actr2/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030659</t>
@@ -2197,7 +2197,7 @@
     <t xml:space="preserve">496/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Appl2/Rph3al/Abcb6/Snca/H2-T23/Wdr81/Pip4p1/Ctsd/Tfrc/Washc2/Ubap1/Snx8/Washc5/Vps26a/Atg9a/Slc11a2/Lamp1/Ldlr/Cltc/Atp6v0a1/Anxa3/Nrgn/Pikfyve/Actn1/Lamtor1/Syn1/Atp6ap2/Igf2r/Epn1/Clcn3/Tmem199/Atp2b1/Dnajc13/Atp7a/Lamtor3/Ap3d1/Chmp3/Ehd1/Rap2b/Vps35/Gripap1/Rmc1/Washc4/Snx2/Ap2m1/Clec16a/Uso1/Pi4ka/Snx3/Vps4b/Gpr89/Sec61a1/Ifitm2/Copg2/Ap1g1/Sar1b/Snx5/Ehd3/Rap2c/Fzd7/Lin7c/Abca2/Mfsd10/Unc13a/Tmed3/Cyb561/Cmtm6/Snx10/Vamp5/Rac1/Rcc2/Ptprs/Sytl4</t>
+    <t xml:space="preserve">Ctsd/Snca/Appl2/Ptprs/Abcb6/Slc6a9/Vps26a/Cltc/Rph3al/Slc11a2/Washc5/Washc2/Lamp1/Pip4p1/Rac1/Rcc2/Actn1/Abca2/Wdr81/Snx8/Ubap1/Vamp5/Epn1/Atp2b1/Lin7c/Igf2r/Ldlr/Pikfyve/Cmtm6/Atp6ap2/Tmed3/Atg9a/Dnajc13/Rap2b/Ehd1/Ap1g1/Mfsd10/Clcn3/Atp6v0a1/H2-T23/Cyb561/Sytl4/Rap2c/Fzd7/Lamtor3/Snx10/Lamtor1/Ap3d1/Vps35/Copg2/Chmp3/Anxa3/Tfrc/Nrgn/Snx5/Sar1b/Tmem199/Ehd3/Atp7a/Ap2m1/Washc4/Snx2/Rmc1/Sec61a1/Ifitm2/Gripap1/Unc13a/Vps4b/Gpr89/Clec16a/Snx3/Syn1/Pi4ka/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045637</t>
@@ -2209,7 +2209,7 @@
     <t xml:space="preserve">173/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Fam210b/Abcb10/Tal1/Mturn/Cnot4/Fos/Ubash3b/Fbxw7/Cib1/Rara/Gnas/Rb1/Gfi1b/Asxl2/Smap1/Ctnnb1/Ldb1/Hcls1/Prkca/Prmt1/Stat5a/Lmo2/Stat5b/Gata2/Zfp36l1/Il4/Csf1/Fes/Tgfb1/Spi1/Tyrobp/Cdk6</t>
+    <t xml:space="preserve">Car2/Fam210b/Abcb10/Tgfb1/Cdk6/Tal1/Spi1/Cnot4/Stat5b/Gnas/Mturn/Fbxw7/Ldb1/Tyrobp/Stat5a/Il4/Gata2/Lmo2/Prmt1/Fes/Zfp36l1/Csf1/Ctnnb1/Rb1/Hcls1/Smap1/Cib1/Prkca/Ubash3b/Fos/Rara/Gfi1b/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016197</t>
@@ -2221,7 +2221,7 @@
     <t xml:space="preserve">210/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Itsn1/Mcoln1/Washc2/Snx8/Washc5/Vps26a/Pheta2/Als2/Picalm/Ptpn23/Micall2/Cltc/Pikfyve/Lamtor1/Tmcc1/Ccdc93/Ap3d1/Chmp3/Ehd1/Vps29/Vps35/Gripap1/Washc4/Arl8b/Snx2/Itsn2/Clec16a/Snx3/Vps4b/Was/Snx5/Ehd3/Akap5/Dennd1c/Cmtm6/Vps53/Ankrd27/Tbc1d10c</t>
+    <t xml:space="preserve">Picalm/Vps26a/Cltc/Washc5/Washc2/Ankrd27/Itsn1/Ptpn23/Tbc1d10c/Vps53/Mcoln1/Pheta2/Micall2/Snx8/Als2/Pikfyve/Cmtm6/Ehd1/Tmcc1/Lamtor1/Ap3d1/Vps35/Vps29/Ccdc93/Chmp3/Snx5/Arl8b/Ehd3/Washc4/Snx2/Dennd1c/Gripap1/Vps4b/Clec16a/Akap5/Snx3/Itsn2/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903039</t>
@@ -2230,7 +2230,7 @@
     <t xml:space="preserve">positive regulation of leukocyte cell-cell adhesion</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Cd47/Tfrc/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Phf10/Hspd1/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Irak1/Il27ra/Fut4/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Tgfb1/Ccdc88b/Cd44/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Spn/Cd44/Cd47/Dock8/Cbfb/Lgals9/Stat5b/Dpp4/Irak1/Smarcd1/Egr3/Zbtb7b/Fut4/Stat5a/Il4/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Vsir/Hspd1/Rara/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903960</t>
@@ -2239,7 +2239,7 @@
     <t xml:space="preserve">negative regulation of anion transmembrane transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc43a1/Grk6/Gopc/Prkca/Slc43a2/Rgs2</t>
+    <t xml:space="preserve">Slc43a1/Rgs2/Prkca/Slc43a2/Grk6/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0072521</t>
@@ -2251,7 +2251,7 @@
     <t xml:space="preserve">390/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Abcg2/Snca/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Oard1/Fasn/Mlst8/Atp6v1a/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Adal/Gcdh/Acaca/Ndufa10/Psen1/Cs/Parp1/Gpi1/Adss/Prps1/Dlat/Impdh2/Guk1/Pdha1/Mtap/Aprt/Adsl/Mthfd1/Macrod1/Suclg2/Prkag2/Khk/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Pgm2/Il4/Tgfb1/Nme4/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Abcg2/Pfkfb2/Nme4/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Pkm/Atp6v1a/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/Pgm2/Oard1/Gmpr/Impdh2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Prps1/Eno3/Dlat/Acaca/Atp7a/Adal/Hk2/Flcn/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Mtap/Adss/Parp1/Macrod1/Pmvk/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030424</t>
@@ -2263,7 +2263,7 @@
     <t xml:space="preserve">547/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Aldh1a1/Car2/Ank1/Atp6v0d1/Scn10a/Snca/Itsn1/Map1a/Optn/Hmbs/Mylk2/Prnp/Als2/Ache/Tsc1/Slc38a2/Map1lc3b/Anxa3/Nrgn/Dpysl2/Syn1/Hdac5/Trak2/Clcn3/Myo6/Map3k12/Kif13b/Nmnat3/Atp7a/Usp9x/Polg/Cib1/Slc38a7/Ap3d1/Ppp1r9b/Dag1/Dip2b/C9orf72/Cdkl5/Uhmk1/Dyrk1a/Myo9a/Acap3/Elk1/Arl8b/Cttn/Homer1/Sirt1/Psen1/Iqgap1/Got1/Phb2/Cbl/Fkbp1a/Hsp90ab1/Stau2/Copg2/Myh10/Igf1r/Sptan1/Prkca/Flna/Kif1c/Unc13a/Arpc2/Slc4a8/Atp1a3/Cplx2/Cadm1/Kcnab2/Vim/Gsto1/Cxcr4/Tgfb1/Coro1a/Tspoap1/P2rx7/Rin3</t>
+    <t xml:space="preserve">Car2/Spta1/Atp6v0d1/Cobl/Aldh1a1/Snca/Coro1a/Tspoap1/Prnp/Tgfb1/Tsc1/Ank1/Gsto1/Itsn1/Kcnab2/Hmbs/P2rx7/Rin3/Vim/Optn/Cxcr4/Als2/Arpc2/Map1lc3b/Dyrk1a/Ache/Flna/Scn10a/Dip2b/Slc38a2/Kif1c/Polg/Map1a/Myo6/Clcn3/Usp9x/Dag1/Dpysl2/Myh10/Ppp1r9b/Ap3d1/Hdac5/Copg2/Uhmk1/Slc4a8/Anxa3/Nrgn/Sptan1/Mylk2/Trak2/Cib1/Cplx2/Prkca/Arl8b/Hsp90ab1/Atp1a3/Atp7a/Cadm1/Elk1/Psen1/Kif13b/Sirt1/Fkbp1a/C9orf72/Iqgap1/Cdkl5/Stau2/Got1/Map3k12/Phb2/Homer1/Unc13a/Igf1r/Cbl/Cttn/Acap3/Myo9a/Slc38a7/Syn1/Nmnat3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030183</t>
@@ -2275,7 +2275,7 @@
     <t xml:space="preserve">124/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Hdac5/Bax/Fnip1/Tcf3/Irf2bp2/Stat5a/Trp53/Stat5b/Ptpn6/Plcg2/Traf3ip2/Zfp36l1/Mmp14/Laptm5/Spi1/Hdac7/Btk/Ptprc/Myb/Cmtm7/Jak3/Lgals1/Dpp4/Nfam1/Syk</t>
+    <t xml:space="preserve">Lgals1/Hdac7/Btk/Cmtm7/Jak3/Laptm5/Nfam1/Syk/Myb/Ptprc/St3gal1/Spi1/Plcg2/Stat5b/Ptpn6/Dpp4/Irf2bp2/Trp53/Stat5a/Mmp14/Zfp36l1/Hdac5/Tcf3/Traf3ip2/Fnip1/Bax</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009259</t>
@@ -2287,7 +2287,7 @@
     <t xml:space="preserve">358/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Fasn/Mlst8/Atp6v1a/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Gcdh/Acaca/Ndufa10/Psen1/Cs/Parp1/Gpi1/Adss/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Umps/Suclg2/Prkag2/Cad/Khk/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Uprt/Il4/Tgfb1/Nme4/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Uprt/Pfkfb2/Nme4/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Cad/Pkm/Atp6v1a/Umps/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/Gmpr/Impdh2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Eno3/Dlat/Acaca/Atp7a/Hk2/Flcn/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Adss/Parp1/Pmvk/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097242</t>
@@ -2296,7 +2296,7 @@
     <t xml:space="preserve">amyloid-beta clearance</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Picalm/Ldlr/Cltc/Hmgcr/Ifngr1/Igf1r/Srf/Itgb2/Il4/Apoe</t>
+    <t xml:space="preserve">Picalm/Cltc/Apoe/Cd36/Ldlr/Il4/Srf/Hmgcr/Itgb2/Ifngr1/Igf1r</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016072</t>
@@ -2308,7 +2308,7 @@
     <t xml:space="preserve">241/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slfn14/Mrm1/Isg20/Pop5/Utp14b/Dedd/Helq/Ddx27/Rpl35/Ddx18/Snu13/Pa2g4/Ddx21/Ddx49/Gtpbp4/Rcl1/Ebna1bp2/Wdr36/Rrp1b/Urb1/Pwp1/Polr1a/Tcof1/Trmt2b/Exosc1/Lyar/Wdr43/Exosc5/Spin1/Mdn1/Heatr1/Nat10/Naf1/Rrp12/Rpl10a/Nol6/Trp53/Polr1b/Wdr46/Tfb2m/Rrp9/Npm3</t>
+    <t xml:space="preserve">Slfn14/Npm3/Nat10/Rpl10a/Tcof1/Rrp9/Wdr46/Trp53/Utp14b/Spin1/Trmt2b/Mrm1/Nol6/Polr1b/Pop5/Naf1/Tfb2m/Isg20/Rrp12/Heatr1/Mdn1/Pwp1/Polr1a/Urb1/Wdr43/Exosc5/Ddx18/Rcl1/Exosc1/Snu13/Wdr36/Lyar/Gtpbp4/Ebna1bp2/Ddx21/Helq/Ddx27/Ddx49/Dedd/Rpl35/Pa2g4/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071496</t>
@@ -2317,7 +2317,7 @@
     <t xml:space="preserve">cellular response to external stimulus</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Tfrc/Rragc/Tsc1/Fos/Sesn1/Map1lc3b/Pim1/Gba/Mlst8/Bhlha15/Habp4/Flcn/Dag1/Sesn3/Xpr1/Gabarap/Rictor/Mtmr3/Ncoa1/Arhgap35/Sirt1/Fnip1/Clec16a/Sh3glb1/Ctnnb1/Plin2/Got1/Pik3c2b/Srf/Pcsk9/Mybbp1a/Prkag2/Tcf7l2/Ripor1/Trp53/Pmaip1/Rac1/Ripor2/Fes/Ptprc/P2rx7</t>
+    <t xml:space="preserve">Ptprc/Rragc/Tsc1/Cpeb4/Rac1/Ripor2/P2rx7/Ripor1/Map1lc3b/Sesn1/Xpr1/Pmaip1/Gba/Mlst8/Trp53/Dag1/Gabarap/Habp4/Mtmr3/Prkag2/Srf/Fes/Ctnnb1/Mybbp1a/Sh3glb1/Tfrc/Flcn/Bhlha15/Sesn3/Sirt1/Fos/Ncoa1/Fnip1/Pcsk9/Got1/Arhgap35/Tcf7l2/Clec16a/Pim1/Plin2/Pik3c2b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031334</t>
@@ -2329,7 +2329,7 @@
     <t xml:space="preserve">174/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Map3k1/Tal1/Snca/Tfrc/Fnip2/Slf2/Mlst8/Epn1/1810058I24Rik/Bax/Ppp2r5b/Nckap1/Nck1/Bcl2l11/Rictor/Bid/Rap1b/Togaram1/Cttn/Fnip1/Sh3glb1/Rack1/Dhx33/Slain2/Arpc2/Trp53/Plcg2/Rac1/Fes/Tgfb1/Syk/Lcp1</t>
+    <t xml:space="preserve">Map3k1/Snca/Syk/Tgfb1/Tal1/Rac1/Fnip2/Lcp1/Plcg2/Slf2/Arpc2/Epn1/Cd36/Mlst8/Trp53/1810058I24Rik/Fes/Nckap1/Slain2/Sh3glb1/Togaram1/Tfrc/Bcl2l11/Dhx33/Rap1b/Bid/Fnip1/Bax/Nck1/Ppp2r5b/Cttn/Rack1/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006887</t>
@@ -2338,7 +2338,7 @@
     <t xml:space="preserve">exocytosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Pld2/Exoc3l4/Rph3al/Dmtn/Snca/Itsn1/Glrx/Washc5/Vps11/Lamp1/D6Wsu163e/Anxa3/Rab3ip/Arfgef2/Myo6/Smcr8/C9orf72/Exoc8/Tmem167b/Rap1b/Exoc1/Arl8b/Cdk16/Snap29/Mia3/Vps4b/Psen1/Myh10/Ap1g1/Prkca/P2rx1/Itgb2/Lin7c/Unc13a/Slc4a8/Gata2/Unc13d/Cplx2/Gab2/Rac2/Il4/Ywhaz/Fes/Lgals9/Sytl4/Spi1/Coro1a/Myo1g/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Rab3il1/Snca/Myo1g/Syk/Coro1a/Rac2/Ywhaz/Rph3al/Washc5/Dmtn/Lamp1/Cd84/Itsn1/Spi1/Gab2/P2rx7/Vps11/Lgals9/Arfgef2/Glrx/Lin7c/Pld2/Unc13d/Ap1g1/Myo6/D6Wsu163e/Exoc3l4/Rab3ip/Sytl4/Il4/Myh10/Gata2/Fes/Smcr8/Slc4a8/Anxa3/Exoc8/Tmem167b/Cplx2/Itgb2/Prkca/Arl8b/Cdk16/Exoc1/Rap1b/Psen1/C9orf72/Unc13a/Vps4b/Mia3/P2rx1/Snap29</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043410</t>
@@ -2350,7 +2350,7 @@
     <t xml:space="preserve">375/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Mink1/Map3k1/Slc30a10/Mturn/Prdx2/Hipk2/Gab1/Traf4/Lamtor1/Arrb1/Epor/Fzd5/Map3k12/Akap12/Fbxw7/Hmgcr/Cib1/Lamtor3/Stk25/Dvl2/Glipr2/Rara/Garem1/Rap1b/Avpi1/Bnip2/Taok1/Psen1/Iqgap1/Dnajc27/Ctnnb1/Phb2/Maged1/Dhx33/Ndst1/Igf1r/Prkca/Traf3/Prmt1/Pik3r5/Map4k1/Irak1/Vangl2/Plcg2/Havcr2/Pik3r6/Cxcr4/Apoe/Tgfb1/Cd44/Laptm5/Mst1r/Spi1/Ptprc/P2rx7/Cd84/Igfbp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Map3k1/Laptm5/Syk/Ptprc/Mink1/Igfbp4/Tgfb1/Slc30a10/Cd44/Cd84/Gab1/Spi1/P2rx7/Plcg2/Cxcr4/Apoe/Mst1r/Cd36/Hipk2/Irak1/Mturn/Traf4/Fbxw7/Stk25/Epor/Traf3/Fzd5/Map4k1/Prmt1/Pik3r6/Maged1/Lamtor3/Lamtor1/Ctnnb1/Havcr2/Arrb1/Vangl2/Dvl2/Hmgcr/Ndst1/Cib1/Prkca/Dhx33/Rap1b/Psen1/Taok1/Iqgap1/Garem1/Rara/Avpi1/Map3k12/Phb2/Akap12/Bnip2/Igf1r/Dnajc27/Pik3r5/Glipr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903037</t>
@@ -2362,7 +2362,7 @@
     <t xml:space="preserve">280/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Cd47/Prdx2/Tfrc/Prnp/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Mia3/Phf10/Hspd1/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Irak1/Ptpn6/Il27ra/Zdhhc21/Cd37/Fut4/Cbfb/Ripor2/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Jak3/Laptm5/Syk/Slc4a1/Myb/Ptprc/Coro1a/Prnp/Ccdc88b/Tgfb1/Spn/Cd44/Cd47/Dock8/Ripor2/Cbfb/Lgals9/Zdhhc21/Stat5b/Ptpn6/Dpp4/Irak1/Smarcd1/Egr3/Zbtb7b/Fut4/Stat5a/Il4/Lgals7/Cd37/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Vsir/Hspd1/Rara/Nck1/Mia3/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903828</t>
@@ -2371,7 +2371,7 @@
     <t xml:space="preserve">negative regulation of protein localization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Trp53inp2/Dmtn/Map1a/Insig1/Rhbdf1/Picalm/Yod1/Cltc/Numb/Ppp2r5a/Hmgcr/Flcn/Ttbk2/Vps35/Otud7b/Sirt1/Ap2m1/Snx3/Gopc/Maged1/Lztfl1/Polr1a/Sp100/Idh2/Fkbp1b/Hadh/Pim3/Ripor2/Lypla1/Apoe/Tgfb1/Sytl4/Spi1</t>
+    <t xml:space="preserve">Picalm/Tgfb1/Cltc/Dmtn/Trp53inp2/Lypla1/Ripor2/Spi1/Ppp2r5a/Apoe/Cd36/Yod1/Insig1/Pim3/Hadh/Map1a/Numb/Idh2/Sytl4/Maged1/Vps35/Rhbdf1/Hmgcr/Polr1a/Otud7b/Ttbk2/Ap2m1/Flcn/Sirt1/Lztfl1/Fkbp1b/Sp100/Snx3/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032760</t>
@@ -2386,7 +2386,7 @@
     <t xml:space="preserve">85/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ticam1/Arfgef2/Fzd5/Akap12/Psen1/Ifngr1/Hspd1/Ifih1/Fcgr3/Plcg2/Havcr2/Lgals9/Arhgef2/Spn/Tyrobp/Ptprc/Cd84/Syk/Oas2</t>
+    <t xml:space="preserve">Syk/Arhgef2/Ptprc/Spn/Oas2/Cd84/Plcg2/Lgals9/Arfgef2/Cd36/Ticam1/Tyrobp/Fzd5/Havcr2/Fcgr3/Psen1/Ifih1/Hspd1/Ifngr1/Akap12</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046916</t>
@@ -2395,7 +2395,7 @@
     <t xml:space="preserve">cellular transition metal ion homeostasis</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Atp6v0d1/Slc30a10/Abcb6/Tfrc/Prnp/Ankrd9/Slc11a2/Slc30a9/Tmem199/Atp6v1a/Ftl1/Atp7a/Ap3d1/Aco1/Atp6v1g1/Slc39a8/Tfr2/Frrs1/Cyb561</t>
+    <t xml:space="preserve">Alas2/Atp6v0d1/Abcb6/Prnp/Slc30a10/Slc11a2/Slc30a9/Frrs1/Atp6v1a/Tfr2/Cyb561/Ankrd9/Aco1/Ap3d1/Tfrc/Tmem199/Atp7a/Ftl1/Slc39a8/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005938</t>
@@ -2407,7 +2407,7 @@
     <t xml:space="preserve">242/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cobl/Spta1/Tmod1/Gypc/Ank1/Epb42/Exoc3l4/Dmtn/Sptb/Snca/Zhx3/Epb41/Tsc1/Rhof/Actn1/Wasl/Gpsm2/Ppp1r9b/Dvl2/Mpp1/Exoc8/Exoc1/Cttn/Actr1a/Psen1/Iqgap1/Actr2/Ctnnb1/Nedd4/Wdr1/Myh10/Hcls1/Sptan1/Flna/Cap1/Unc13a/Pdlim2/Frmpd1/Rac1/Rac2/Coro1a</t>
+    <t xml:space="preserve">Spta1/Cobl/Sptb/Gypc/Snca/Slc4a1/Coro1a/Tmod1/Rac2/Tsc1/Dmtn/Ank1/Rac1/Epb42/Cap1/Zhx3/Actn1/Flna/Epb41/Exoc3l4/Myh10/Wasl/Ppp1r9b/Ctnnb1/Wdr1/Nedd4/Dvl2/Gpsm2/Hcls1/Sptan1/Exoc8/Mpp1/Frmpd1/Actr1a/Exoc1/Psen1/Pdlim2/Actr2/Iqgap1/Rhof/Unc13a/Cttn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055037</t>
@@ -2419,7 +2419,7 @@
     <t xml:space="preserve">139/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Sh3tc2/Usp32/Slc30a10/Agtr1a/Tfrc/Tpp1/Abcg1/Pheta2/Atg9a/Slc11a2/Ldlr/Micall2/Arfgef2/Clcn3/Tuba1a/Ehd1/Rap2b/Gripap1/Gnas/Ap1g1/Ehd3/Rap2c/Fzd7/Akap5/Tmem230/Cmtm6/Vps53/Rac1</t>
+    <t xml:space="preserve">Sh3tc2/Usp32/Tpp1/Slc30a10/Slc11a2/Abcg1/Rac1/Vps53/Pheta2/Micall2/Arfgef2/Ldlr/Cmtm6/Gnas/Atg9a/Rap2b/Ehd1/Ap1g1/Clcn3/Agtr1a/Tuba1a/Rap2c/Fzd7/Tfrc/Ehd3/Tmem230/Gripap1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006167</t>
@@ -2431,7 +2431,7 @@
     <t xml:space="preserve">14/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Adss/Aprt/Adsl/Adssl1/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">Gart/Pfas/Atic/Adssl1/Adsl/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051338</t>
@@ -2443,7 +2443,7 @@
     <t xml:space="preserve">678/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Wnk4/Map3k1/Snca/Prkar2b/Wdr81/Agtr1a/Prnp/Pfkfb2/Nedd9/Als2/Gab1/Traf4/Tsc1/Uvrag/Stil/Cdc25b/Cdc6/Pim1/Ubash3b/Mapre3/Gba/Fzd5/Ppp2r5a/Smcr8/Map3k12/Cdkn2c/Fbxw7/Fbxo5/Dcun1d3/Cln8/Hmgcr/Ggnbp2/Cib1/Ppp1r3f/Shb/Dag1/Dvl2/Rap2b/Serinc5/Stradb/Hexim1/Rb1/Acd/Pip4k2c/Sirt1/Dcun1d1/Sh3glb1/Abi1/Qars/Psen1/Iqgap1/Ctnnb1/Rfc2/Parn/Phb2/Lrp5/Cct2/Gtpbp4/Maged1/Cbl/Dgkz/Hsp90ab1/Ldb1/Ube2s/Igf1r/Eif4a2/Prkca/Dtx3l/Pik3r5/Rap2c/Prkag2/Naf1/Ccng1/Trp53/Irak1/Vangl2/Ptpn6/Xrcc5/Rgs2/Rac1/Mmd/Pik3r6/Tfap4/Il4/Csf1/Rgs14/Apoe/Trib2/Tgfb1/Mst1r/Ptprc/P2rx7/Pik3ip1/Syk</t>
+    <t xml:space="preserve">Egr1/Map3k1/Prkar2b/Snca/Syk/Ptprc/Wnk4/Prnp/Tgfb1/Tsc1/Rac1/Trib2/Pfkfb2/Gab1/Ppp2r5a/Pik3ip1/P2rx7/Wdr81/Als2/Ccng1/Apoe/Cdc25b/Mst1r/Mmd/Ptpn6/Xrcc5/Cdc6/Irak1/Tfap4/Traf4/Uvrag/Fbxw7/Rap2b/Gba/Rgs14/Trp53/Cdkn2c/Dag1/Ldb1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Rgs2/Rap2c/Prkag2/Dgkz/Pik3r6/Eif4a2/Naf1/Ggnbp2/Maged1/Csf1/Ctnnb1/Smcr8/Rb1/Sh3glb1/Vangl2/Fbxo5/Dvl2/Cct2/Hmgcr/Hexim1/Ube2s/Dtx3l/Lrp5/Cib1/Prkca/Rfc2/Ubash3b/Hsp90ab1/Mapre3/Psen1/Serinc5/Sirt1/Acd/Iqgap1/Dcun1d1/Stradb/Ppp1r3f/Map3k12/Phb2/Gtpbp4/Dcun1d3/Abi1/Igf1r/Cbl/Qars/Pim1/Cln8/Parn/Shb/Pik3r5/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0040017</t>
@@ -2455,7 +2455,7 @@
     <t xml:space="preserve">467/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Egr1/Pld2/Dmtn/Cd47/Sema4b/Grn/Nedd9/Gab1/Adam10/Anxa3/Numb/Ssh2/Mospd2/Akap12/Tbc1d24/Wasl/Foxo4/Fbxo5/Atp7a/Cib1/Glipr2/Vps35/Ago2/Ccar1/Swap70/Cttn/Sirt1/Rps6kb1/Mia3/Rack1/Iqgap1/Elp3/Gpi1/Pde4d/Igf1r/Prkca/Megf8/Flna/Stat5a/Vsir/Ripor1/Pik3cd/Arpc2/Trp53/Sema4a/Gata2/Plcg2/Ano6/Fut4/Gab2/Plvap/Itga5/Rac1/Ripor2/Dock8/Rac2/Fermt3/Il4/Csf1/Cxcr4/Lgals9/Arhgef2/Spn/Mmp14/Tgfb1/Spi1/Hdac7/Ptprc/Coro1a</t>
+    <t xml:space="preserve">Hdac7/Egr1/Cldn13/Arhgef2/Ptprc/Coro1a/Ano6/Rac2/Tgfb1/Grn/Spn/Dmtn/Rac1/Cd47/Dock8/Ripor2/Gab1/Spi1/Gab2/Fermt3/Ripor1/Plcg2/Lgals9/Cxcr4/Arpc2/Adam10/Pld2/Tbc1d24/Itga5/Megf8/Flna/Trp53/Ssh2/Numb/Nedd9/Sema4b/Fut4/Pik3cd/Stat5a/Il4/Gata2/Mmp14/Wasl/Sema4a/Csf1/Vps35/Mospd2/Plvap/Fbxo5/Ccar1/Anxa3/Cib1/Prkca/Atp7a/Swap70/Vsir/Sirt1/Iqgap1/Foxo4/Ago2/Akap12/Igf1r/Mia3/Cttn/Rack1/Rps6kb1/Elp3/Pde4d/Glipr2/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005543</t>
@@ -2467,7 +2467,7 @@
     <t xml:space="preserve">369/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Appl2/Snca/Tpp1/Washc2/Rubcnl/Snx8/Epb41/Picalm/Plek2/Pcyt1b/Prex1/Hs1bp3/Snx25/Anxa3/Nrgn/Wdfy1/Zfyve26/Epn1/Sgk3/Chmp3/Atg2b/Ttpal/Exoc8/Syt14/Twf1/Exoc1/Arhgap35/Cpne1/Snx2/Snx3/Iqgap1/Got2/Flii/Esyt1/Anxa11/Snx5/Arhgap9/Fzd7/Faah/Sh3pxd2b/Unc13a/Dennd1c/Snx10/Gab2/Pitpnm2/Plcb2/Capg/Fes/Phlda2/Apoe/Nme4/Sytl4/Adap1/Vill/Btk/Myo1g/Arap3</t>
+    <t xml:space="preserve">Arap3/Btk/Snca/Myo1g/Appl2/Picalm/Vill/Tpp1/Washc2/Capg/Nme4/Gab2/Pitpnm2/Plcb2/Snx25/Snx8/Epn1/Apoe/Prex1/Pld2/Hs1bp3/Wdfy1/Adap1/Epb41/Sh3pxd2b/Atg2b/Phlda2/Sytl4/Pcyt1b/Fzd7/Zfyve26/Fes/Snx10/Anxa11/Flii/Faah/Twf1/Got2/Esyt1/Chmp3/Anxa3/Nrgn/Exoc8/Snx5/Arhgap9/Rubcnl/Exoc1/Cpne1/Snx2/Plek2/Ttpal/Iqgap1/Dennd1c/Sgk3/Syt14/Arhgap35/Unc13a/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002573</t>
@@ -2479,7 +2479,7 @@
     <t xml:space="preserve">183/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Tal1/Cited2/Tfrc/Fos/Fasn/Ubash3b/Gba/Junb/Fbxw7/Rara/Gnas/Rb1/Gfi1b/Asxl2/Sirt1/Psen1/Ctnnb1/Hcls1/Prkca/Stat5a/Gata2/Lrrk1/Zfp36l1/Snx10/Nrros/Gab2/Il4/Csf1/Fes/Tgfb1/Spi1/Tyrobp/Cdk6</t>
+    <t xml:space="preserve">Car2/Tgfb1/Cdk6/Tal1/Spi1/Gab2/Cited2/Fasn/Gnas/Lrrk1/Fbxw7/Gba/Nrros/Tyrobp/Stat5a/Il4/Gata2/Fes/Zfp36l1/Csf1/Snx10/Ctnnb1/Rb1/Tfrc/Hcls1/Prkca/Ubash3b/Psen1/Sirt1/Fos/Junb/Rara/Gfi1b/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030834</t>
@@ -2491,7 +2491,7 @@
     <t xml:space="preserve">49/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Add2/Dmtn/Sptb/Swap70/Twf1/Flii/Wdr1/Sptan1/Arpc2/Pdxp/Capg/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Vill/Tmod1/Dmtn/Capg/Arpc2/Pdxp/Wdr1/Flii/Twf1/Sptan1/Swap70</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032984</t>
@@ -2503,7 +2503,7 @@
     <t xml:space="preserve">213/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Mcoln1/Rubcnl/Ddit4/Map1lc3b/Uvrag/Gba/Vps33a/Smcr8/Cib1/Ttbk2/Camsap2/Swap70/Twf1/Snap29/Taok1/Clec16a/Scaf4/Vps4b/Ubqln4/Flii/Wdr1/Igf1r/Sptan1/Smarcd1/Akap5/Arpc2/Pdxp/Ogfod1/Capg/Arhgef2/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Mcoln1/Ddit4/Arpc2/Map1lc3b/Uvrag/Gba/Smarcd1/Map1a/Pdxp/Ogfod1/Vps33a/Wdr1/Smcr8/Flii/Twf1/Camsap2/Ubqln4/Sptan1/Cib1/Swap70/Ttbk2/Rubcnl/Taok1/Scaf4/Igf1r/Vps4b/Clec16a/Akap5/Snap29</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030335</t>
@@ -2515,7 +2515,7 @@
     <t xml:space="preserve">435/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Egr1/Pld2/Dmtn/Cd47/Sema4b/Grn/Nedd9/Gab1/Adam10/Anxa3/Numb/Ssh2/Mospd2/Akap12/Tbc1d24/Foxo4/Fbxo5/Atp7a/Cib1/Glipr2/Ago2/Ccar1/Swap70/Sirt1/Rps6kb1/Mia3/Rack1/Iqgap1/Elp3/Gpi1/Pde4d/Igf1r/Prkca/Flna/Stat5a/Vsir/Ripor1/Pik3cd/Arpc2/Trp53/Sema4a/Gata2/Plcg2/Ano6/Fut4/Gab2/Plvap/Itga5/Rac1/Ripor2/Dock8/Rac2/Fermt3/Il4/Csf1/Cxcr4/Lgals9/Arhgef2/Spn/Mmp14/Tgfb1/Spi1/Hdac7/Ptprc/Coro1a</t>
+    <t xml:space="preserve">Hdac7/Egr1/Cldn13/Arhgef2/Ptprc/Coro1a/Ano6/Rac2/Tgfb1/Grn/Spn/Dmtn/Rac1/Cd47/Dock8/Ripor2/Gab1/Spi1/Gab2/Fermt3/Ripor1/Plcg2/Lgals9/Cxcr4/Arpc2/Adam10/Pld2/Tbc1d24/Itga5/Flna/Trp53/Ssh2/Numb/Nedd9/Sema4b/Fut4/Pik3cd/Stat5a/Il4/Gata2/Mmp14/Sema4a/Csf1/Mospd2/Plvap/Fbxo5/Ccar1/Anxa3/Cib1/Prkca/Atp7a/Swap70/Vsir/Sirt1/Iqgap1/Foxo4/Ago2/Akap12/Igf1r/Mia3/Rack1/Rps6kb1/Elp3/Pde4d/Glipr2/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0022411</t>
@@ -2527,7 +2527,7 @@
     <t xml:space="preserve">379/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Optn/Mcoln1/Rubcnl/Ddit4/Atg9a/Map1lc3b/Uvrag/Gba/Dnase2a/Vps33a/Retreg2/Smcr8/Fbxw7/Cib1/Atg2b/Bax/Ttbk2/Gabarap/Camsap2/Exoc8/Atg4d/Swap70/Twf1/Lamc1/Cttn/Snap29/Taok1/Clec16a/Scaf4/Vps4b/Plin2/Ubqln4/Phb2/Flii/Wdr1/Ulk2/Igf1r/Sptan1/Smarcd1/Sh3pxd2b/Akap5/Arpc2/Trp53/Pdxp/Ogfod1/Hk2/Capg/Arhgef2/Vill/Dpp4/Lcp1/Eng</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Eng/Mcoln1/Lcp1/Ddit4/Optn/Arpc2/Map1lc3b/Dpp4/Atg9a/Uvrag/Fbxw7/Gba/Sh3pxd2b/Atg2b/Smarcd1/Trp53/Map1a/Gabarap/Retreg2/Dnase2a/Pdxp/Ogfod1/Vps33a/Wdr1/Smcr8/Flii/Twf1/Camsap2/Ubqln4/Sptan1/Exoc8/Cib1/Swap70/Lamc1/Ttbk2/Hk2/Rubcnl/Ulk2/Taok1/Bax/Phb2/Scaf4/Igf1r/Vps4b/Cttn/Clec16a/Akap5/Snap29/Atg4d/Plin2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001818</t>
@@ -2539,7 +2539,7 @@
     <t xml:space="preserve">214/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Prnp/Serpinb1a/Atg9a/Gba/Arrb1/Sars/Atp2b1/Rara/Otud7b/Tusc2/Sirt1/Ppm1b/Parp1/Hsp90ab1/Vsir/Srgn/Ptpn6/Il27ra/Pdcd4/Rac1/Havcr2/Il4/Ptprs/Rnf125/Lgals9/Trib2/Lgals7/Tgfb1/Laptm5/Tyrobp/Hdac7/Adcy7/Btk/Ptprc/Jak3/Il1rl1/Cd84</t>
+    <t xml:space="preserve">Hdac7/Btk/Jak3/Adcy7/Laptm5/Appl2/Il1rl1/Ptprs/Ptprc/Prnp/Tgfb1/Rac1/Trib2/Cd84/Lgals9/Atp2b1/Rnf125/Ptpn6/Serpinb1a/Atg9a/Gba/Sars/Tyrobp/Il4/Lgals7/Il27ra/Havcr2/Arrb1/Srgn/Otud7b/Hsp90ab1/Pdcd4/Vsir/Tusc2/Sirt1/Rara/Parp1/Ppm1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051668</t>
@@ -2554,7 +2554,7 @@
     <t xml:space="preserve">579/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ank1/Dmtn/Tspan33/Optn/Prnp/Kalrn/Vps26a/Picalm/Adam10/Ptpn23/Micall2/Cltc/Gga2/Numb/Pikfyve/Rab3ip/Arfgef2/Ppp2r5a/Rabep1/Ccdc93/Cib1/Mtch2/Ap3d1/Ppp1r9b/Dag1/Bax/Ehd1/Vps29/Exoc8/Golga4/Vps35/Gripap1/Sorbs1/Bid/Pacs2/Exoc1/Stom/Ap2m1/Sav1/Sh3glb1/Sec62/Snx3/Rack1/Sec61a1/Gorasp2/Gopc/Ttc7b/Scp2/Lztfl1/Pgrmc1/Atad1/Syngap1/Flna/Ptpn9/Ehd3/Itgb2/Zdhhc23/Sh3pxd2b/Lin7c/Agk/Akap5/Arpc2/Dennd1c/Cmtm6/Pmaip1/Pgap2/Zdhhc21/Rangrf/Vps53/Ankrd27/Frmpd1/Vamp5/Rac1/Lypla1/Dock2/Mmp14/Apoe/Tgfb1/Fyb/Emc4/Ptprc/Rftn1</t>
+    <t xml:space="preserve">Dock2/Rftn1/Picalm/Slc4a1/Ptprc/Prnp/Vps26a/Tgfb1/Emc4/Cltc/Ankrd27/Dmtn/Ank1/Fyb/Tspan33/Rac1/Gga2/Lypla1/Ptpn23/Ppp2r5a/Vps53/Micall2/Zdhhc21/Optn/Arfgef2/Vamp5/Arpc2/Apoe/Rabep1/Adam10/Lin7c/Pikfyve/Cmtm6/Kalrn/Flna/Mtch2/Pmaip1/Pgap2/Ehd1/Pacs2/Sh3pxd2b/Dag1/Numb/Agk/Rangrf/Rab3ip/Atad1/Mmp14/Ppp1r9b/Ptpn9/Ap3d1/Vps35/Sh3glb1/Gorasp2/Vps29/Ccdc93/Exoc8/Frmpd1/Cib1/Itgb2/Ehd3/Ap2m1/Exoc1/Bid/Sec61a1/Sav1/Pgrmc1/Golga4/Dennd1c/Bax/Scp2/Ttc7b/Syngap1/Lztfl1/Sorbs1/Gripap1/Sec62/Stom/Rack1/Akap5/Snx3/Gopc/Zdhhc23</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042129</t>
@@ -2566,7 +2566,7 @@
     <t xml:space="preserve">148/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Tfrc/Prnp/Zbtb7b/Nck1/Bid/Ctnnb1/Stat5a/Vsir/Stat5b/Ptpn6/Il27ra/Cd37/Ripor2/Rac2/Havcr2/Il4/Lgals9/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Ptprc/Coro1a/Jak3/Syk</t>
+    <t xml:space="preserve">Spta1/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Ripor2/Lgals9/Stat5b/Ptpn6/Zbtb7b/Stat5a/Il4/Lgals7/Cd37/Ctnnb1/Il27ra/Havcr2/Tfrc/Vsir/Bid/Nck1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060538</t>
@@ -2575,7 +2575,7 @@
     <t xml:space="preserve">skeletal muscle organ development</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Btg2/Egr2/Cited2/Hlf/Gpcpd1/Mylk2/Arntl/Mylpf/Fos/Nupr1/Kel/Hdac5/Hmgcr/Xk/Dag1/Rb1/Med20/Homer1/Rps6kb1/Nras/Ctnnb1/Tcf7l2/Popdc2/Nr1d2/Vamp5/Des/Ripor2/Tgfb1</t>
+    <t xml:space="preserve">Egr1/Btg2/Tgfb1/Ripor2/Cited2/Hlf/Vamp5/Nr1d2/Des/Arntl/Dag1/Egr2/Xk/Ctnnb1/Hdac5/Kel/Rb1/Gpcpd1/Hmgcr/Mylpf/Mylk2/Fos/Nupr1/Nras/Popdc2/Homer1/Med20/Tcf7l2/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031252</t>
@@ -2587,7 +2587,7 @@
     <t xml:space="preserve">347/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Pld2/Appl2/Ank1/Itsn1/Mpp2/Als2/Tsc1/Asap3/Actn1/Myo6/Atp2b1/Wasl/Atp6v1b2/Atp7a/Cib1/Ppp1r9b/Dag1/Cdkl5/Nckap1/Pkn2/Exoc8/Gnas/Twf1/Cttn/Cdc42bpa/Abi1/Iqgap1/Actr2/Ctnnb1/Dgkz/Ldb1/Myh10/Ripor1/Akap5/Arpc2/Pdxp/Plcg2/Arhgef6/Itga5/Rac1/Ripor2/Dock8/Rac2/Vim/Ywhaz/Cxcr4/Arhgef2/Adgre5/Cd44/Cdk6/Coro1a/Dpp4/Myo1g/Lcp1</t>
+    <t xml:space="preserve">Cobl/Myo1g/Appl2/Arhgef2/Coro1a/Rac2/Ywhaz/Cdk6/Tsc1/Ank1/Cd44/Rac1/Dock8/Adgre5/Itsn1/Ripor2/Actn1/Lcp1/Ripor1/Plcg2/Vim/Mpp2/Cxcr4/Als2/Arpc2/Atp2b1/Pld2/Dpp4/Itga5/Gnas/Arhgef6/Atp6v1b2/Myo6/Dag1/Ldb1/Pdxp/Pkn2/Myh10/Dgkz/Wasl/Ppp1r9b/Ctnnb1/Nckap1/Twf1/Asap3/Exoc8/Cib1/Atp7a/Actr2/Iqgap1/Cdkl5/Cdc42bpa/Abi1/Cttn/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019900</t>
@@ -2599,7 +2599,7 @@
     <t xml:space="preserve">760/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Phyhip/Pld2/Mst1/Map3k1/Add2/Inka2/Prkar2b/Agtr1a/Tfrc/Pfkfb2/Nedd9/Traf4/Adam10/Ptpn23/Tollip/Cltc/Ticam1/Cdc25b/Cdc6/Rhof/Dpysl2/Mapre3/Arrb1/Pea15a/Zfyve26/Syn1/Hdac5/Fzd5/Ppp2r5a/Dact3/Smcr8/Map3k12/Cdkn2c/Ccnt1/Fbxo5/Kif13b/Cib1/Ppp1r9b/Tob1/Dvl2/Rara/Polr2a/Nck1/Slc12a7/Bcl2l11/Sorbs1/Rictor/Rb1/Nbr1/Sirt1/Acaca/Taok1/Usp37/Qars/Rack1/Nap1l1/Iqgap1/Parp1/Ctnnb1/Parn/Tcf3/Was/Nek9/Cbl/Rbck1/Hsp90ab1/Stau2/Tnni3/Syngap1/Hcls1/Traf3/Sp100/Flna/Prmt1/Ttc28/Itgb2/Prkag2/Rnf138/Tcf7l2/Akap5/Trp53/Irak1/Ptpn6/Plcg2/Spred2/Gab2/Rac1/Rcc2/Pitpnm2/Rac2/Vim/Irf5/Prr7/Ywhaz/Rgs14/Trib2/Cd44/Gdf3/Hdac7/Ptprc/Dok2/Pik3ip1/Syk</t>
+    <t xml:space="preserve">Rab3il1/Hdac7/Add2/Map3k1/Prkar2b/Syk/Ptprc/Rac2/Ywhaz/Cltc/Mst1/Dok2/Phyhip/Cd44/Rac1/Trib2/Rcc2/Pfkfb2/Ptpn23/Gab2/Ppp2r5a/Pitpnm2/Pik3ip1/Tollip/Plcg2/Vim/Cdc25b/Adam10/Pld2/Ptpn6/Cdc6/Flna/Irak1/Traf4/Polr2a/Rgs14/Gdf3/Inka2/Trp53/Cdkn2c/Spred2/Dpysl2/Nedd9/Irf5/Traf3/Agtr1a/Ticam1/Rnf138/Fzd5/Prkag2/Prmt1/Ccnt1/Ppp1r9b/Zfyve26/Pea15a/Ctnnb1/Hdac5/Prr7/Smcr8/Rb1/Nek9/Rbck1/Ttc28/Arrb1/Fbxo5/Dvl2/Tfrc/Hcls1/Tob1/Cib1/Bcl2l11/Itgb2/Tcf3/Hsp90ab1/Acaca/Dact3/Mapre3/Kif13b/Sirt1/Taok1/Tnni3/Iqgap1/Slc12a7/Rara/Rhof/Stau2/Syngap1/Map3k12/Sorbs1/Nbr1/Nck1/Parp1/Tcf7l2/Cbl/Qars/Usp37/Nap1l1/Rack1/Akap5/Parn/Sp100/Syn1/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098876</t>
@@ -2611,7 +2611,7 @@
     <t xml:space="preserve">127/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Optn/Vps26a/Ptpn23/Micall2/Gga2/Arfgef2/Rabep1/Ccdc93/Ehd1/Vps29/Exoc8/Golga4/Vps35/Gripap1/Exoc1/Snx3/Rack1/Gopc/Ehd3/Akap5/Dennd1c/Cmtm6/Vps53/Ankrd27/Vamp5/Lypla1</t>
+    <t xml:space="preserve">Vps26a/Ankrd27/Gga2/Lypla1/Ptpn23/Vps53/Micall2/Optn/Arfgef2/Vamp5/Rabep1/Cmtm6/Ehd1/Vps35/Vps29/Ccdc93/Exoc8/Ehd3/Exoc1/Golga4/Dennd1c/Gripap1/Rack1/Akap5/Snx3/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044089</t>
@@ -2623,7 +2623,7 @@
     <t xml:space="preserve">429/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Cd36/Map3k1/Tal1/Cd47/Snca/Tfrc/Tsc1/Fnip2/Plek2/Stil/Slf2/Mlst8/Epn1/Wasl/1810058I24Rik/Gpsm2/Atp7a/Dag1/Bax/Ppp2r5b/Nckap1/Ttbk2/Nck1/Bcl2l11/Rictor/Bid/Rap1b/Tapt1/Swap70/Togaram1/Morc2a/Pip4k2c/Arhgap35/Cttn/Fnip1/Sh3glb1/Setdb1/Vps4b/Rack1/Iqgap1/Actr2/Trim28/Stau2/Dhx33/Def8/Prkca/Slain2/Flna/Srf/Sh3pxd2b/Arpc2/Trp53/Sema4a/Plcg2/Rac1/Ripor2/Rac2/Fes/Adgre5/Apoe/Tgfb1/P2rx7/Syk/Lcp1</t>
+    <t xml:space="preserve">Cobl/Map3k1/Snca/Syk/Rac2/Tgfb1/Tal1/Tsc1/Rac1/Cd47/Adgre5/Ripor2/Fnip2/P2rx7/Lcp1/Plcg2/Slf2/Arpc2/Epn1/Apoe/Cd36/Flna/Mlst8/Sh3pxd2b/Trp53/Dag1/1810058I24Rik/Stil/Tapt1/Wasl/Sema4a/Srf/Fes/Nckap1/Slain2/Sh3glb1/Morc2a/Togaram1/Gpsm2/Tfrc/Def8/Bcl2l11/Prkca/Atp7a/Swap70/Trim28/Ttbk2/Dhx33/Rap1b/Bid/Plek2/Actr2/Iqgap1/Fnip1/Bax/Setdb1/Stau2/Arhgap35/Nck1/Vps4b/Ppp2r5b/Cttn/Rack1/Pip4k2c/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000145</t>
@@ -2638,7 +2638,7 @@
     <t xml:space="preserve">796/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Egr1/Pld2/Appl2/Mink1/Mst1/Map3k1/Dmtn/Cd47/Cited2/Sema4b/Grn/Nedd9/Gab1/Adam10/Ptpn23/Anxa3/Numb/Ssh2/Trp53inp1/Hdac5/Mospd2/Ppard/Akap12/Tbc1d24/Wasl/Fbxw7/Hace1/Foxo4/Fbxo5/Flcn/Atp7a/Cib1/Dag1/Glipr2/Mpp1/Ttbk2/Pkn2/Rap2b/Nck1/Ago2/Ccar1/Swap70/Gna13/Vcl/Sirt1/Rps6kb1/Adipor2/Mia3/Rack1/Iqgap1/Was/Elp3/Gpi1/Gtpbp4/Pde4d/Ptpru/Ldb1/Igf1r/Prkca/Sp100/Idh2/Flna/Srf/Stat5a/Vsir/Rap2c/Ripor1/Pik3cd/Arpc2/Trp53/Il27ra/Sema4a/Atp1b2/Gata2/Plcg2/Ano6/Fut4/Gab2/Plvap/Itga5/Rac1/Rcc2/Plxnc1/Ripor2/Dock8/Rac2/Vim/Fermt3/Il4/Csf1/Fes/Phlda2/Cxcr4/Lgals9/Arhgef2/Spn/Mmp14/Apoe/Tgfb1/Spi1/Hdac7/Ptprc/Coro1a/Dpp4/Arhgdib/Eng/Rin3</t>
+    <t xml:space="preserve">Hdac7/Egr1/Map3k1/Cldn13/Appl2/Arhgef2/Ptprc/Mink1/Coro1a/Ano6/Rac2/Tgfb1/Mst1/Grn/Spn/Dmtn/Rac1/Cd47/Dock8/Ripor2/Rcc2/Ptpn23/Gab1/Spi1/Gab2/Fermt3/Cited2/Eng/Rin3/Ripor1/Plcg2/Lgals9/Vim/Arhgdib/Cxcr4/Arpc2/Apoe/Adam10/Pld2/Tbc1d24/Dpp4/Itga5/Flna/Fbxw7/Rap2b/Trp53/Ssh2/Phlda2/Dag1/Ldb1/Numb/Nedd9/Pkn2/Hace1/Sema4b/Idh2/Fut4/Trp53inp1/Pik3cd/Stat5a/Il4/Gata2/Rap2c/Mmp14/Wasl/Sema4a/Gna13/Srf/Fes/Csf1/Il27ra/Ppard/Hdac5/Mospd2/Plvap/Fbxo5/Atp1b2/Ccar1/Anxa3/Plxnc1/Mpp1/Cib1/Prkca/Atp7a/Swap70/Adipor2/Ttbk2/Flcn/Vsir/Sirt1/Iqgap1/Foxo4/Ago2/Gtpbp4/Akap12/Ptpru/Igf1r/Nck1/Mia3/Rack1/Sp100/Vcl/Rps6kb1/Elp3/Pde4d/Glipr2/Gpi1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903557</t>
@@ -2659,7 +2659,7 @@
     <t xml:space="preserve">50/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Fos/Gnas/Rb1/Gfi1b/Asxl2/Hcls1/Prkca/Stat5a/Zfp36l1/Csf1/Fes/Tgfb1/Tyrobp</t>
+    <t xml:space="preserve">Car2/Tgfb1/Gnas/Tyrobp/Stat5a/Fes/Zfp36l1/Csf1/Rb1/Hcls1/Prkca/Fos/Gfi1b/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010563</t>
@@ -2671,7 +2671,7 @@
     <t xml:space="preserve">381/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Wnk4/Dmtn/Snca/Prkar2b/Prnp/Dusp6/Ddit4/Nupr1/Snx25/Ubash3b/Ppp1r15b/Gba/Arrb1/Ppp2r5a/Smcr8/Cdkn2c/Hmgcr/Dnajc10/Flcn/Ggnbp2/Cib1/Mtch2/Shb/Ppp1r9b/Bax/C9orf72/Nck1/Hexim1/Swap70/Rb1/Pip4k2c/Sirt1/Qars/Rack1/Psen1/Iqgap1/Parp1/Lrp5/Pde4d/Cbl/Pwp1/Prkca/Samsn1/Fkbp1b/Prkag2/Abca2/Trp53/Ptpn6/Lrrk1/Spred2/Rgs2/Tfap4/Rgs14/Apoe/Tgfb1/Ptprc/Pik3ip1/Eng</t>
+    <t xml:space="preserve">Prkar2b/Snca/Slc4a1/Ptprc/Wnk4/Prnp/Tgfb1/Dmtn/Ppp2r5a/Eng/Pik3ip1/Abca2/Snx25/Ddit4/Apoe/Ptpn6/Lrrk1/Mtch2/Tfap4/Gba/Rgs14/Trp53/Cdkn2c/Spred2/Dnajc10/Dusp6/Rgs2/Prkag2/Ppp1r15b/Ppp1r9b/Ggnbp2/Smcr8/Rb1/Arrb1/Hmgcr/Pwp1/Hexim1/Lrp5/Cib1/Prkca/Ubash3b/Swap70/Flcn/Psen1/Sirt1/C9orf72/Iqgap1/Samsn1/Bax/Nupr1/Fkbp1b/Nck1/Parp1/Cbl/Qars/Rack1/Shb/Pip4k2c/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045936</t>
@@ -2689,7 +2689,7 @@
     <t xml:space="preserve">142/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Washc5/Micall2/Ssh2/Mlst8/Wasl/Plekhg2/Nckap1/Nck1/Rictor/Twf1/Cttn/Was/Flii/Hcls1/Sptan1/Arpc2/Rac1/Capg/Vill/Coro1a</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Map3k1/Vill/Coro1a/Tmod1/Washc5/Dmtn/Rac1/Capg/Micall2/Arpc2/Mlst8/Ssh2/Wasl/Nckap1/Flii/Twf1/Plekhg2/Hcls1/Sptan1/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048471</t>
@@ -2701,7 +2701,7 @@
     <t xml:space="preserve">590/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Dmtn/S100a4/Snca/Prkar2b/Dnajb2/Optn/Tfrc/Hmbs/Kalrn/Mospd1/Ache/Tsc1/Picalm/Adam10/Slc11a2/Lamp1/Tollip/Nupr1/Atp6v0a1/Pikfyve/Mapre3/Rab3ip/Igf2r/Fzd5/Vps33a/Myo6/Fbxw7/Dcun1d3/Atp7a/Cib1/Bax/Cdkl5/Hectd3/Rara/Ehd1/Pkn2/Gabarap/Vps35/Ddx6/Cpd/Gnas/Twf1/Stom/Srcap/Rps6kb1/Taok1/Uso1/Rack1/Psen1/Ctnnb1/Nedd4/Gtpbp4/Rhbdd2/Pde4d/Cbl/Hsp90ab1/Set/Itm2c/Ap1g1/Cul7/Eif4a2/Prkca/Flna/Snx5/Ehd3/Pcsk9/Ankrd13b/Ccng1/Akap5/Prdx6/Plcg2/Vapa/Pde4b/Vps53/Clic1/Vamp5/Vim/Prr7/Csf1/Ywhaz/Laptm5/Lcp1/Oas2</t>
+    <t xml:space="preserve">Cobl/Prkar2b/Laptm5/Snca/Picalm/Ywhaz/Slc11a2/Tsc1/Dmtn/Oas2/Lamp1/Hmbs/Clic1/Tollip/Vps53/Vapa/Lcp1/Plcg2/Vim/Optn/Vamp5/Ccng1/Adam10/Igf2r/Mospd1/Pikfyve/Kalrn/Gnas/Ache/Flna/S100a4/Fbxw7/Ehd1/Ap1g1/Prdx6/Myo6/Gabarap/Atp6v0a1/Ddx6/Pkn2/Rab3ip/Ankrd13b/Fzd5/Cul7/Eif4a2/Csf1/Ctnnb1/Dnajb2/Vps33a/Prr7/Vps35/Twf1/Nedd4/Tfrc/Snx5/Cpd/Cib1/Prkca/Pde4b/Hsp90ab1/Srcap/Ehd3/Atp7a/Mapre3/Psen1/Set/Taok1/Hectd3/Pcsk9/Rara/Bax/Cdkl5/Nupr1/Itm2c/Gtpbp4/Dcun1d3/Rhbdd2/Cbl/Stom/Rack1/Akap5/Rps6kb1/Pde4d/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009150</t>
@@ -2713,7 +2713,7 @@
     <t xml:space="preserve">341/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Fasn/Mlst8/Atp6v1a/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Gcdh/Acaca/Ndufa10/Psen1/Cs/Parp1/Gpi1/Adss/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Suclg2/Prkag2/Khk/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Il4/Tgfb1/Nme4/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Pfkfb2/Nme4/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Pkm/Atp6v1a/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/Gmpr/Impdh2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Eno3/Dlat/Acaca/Atp7a/Hk2/Flcn/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Adss/Parp1/Pmvk/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902107</t>
@@ -2728,7 +2728,7 @@
     <t xml:space="preserve">164/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Egr3/Fos/Zbtb7b/Ap3d1/Shb/Rara/Gnas/Rb1/Gfi1b/Asxl2/Phf10/Hcls1/Prkca/Stat5a/Vsir/Smarcd1/Stat5b/Zfp36l1/Cbfb/Pik3r6/Il4/Csf1/Fes/Lgals9/Mmp14/Tgfb1/Tyrobp/Ptprc/Myb/Syk</t>
+    <t xml:space="preserve">Car2/Syk/Myb/Ptprc/Tgfb1/Cbfb/Lgals9/Stat5b/Gnas/Smarcd1/Egr3/Zbtb7b/Tyrobp/Stat5a/Il4/Mmp14/Pik3r6/Fes/Zfp36l1/Csf1/Ap3d1/Rb1/Hcls1/Prkca/Vsir/Fos/Rara/Gfi1b/Asxl2/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903708</t>
@@ -2749,7 +2749,7 @@
     <t xml:space="preserve">157/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Btnl10/Cd47/Prnp/Ermap/Usp9x/Shb/Elf1/Bax/Fcho1/Nras/Psen1/Pde4d/Rbck1/Dgkz/Lpxn/Ptpn6/Plcg2/Ubash3a/Pde4b/Lcp2/Laptm5/Fyb/Tyrobp/Btk/Ptprc/Myo1g/Rftn1/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Laptm5/Nfam1/Myo1g/Appl2/Rftn1/Syk/Ptprc/Prnp/Btnl10/Ermap/Fyb/Cd47/Plcg2/Ptpn6/Usp9x/Lcp2/Ubash3a/Tyrobp/Elf1/Dgkz/Rbck1/Pde4b/Psen1/Bax/Nras/Fcho1/Shb/Pde4d/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002683</t>
@@ -2761,7 +2761,7 @@
     <t xml:space="preserve">342/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd47/Prdx2/Grn/Prnp/Atg9a/Ldlr/Zbtb7b/Ubash3b/Smcr8/Wasl/Fbxw7/Elf1/C9orf72/Rara/Tsc22d3/Mia3/Usp15/Ctnnb1/Cnot7/Dgkz/Lyar/Stat5a/Samsn1/Vsir/Lpxn/Cst7/Ptpn6/Il27ra/Gata2/Ubash3a/Cd37/Serpinb9/Nr1d1/Cbfb/Ripor2/Havcr2/Il4/Lgals9/Spn/Lgals7/Tgfb1/Cd44/Laptm5/Spi1/Tyrobp/Btk/Ptprc/Cdk6/Jak3/Dpp4/Tbc1d10c/Il1rl1/Cd84/Rin3</t>
+    <t xml:space="preserve">Prdx2/Btk/Jak3/Laptm5/Il1rl1/Ptprc/Prnp/Tgfb1/Cdk6/Grn/Spn/Cd44/Cd47/Cd84/Ripor2/Cbfb/Spi1/Tbc1d10c/Rin3/Lgals9/Ldlr/Ptpn6/Dpp4/Atg9a/Fbxw7/Zbtb7b/Ubash3a/Tyrobp/Elf1/Stat5a/Il4/Gata2/Lgals7/Dgkz/Wasl/Cd37/Ctnnb1/Il27ra/Smcr8/Nr1d1/Havcr2/Serpinb9/Ubash3b/Usp15/Vsir/C9orf72/Samsn1/Rara/Lyar/Tsc22d3/Mia3/Cst7/Cnot7/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903706</t>
@@ -2770,7 +2770,7 @@
     <t xml:space="preserve">regulation of hemopoiesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Egr3/Fam210b/Abcb10/Tal1/Mturn/Prdx2/Cnot4/Fos/Zbtb7b/Ubash3b/Fbxw7/Cib1/Ap3d1/Shb/Rara/Gnas/Rb1/Gfi1b/Asxl2/Smap1/Kat6a/Phf10/Ctnnb1/Ldb1/Hcls1/Prkca/Prmt1/Stat5a/Vsir/Smarcd1/Lmo2/Stat5b/Ptpn6/Kat2a/Gata2/Zfp36l1/Cbfb/Pik3r6/Il4/Csf1/Fes/Lgals9/Mmp14/Tgfb1/Cd44/Spi1/Tyrobp/Ptprc/Myb/Cdk6/Jak3/Nfam1/Syk</t>
+    <t xml:space="preserve">Car2/Prdx2/Fam210b/Jak3/Nfam1/Syk/Myb/Ptprc/Abcb10/Tgfb1/Cdk6/Tal1/Cd44/Cbfb/Spi1/Lgals9/Kat2a/Cnot4/Stat5b/Ptpn6/Gnas/Mturn/Fbxw7/Smarcd1/Egr3/Zbtb7b/Ldb1/Tyrobp/Stat5a/Il4/Gata2/Lmo2/Mmp14/Prmt1/Pik3r6/Fes/Zfp36l1/Csf1/Ctnnb1/Ap3d1/Rb1/Hcls1/Smap1/Cib1/Prkca/Ubash3b/Vsir/Fos/Rara/Kat6a/Gfi1b/Asxl2/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032944</t>
@@ -2782,7 +2782,7 @@
     <t xml:space="preserve">194/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Tfrc/Prnp/Ticam1/Zbtb7b/Nck1/Bid/Ctnnb1/Tcf3/Cd320/Stat5a/Vsir/Stat5b/Ptpn6/Il27ra/Cd37/Ripor2/Rac2/Havcr2/Il4/Csf1/Lgals9/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Tyrobp/Btk/Ptprc/Coro1a/Jak3/Syk</t>
+    <t xml:space="preserve">Spta1/Btk/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Ripor2/Lgals9/Stat5b/Ptpn6/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Lgals7/Cd37/Csf1/Ctnnb1/Il27ra/Havcr2/Tfrc/Tcf3/Vsir/Bid/Cd320/Nck1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051493</t>
@@ -2791,7 +2791,7 @@
     <t xml:space="preserve">regulation of cytoskeleton organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Snca/Map1a/Mdm1/Washc2/Washc5/Tsc1/Asap3/Cltc/Stil/Rhof/Mapre3/Ssh2/Mlst8/Wasl/Gpsm2/Plekhg2/Ska2/Cib1/C9orf72/Nckap1/Ttbk2/Dyrk1a/Camsap2/Nck1/Rictor/Swap70/Twf1/Togaram1/Washc4/Arhgap35/Cttn/Taok1/Vps4b/Iqgap1/Was/Flii/Wdr1/Stau2/Hcls1/Sptan1/Slain2/Flna/Sh3pxd2b/Arpc2/Pdxp/Vangl2/Kat2a/Rangrf/Rac1/Ripor2/Rac2/Capg/Fes/Arhgef2/Tgfb1/Vill/Coro1a/Arhgef18/P2rx7/Arhgdib</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Snca/Arhgef2/Vill/Mid1ip1/Coro1a/Tmod1/Rac2/Tgfb1/Cltc/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Ripor2/Mdm1/P2rx7/Arhgdib/Kat2a/Arpc2/Arhgef18/Dyrk1a/Flna/Mlst8/Sh3pxd2b/Map1a/Ssh2/Pdxp/Rangrf/Stil/Wasl/Fes/Nckap1/Slain2/Wdr1/Flii/Twf1/Vangl2/Togaram1/Camsap2/Gpsm2/Plekhg2/Hcls1/Asap3/Sptan1/Cib1/Swap70/Ttbk2/Washc4/Mapre3/C9orf72/Taok1/Iqgap1/Rhof/Stau2/Arhgap35/Nck1/Vps4b/Cttn/Ska2/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000112</t>
@@ -2806,7 +2806,7 @@
     <t xml:space="preserve">424/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Slc6a9/Cd36/Btg2/Slc25a37/Abcb10/Fech/Tnrc6b/Tsc1/Pkm/Ppp1r15b/Gba/Gigyf2/Rnf139/Habp4/Ppp1r3f/Tob1/Rara/Uhmk1/Nck1/Ddx6/Aco1/Ago2/Sorbs1/Tnrc6c/Mknk1/Tut7/Mknk2/Rps6kb1/Celf1/Rack1/Ctnnb1/Parn/Cnot7/Pa2g4/Pus7/Zfp706/Itm2c/Eif4g2/Ldb1/Mov10/Tcof1/Cnbp/Trnau1ap/Prkca/Exosc5/Prmt1/Dph6/Eif4ebp2/Otud6b/Pomt1/Nat10/Mrps27/Tcf7l2/Abca2/Dapk1/Bzw2/Ogfod1/Zfp36l1/Msi1/Rgs2/Ago4/Vim/Jak3</t>
+    <t xml:space="preserve">Jak3/Btg2/Slc6a9/Abcb10/Fech/Tsc1/Cpeb4/Gigyf2/Tnrc6b/Abca2/Vim/Cd36/Ago4/Gba/Eif4ebp2/Bzw2/Nat10/Pkm/Tcof1/Rnf139/Slc25a37/Ldb1/Ddx6/Habp4/Ogfod1/Mrps27/Rgs2/Ppp1r15b/Prmt1/Aco1/Zfp36l1/Msi1/Ctnnb1/Otud6b/Pomt1/Dapk1/Uhmk1/Celf1/Cnbp/Tob1/Mov10/Pus7/Mknk2/Prkca/Zfp706/Dph6/Exosc5/Eif4g2/Rara/Ppp1r3f/Itm2c/Ago2/Tut7/Sorbs1/Trnau1ap/Tnrc6c/Nck1/Tcf7l2/Cnot7/Mknk1/Rack1/Parn/Pa2g4/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033006</t>
@@ -2815,7 +2815,7 @@
     <t xml:space="preserve">regulation of mast cell activation involved in immune response</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Ptpn6/Gata2/Unc13d/Gab2/Rac2/Il4/Fes/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Cd84/Gab2/Pld2/Ptpn6/Unc13d/D6Wsu163e/Il4/Gata2/Fes</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055088</t>
@@ -2827,7 +2827,7 @@
     <t xml:space="preserve">136/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Scd1/Insig1/Abcg1/Washc5/Ldlr/Mylip/Acox1/Lamtor1/Cln8/Mtch2/Ehd1/Med13/Sirt1/Acaca/Mia2/Got1/Lrp5/Tmem97/Sar1b/Adck1/Pcsk9/Abca2/Surf4/Nr1d2/Nr1d1/Apoe/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Washc5/Abcg1/Surf4/Abca2/Apoe/Ldlr/Insig1/Nr1d2/Mtch2/Acox1/Ehd1/Scd1/Med13/Lamtor1/Mylip/Nr1d1/Mia2/Lrp5/Sar1b/Acaca/Sirt1/Adck1/Pcsk9/Got1/Tmem97/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002831</t>
@@ -2839,7 +2839,7 @@
     <t xml:space="preserve">287/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Prdx2/Optn/Grn/Serpinb1a/Lamp1/Trim56/Tbk1/Elmod2/Rnf185/Hexim1/Ppm1b/Fbxo38/Usp15/Nono/Cnot7/Matr3/Hspd1/Ap1g1/Lyar/Prkca/Traf3/Dtx3l/Stat5a/Oasl1/Stat5b/Dapk1/Xrcc5/Plcg2/Traf3ip2/Vav1/Apobec3/Cadm1/Cd37/Serpinb9/Havcr2/Pik3r6/Il4/Rnf125/Lgals9/Spn/Apoe/Spi1/Tyrobp/Dpp4/Cd84/Syk</t>
+    <t xml:space="preserve">Prdx2/Appl2/Syk/Grn/Spn/Lamp1/Cd84/Spi1/Vav1/Plcg2/Lgals9/Optn/Apoe/Stat5b/Rnf125/Dpp4/Xrcc5/Serpinb1a/Tbk1/Apobec3/Ap1g1/Trim56/Traf3/Tyrobp/Stat5a/Il4/Cd37/Pik3r6/Nono/Dapk1/Havcr2/Matr3/Serpinb9/Hexim1/Dtx3l/Prkca/Usp15/Cadm1/Fbxo38/Traf3ip2/Hspd1/Rnf185/Lyar/Cnot7/Oasl1/Elmod2/Ppm1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043408</t>
@@ -2851,7 +2851,7 @@
     <t xml:space="preserve">542/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Grap2/Mink1/Map3k1/Slc30a10/Mturn/Prdx2/Mylk2/Hipk2/Dusp6/Gab1/Traf4/Lamtor1/Gba/Arrb1/Epor/Atp6ap2/Fzd5/Map3k12/Akap12/Fbxw7/Hmgcr/Flcn/Cib1/Lamtor3/Stk25/Dag1/Dvl2/Glipr2/Rara/Ash1l/Garem1/Rap1b/Avpi1/Nbr1/Bnip2/Taok1/Qars/Psen1/Iqgap1/Dnajc27/Ctnnb1/Phb2/Maged1/Dhx33/Ndst1/Syngap1/Igf1r/Prkca/Traf3/Prmt1/Pik3r5/Map4k1/Irak1/Vangl2/Ptpn6/Plcg2/Spred2/Rgs2/Rac1/Havcr2/Pik3r6/Ywhaz/Rgs14/Cxcr4/Apoe/Tgfb1/Cd44/Laptm5/Mst1r/Spi1/Ptprc/Dok2/P2rx7/Tbc1d10c/Cd84/Igfbp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Map3k1/Laptm5/Syk/Ptprc/Mink1/Igfbp4/Tgfb1/Ywhaz/Slc30a10/Dok2/Cd44/Rac1/Cd84/Gab1/Spi1/Tbc1d10c/P2rx7/Plcg2/Cxcr4/Apoe/Mst1r/Cd36/Atp6ap2/Ptpn6/Hipk2/Grap2/Irak1/Mturn/Traf4/Fbxw7/Gba/Stk25/Rgs14/Spred2/Dag1/Epor/Traf3/Dusp6/Fzd5/Rgs2/Map4k1/Prmt1/Pik3r6/Maged1/Lamtor3/Lamtor1/Ctnnb1/Havcr2/Arrb1/Vangl2/Dvl2/Hmgcr/Mylk2/Ndst1/Cib1/Prkca/Dhx33/Flcn/Rap1b/Psen1/Taok1/Ash1l/Iqgap1/Garem1/Rara/Avpi1/Syngap1/Map3k12/Phb2/Akap12/Nbr1/Bnip2/Igf1r/Qars/Dnajc27/Pik3r5/Glipr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002102</t>
@@ -2860,7 +2860,7 @@
     <t xml:space="preserve">podosome</t>
   </si>
   <si>
-    <t xml:space="preserve">Vcl/Cttn/Actr2/Lpxn/Sh3pxd2b/Arpc2/Fermt3/Arhgef2/Lcp1</t>
+    <t xml:space="preserve">Arhgef2/Fermt3/Lcp1/Arpc2/Sh3pxd2b/Actr2/Cttn/Vcl/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046033</t>
@@ -2869,7 +2869,7 @@
     <t xml:space="preserve">AMP metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Aprt/Adsl/Adssl1/Atic/Ak4/Pfas/Gart</t>
+    <t xml:space="preserve">Ampd3/Gart/Pfas/Atic/Adssl1/Adsl/Ak4/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904376</t>
@@ -2878,7 +2878,7 @@
     <t xml:space="preserve">negative regulation of protein localization to cell periphery</t>
   </si>
   <si>
-    <t xml:space="preserve">Picalm/Cltc/Numb/Ppp2r5a/Ap2m1/Gopc/Lztfl1/Lypla1/Tgfb1</t>
+    <t xml:space="preserve">Picalm/Tgfb1/Cltc/Lypla1/Ppp2r5a/Numb/Ap2m1/Lztfl1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006188</t>
@@ -2890,7 +2890,7 @@
     <t xml:space="preserve">15/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Aprt/Adsl/Atic/Pfas/Gmpr/Gart</t>
+    <t xml:space="preserve">Ampd3/Gart/Pfas/Atic/Adsl/Gmpr/Aprt</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2001244</t>
@@ -2902,7 +2902,7 @@
     <t xml:space="preserve">63/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Nupr1/Fbxw7/Flcn/Mtch2/Bax/Nck1/Bcl2l11/Bid/Mcl1/Siah1b/Sirt1/Sh3glb1/Rack1/Serinc3/Trp53/Pmaip1</t>
+    <t xml:space="preserve">Mtch2/Pmaip1/Fbxw7/Trp53/Sh3glb1/Mcl1/Bcl2l11/Flcn/Bid/Sirt1/Bax/Nupr1/Serinc3/Siah1b/Nck1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042267</t>
@@ -2911,7 +2911,7 @@
     <t xml:space="preserve">natural killer cell mediated cytotoxicity</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Arl8b/Ap1g1/Stat5a/Stat5b/Ptpn6/Unc13d/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9/Coro1a</t>
+    <t xml:space="preserve">Coro1a/Lamp1/Vav1/Lgals9/Stat5b/Ptpn6/Unc13d/Ap1g1/Stat5a/Pik3r6/Havcr2/Serpinb9/Arl8b/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1905476</t>
@@ -2923,7 +2923,7 @@
     <t xml:space="preserve">29/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Picalm/Cltc/Numb/Ppp2r5a/Ap2m1/Gopc/Lztfl1/Lypla1/Tgfb1</t>
+    <t xml:space="preserve">Picalm/Tgfb1/Cltc/Dmtn/Lypla1/Ppp2r5a/Numb/Ap2m1/Lztfl1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002757</t>
@@ -2944,7 +2944,7 @@
     <t xml:space="preserve">195/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Hbq1b/Cd36/Ctns/Slc30a10/Snca/Prdx2/Agtr1a/Ddit4/Sesn1/Prex1/Acox1/Pikfyve/Clcn3/Atp7a/Brca1/Tusc2/Sirt1/Ncf2/Hspd1/Prdx4/Itgb2/Sh3pxd2b/Trp53/Prdx6/Plcg2/Vav1/Pmaip1/Hk2/Nrros/Aldh2/Il4/Tgfb1/Tyrobp/P2rx7/Syk</t>
+    <t xml:space="preserve">Prdx2/Hbq1b/Snca/Syk/Tgfb1/Slc30a10/Ctns/Aldh2/Vav1/P2rx7/Plcg2/Ddit4/Cd36/Prex1/Pikfyve/Sesn1/Pmaip1/Acox1/Sh3pxd2b/Trp53/Prdx6/Clcn3/Nrros/Agtr1a/Tyrobp/Il4/Itgb2/Prdx4/Atp7a/Hk2/Ncf2/Tusc2/Sirt1/Hspd1/Brca1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031331</t>
@@ -2953,7 +2953,7 @@
     <t xml:space="preserve">positive regulation of cellular catabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Btg2/Trp53inp2/Scoc/Snca/Dnajb2/Optn/Zswim8/Tnrc6b/Tsc1/Ldlr/Sesn1/Ticam1/Rchy1/Rnf14/Gba/Trp53inp1/Mlst8/Gigyf2/Smcr8/Rnf139/Tbk1/Fbxw7/Flcn/Tob1/Bax/C9orf72/Sesn3/Gabarap/Bcl2l11/Ago2/Bid/Tnrc6c/Pip4k2c/Tut7/Pias1/Sirt1/Clec16a/Sh3glb1/Celf1/Rack1/Psen1/Parn/Cnot7/Mov10/Ulk2/Exosc5/Dtx3l/Pcsk9/Abca2/Dapk1/Acsl5/Sh3d19/Zfp36l1/Il4/Apoe/Trib2/Laptm5/P2rx7</t>
+    <t xml:space="preserve">Laptm5/Snca/Btg2/Tsc1/Trp53inp2/Trib2/Gigyf2/Scoc/Tnrc6b/Zswim8/P2rx7/Abca2/Acsl5/Optn/Apoe/Ldlr/Rnf14/Sesn1/Fbxw7/Tbk1/Gba/Mlst8/Rchy1/Rnf139/Gabarap/Ticam1/Trp53inp1/Il4/Sh3d19/Zfp36l1/Dnajb2/Smcr8/Dapk1/Sh3glb1/Celf1/Tob1/Mov10/Dtx3l/Bcl2l11/Flcn/Psen1/Bid/Sesn3/Exosc5/Ulk2/Sirt1/C9orf72/Pcsk9/Bax/Pias1/Ago2/Tut7/Tnrc6c/Cnot7/Rack1/Clec16a/Parn/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051235</t>
@@ -2965,7 +2965,7 @@
     <t xml:space="preserve">272/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Snca/Insig1/Mcoln1/Abcg1/Stard4/Uvrag/Sqle/Ubash3b/Gba/Ppard/Gpsm2/Ftl1/Hexa/Ap3d1/Bax/Ehd1/Tapt1/Twf1/Asxl2/Sirt1/Psen1/Plin2/Gopc/Pde4d/Rbck1/Fkbp1a/Sp100/Flna/Stat5a/Fkbp1b/Srgn/Stat5b/Ptpn6/Plcg2/B4galnt1/Hk2/Nrros/Gsto1/Lgals9/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Snca/Ptprc/Coro1a/Tgfb1/Abcg1/Gsto1/P2rx7/Mcoln1/Stard4/Plcg2/Lgals9/Apoe/Stat5b/Cd36/Insig1/Ptpn6/Sqle/Flna/Uvrag/Gba/Ehd1/Nrros/Stat5a/Tapt1/Ap3d1/Ppard/Rbck1/Twf1/Gpsm2/B4galnt1/Srgn/Ubash3b/Hk2/Ftl1/Psen1/Hexa/Sirt1/Fkbp1a/Bax/Fkbp1b/Asxl2/Sp100/Gopc/Plin2/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002761</t>
@@ -2977,7 +2977,7 @@
     <t xml:space="preserve">102/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Tal1/Fos/Ubash3b/Fbxw7/Rara/Gnas/Rb1/Gfi1b/Asxl2/Ctnnb1/Hcls1/Prkca/Stat5a/Gata2/Zfp36l1/Il4/Csf1/Fes/Tgfb1/Tyrobp/Cdk6</t>
+    <t xml:space="preserve">Car2/Tgfb1/Cdk6/Tal1/Gnas/Fbxw7/Tyrobp/Stat5a/Il4/Gata2/Fes/Zfp36l1/Csf1/Ctnnb1/Rb1/Hcls1/Prkca/Ubash3b/Fos/Rara/Gfi1b/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050870</t>
@@ -2986,7 +2986,7 @@
     <t xml:space="preserve">positive regulation of T cell activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Cd47/Tfrc/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Phf10/Hspd1/Stat5a/Vsir/Smarcd1/Stat5b/Il27ra/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Tgfb1/Ccdc88b/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Spn/Cd47/Dock8/Cbfb/Lgals9/Stat5b/Dpp4/Smarcd1/Egr3/Zbtb7b/Stat5a/Il4/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Vsir/Hspd1/Rara/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048871</t>
@@ -2998,7 +2998,7 @@
     <t xml:space="preserve">426/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Egr1/Cd36/Aldh1a1/Appl2/Car2/Ampd3/Trp53inp2/Rhag/Map1a/Scd1/Tfrc/Tpp1/Arntl/Ache/Slc11a2/Rhd/Zbtb7b/Ubash3b/Gba/Gigyf2/Clcn3/Acot13/Cln8/Flcn/Bax/Ip6k1/Gnas/Rb1/Slc39a8/Homer1/Sirt1/Adipor2/Acaca/Ctnnb1/Wdr36/Def8/Ldb1/Igf1r/Mllt6/Prkca/Slc22a5/Srf/Ugcg/Mex3c/Hadh/Atp1b2/Gata2/Lrrk1/Snx10/Nr1d2/Tjp3/Rac1/Nr1d1/Rac2/Col11a2/Il4/Csf1/Cxcr4/Tgfb1/Coro1a/P2rx7/Syk/Muc13</t>
+    <t xml:space="preserve">Car2/Egr1/Ampd3/Cldn13/Aldh1a1/Appl2/Syk/Coro1a/Tpp1/Rac2/Tgfb1/Slc11a2/Trp53inp2/Rac1/Gigyf2/Rhag/P2rx7/Muc13/Cxcr4/Cd36/Ugcg/Nr1d2/Mex3c/Hadh/Gnas/Lrrk1/Ache/Gba/Arntl/Map1a/Clcn3/Zbtb7b/Ldb1/Rhd/Col11a2/Mllt6/Scd1/Il4/Gata2/Srf/Csf1/Snx10/Ctnnb1/Tjp3/Rb1/Nr1d1/Atp1b2/Tfrc/Def8/Prkca/Ubash3b/Acaca/Adipor2/Flcn/Acot13/Sirt1/Ip6k1/Bax/Slc22a5/Wdr36/Slc39a8/Homer1/Igf1r/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002244</t>
@@ -3010,7 +3010,7 @@
     <t xml:space="preserve">137/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Cited2/Herc6/Chd2/Zfat/Wdr7/Flcn/Rara/Zbtb24/Fnip1/N4bp2l2/Psen1/Pus7/Srf/Trp53/Terc/Tmem143/Ptpn6/Xrcc5/Gata2/Apobec3/Kcnab2/Tgfb1/Spi1/Ptprc/Myb/Cdk6</t>
+    <t xml:space="preserve">Myb/Ptprc/Tgfb1/Cdk6/Tal1/Kcnab2/Spi1/Cited2/Ptpn6/Xrcc5/Herc6/Chd2/Apobec3/Wdr7/Trp53/Gata2/Srf/Terc/Zfat/Tmem143/Pus7/Flcn/Psen1/Fnip1/Rara/N4bp2l2/Zbtb24</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008064</t>
@@ -3019,7 +3019,7 @@
     <t xml:space="preserve">regulation of actin polymerization or depolymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Ssh2/Mlst8/Plekhg2/Nckap1/Nck1/Rictor/Swap70/Twf1/Arhgap35/Cttn/Was/Flii/Wdr1/Hcls1/Sptan1/Arpc2/Pdxp/Rac1/Capg/Vill/Coro1a</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Vill/Coro1a/Tmod1/Dmtn/Rac1/Capg/Arpc2/Mlst8/Ssh2/Pdxp/Nckap1/Wdr1/Flii/Twf1/Plekhg2/Hcls1/Sptan1/Swap70/Arhgap35/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050851</t>
@@ -3031,7 +3031,7 @@
     <t xml:space="preserve">130/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Btnl10/Prnp/Ermap/Usp9x/Shb/Elf1/Bax/Fcho1/Nras/Psen1/Pde4d/Rbck1/Dgkz/Lpxn/Ptpn6/Plcg2/Ubash3a/Pde4b/Lcp2/Laptm5/Fyb/Btk/Ptprc/Rftn1/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Laptm5/Nfam1/Rftn1/Syk/Ptprc/Prnp/Btnl10/Ermap/Fyb/Plcg2/Ptpn6/Usp9x/Lcp2/Ubash3a/Elf1/Dgkz/Rbck1/Pde4b/Psen1/Bax/Nras/Fcho1/Shb/Pde4d/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051249</t>
@@ -3043,7 +3043,7 @@
     <t xml:space="preserve">394/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Cd47/Prdx2/Tfrc/Prnp/Aplf/Lamp1/Ticam1/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Bid/Phf10/Ctnnb1/Tcf3/Hspd1/Ap1g1/Cd320/Shld2/Stat5a/Samsn1/Vsir/Smarcd1/Stat5b/Ptpn6/Il27ra/Kat2a/Zfp36l1/Cd37/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Il4/Lgals9/Spn/Mmp14/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Tyrobp/Btk/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Tbc1d10c/Nfam1/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Btk/Jak3/Laptm5/Nfam1/Syk/Slc4a1/Myb/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Lamp1/Cd44/Cd47/Dock8/Ripor2/Cbfb/Tbc1d10c/Lgals9/Kat2a/Stat5b/Ptpn6/Dpp4/Ap1g1/Smarcd1/Aplf/Egr3/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Lgals7/Mmp14/Cd37/Pik3r6/Zfp36l1/Ctnnb1/Ap3d1/Il27ra/Havcr2/Tfrc/Tcf3/Vsir/Bid/Samsn1/Hspd1/Rara/Cd320/Shld2/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0090407</t>
@@ -3055,7 +3055,7 @@
     <t xml:space="preserve">461/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Ampd3/Snca/Serac1/Mvd/Pkm/Pcyt1b/Pcx/Uvrag/Isyna1/Ppard/Socs2/Nmnat3/Flcn/Lpcat3/Pmvk/Gcdh/Sord/Serinc5/Ip6k1/Pip4k2c/Sh3glb1/Pi4ka/Ndufa10/Ppip5k2/Parp1/Ttc7b/Scp2/Adss/Prps1/Pik3c2b/Dlat/Dgkz/Dut/Pigt/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Idh2/Umps/Mboat7/Gk/Abca2/Pik3cd/Qprt/Cad/Adssl1/Acsl5/Atic/Ak4/Pfas/Plcg2/Vapa/Papss2/Gmpr/Pgap2/Gart/Npr2/Uprt/Il4/Lpcat2/Tgfb1/Nme4/Dctd/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Uprt/Nme4/Dctd/Serac1/Gart/Abca2/Pfas/Vapa/Plcg2/Acsl5/Pld2/Pdha1/Pcx/Isyna1/Atic/Uvrag/Pgap2/Cad/Pkm/Umps/Socs2/Idh2/Mvd/Lpcat2/Pik3cd/Pcyt1b/Il4/Gk/Adssl1/Npr2/Dgkz/Adsl/Gmpr/Mboat7/Impdh2/Ppard/Dut/Sh3glb1/Ppip5k2/Mthfd1/Papss2/Guk1/Prps1/Lpcat3/Dlat/Pigt/Qprt/Flcn/Serinc5/Gcdh/Ip6k1/Ak4/Ndufa10/Scp2/Aprt/Ttc7b/Adss/Parp1/Pmvk/Sord/Pip4k2c/Nmnat3/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008610</t>
@@ -3067,7 +3067,7 @@
     <t xml:space="preserve">537/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Aldh1a1/Pld2/Dhrs11/Fads3/Mid1ip1/St3gal1/Scd1/Serac1/Insig1/Abcg1/Scd2/Mvd/Pcyt1b/Ldlr/Msmo1/Stard4/Pcx/Uvrag/Lss/Fasn/Sqle/St3gal2/Gba/Mlst8/Isyna1/Ppard/Socs2/Hmgcr/Lpcat3/Pmvk/Gcdh/Sc5d/Serinc5/Ip6k1/Sorbs1/Brca1/Pip4k2c/Cyb5r3/Sirt1/Acaca/Sh3glb1/Pi4ka/Prpf19/Cers5/Ttc7b/Dctn6/Scp2/Pik3c2b/Dgkz/Pigt/St6galnac4/Igf1r/Agps/P2rx1/Mboat7/Ugcg/Prkag2/Tcf7l2/Abca2/Agk/Pik3cd/Acsl5/H6pd/Plcg2/Hsd17b11/Vapa/B4galnt1/Pgap2/Fut4/Nr1d1/Acsbg1/Pla2g1b/Lpcat2/Apoe/Sptssa/P2rx7</t>
+    <t xml:space="preserve">Egr1/Fads3/Aldh1a1/Mid1ip1/Sptssa/Abcg1/St3gal1/Dhrs11/Serac1/P2rx7/Stard4/Abca2/Vapa/Plcg2/Acsl5/Apoe/Ugcg/Pld2/Ldlr/Insig1/Fasn/Sqle/Pcx/Isyna1/Agps/Uvrag/Pgap2/Gba/Mlst8/Msmo1/Agk/Socs2/Fut4/Scd1/Mvd/Lpcat2/Pik3cd/Pcyt1b/Prkag2/Dgkz/Pla2g1b/Acsbg1/H6pd/Hsd17b11/Mboat7/Ppard/Lss/Nr1d1/Sh3glb1/B4galnt1/Hmgcr/Scd2/Lpcat3/Pigt/Cyb5r3/Prpf19/Acaca/Serinc5/St3gal2/Gcdh/Sirt1/Sc5d/Ip6k1/Scp2/Ttc7b/Brca1/St6galnac4/Cers5/Sorbs1/Igf1r/Tcf7l2/P2rx1/Pmvk/Pip4k2c/Dctn6/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016772</t>
@@ -3079,7 +3079,7 @@
     <t xml:space="preserve">753/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Fn3k/Mink1/Wnk4/Map3k1/Uap1l1/Poln/Bmp2k/Mylk2/Kalrn/Pfkfb2/Hipk2/Dmpk/Gdpgp1/Pkm/Pcyt1b/Pim1/Pikfyve/Grk5/Stk38l/Map3k12/Tbk1/Nmnat3/Sgk3/Tent5c/Polg/Pmvk/Stk25/Ppp1r9b/Cdkl5/Uhmk1/Ttbk2/Pkn2/Dyrk1a/Polr2a/N4bp2/Clk3/Selenoo/Polh/Ip6k1/Twf1/Mknk1/Pip4k2c/Tut7/Dbf4/Cdk16/Mknk2/Rps6kb1/Taok1/Cdc42bpa/Pi4ka/Grk6/Ppip5k2/Trim28/Nek4/Nek9/Prps1/Pik3c2b/Dgkz/Pfkfb3/Polr1a/Guk1/Ulk2/Igf1r/Prkca/Rps6ka2/Adck1/Polr3e/Gk/Prkag2/Map4k1/Map3k15/Agk/Oasl1/Pik3cd/Dpagt1/Amhr2/Terc/Dapk1/Cad/Polr1b/Irak1/Khk/Ak4/Lrrk1/Papss2/Hk2/Npr2/Pim3/Mmd/Pgm2/Pik3r6/Fes/Map3k6/Trib2/Nme4/Mst1r/Btk/Cdk6/Jak3/Syk/Eng/Oas2</t>
+    <t xml:space="preserve">Btk/Map3k1/Jak3/Syk/Wnk4/Mink1/Cdk6/Oas2/Trib2/Pfkfb2/Nme4/Fn3k/Bmp2k/Eng/Mst1r/Pikfyve/Mmd/Khk/Dyrk1a/Pim3/Kalrn/Hipk2/Uap1l1/Lrrk1/Irak1/Tbk1/Cad/Stk25/Polr2a/Stk38l/Pkm/Polg/Pkn2/Agk/Polr1b/Pik3cd/Pcyt1b/Gk/Prkag2/Npr2/Dgkz/Map4k1/Map3k6/Ppp1r9b/Pgm2/Poln/Pik3r6/Dpagt1/Fes/Terc/Polr3e/Grk5/Gdpgp1/Dapk1/Uhmk1/Nek9/Amhr2/Dmpk/Twf1/Ppip5k2/Map3k15/Papss2/Polr1a/Mylk2/Guk1/Prps1/Mknk2/Clk3/Prkca/Cdk16/Tent5c/Trim28/Ttbk2/Hk2/Rps6ka2/Selenoo/Ulk2/Polh/Adck1/Ip6k1/Ak4/Taok1/Nek4/Cdkl5/Cdc42bpa/Map3k12/Tut7/Sgk3/Pfkfb3/N4bp2/Igf1r/Dbf4/Grk6/Pmvk/Mknk1/Oasl1/Pim1/Rps6kb1/Pip4k2c/Nmnat3/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030832</t>
@@ -3097,7 +3097,7 @@
     <t xml:space="preserve">regulation of tumor necrosis factor production</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Cd47/Ticam1/Arfgef2/Fzd5/Akap12/Rara/Sirt1/Psen1/Ifngr1/Hspd1/Ifih1/Vsir/Fcgr3/Ptpn6/Il27ra/Plcg2/Havcr2/Il4/Lgals9/Arhgef2/Spn/Tyrobp/Ptprc/Cd84/Syk/Oas2</t>
+    <t xml:space="preserve">Syk/Arhgef2/Ptprc/Spn/Oas2/Cd47/Cd84/Plcg2/Lgals9/Arfgef2/Cd36/Ptpn6/Ticam1/Tyrobp/Fzd5/Il4/Il27ra/Havcr2/Fcgr3/Vsir/Psen1/Ifih1/Sirt1/Hspd1/Ifngr1/Rara/Akap12</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045576</t>
@@ -3109,7 +3109,7 @@
     <t xml:space="preserve">64/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Fcgr3/Ptpn6/Gata2/Unc13d/Cplx2/Gab2/Rac2/Cd48/Il4/Ywhaz/Fes/Lcp2/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Ywhaz/Cd84/Gab2/Pld2/Ptpn6/Unc13d/Cd48/Lcp2/D6Wsu163e/Il4/Gata2/Fes/Fcgr3/Cplx2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043177</t>
@@ -3121,7 +3121,7 @@
     <t xml:space="preserve">110/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Hbq1b/Cd36/Ogfod2/Snca/Sesn1/Pcx/Igf2r/Ppard/Rara/Sesn3/Acaca/Got2/Mat2a/Scp2/Plod3/Cad/Ogfod1/Grin2d/Hlcs/Alox5ap/Slc19a1/Prodh/P4ha3</t>
+    <t xml:space="preserve">Hbq1b/Snca/Ogfod2/Alox5ap/Hlcs/Cd36/Igf2r/Sesn1/P4ha3/Pcx/Prodh/Cad/Slc19a1/Ogfod1/Ppard/Plod3/Got2/Acaca/Grin2d/Sesn3/Rara/Scp2/Mat2a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044703</t>
@@ -3130,7 +3130,7 @@
     <t xml:space="preserve">multi-organism reproductive process</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Abcg2/Cited2/Grn/Kalrn/Arntl/Epor/Epn1/Junb/Ppard/Kpna6/Ash1l/Ago2/Exoc1/Dedd/Trim28/P2rx1/Stat5a/Stat5b/Polr1b/Havcr2/Lgals9/Arhgdib</t>
+    <t xml:space="preserve">Mst1/Grn/Abcg2/Cited2/Lgals9/Arhgdib/Epn1/Stat5b/Kalrn/Arntl/Epor/Kpna6/Polr1b/Stat5a/Ppard/Havcr2/Trim28/Exoc1/Ash1l/Junb/Ago2/P2rx1/Dedd</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0000165</t>
@@ -3142,7 +3142,7 @@
     <t xml:space="preserve">597/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Grap2/Mink1/Wnk4/Map3k1/Slc30a10/Mturn/Prdx2/Mylk2/Hipk2/Dusp6/Gab1/Traf4/Lamtor1/Gba/Arrb1/Epor/Pea15a/Atp6ap2/Fzd5/Map3k12/Akap12/Fbxw7/Hmgcr/Flcn/Cib1/Lamtor3/Stk25/Dag1/Dvl2/Glipr2/Rara/Ash1l/Garem1/Stradb/Rap1b/Avpi1/Nbr1/Bnip2/Taok1/Qars/Psen1/Iqgap1/Dnajc27/Ctnnb1/Phb2/Maged1/Dhx33/Ndst1/Syngap1/Igf1r/Prkca/Traf3/Prmt1/Pik3r5/Map4k1/Map3k15/Irak1/Vangl2/Ptpn6/Plcg2/Spred2/Zfp36l1/Rgs2/Plvap/Rac1/Havcr2/Pik3r6/Ywhaz/Rgs14/Cxcr4/Apoe/Tgfb1/Cd44/Laptm5/Mst1r/Spi1/Ptprc/Dok2/P2rx7/Tbc1d10c/Cd84/Igfbp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Map3k1/Laptm5/Syk/Ptprc/Wnk4/Mink1/Igfbp4/Tgfb1/Ywhaz/Slc30a10/Dok2/Cd44/Rac1/Cd84/Gab1/Spi1/Tbc1d10c/P2rx7/Plcg2/Cxcr4/Apoe/Mst1r/Cd36/Atp6ap2/Ptpn6/Hipk2/Grap2/Irak1/Mturn/Traf4/Fbxw7/Gba/Stk25/Rgs14/Spred2/Dag1/Epor/Traf3/Dusp6/Fzd5/Rgs2/Map4k1/Prmt1/Pik3r6/Zfp36l1/Maged1/Pea15a/Lamtor3/Lamtor1/Ctnnb1/Havcr2/Arrb1/Vangl2/Map3k15/Plvap/Dvl2/Hmgcr/Mylk2/Ndst1/Cib1/Prkca/Dhx33/Flcn/Rap1b/Psen1/Taok1/Ash1l/Iqgap1/Garem1/Rara/Stradb/Avpi1/Syngap1/Map3k12/Phb2/Akap12/Nbr1/Bnip2/Igf1r/Qars/Dnajc27/Pik3r5/Glipr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032103</t>
@@ -3154,7 +3154,7 @@
     <t xml:space="preserve">330/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd47/Snca/Optn/Grn/Adam10/Lamp1/Nupr1/Ldlr/Mospd2/Trim56/Tbk1/Wasl/Rnf185/Hexim1/Swap70/Cttn/Usp15/Nono/Matr3/Hspd1/Ap1g1/Igf1r/Prkca/Megf8/Flna/Stat5a/Fkbp1b/Oasl1/Stat5b/Fcgr3/Xrcc5/Pdcd4/Plcg2/Vav1/Ano6/Cadm1/Alox5ap/Rac1/Ripor2/Rac2/Havcr2/Il4/Csf1/Cxcr4/Lgals9/Tgfb1/Spi1/Tyrobp/Lgals1/Dpp4/Il1rl1/Syk</t>
+    <t xml:space="preserve">Lgals1/Snca/Il1rl1/Syk/Ano6/Rac2/Tgfb1/Grn/Lamp1/Rac1/Cd47/Ripor2/Spi1/Vav1/Alox5ap/Plcg2/Lgals9/Optn/Cxcr4/Stat5b/Adam10/Ldlr/Dpp4/Xrcc5/Megf8/Flna/Tbk1/Ap1g1/Trim56/Tyrobp/Stat5a/Il4/Wasl/Csf1/Nono/Mospd2/Havcr2/Matr3/Fcgr3/Hexim1/Prkca/Usp15/Swap70/Cadm1/Pdcd4/Hspd1/Nupr1/Rnf185/Fkbp1b/Igf1r/Cttn/Oasl1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030042</t>
@@ -3172,7 +3172,7 @@
     <t xml:space="preserve">190/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Tfrc/Prnp/Ticam1/Zbtb7b/Nck1/Bid/Ctnnb1/Tcf3/Cd320/Stat5a/Vsir/Stat5b/Ptpn6/Il27ra/Cd37/Ripor2/Rac2/Havcr2/Il4/Lgals9/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Tyrobp/Btk/Ptprc/Coro1a/Jak3/Syk</t>
+    <t xml:space="preserve">Spta1/Btk/Jak3/Laptm5/Syk/Slc4a1/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Ripor2/Lgals9/Stat5b/Ptpn6/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Lgals7/Cd37/Ctnnb1/Il27ra/Havcr2/Tfrc/Tcf3/Vsir/Bid/Cd320/Nck1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009066</t>
@@ -3184,7 +3184,7 @@
     <t xml:space="preserve">25/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Got1/Got2/Adss/Enoph1/Mtap/Plod3/Mthfd1/Adssl1/Sdsl</t>
+    <t xml:space="preserve">Sdsl/Adssl1/Plod3/Mthfd1/Got2/Mtap/Got1/Enoph1/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031400</t>
@@ -3196,7 +3196,7 @@
     <t xml:space="preserve">447/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Wnk4/Dmtn/Snca/Prkar2b/Dnajb2/Prnp/Dusp6/Ddit4/Snx25/Ubash3b/Ppp1r15b/Gba/Arrb1/Smcr8/Cdkn2c/Tbc1d24/Fbxo5/Dcun1d3/Hmgcr/Dnajc10/Flcn/Ggnbp2/Cib1/Shb/Ppp1r9b/Bax/C9orf72/Nck1/Kdm4c/Brca1/Hexim1/Swap70/Rb1/Gfi1b/Trip12/Nxn/Sirt1/Qars/Rack1/Psen1/Ctnnb1/Lrp5/Gtpbp4/Pde4d/Cbl/Pwp1/Crtap/Mllt6/Prkca/Dtx3l/Samsn1/Fkbp1b/Prkag2/Dnmt3b/Ptpn6/Lrrk1/Spred2/Rgs2/Prr7/Tfap4/Rgs14/Apoe/Tgfb1/Spi1/Ptprc/Eng</t>
+    <t xml:space="preserve">Prkar2b/Snca/Ptprc/Wnk4/Prnp/Tgfb1/Dmtn/Spi1/Eng/Snx25/Ddit4/Apoe/Tbc1d24/Ptpn6/Lrrk1/Tfap4/Gba/Dnmt3b/Rgs14/Cdkn2c/Spred2/Dnajc10/Dusp6/Mllt6/Rgs2/Prkag2/Ppp1r15b/Ppp1r9b/Ggnbp2/Ctnnb1/Dnajb2/Prr7/Smcr8/Rb1/Arrb1/Fbxo5/Hmgcr/Pwp1/Trip12/Hexim1/Dtx3l/Lrp5/Cib1/Prkca/Ubash3b/Swap70/Flcn/Psen1/Sirt1/Kdm4c/C9orf72/Samsn1/Bax/Brca1/Crtap/Gtpbp4/Gfi1b/Dcun1d3/Fkbp1b/Nck1/Nxn/Cbl/Qars/Rack1/Shb/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044283</t>
@@ -3205,7 +3205,7 @@
     <t xml:space="preserve">small molecule biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Aldh1a1/Fads3/Mid1ip1/Mgst3/Snca/Scd1/Insig1/Abcg1/Scd2/Mvd/Pkm/Pycr1/Msmo1/Coq10a/Stard4/Pcx/Lss/Fasn/Gba/Gnpda1/Isyna1/Hmgcr/Lpcat3/Pmvk/Adal/Sord/Sc5d/Ip6k1/Brca1/Cyb5r3/Sirt1/Acaca/Gls/Pycr2/Ppip5k2/Got1/Got2/Gpi1/Scp2/Prps1/Enoph1/Mtap/Aprt/Plod3/Ilvbl/Mthfd1/Prkag2/Tcf7l2/Abca2/Mthfd1l/Cad/H6pd/Kat2a/Plcg2/Sdsl/Alox5ap/G6pc3/Nr1d1/Pgm2/Acsbg1/Gsto1/Pla2g1b/Apoe/Sptssa/Syk</t>
+    <t xml:space="preserve">Egr1/Fads3/Aldh1a1/Snca/Mgst3/Syk/Mid1ip1/Sptssa/Abcg1/Gsto1/Stard4/Abca2/Alox5ap/Plcg2/Kat2a/Apoe/Insig1/Fasn/Sdsl/Pcx/Isyna1/Gba/Cad/Pkm/Msmo1/G6pc3/Scd1/Mvd/Coq10a/Prkag2/Pla2g1b/Acsbg1/Gnpda1/Pgm2/H6pd/Plod3/Lss/Nr1d1/Ppip5k2/Mthfd1/Got2/Hmgcr/Mthfd1l/Scd2/Prps1/Lpcat3/Cyb5r3/Acaca/Adal/Sirt1/Sc5d/Ip6k1/Pycr1/Scp2/Aprt/Brca1/Mtap/Got1/Enoph1/Tcf7l2/Ilvbl/Pmvk/Sord/Pycr2/Gls/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031668</t>
@@ -3220,7 +3220,7 @@
     <t xml:space="preserve">206/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Tfrc/Rragc/Tsc1/Fos/Sesn1/Map1lc3b/Pim1/Gba/Mlst8/Bhlha15/Flcn/Sesn3/Xpr1/Gabarap/Rictor/Mtmr3/Ncoa1/Arhgap35/Sirt1/Fnip1/Clec16a/Sh3glb1/Plin2/Pik3c2b/Srf/Pcsk9/Mybbp1a/Prkag2/Tcf7l2/Ripor1/Trp53/Pmaip1/Fes/Ptprc/P2rx7</t>
+    <t xml:space="preserve">Ptprc/Rragc/Tsc1/Cpeb4/P2rx7/Ripor1/Map1lc3b/Sesn1/Xpr1/Pmaip1/Gba/Mlst8/Trp53/Gabarap/Mtmr3/Prkag2/Srf/Fes/Mybbp1a/Sh3glb1/Tfrc/Flcn/Bhlha15/Sesn3/Sirt1/Fos/Ncoa1/Fnip1/Pcsk9/Arhgap35/Tcf7l2/Clec16a/Pim1/Plin2/Pik3c2b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0120035</t>
@@ -3232,7 +3232,7 @@
     <t xml:space="preserve">600/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Dmtn/Sema4b/Grn/Prnp/Kalrn/Neu1/Washc5/Ache/Tsc1/Picalm/Adam10/Plek2/Mylip/Numb/Kel/Dpysl2/Rab3ip/Epor/Trak2/Tbc1d24/Wasl/Serpini1/Kif13b/Atp7a/Xk/Cib1/Stk25/Pias2/Dip2b/Ppp2r5b/Cdkl5/Ehd1/Nckap1/Ttbk2/Camsap2/Golga4/Vps35/Nck1/Acap3/Tapt1/Twf1/Arhgap35/Homer1/Sirt1/Fbxo38/Sh3glb1/Snx3/Psen1/Iqgap1/Rpl4/Actr2/Was/Nedd4/Itm2c/Stau2/Def8/Syngap1/Ulk2/Cul7/Igf1r/Megf8/Flna/Srf/Ptpn9/Fkbp1b/Akap5/Arpc2/Sema4a/Atp1b2/Ankrd27/Rgs2/Rac1/Rcc2/Plxnc1/Ripor2/Rac2/Vim/Ptprs/Fes/Apoe/Cd44/Lgals1/P2rx7</t>
+    <t xml:space="preserve">Lgals1/Cobl/Picalm/Ptprs/Prnp/Rac2/Grn/Washc5/Ankrd27/Tsc1/Dmtn/Cd44/Rac1/Ripor2/Rcc2/P2rx7/Vim/Arpc2/Apoe/Adam10/Tbc1d24/Kalrn/Ache/Megf8/Flna/Dip2b/Ehd1/Neu1/Stk25/Dpysl2/Epor/Numb/Pias2/Sema4b/Rab3ip/Xk/Tapt1/Rgs2/Cul7/Wasl/Sema4a/Srf/Fes/Ptpn9/Mylip/Nckap1/Kel/Vps35/Sh3glb1/Twf1/Nedd4/Camsap2/Atp1b2/Plxnc1/Trak2/Def8/Cib1/Atp7a/Ttbk2/Psen1/Kif13b/Ulk2/Plek2/Fbxo38/Sirt1/Actr2/Iqgap1/Golga4/Cdkl5/Rpl4/Serpini1/Stau2/Syngap1/Itm2c/Homer1/Arhgap35/Fkbp1b/Igf1r/Nck1/Ppp2r5b/Akap5/Acap3/Snx3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0000221</t>
@@ -3241,7 +3241,7 @@
     <t xml:space="preserve">vacuolar proton-transporting V-type ATPase, V1 domain</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v1c1/Atp6v1e1/Atp6v1a/Atp6v1b2/Atp6v1g1</t>
+    <t xml:space="preserve">Atp6v1c1/Atp6v1e1/Atp6v1b2/Atp6v1a/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043320</t>
@@ -3250,7 +3250,7 @@
     <t xml:space="preserve">natural killer cell degranulation</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Ap1g1/Unc13d/Lgals9/Coro1a</t>
+    <t xml:space="preserve">Coro1a/Lamp1/Lgals9/Unc13d/Ap1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097292</t>
@@ -3259,7 +3259,7 @@
     <t xml:space="preserve">XMP metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Impdh2/Adsl/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">Gart/Pfas/Atic/Adsl/Impdh2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097293</t>
@@ -3283,7 +3283,7 @@
     <t xml:space="preserve">549/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slfn14/Egr1/Ell2/Mrm1/Zswim8/Fos/Isg20/Pop5/Zfp143/Trmt12/Utp14b/Nr2f1/Sars/Ppard/Rara/Ago2/Trmt1l/Dedd/Tut7/Helq/Ints8/Ctcf/Qars/Zc3h7b/Vars2/Ddx27/Parn/Elp3/Rpl35/Ddx18/Farsb/Snu13/Pa2g4/Ddx21/Ddx49/Gtpbp4/Pus7/Rcl1/Ebna1bp2/Wdr36/Rrp1b/Urb1/Pwp1/Polr1a/Tcof1/Tyw1/Trmt2b/Exosc1/Lyar/Wdr43/Tars2/Exosc5/Srf/Spin1/Tdrd9/Tarbp1/Wdr4/Mdn1/Heatr1/Nat10/Naf1/Rrp12/Rpl10a/Mettl1/Nol6/Trp53/Polr1b/Wdr46/Gata2/Tfb2m/Trub1/Rrp9/Tsen15/Npm3/Ago4/2210016F16Rik/Tgfb1/Spi1</t>
+    <t xml:space="preserve">Ell2/Egr1/Tgfb1/Slfn14/Spi1/Zswim8/Npm3/Tars2/Ago4/Trub1/Nat10/Rpl10a/Tsen15/Tcof1/Rrp9/Wdr46/Trp53/Utp14b/Zfp143/Spin1/Trmt2b/Mrm1/Sars/Nol6/Polr1b/Gata2/Pop5/Srf/Naf1/Tfb2m/Isg20/2210016F16Rik/Ppard/Rrp12/Heatr1/Tdrd9/Mdn1/Wdr4/Pwp1/Polr1a/Pus7/Urb1/Tyw1/Ints8/Wdr43/Exosc5/Ddx18/Fos/Rcl1/Exosc1/Nr2f1/Rara/Tarbp1/Mettl1/Trmt12/Snu13/Wdr36/Lyar/Farsb/Trmt1l/Ago2/Tut7/Gtpbp4/Vars2/Ctcf/Ebna1bp2/Ddx21/Helq/Zc3h7b/Ddx27/Ddx49/Qars/Dedd/Parn/Rpl35/Pa2g4/Elp3/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002279</t>
@@ -3295,7 +3295,7 @@
     <t xml:space="preserve">13/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Ptpn6/Gata2/Unc13d/Cplx2/Gab2/Rac2/Il4/Ywhaz/Fes/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Ywhaz/Cd84/Gab2/Pld2/Ptpn6/Unc13d/D6Wsu163e/Il4/Gata2/Fes/Cplx2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043068</t>
@@ -3307,7 +3307,7 @@
     <t xml:space="preserve">516/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Aldh1a1/Map3k1/Optn/Ctsd/Grn/Prnp/Dusp6/Adam10/Nupr1/Trp53inp1/Arrb1/Pea15a/Igf2r/Rbm5/Akap12/Fbxw7/Dcun1d3/Hmgcr/Flcn/Mtch2/Bax/Nck1/Bcl2l11/Ccar1/Bid/Mcl1/Ncoa1/Siah1b/Sirt1/Sav1/Fnip1/Sh3glb1/Rack1/Psen1/Serinc3/Ctnnb1/Ncf2/Trim35/Maged1/Scp2/Rbck1/Itm2c/Rrp1b/Hspd1/Rps6ka2/Calhm2/Tnfrsf26/Pcsk9/Mybbp1a/Tcf7l2/Pik3cd/Trp53/Dapk1/Ppp2r1a/Pdcd4/Pmaip1/Ano6/Zfas1/Casp7/Irf5/Prr7/Tfap4/Pla2g1b/Phlda2/Tgfb1/Cd44/Laptm5/Tyrobp/Ptprc/Jak3/Lgals1/P2rx7/Syk</t>
+    <t xml:space="preserve">Lgals1/Egr1/Map3k1/Jak3/Ctsd/Laptm5/Aldh1a1/Syk/Ptprc/Ano6/Prnp/Tgfb1/Casp7/Grn/Cd44/Ppp2r1a/P2rx7/Optn/Adam10/Igf2r/Mtch2/Tfap4/Pmaip1/Fbxw7/Trp53/Phlda2/Rbm5/Irf5/Zfas1/Dusp6/Trp53inp1/Tyrobp/Pik3cd/Pla2g1b/Maged1/Pea15a/Ctnnb1/Mybbp1a/Prr7/Dapk1/Rbck1/Sh3glb1/Arrb1/Mcl1/Ccar1/Hmgcr/Bcl2l11/Rps6ka2/Flcn/Pdcd4/Ncf2/Psen1/Bid/Sirt1/Ncoa1/Sav1/Hspd1/Fnip1/Pcsk9/Bax/Nupr1/Scp2/Serinc3/Trim35/Itm2c/Dcun1d3/Akap12/Siah1b/Calhm2/Nck1/Tcf7l2/Tnfrsf26/Rack1/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005096</t>
@@ -3319,7 +3319,7 @@
     <t xml:space="preserve">207/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Arhgap23/Agfg2/Als2/Asap3/Arhgap12/Arrb1/Rabep1/Tbc1d24/Arhgef12/Arhgap15/Flcn/Elmod2/Myo9a/Acap3/Rabgap1/Arhgap35/Smap1/Usp6nl/Iqgap1/Syngap1/Arhgap9/Arhgef1/Ankrd27/Rgs2/Gmip/Arhgdig/Rgs1/Rgs14/Dock2/Adap1/Rgs18/Arhgap27/Tbc1d10c/Arap3/Arhgdib/Rin3</t>
+    <t xml:space="preserve">Arap3/Dock2/Arhgap23/Ankrd27/Arhgef1/Arhgap27/Tbc1d10c/Rin3/Agfg2/Arhgdib/Als2/Rabep1/Tbc1d24/Gmip/Rgs18/Arhgdig/Adap1/Rgs14/Rabgap1/Arhgef12/Rgs2/Rgs1/Arhgap12/Arrb1/Asap3/Smap1/Arhgap9/Flcn/Iqgap1/Syngap1/Arhgap15/Arhgap35/Elmod2/Acap3/Myo9a/Usp6nl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006531</t>
@@ -3331,7 +3331,7 @@
     <t xml:space="preserve">4/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Got1/Got2/Adss/Adssl1</t>
+    <t xml:space="preserve">Adssl1/Got2/Got1/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0036446</t>
@@ -3340,7 +3340,7 @@
     <t xml:space="preserve">myofibroblast differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp1/Rb1/Parp1/Pdcd4</t>
+    <t xml:space="preserve">Trp53inp1/Rb1/Pdcd4/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097422</t>
@@ -3349,7 +3349,7 @@
     <t xml:space="preserve">tubular endosome</t>
   </si>
   <si>
-    <t xml:space="preserve">Vps26a/Vps35/Snx5/Ankrd27</t>
+    <t xml:space="preserve">Vps26a/Ankrd27/Vps35/Snx5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904760</t>
@@ -3367,7 +3367,7 @@
     <t xml:space="preserve">399/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cldn13/Cgn/Wnk4/Mpp2/Gab1/Traf4/Ubn1/Micall2/Frmd6/Pikfyve/Actn1/Fzd5/Flcn/Usp53/Dag1/Mpp1/Pkn2/Rap2b/Nck1/Ash1l/Ddx6/Sorbs1/Rap1b/Twf1/Vcl/Sav1/Cdc42bpa/Iqgap1/Ctnnb1/Was/Wdr1/Ptpru/Sptan1/Prkca/Flna/Rap2c/Lin7c/Pdxp/Vangl2/Ptpn6/Pdlim2/Vapa/Vav1/Rangrf/Cadm1/Arhgef6/Vamp5/Des/Tjp3/Itga5/Cxcr4/Arhgef2/Lcp2/Def6/Plxdc1/Coro1a/Dpp4/P2rx7/Cd53</t>
+    <t xml:space="preserve">Cldn13/Arhgef2/Slc4a1/Wnk4/Coro1a/Ubn1/Cgn/Def6/Gab1/Vav1/Actn1/Cd53/P2rx7/Micall2/Vapa/Mpp2/Cxcr4/Vamp5/Lin7c/Pikfyve/Ptpn6/Dpp4/Itga5/Flna/Frmd6/Des/Traf4/Arhgef6/Rap2b/Dag1/Lcp2/Plxdc1/Ddx6/Pdxp/Pkn2/Rangrf/Fzd5/Rap2c/Ctnnb1/Wdr1/Tjp3/Twf1/Vangl2/Sptan1/Mpp1/Usp53/Prkca/Cadm1/Flcn/Rap1b/Pdlim2/Ash1l/Iqgap1/Sav1/Cdc42bpa/Sorbs1/Ptpru/Nck1/Vcl/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044706</t>
@@ -3376,7 +3376,7 @@
     <t xml:space="preserve">multi-multicellular organism process</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Abcg2/Cited2/Grn/Kalrn/Arntl/Epor/Epn1/Junb/Ppard/Kpna6/Ash1l/Ago2/Exoc1/Dedd/Trim28/P2rx1/Stat5a/Sh3pxd2b/Stat5b/Polr1b/Havcr2/Lgals9/Arhgdib</t>
+    <t xml:space="preserve">Mst1/Grn/Abcg2/Cited2/Lgals9/Arhgdib/Epn1/Stat5b/Kalrn/Arntl/Sh3pxd2b/Epor/Kpna6/Polr1b/Stat5a/Ppard/Havcr2/Trim28/Exoc1/Ash1l/Junb/Ago2/P2rx1/Dedd</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0106380</t>
@@ -3388,7 +3388,7 @@
     <t xml:space="preserve">16/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Impdh2/Aprt/Adsl/Adssl1/Gmpr</t>
+    <t xml:space="preserve">Ampd3/Adssl1/Adsl/Gmpr/Impdh2/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051251</t>
@@ -3400,7 +3400,7 @@
     <t xml:space="preserve">254/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Cd47/Tfrc/Lamp1/Ticam1/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Phf10/Tcf3/Hspd1/Ap1g1/Cd320/Shld2/Stat5a/Vsir/Smarcd1/Stat5b/Il27ra/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Mmp14/Tgfb1/Ccdc88b/Tyrobp/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Spn/Lamp1/Cd47/Dock8/Cbfb/Lgals9/Stat5b/Dpp4/Ap1g1/Smarcd1/Egr3/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Mmp14/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Tcf3/Vsir/Hspd1/Rara/Cd320/Shld2/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902882</t>
@@ -3409,7 +3409,7 @@
     <t xml:space="preserve">regulation of response to oxidative stress</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Glrx/Tsc1/Pycr1/Sesn1/Epor/Tbc1d24/Fbxw7/Rnf146/Sesn3/Mcl1/Sirt1/Rack1/Parp1/Nono/Ctnnb1/Lancl1/Fut8/Trp53</t>
+    <t xml:space="preserve">Tsc1/Glrx/Cd36/Tbc1d24/Sesn1/Fbxw7/Trp53/Fut8/Epor/Rnf146/Nono/Ctnnb1/Mcl1/Lancl1/Sesn3/Sirt1/Pycr1/Parp1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030225</t>
@@ -3418,7 +3418,7 @@
     <t xml:space="preserve">macrophage differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Gba/Rb1/Asxl2/Sirt1/Hcls1/Prkca/Gata2/Nrros/Csf1/Tgfb1/Spi1</t>
+    <t xml:space="preserve">Tgfb1/Spi1/Gba/Nrros/Gata2/Csf1/Rb1/Hcls1/Prkca/Sirt1/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051693</t>
@@ -3427,7 +3427,7 @@
     <t xml:space="preserve">actin filament capping</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Add2/Dmtn/Sptb/Twf1/Flii/Sptan1/Arpc2/Capg/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Vill/Tmod1/Dmtn/Capg/Arpc2/Flii/Twf1/Sptan1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005770</t>
@@ -3439,7 +3439,7 @@
     <t xml:space="preserve">200/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Abcb6/Wdr81/Pip4p1/Grn/Mcoln1/Atg9a/Slc11a2/Vps11/Lamp1/Ldlr/Uvrag/Pikfyve/Lamtor1/Zfyve26/Igf2r/Clcn3/Vps33a/Atp7a/Lamtor3/Chmp3/Exoc8/Vps35/Rmc1/Nbr1/Clec16a/Ifitm2/Pcsk9/Cst7/Ankrd13b/Tmem230/Ankrd27/Vamp5/Cxcr4/Apoe</t>
+    <t xml:space="preserve">Abcb6/Slc11a2/Ctns/Grn/Ankrd27/Lamp1/Pip4p1/Mcoln1/Vps11/Wdr81/Cxcr4/Vamp5/Apoe/Igf2r/Ldlr/Pikfyve/Atg9a/Uvrag/Clcn3/Ankrd13b/Zfyve26/Lamtor3/Lamtor1/Vps33a/Vps35/Chmp3/Exoc8/Atp7a/Tmem230/Rmc1/Ifitm2/Pcsk9/Nbr1/Cst7/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042326</t>
@@ -3454,7 +3454,7 @@
     <t xml:space="preserve">326/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Wnk4/Dmtn/Snca/Prkar2b/Prnp/Dusp6/Ddit4/Nupr1/Snx25/Ubash3b/Ppp1r15b/Gba/Arrb1/Ppp2r5a/Smcr8/Cdkn2c/Hmgcr/Dnajc10/Ggnbp2/Cib1/Mtch2/Shb/Bax/C9orf72/Nck1/Hexim1/Rb1/Pip4k2c/Sirt1/Qars/Rack1/Psen1/Lrp5/Pde4d/Cbl/Pwp1/Prkca/Samsn1/Prkag2/Ptpn6/Lrrk1/Spred2/Rgs2/Tfap4/Rgs14/Apoe/Tgfb1/Ptprc/Pik3ip1/Eng</t>
+    <t xml:space="preserve">Prkar2b/Snca/Slc4a1/Ptprc/Wnk4/Prnp/Tgfb1/Dmtn/Ppp2r5a/Eng/Pik3ip1/Snx25/Ddit4/Apoe/Ptpn6/Lrrk1/Mtch2/Tfap4/Gba/Rgs14/Cdkn2c/Spred2/Dnajc10/Dusp6/Rgs2/Prkag2/Ppp1r15b/Ggnbp2/Smcr8/Rb1/Arrb1/Hmgcr/Pwp1/Hexim1/Lrp5/Cib1/Prkca/Ubash3b/Psen1/Sirt1/C9orf72/Samsn1/Bax/Nupr1/Nck1/Cbl/Qars/Rack1/Shb/Pip4k2c/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903555</t>
@@ -3475,7 +3475,7 @@
     <t xml:space="preserve">99/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Ctsd/Atg9a/Nupr1/Map1lc3b/Pikfyve/Rab43/Trp53inp1/Smcr8/Tmem41b/Atg2b/C9orf72/Gabarap/Mtmr3/Atg4d/Trappc8/Pacs2/Pip4k2c/Sh3glb1/Psen1/Ulk2</t>
+    <t xml:space="preserve">Ctsd/Trp53inp2/Map1lc3b/Pikfyve/Atg9a/Rab43/Pacs2/Atg2b/Gabarap/Trp53inp1/Mtmr3/Tmem41b/Smcr8/Trappc8/Sh3glb1/Psen1/Ulk2/C9orf72/Nupr1/Atg4d/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032006</t>
@@ -3484,7 +3484,7 @@
     <t xml:space="preserve">regulation of TOR signaling</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Pip4p1/Arntl/Rragc/Ddit4/Tsc1/Sesn1/Lamtor1/Gba/Mlst8/Smcr8/Flcn/Usp9x/Lamtor3/C9orf72/Sesn3/Rictor/Tti1/Sirt1/Fnip1/Clec16a</t>
+    <t xml:space="preserve">Rragc/Ctns/Tsc1/Pip4p1/Ddit4/Sesn1/Gba/Arntl/Mlst8/Usp9x/Lamtor3/Lamtor1/Smcr8/Flcn/Sesn3/Sirt1/C9orf72/Tti1/Fnip1/Clec16a/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006687</t>
@@ -3493,7 +3493,7 @@
     <t xml:space="preserve">glycosphingolipid metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Neu1/St3gal2/Gba/Hexa/Bax/St6galnac4/Gla/Ugcg/Abca2/B4galnt1/Fut4</t>
+    <t xml:space="preserve">St3gal1/Abca2/Ugcg/Gba/Neu1/Fut4/B4galnt1/Gla/Hexa/St3gal2/Bax/St6galnac4</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030835</t>
@@ -3502,7 +3502,7 @@
     <t xml:space="preserve">negative regulation of actin filament depolymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Add2/Dmtn/Sptb/Swap70/Twf1/Flii/Sptan1/Arpc2/Capg/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Vill/Tmod1/Dmtn/Capg/Arpc2/Flii/Twf1/Sptan1/Swap70</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043094</t>
@@ -3511,7 +3511,7 @@
     <t xml:space="preserve">cellular metabolic compound salvage</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Adss/Impdh2/Enoph1/Mtap/Aprt/Adsl/Adssl1/Gmpr/Pgm2</t>
+    <t xml:space="preserve">Ampd3/Adssl1/Adsl/Pgm2/Gmpr/Impdh2/Aprt/Mtap/Enoph1/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043304</t>
@@ -3520,7 +3520,7 @@
     <t xml:space="preserve">regulation of mast cell degranulation</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Gata2/Unc13d/Gab2/Rac2/Il4/Fes/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Cd84/Gab2/Pld2/Unc13d/D6Wsu163e/Il4/Gata2/Fes</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010876</t>
@@ -3532,7 +3532,7 @@
     <t xml:space="preserve">352/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Wnk4/Abcg2/Slc43a3/Agtr1a/Serac1/Abcg1/Atg9a/Ldlr/Stard4/Sqle/Lamtor1/Gba/Ppard/Hexa/Lpcat3/Tex2/Tmem41b/Atg2b/Ehd1/Asxl2/Arl8b/Sirt1/Rps6kb1/Vps4b/Plin2/Got2/Scp2/Esyt1/Mfsd2b/Pdzd8/Sar1b/Stat5a/Pcsk9/Ugcg/Pla2g12a/Abca2/Stat5b/Irak1/Acsl5/Prelid2/Vapa/B4galnt1/Surf4/Ano6/Rft1/Pitpnm2/Spns3/Pla2g1b/Apoe/Nme4/P2rx7/Syk</t>
+    <t xml:space="preserve">Syk/Slc43a3/Slc4a1/Wnk4/Ano6/Abcg2/Abcg1/Surf4/Nme4/Pitpnm2/Serac1/P2rx7/Stard4/Abca2/Vapa/Acsl5/Apoe/Stat5b/Cd36/Ugcg/Ldlr/Sqle/Irak1/Atg9a/Gba/Ehd1/Atg2b/Pdzd8/Rft1/Agtr1a/Stat5a/Pla2g12a/Pla2g1b/Tex2/Lamtor1/Tmem41b/Ppard/Spns3/Got2/B4galnt1/Esyt1/Lpcat3/Sar1b/Arl8b/Hexa/Sirt1/Prelid2/Pcsk9/Scp2/Asxl2/Vps4b/Rps6kb1/Plin2/Mfsd2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043524</t>
@@ -3544,7 +3544,7 @@
     <t xml:space="preserve">149/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Btg2/Slc30a10/Snca/Prdx2/Itsn1/Optn/Grn/Hipk2/Gba/Arrb1/Epor/Map3k12/Cln8/Atp7a/Bax/Birc5/Sirt1/Psen1/Nono/Gpi1/Hsp90ab1/Set/Syngap1/Hspd1/Il27ra/Apoe/Coro1a</t>
+    <t xml:space="preserve">Prdx2/Snca/Btg2/Coro1a/Slc30a10/Grn/Cpeb4/Itsn1/Optn/Apoe/Hipk2/Gba/Epor/Nono/Il27ra/Arrb1/Hsp90ab1/Atp7a/Birc5/Psen1/Set/Sirt1/Hspd1/Bax/Syngap1/Map3k12/Cln8/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098754</t>
@@ -3556,7 +3556,7 @@
     <t xml:space="preserve">48/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Aldh1a1/Abcg2/Slc30a10/Abcb6/Prdx2/Sesn1/Pim1/Atp7a/Selenot/Prdx6/Slc22a18/Aldh2</t>
+    <t xml:space="preserve">Prdx2/Aldh1a1/Abcb6/Slc30a10/Abcg2/Aldh2/Cd36/Sesn1/Prdx6/Selenot/Atp7a/Slc22a18/Pim1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032970</t>
@@ -3568,7 +3568,7 @@
     <t xml:space="preserve">336/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Mylk2/Washc2/Washc5/Tsc1/Asap3/Frmd6/Rhof/Ssh2/Mlst8/Wasl/Plekhg2/C9orf72/Nckap1/Nck1/Rictor/Swap70/Twf1/Washc4/Arhgap35/Cttn/Taok1/Iqgap1/Was/Flii/Pde4d/Wdr1/Stau2/Hcls1/Sptan1/Flna/Sh3pxd2b/Arpc2/Pdxp/Vangl2/Rangrf/Pde4b/Rac1/Rac2/Capg/Fes/Tgfb1/Vill/Coro1a/Arhgef18/Arhgdib</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Vill/Coro1a/Tmod1/Rac2/Tgfb1/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Arhgdib/Arpc2/Arhgef18/Flna/Frmd6/Mlst8/Sh3pxd2b/Ssh2/Pdxp/Rangrf/Wasl/Fes/Nckap1/Wdr1/Flii/Twf1/Vangl2/Plekhg2/Hcls1/Asap3/Sptan1/Mylk2/Pde4b/Swap70/Washc4/C9orf72/Taok1/Iqgap1/Rhof/Stau2/Arhgap35/Nck1/Cttn/Pde4d/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050780</t>
@@ -3577,7 +3577,7 @@
     <t xml:space="preserve">dopamine receptor binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Ppp1r9b/Vps35/Dnajc14/Gnas/Gna13/Snx5/Atp1a3</t>
+    <t xml:space="preserve">Gnas/Agtr1a/Gna13/Ppp1r9b/Vps35/Dnajc14/Snx5/Atp1a3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016049</t>
@@ -3589,7 +3589,7 @@
     <t xml:space="preserve">427/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Extl3/Dnajb2/Dcbld2/Sema4b/Picalm/Adam10/Sesn1/Dpysl2/Lamtor1/Mlst8/Dact3/Cdkn2c/Cgrrf1/Ppard/Socs2/Dcun1d3/Flcn/Usp9x/Cib1/Ppp1r9b/Dip2b/C9orf72/Cdkl5/Golga4/Rictor/Rb1/Cpne1/Vcl/Cttn/Sirt1/Adipor2/Itsn2/Sh3glb1/Usp47/Rack1/Iqgap1/Rpl4/Ctnnb1/Sec61a1/Ddx49/Hsp90ab1/Wdr36/Eif4g2/Jade2/Ulk2/Megf8/Srf/Mex3c/Unc13a/Jade1/Trp53/Sema4a/Cadm1/Rgs2/Dnajc2/Ptprs/Cxcr4/Mmp14/Apoe/Tgfb1/Cd44/Igfbp4</t>
+    <t xml:space="preserve">Cobl/Picalm/Ptprs/Extl3/Igfbp4/Tgfb1/Dcbld2/Dnajc2/Cd44/Cxcr4/Apoe/Jade1/Adam10/Mex3c/Sesn1/Megf8/Dip2b/Mlst8/Trp53/Cdkn2c/Usp9x/Dpysl2/Sema4b/Socs2/Rgs2/Mmp14/Sema4a/Ppp1r9b/Srf/Lamtor1/Ctnnb1/Dnajb2/Ppard/Rb1/Sh3glb1/Cgrrf1/Cib1/Hsp90ab1/Adipor2/Cadm1/Flcn/Dact3/Cpne1/Ulk2/Sec61a1/Sirt1/C9orf72/Iqgap1/Golga4/Eif4g2/Cdkl5/Rpl4/Wdr36/Dcun1d3/Unc13a/Usp47/Jade2/Cttn/Ddx49/Rack1/Vcl/Rictor/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007519</t>
@@ -3598,7 +3598,7 @@
     <t xml:space="preserve">skeletal muscle tissue development</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Btg2/Egr2/Cited2/Hlf/Gpcpd1/Mylk2/Arntl/Mylpf/Fos/Nupr1/Kel/Hdac5/Hmgcr/Xk/Rb1/Med20/Homer1/Rps6kb1/Nras/Ctnnb1/Tcf7l2/Popdc2/Nr1d2/Vamp5/Ripor2/Tgfb1</t>
+    <t xml:space="preserve">Egr1/Btg2/Tgfb1/Ripor2/Cited2/Hlf/Vamp5/Nr1d2/Arntl/Egr2/Xk/Ctnnb1/Hdac5/Kel/Rb1/Gpcpd1/Hmgcr/Mylpf/Mylk2/Fos/Nupr1/Nras/Popdc2/Homer1/Med20/Tcf7l2/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071402</t>
@@ -3607,7 +3607,7 @@
     <t xml:space="preserve">cellular response to lipoprotein particle stimulus</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Abcg1/Ldlr/Mylip/Ticam1/Mia3/Itgb2/Apoe/Syk</t>
+    <t xml:space="preserve">Syk/Abcg1/Apoe/Cd36/Ldlr/Ticam1/Mylip/Itgb2/Mia3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002696</t>
@@ -3619,7 +3619,7 @@
     <t xml:space="preserve">296/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Pld2/Egr3/Cd47/Tfrc/Lamp1/Ticam1/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Phf10/Tcf3/Hspd1/Ap1g1/Cd320/Shld2/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Il27ra/Gata2/Gab2/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Mmp14/Tgfb1/Ccdc88b/Tyrobp/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Il1rl1/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Il1rl1/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Spn/Lamp1/Cd47/Dock8/Cbfb/Gab2/Lgals9/Stat5b/Pld2/Dpp4/Ap1g1/Smarcd1/Egr3/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Gata2/Mmp14/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Tcf3/Vsir/Hspd1/Rara/Cd320/Shld2/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006163</t>
@@ -3631,7 +3631,7 @@
     <t xml:space="preserve">361/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Ctns/Snca/Pfkfb2/Eno3/Ddit4/Mvd/Pkm/Nupr1/Bpgm/Fasn/Mlst8/Atp6v1a/Hmgcr/Atp6v1b2/Flcn/Atp7a/Pmvk/Mtch2/Gcdh/Acaca/Ndufa10/Psen1/Cs/Parp1/Gpi1/Adss/Prps1/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Suclg2/Prkag2/Khk/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Hk2/Gart/Npr2/Nudt19/Il4/Tgfb1/Nme4/Adcy7/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Slc4a1/Tgfb1/Ctns/Pfkfb2/Nme4/Gart/P2rx7/Pfas/Acsl5/Nudt19/Ddit4/Khk/Fasn/Pdha1/Mtch2/Atic/Atp6v1b2/Mlst8/Pkm/Atp6v1a/Mvd/Il4/Adssl1/Prkag2/Npr2/Adsl/Gmpr/Impdh2/Cs/Mthfd1/Suclg2/Papss2/Hmgcr/Guk1/Prps1/Eno3/Dlat/Acaca/Atp7a/Hk2/Flcn/Psen1/Gcdh/Bpgm/Ak4/Ndufa10/Nupr1/Aprt/Adss/Parp1/Pmvk/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902652</t>
@@ -3643,7 +3643,7 @@
     <t xml:space="preserve">128/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Fech/Pip4p1/Insig1/Abcg1/Mvd/Ldlr/Msmo1/Lss/Sqle/Gba/Cln8/Hmgcr/Lpcat3/Pmvk/Sc5d/Cyb5r3/Idh3g/Lrp5/Scp2/Idh3a/Idh2/Pcsk9/Abca2/Il4/Apoe</t>
+    <t xml:space="preserve">Fech/Abcg1/Pip4p1/Abca2/Apoe/Ldlr/Insig1/Sqle/Gba/Msmo1/Idh2/Mvd/Il4/Lss/Idh3a/Hmgcr/Lpcat3/Lrp5/Cyb5r3/Sc5d/Idh3g/Pcsk9/Scp2/Pmvk/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009898</t>
@@ -3655,7 +3655,7 @@
     <t xml:space="preserve">150/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Ank1/Epn1/Atp2b1/Ppp1r9b/Gnas/Exoc1/Gna13/Cdk16/Ap2m1/Iqgap1/Esyt1/Myh10/Traf3/Snx5/Akap5/Gnb4/Gnat2/Rgs2/Rac1/Kcnab2/Rgs1/Fes/Ptprc/Gng2/Sla/Syk</t>
+    <t xml:space="preserve">Spta1/Syk/Slc4a1/Gng2/Ptprc/Sla/Ank1/Rac1/Kcnab2/Gnb4/Epn1/Atp2b1/Gnas/Traf3/Myh10/Rgs2/Gna13/Ppp1r9b/Fes/Rgs1/Esyt1/Snx5/Cdk16/Ap2m1/Exoc1/Gnat2/Iqgap1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006672</t>
@@ -3667,7 +3667,7 @@
     <t xml:space="preserve">80/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Neu1/St3gal2/Gba/Cln8/Hexa/Sgpl1/Cers5/St6galnac4/Gla/P2rx1/Ugcg/Plpp2/Abca2/Agk/B4galnt1/Sptssa/P2rx7</t>
+    <t xml:space="preserve">Sptssa/St3gal1/P2rx7/Abca2/Ugcg/Gba/Neu1/Agk/B4galnt1/Gla/Plpp2/Hexa/St3gal2/St6galnac4/Cers5/P2rx1/Sgpl1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031901</t>
@@ -3676,7 +3676,7 @@
     <t xml:space="preserve">early endosome membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Abcb6/H2-T23/Wdr81/Washc2/Snx8/Washc5/Pikfyve/Clcn3/Dnajc13/Atp7a/Ehd1/Gripap1/Washc4/Snx3/Snx5/Cmtm6/Rac1/Rcc2</t>
+    <t xml:space="preserve">Abcb6/Washc5/Washc2/Rac1/Rcc2/Wdr81/Snx8/Pikfyve/Cmtm6/Dnajc13/Ehd1/Clcn3/H2-T23/Snx5/Atp7a/Washc4/Gripap1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001894</t>
@@ -3685,7 +3685,7 @@
     <t xml:space="preserve">tissue homeostasis</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldh1a1/Car2/Trp53inp2/Map1a/Tfrc/Tpp1/Ubash3b/Gigyf2/Clcn3/Cln8/Bax/Gnas/Rb1/Slc39a8/Homer1/Acaca/Ctnnb1/Wdr36/Def8/Ldb1/Prkca/Slc22a5/Srf/Atp1b2/Gata2/Lrrk1/Snx10/Tjp3/Rac1/Rac2/Col11a2/Csf1/Tgfb1/Coro1a/P2rx7/Syk/Muc13</t>
+    <t xml:space="preserve">Car2/Aldh1a1/Syk/Coro1a/Tpp1/Rac2/Tgfb1/Trp53inp2/Rac1/Gigyf2/P2rx7/Muc13/Gnas/Lrrk1/Map1a/Clcn3/Ldb1/Col11a2/Gata2/Srf/Csf1/Snx10/Ctnnb1/Tjp3/Rb1/Atp1b2/Tfrc/Def8/Prkca/Ubash3b/Acaca/Bax/Slc22a5/Wdr36/Slc39a8/Homer1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050863</t>
@@ -3697,7 +3697,7 @@
     <t xml:space="preserve">289/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Egr3/Cd47/Prdx2/Tfrc/Prnp/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Bid/Phf10/Ctnnb1/Hspd1/Stat5a/Vsir/Smarcd1/Stat5b/Ptpn6/Il27ra/Kat2a/Cd37/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Il4/Lgals9/Spn/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Jak3/Laptm5/Syk/Slc4a1/Myb/Ptprc/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Cd44/Cd47/Dock8/Ripor2/Cbfb/Lgals9/Kat2a/Stat5b/Ptpn6/Dpp4/Smarcd1/Egr3/Zbtb7b/Stat5a/Il4/Lgals7/Cd37/Pik3r6/Ctnnb1/Ap3d1/Il27ra/Havcr2/Tfrc/Vsir/Bid/Hspd1/Rara/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002715</t>
@@ -3709,7 +3709,7 @@
     <t xml:space="preserve">37/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Ap1g1/Stat5a/Stat5b/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9/Dpp4</t>
+    <t xml:space="preserve">Lamp1/Vav1/Lgals9/Stat5b/Dpp4/Ap1g1/Stat5a/Pik3r6/Havcr2/Serpinb9/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990748</t>
@@ -3718,7 +3718,7 @@
     <t xml:space="preserve">cellular detoxification</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Aldh1a1/Abcg2/Abcb6/Prdx2/Sesn1/Pim1/Atp7a/Selenot/Prdx6/Aldh2</t>
+    <t xml:space="preserve">Prdx2/Aldh1a1/Abcb6/Abcg2/Aldh2/Cd36/Sesn1/Prdx6/Selenot/Atp7a/Pim1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901215</t>
@@ -3730,7 +3730,7 @@
     <t xml:space="preserve">203/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Btg2/Slc30a10/Snca/Prdx2/Itsn1/Optn/Grn/Hipk2/Tsc1/Gba/Arrb1/Epor/Map3k12/Tbc1d24/Cln8/Atp7a/Bax/Birc5/Vps35/Sirt1/Rack1/Psen1/Nono/Ctnnb1/Gpi1/Cbl/Hsp90ab1/Set/Syngap1/Hspd1/Il27ra/Csf1/Apoe/Coro1a</t>
+    <t xml:space="preserve">Prdx2/Snca/Btg2/Coro1a/Slc30a10/Grn/Tsc1/Cpeb4/Itsn1/Optn/Apoe/Tbc1d24/Hipk2/Gba/Epor/Csf1/Nono/Ctnnb1/Il27ra/Vps35/Arrb1/Hsp90ab1/Atp7a/Birc5/Psen1/Set/Sirt1/Hspd1/Bax/Syngap1/Map3k12/Cbl/Rack1/Cln8/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051258</t>
@@ -3739,7 +3739,7 @@
     <t xml:space="preserve">protein polymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Mid1ip1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Snca/Washc5/Micall2/Mapre3/Ssh2/Mlst8/Wasl/Fbxo5/Plekhg2/Nckap1/Dyrk1a/Camsap2/Nck1/Rictor/Twf1/Togaram1/Cttn/Was/Flii/Ube2s/Hcls1/Sptan1/Slain2/Arpc2/Rangrf/Rac1/Capg/Fes/Vill/Coro1a</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Map3k1/Snca/Vill/Mid1ip1/Coro1a/Tmod1/Washc5/Dmtn/Rac1/Capg/Micall2/Arpc2/Dyrk1a/Mlst8/Ssh2/Rangrf/Wasl/Fes/Nckap1/Slain2/Flii/Twf1/Togaram1/Camsap2/Fbxo5/Plekhg2/Hcls1/Sptan1/Ube2s/Mapre3/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001568</t>
@@ -3748,7 +3748,7 @@
     <t xml:space="preserve">blood vessel development</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Prokr1/Egr3/Egr2/Nfe2/Tal1/Cited2/Agtr1a/Grn/Hipk2/Gab1/Pkm/Ldlr/Anxa3/Epor/Hdac5/Epn1/Fzd5/Junb/Sars/Plcd3/Fbxw7/Foxo4/Flcn/Atp7a/Ggnbp2/Cib1/Shb/Pknox1/Bax/Luzp1/Ago2/Brca1/Gna13/Sirt1/Adipor2/Kat6a/Mia3/Nras/Sgpl1/Psen1/Ctnnb1/Nedd4/Ppp3r1/Lrp5/Ndst1/Tnni3/Myh10/Cul7/Prkca/Megf8/Sp100/Flna/Srf/Gtf2i/Itgb2/Tcf7l2/Pik3cd/Vangl2/Sema4a/Gata2/Zfp36l1/Hk2/Itga5/Hif3a/Pik3r6/Ywhaz/Cxcr4/Apoe/Tgfb1/Col5a1/Spi1/Hdac7/Plxdc1/Vash2/Syk/Eng</t>
+    <t xml:space="preserve">Hdac7/Egr1/Syk/Tgfb1/Ywhaz/Prokr1/Grn/Tal1/Nfe2/Vash2/Gab1/Spi1/Cited2/Eng/Hif3a/Cxcr4/Epn1/Apoe/Cd36/Ldlr/Col5a1/Itga5/Hipk2/Gtf2i/Megf8/Flna/Fbxw7/Pkm/Egr3/Plxdc1/Epor/Sars/Agtr1a/Egr2/Pik3cd/Fzd5/Myh10/Gata2/Cul7/Sema4a/Gna13/Pik3r6/Srf/Ggnbp2/Zfp36l1/Pknox1/Ctnnb1/Hdac5/Vangl2/Nedd4/Anxa3/Luzp1/Ndst1/Lrp5/Cib1/Itgb2/Prkca/Atp7a/Adipor2/Hk2/Flcn/Psen1/Sirt1/Tnni3/Junb/Ppp3r1/Bax/Nras/Brca1/Kat6a/Foxo4/Ago2/Plcd3/Tcf7l2/Mia3/Sgpl1/Sp100/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001933</t>
@@ -3757,7 +3757,7 @@
     <t xml:space="preserve">negative regulation of protein phosphorylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Wnk4/Dmtn/Snca/Prkar2b/Prnp/Dusp6/Ddit4/Snx25/Ubash3b/Ppp1r15b/Gba/Arrb1/Smcr8/Cdkn2c/Hmgcr/Dnajc10/Ggnbp2/Cib1/Shb/Bax/C9orf72/Nck1/Hexim1/Rb1/Sirt1/Qars/Rack1/Psen1/Lrp5/Pde4d/Cbl/Pwp1/Prkca/Samsn1/Prkag2/Ptpn6/Lrrk1/Spred2/Rgs2/Tfap4/Rgs14/Apoe/Tgfb1/Ptprc/Eng</t>
+    <t xml:space="preserve">Prkar2b/Snca/Ptprc/Wnk4/Prnp/Tgfb1/Dmtn/Eng/Snx25/Ddit4/Apoe/Ptpn6/Lrrk1/Tfap4/Gba/Rgs14/Cdkn2c/Spred2/Dnajc10/Dusp6/Rgs2/Prkag2/Ppp1r15b/Ggnbp2/Smcr8/Rb1/Arrb1/Hmgcr/Pwp1/Hexim1/Lrp5/Cib1/Prkca/Ubash3b/Psen1/Sirt1/C9orf72/Samsn1/Bax/Nck1/Cbl/Qars/Rack1/Shb/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002011</t>
@@ -3769,7 +3769,7 @@
     <t xml:space="preserve">43/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Map3k1/Arhgap12/Dag1/Dvl2/Arhgap35/Megf8/Flna/Srf/Lin7c/Vangl2/Col5a1/Cd44</t>
+    <t xml:space="preserve">Map3k1/Cd44/Lin7c/Col5a1/Megf8/Flna/Dag1/Srf/Arhgap12/Vangl2/Dvl2/Arhgap35</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032653</t>
@@ -3778,7 +3778,7 @@
     <t xml:space="preserve">regulation of interleukin-10 production</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd47/Tusc2/Hspd1/Vsir/Plcg2/Il4/Lgals9/Trib2/Tyrobp/Jak3/Cd84/Syk</t>
+    <t xml:space="preserve">Jak3/Syk/Cd47/Trib2/Cd84/Plcg2/Lgals9/Tyrobp/Il4/Vsir/Tusc2/Hspd1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000147</t>
@@ -3799,7 +3799,7 @@
     <t xml:space="preserve">94/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Kalrn/Nedd9/Ache/Prex1/Numb/Tbc1d24/Cib1/Pias2/Cdkl5/Sh3glb1/Actr2/Stau2/Cul7/Flna/Akap5/Arpc2/Unc13d/Ankrd27/Rac1</t>
+    <t xml:space="preserve">Ankrd27/Dmtn/Rac1/Arpc2/Prex1/Tbc1d24/Kalrn/Ache/Unc13d/Flna/Numb/Nedd9/Pias2/Cul7/Sh3glb1/Cib1/Actr2/Cdkl5/Stau2/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006879</t>
@@ -3808,7 +3808,7 @@
     <t xml:space="preserve">cellular iron ion homeostasis</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Atp6v0d1/Tfrc/Slc11a2/Tmem199/Atp6v1a/Ftl1/Aco1/Atp6v1g1/Slc39a8/Tfr2/Frrs1/Cyb561</t>
+    <t xml:space="preserve">Alas2/Atp6v0d1/Slc11a2/Frrs1/Atp6v1a/Tfr2/Cyb561/Aco1/Tfrc/Tmem199/Ftl1/Slc39a8/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019209</t>
@@ -3820,7 +3820,7 @@
     <t xml:space="preserve">101/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Itsn1/Als2/Pim1/Mlst8/Map3k12/Mob3c/Ccnt1/Lamtor3/Rictor/Stradb/Dbf4/Taok1/Abi1/Iqgap1/Tcf3/Prkag2/Mob3b/Lgals9/Tgfb1/P2rx7</t>
+    <t xml:space="preserve">Tgfb1/Tal1/Itsn1/P2rx7/Lgals9/Als2/Mlst8/Mob3b/Prkag2/Ccnt1/Lamtor3/Tcf3/Taok1/Iqgap1/Stradb/Map3k12/Abi1/Mob3c/Dbf4/Pim1/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006665</t>
@@ -3832,7 +3832,7 @@
     <t xml:space="preserve">115/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Neu1/St3gal2/Gba/Cln8/Hexa/Bax/Serinc5/Sgpl1/Serinc3/Cers5/St6galnac4/Gla/P2rx1/Ugcg/Plpp2/Abca2/Agk/Vapa/B4galnt1/Fut4/Sptssa/P2rx7</t>
+    <t xml:space="preserve">Sptssa/St3gal1/P2rx7/Abca2/Vapa/Ugcg/Gba/Neu1/Agk/Fut4/B4galnt1/Gla/Plpp2/Hexa/Serinc5/St3gal2/Bax/Serinc3/St6galnac4/Cers5/P2rx1/Sgpl1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051261</t>
@@ -3844,7 +3844,7 @@
     <t xml:space="preserve">108/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Add2/Dmtn/Sptb/Map1a/Cib1/Ttbk2/Camsap2/Swap70/Twf1/Taok1/Vps4b/Flii/Wdr1/Sptan1/Arpc2/Pdxp/Capg/Arhgef2/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Arhgef2/Vill/Mid1ip1/Tmod1/Dmtn/Capg/Arpc2/Map1a/Pdxp/Wdr1/Flii/Twf1/Camsap2/Sptan1/Cib1/Swap70/Ttbk2/Taok1/Vps4b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030036</t>
@@ -3856,7 +3856,7 @@
     <t xml:space="preserve">601/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Mink1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Specc1/Cd47/Washc2/Nedd9/Epb41/Washc5/Gab1/Tsc1/Asap3/Plek2/Micall2/Frmd6/Samd14/Rhof/Actn1/Arhgap12/Mybpc3/Ssh2/Mlst8/Arrb1/Myo6/Wasl/Plekhg2/Ppp1r9b/C9orf72/Nckap1/Nck1/Sorbs1/Rictor/Swap70/Twf1/Washc4/Arhgap35/Daam1/Cttn/Taok1/Cdc42bpa/Abi1/Iqgap1/Actr2/Was/Flii/Wdr1/Sdad1/Stau2/Parvg/Myh10/Wipf1/Hcls1/Sptan1/Flna/Srf/Cap1/Sh3pxd2b/Epb41l1/Arpc2/Pdxp/Vangl2/Pdlim2/Rac1/Rac2/Capg/Fes/Arhgef2/Dock2/Tgfb1/Vill/Tyrobp/Coro1a/Arhgef18/Myo1g/Elmo1/Lcp1/Arhgdib</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Dock2/Map3k1/Myo1g/Arhgef2/Vill/Mink1/Coro1a/Tmod1/Rac2/Tgfb1/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Elmo1/Gab1/Cap1/Actn1/Micall2/Lcp1/Arhgdib/Arpc2/Arhgef18/Specc1/Flna/Frmd6/Samd14/Mlst8/Epb41/Sh3pxd2b/Ssh2/Myo6/Nedd9/Pdxp/Tyrobp/Myh10/Wasl/Ppp1r9b/Srf/Fes/Nckap1/Wdr1/Flii/Arhgap12/Arrb1/Twf1/Vangl2/Plekhg2/Hcls1/Asap3/Wipf1/Sptan1/Swap70/Washc4/Sdad1/Pdlim2/Plek2/C9orf72/Actr2/Taok1/Epb41l1/Iqgap1/Parvg/Rhof/Stau2/Cdc42bpa/Sorbs1/Abi1/Arhgap35/Nck1/Cttn/Daam1/Rictor/Mybpc3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098794</t>
@@ -3868,7 +3868,7 @@
     <t xml:space="preserve">558/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Slc6a9/Ank1/Add2/Dmtn/Prkar2b/Itsn1/Map1a/Mpp2/Sema4b/Mylk2/Prnp/Kalrn/Als2/Ache/Tsc1/Picalm/Adam10/Samd14/Numb/Nrgn/Actn1/Arrb1/Arfgef2/Syn1/Atp6ap2/Epn1/Clcn3/Myo6/Smcr8/Atp2b1/Wasl/Ap3d1/Ppp1r9b/Dag1/Rnf10/C9orf72/Cdkl5/Nckap1/Vps35/Gripap1/Homer1/Abi1/Rpl4/Actr2/Ctnnb1/Nedd4/Phb2/Ifngr1/Dgkz/Atad1/Eif4g2/Myh10/Syngap1/P2rx1/Flna/Eif4ebp2/Srgn/Rpl10a/Lin7c/Epb41l1/Akap5/Arpc2/Atp1a3/Cplx2/Grin2d/Cadm1/Pde4b/Rac1/Nr1d1/Slc29a1/Kcnab2/Prr7/Ptprs/Ywhaz/Rgs14/Arhgef2/Sla</t>
+    <t xml:space="preserve">Add2/Prkar2b/Picalm/Arhgef2/Ptprs/Slc6a9/Prnp/Slc29a1/Ywhaz/Tsc1/Dmtn/Sla/Ank1/Cpeb4/Rac1/Itsn1/Kcnab2/Actn1/Mpp2/Als2/Arfgef2/Arpc2/Epn1/Atp2b1/Adam10/Lin7c/Atp6ap2/Kalrn/Ache/Flna/Samd14/Eif4ebp2/Rgs14/Rpl10a/Map1a/Myo6/Clcn3/Dag1/Numb/Sema4b/Myh10/Atad1/Dgkz/Wasl/Ppp1r9b/Ctnnb1/Ap3d1/Nckap1/Rnf10/Prr7/Smcr8/Vps35/Nr1d1/Arrb1/Nedd4/Nrgn/Mylk2/Srgn/Cplx2/Pde4b/Atp1a3/Cadm1/Grin2d/C9orf72/Actr2/Epb41l1/Eif4g2/Ifngr1/Cdkl5/Rpl4/Syngap1/Phb2/Homer1/Gripap1/Abi1/P2rx1/Akap5/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043065</t>
@@ -3883,7 +3883,7 @@
     <t xml:space="preserve">507/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Aldh1a1/Map3k1/Optn/Ctsd/Grn/Prnp/Dusp6/Adam10/Nupr1/Trp53inp1/Arrb1/Pea15a/Igf2r/Rbm5/Akap12/Fbxw7/Dcun1d3/Hmgcr/Flcn/Mtch2/Bax/Nck1/Bcl2l11/Ccar1/Bid/Mcl1/Ncoa1/Siah1b/Sirt1/Sav1/Fnip1/Sh3glb1/Rack1/Psen1/Serinc3/Ctnnb1/Ncf2/Trim35/Maged1/Scp2/Rbck1/Itm2c/Rrp1b/Hspd1/Rps6ka2/Calhm2/Tnfrsf26/Pcsk9/Mybbp1a/Tcf7l2/Pik3cd/Trp53/Dapk1/Ppp2r1a/Pdcd4/Pmaip1/Ano6/Zfas1/Casp7/Irf5/Prr7/Tfap4/Pla2g1b/Phlda2/Tgfb1/Cd44/Tyrobp/Ptprc/Jak3/Lgals1/P2rx7</t>
+    <t xml:space="preserve">Lgals1/Egr1/Map3k1/Jak3/Ctsd/Aldh1a1/Ptprc/Ano6/Prnp/Tgfb1/Casp7/Grn/Cd44/Ppp2r1a/P2rx7/Optn/Adam10/Igf2r/Mtch2/Tfap4/Pmaip1/Fbxw7/Trp53/Phlda2/Rbm5/Irf5/Zfas1/Dusp6/Trp53inp1/Tyrobp/Pik3cd/Pla2g1b/Maged1/Pea15a/Ctnnb1/Mybbp1a/Prr7/Dapk1/Rbck1/Sh3glb1/Arrb1/Mcl1/Ccar1/Hmgcr/Bcl2l11/Rps6ka2/Flcn/Pdcd4/Ncf2/Psen1/Bid/Sirt1/Ncoa1/Sav1/Hspd1/Fnip1/Pcsk9/Bax/Nupr1/Scp2/Serinc3/Trim35/Itm2c/Dcun1d3/Akap12/Siah1b/Calhm2/Nck1/Tcf7l2/Tnfrsf26/Rack1/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046903</t>
@@ -3895,7 +3895,7 @@
     <t xml:space="preserve">786/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Slc6a9/Pld2/Car2/Wnk4/Exoc3l4/Rph3al/Dmtn/Snca/Itsn1/Agtr1a/Glrx/Kalrn/Pfkfb2/Abcg1/Arntl/Washc5/Slc16a10/Rhbdf1/Vps11/Lamp1/Ptpn23/D6Wsu163e/Map1lc3b/Anxa3/Zbtb7b/Dpysl2/Rab3ip/Arrb1/Arfgef2/Syn1/Myo6/Smcr8/Ppard/Socs2/Hmgcr/Ccdc186/C9orf72/Birc5/Exoc8/Vps35/Tmem167b/Gnas/Rap1b/Exoc1/Arl8b/Cdk16/Sirt1/Snap29/Mia3/Vps4b/Mia2/Psen1/Lrp5/Tm7sf3/Selenot/Copg2/Myh10/Aprt/Ap1g1/Prkca/P2rx1/Idh2/Snx5/Stat5a/Ier3ip1/Fkbp1b/Itgb2/Pla2g12a/Tcf7l2/Lin7c/Unc13a/Akap5/Tfr2/Hadh/Stat5b/Slc4a8/Fcgr3/Gata2/Traf3ip2/Unc13d/Snx10/Cplx2/Gab2/Pim3/Rac1/Nr1d1/Rac2/Il4/Ywhaz/Pla2g1b/Fes/Lgals9/Ltbp4/Apoe/Tgfb1/Sytl4/Spi1/Coro1a/Myo1g/P2rx7/Cd84/Syk/Oas2</t>
+    <t xml:space="preserve">Car2/Rab3il1/Snca/Myo1g/Syk/Wnk4/Coro1a/Slc6a9/Rac2/Tgfb1/Ywhaz/Rph3al/Washc5/Abcg1/Dmtn/Oas2/Lamp1/Rac1/Cd84/Itsn1/Pfkfb2/Ptpn23/Spi1/Gab2/P2rx7/Vps11/Slc16a10/Lgals9/Arfgef2/Glrx/Apoe/Stat5b/Map1lc3b/Lin7c/Pld2/Ltbp4/Pim3/Kalrn/Hadh/Gnas/Unc13d/Arntl/Ap1g1/Myo6/Zbtb7b/Dpysl2/Tfr2/D6Wsu163e/Agtr1a/Exoc3l4/Socs2/Idh2/Rab3ip/Stat5a/Pla2g12a/Sytl4/Il4/Myh10/Gata2/Pla2g1b/Fes/Snx10/Selenot/Ppard/Smcr8/Vps35/Copg2/Nr1d1/Rhbdf1/Arrb1/Fcgr3/Slc4a8/Anxa3/Hmgcr/Exoc8/Mia2/Snx5/Lrp5/Tmem167b/Cplx2/Itgb2/Prkca/Arl8b/Cdk16/Ier3ip1/Birc5/Exoc1/Rap1b/Psen1/Sirt1/C9orf72/Traf3ip2/Tm7sf3/Aprt/Unc13a/Fkbp1b/Tcf7l2/Ccdc186/Vps4b/Mia3/P2rx1/Akap5/Snap29/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009615</t>
@@ -3907,7 +3907,7 @@
     <t xml:space="preserve">283/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ddit4/Isg20/Ticam1/Trim56/Tbk1/Bax/Elmod2/Xpr1/Rnf185/Serinc5/Irf2/Ppm1b/Usp15/Serinc3/Trim28/Cnot7/Phb2/Ifitm2/Ddx21/Trim35/Ifngr1/Rrp1b/Mov10/Traf3/Exosc5/Dtx3l/Polr3e/Ifih1/Oasl1/Traf3ip2/Unc13d/Apobec3/Pmaip1/Cd37/Wdfy4/Irf5/Il4/Rnf125/Lgals9/Spn/Tgfb1/Mst1r/Unc93b1/Ptprc/Oas2</t>
+    <t xml:space="preserve">Wdfy4/Ptprc/Tgfb1/Spn/Oas2/Lgals9/Ddit4/Unc93b1/Mst1r/Rnf125/Unc13d/Xpr1/Pmaip1/Tbk1/Apobec3/Irf5/Trim56/Traf3/Ticam1/Il4/Cd37/Isg20/Polr3e/Mov10/Dtx3l/Usp15/Trim28/Ifih1/Serinc5/Exosc5/Ifitm2/Traf3ip2/Ifngr1/Bax/Serinc3/Rnf185/Trim35/Phb2/Irf2/Ddx21/Cnot7/Oasl1/Elmod2/Ppm1b/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097190</t>
@@ -3919,7 +3919,7 @@
     <t xml:space="preserve">525/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Prdx2/Hipk2/Ddit4/Fnip2/Nupr1/Ticam1/Pea15a/Ppard/Fbxw7/Grina/Sgk3/Dnajc10/Flcn/Atp7a/Mtch2/Ppp1r13b/Stk25/Bax/Bex3/Gabarap/Nck1/Bcl2l11/Stradb/Bid/Brca1/Mcl1/Rb1/Mknk1/Dedd/Siah1b/Mknk2/Cttn/Sirt1/Rps6kb1/Sh3glb1/Usp47/Qars/Rack1/Sgpl1/Psen1/Parp1/Serinc3/Nono/Ctnnb1/Maged1/Armc10/Rbck1/Itm2c/Mnt/Prkca/Sp100/Tmem109/Timm50/Ppif/Tnfrsf26/Mybbp1a/Trp53/Dapk1/Acsl5/Ppp2r1a/Pcgf2/Pmaip1/Zfas1/Casp7/Aldh2/Il4/Spn/Tgfb1/Cd44/Spi1/Tyrobp/Ptprc/Jak3/P2rx7</t>
+    <t xml:space="preserve">Prdx2/Jak3/Ptprc/Tgfb1/Casp7/Spn/Aldh2/Cd44/Fnip2/Spi1/Ppp2r1a/P2rx7/Acsl5/Ddit4/Hipk2/Mtch2/Pmaip1/Fbxw7/Stk25/Trp53/Gabarap/Dnajc10/Zfas1/Ticam1/Tyrobp/Timm50/Pcgf2/Il4/Maged1/Pea15a/Nono/Ctnnb1/Mybbp1a/Ppard/Dapk1/Rb1/Rbck1/Sh3glb1/Ppif/Mcl1/Armc10/Ppp1r13b/Mknk2/Bcl2l11/Prkca/Atp7a/Flcn/Tmem109/Psen1/Bid/Sirt1/Grina/Bax/Bex3/Nupr1/Serinc3/Stradb/Brca1/Itm2c/Mnt/Sgk3/Siah1b/Nck1/Parp1/Usp47/Cttn/Tnfrsf26/Qars/Dedd/Mknk1/Sgpl1/Rack1/Sp100/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043549</t>
@@ -3931,7 +3931,7 @@
     <t xml:space="preserve">568/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Wnk4/Map3k1/Snca/Prkar2b/Wdr81/Agtr1a/Prnp/Pfkfb2/Nedd9/Als2/Gab1/Traf4/Tsc1/Uvrag/Stil/Cdc25b/Cdc6/Pim1/Ubash3b/Mapre3/Gba/Fzd5/Ppp2r5a/Smcr8/Map3k12/Cdkn2c/Fbxw7/Hmgcr/Ggnbp2/Cib1/Shb/Dag1/Dvl2/Rap2b/Stradb/Hexim1/Rb1/Pip4k2c/Sirt1/Sh3glb1/Abi1/Qars/Psen1/Iqgap1/Phb2/Lrp5/Gtpbp4/Maged1/Cbl/Dgkz/Hsp90ab1/Ldb1/Igf1r/Prkca/Pik3r5/Rap2c/Prkag2/Ccng1/Irak1/Vangl2/Ptpn6/Xrcc5/Rgs2/Rac1/Mmd/Pik3r6/Tfap4/Il4/Csf1/Rgs14/Apoe/Trib2/Tgfb1/Mst1r/Ptprc/P2rx7/Pik3ip1/Syk</t>
+    <t xml:space="preserve">Egr1/Map3k1/Prkar2b/Snca/Syk/Ptprc/Wnk4/Prnp/Tgfb1/Tsc1/Rac1/Trib2/Pfkfb2/Gab1/Ppp2r5a/Pik3ip1/P2rx7/Wdr81/Als2/Ccng1/Apoe/Cdc25b/Mst1r/Mmd/Ptpn6/Xrcc5/Cdc6/Irak1/Tfap4/Traf4/Uvrag/Fbxw7/Rap2b/Gba/Rgs14/Cdkn2c/Dag1/Ldb1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Rgs2/Rap2c/Prkag2/Dgkz/Pik3r6/Ggnbp2/Maged1/Csf1/Smcr8/Rb1/Sh3glb1/Vangl2/Dvl2/Hmgcr/Hexim1/Lrp5/Cib1/Prkca/Ubash3b/Hsp90ab1/Mapre3/Psen1/Sirt1/Iqgap1/Stradb/Map3k12/Phb2/Gtpbp4/Abi1/Igf1r/Cbl/Qars/Pim1/Shb/Pik3r5/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901983</t>
@@ -3943,7 +3943,7 @@
     <t xml:space="preserve">88/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Nfe2/Snca/Arntl/Wbp2/Arrb1/Flcn/Dip2b/Brca1/Sirt1/Taok1/Ctcf/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Kat2a/Gata2/Tgfb1/Spi1</t>
+    <t xml:space="preserve">Snca/Tgfb1/Nfe2/Spi1/Glyr1/Kat2a/Wbp2/Dip2b/Arntl/Gata2/Mybbp1a/Arrb1/Ruvbl2/Flcn/Sirt1/Taok1/Brca1/Ctcf/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060284</t>
@@ -3955,7 +3955,7 @@
     <t xml:space="preserve">474/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Egr2/Dmtn/Sema4b/Grn/Kalrn/Arntl/Nedd9/Ache/Picalm/Ldlr/Prex1/Numb/Hdac5/Trak2/Tbc1d24/Fbxw7/Cib1/Shb/Stk25/Dag1/Pias2/Dip2b/Rnf10/Cdkl5/Plag1/Golga4/Rb1/Vcl/Sh3glb1/Nap1l1/Psen1/Rpl4/Actr2/Ctnnb1/Prpf19/Kifap3/Stau2/Jade2/Syngap1/Ulk2/Cul7/Megf8/Idh2/Flna/Srf/Akap5/Arpc2/Trp53/Sema4a/Xrcc5/Unc13d/Zdhhc21/Npr2/Ankrd27/Rac1/Rcc2/Nr1d1/Plxnc1/Vim/Ptprs/Tenm4/Rgs14/Cxcr4/Arhgef2/Apoe/Tgfb1/Tyrobp</t>
+    <t xml:space="preserve">Appl2/Picalm/Arhgef2/Ptprs/Tgfb1/Grn/Ankrd27/Dmtn/Rac1/Rcc2/Vim/Zdhhc21/Cxcr4/Arpc2/Apoe/Prex1/Tbc1d24/Ldlr/Xrcc5/Kalrn/Ache/Megf8/Unc13d/Flna/Dip2b/Fbxw7/Arntl/Stk25/Rgs14/Tenm4/Trp53/Dag1/Numb/Nedd9/Pias2/Sema4b/Egr2/Idh2/Tyrobp/Cul7/Npr2/Sema4a/Srf/Ctnnb1/Rnf10/Hdac5/Rb1/Nr1d1/Sh3glb1/Plxnc1/Trak2/Cib1/Prpf19/Plag1/Psen1/Ulk2/Actr2/Golga4/Cdkl5/Rpl4/Stau2/Syngap1/Jade2/Nap1l1/Kifap3/Akap5/Shb/Vcl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007517</t>
@@ -3967,7 +3967,7 @@
     <t xml:space="preserve">252/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Btg2/Dpf3/Egr2/Cited2/Hlf/Gpcpd1/Mylk2/Arntl/Chd2/Mylpf/Fos/Nupr1/Kel/Mybpc3/Epor/Hdac5/Coprs/Foxo4/Hmgcr/Xk/Dag1/Rb1/Med20/Homer1/Sirt1/Rps6kb1/Nras/Ctnnb1/Fkbp1a/Tnni3/Tcf7l2/Vangl2/Popdc2/Nr1d2/Vamp5/Des/Ripor2/Tgfb1/Hdac7/Eng</t>
+    <t xml:space="preserve">Hdac7/Egr1/Btg2/Tgfb1/Dpf3/Ripor2/Cited2/Eng/Hlf/Vamp5/Nr1d2/Des/Chd2/Arntl/Dag1/Epor/Egr2/Xk/Ctnnb1/Hdac5/Kel/Rb1/Vangl2/Gpcpd1/Hmgcr/Mylpf/Coprs/Mylk2/Sirt1/Fkbp1a/Fos/Tnni3/Nupr1/Nras/Popdc2/Foxo4/Homer1/Med20/Tcf7l2/Rps6kb1/Mybpc3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0021700</t>
@@ -3976,7 +3976,7 @@
     <t xml:space="preserve">developmental maturation</t>
   </si>
   <si>
-    <t xml:space="preserve">Slfn14/Fam210b/Epb42/Tal1/Washc5/Picalm/Gdf11/Klf1/Cdc25b/Gba/Atp6ap2/Fzd5/Clcn3/Bhlha15/Ppard/Fbxo5/Ap3d1/Shb/Dag1/Tusc2/Rb1/Tut7/Asxl2/Psen1/Ctnnb1/Wdr77/Ap1g1/Mbtps2/Rps6ka2/Unc13a/Akap5/Ppp2r1a/Nfia/Gata2/Snx10/Ano6/Npr2/Ankrd27/Rac1/Cbfb/Ywhaz/Tgfb1/Btk</t>
+    <t xml:space="preserve">Btk/Fam210b/Picalm/Ano6/Tgfb1/Ywhaz/Slfn14/Washc5/Ankrd27/Tal1/Rac1/Epb42/Cbfb/Klf1/Ppp2r1a/Nfia/Cdc25b/Atp6ap2/Gba/Ap1g1/Gdf11/Clcn3/Dag1/Fzd5/Gata2/Npr2/Snx10/Ctnnb1/Ap3d1/Ppard/Rb1/Fbxo5/Rps6ka2/Psen1/Bhlha15/Tusc2/Mbtps2/Tut7/Wdr77/Unc13a/Asxl2/Akap5/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050852</t>
@@ -3985,7 +3985,7 @@
     <t xml:space="preserve">T cell receptor signaling pathway</t>
   </si>
   <si>
-    <t xml:space="preserve">Btnl10/Prnp/Ermap/Usp9x/Shb/Elf1/Fcho1/Nras/Psen1/Pde4d/Rbck1/Dgkz/Ptpn6/Plcg2/Ubash3a/Pde4b/Lcp2/Laptm5/Fyb/Ptprc/Rftn1</t>
+    <t xml:space="preserve">Laptm5/Rftn1/Ptprc/Prnp/Btnl10/Ermap/Fyb/Plcg2/Ptpn6/Usp9x/Lcp2/Ubash3a/Elf1/Dgkz/Rbck1/Pde4b/Psen1/Nras/Fcho1/Shb/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007041</t>
@@ -3994,7 +3994,7 @@
     <t xml:space="preserve">lysosomal transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Als2/Vps11/Lamp1/Igf2r/Trak2/Vps33a/Ap3d1/Chmp3/C9orf72/Vps35/Arl8b/Clec16a/Vps4b/Nedd4/Ap1g1/Dtx3l/Ehd3/Pcsk9/Aktip/Vps53/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Grn/Lamp1/Vps53/Vps11/Als2/Igf2r/Ap1g1/Ap3d1/Vps33a/Vps35/Aktip/Nedd4/Chmp3/Trak2/Dtx3l/Arl8b/Ehd3/C9orf72/Pcsk9/Vps4b/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032640</t>
@@ -4015,7 +4015,7 @@
     <t xml:space="preserve">333/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Alas2/Atp6v0d1/Slc30a10/Abcb6/Snca/Tfrc/Mcoln1/Prnp/Dmpk/Ankrd9/Slc11a2/Kel/Ubash3b/Micu1/Slc30a9/Tmem199/Atp2b1/Smdt1/Grina/Atp6v1a/Ftl1/Atp7a/Xk/Ap3d1/Bax/Aco1/Pacs2/Atp6v1g1/Slc39a8/Psen1/Pde4d/Fkbp1a/Pdzd8/Tnni3/Prkca/P2rx1/Flna/Fkbp1b/Tfr2/Frrs1/Cyb561/Ptpn6/Atp1b2/Plcg2/Atp1a3/Gsto1/Apoe/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Alas2/Atp6v0d1/Snca/Ptprc/Coro1a/Abcb6/Prnp/Tgfb1/Slc30a10/Slc11a2/Gsto1/P2rx7/Mcoln1/Slc30a9/Plcg2/Atp2b1/Apoe/Ptpn6/Micu1/Flna/Frrs1/Pacs2/Pdzd8/Atp6v1a/Tfr2/Cyb561/Smdt1/Xk/Ankrd9/Aco1/Ap3d1/Kel/Dmpk/Atp1b2/Tfrc/Prkca/Ubash3b/Tmem199/Atp1a3/Atp7a/Ftl1/Psen1/Fkbp1a/Tnni3/Grina/Bax/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903077</t>
@@ -4024,7 +4024,7 @@
     <t xml:space="preserve">negative regulation of protein localization to plasma membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Picalm/Cltc/Numb/Ppp2r5a/Ap2m1/Gopc/Lypla1/Tgfb1</t>
+    <t xml:space="preserve">Picalm/Tgfb1/Cltc/Lypla1/Ppp2r5a/Numb/Ap2m1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005765</t>
@@ -4036,7 +4036,7 @@
     <t xml:space="preserve">175/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Abcb6/H2-T23/Wdr81/Pip4p1/Ctsd/Grn/Mcoln1/Clcn7/Slc11a2/Lamp1/Lamtor1/Gba/Atp6ap2/Clcn3/Flcn/Lamtor3/Chmp3/Lrrc8a/Atp6v1g1/Arl8b/Slc39a8/Fnip1/Clec16a/Psen1/Ifitm2/Hsp90ab1/Ap1g1/Abca2/Cyb561/Laptm5</t>
+    <t xml:space="preserve">Ctsd/Laptm5/Abcb6/Slc11a2/Ctns/Grn/Lamp1/Pip4p1/Mcoln1/Abca2/Wdr81/Clcn7/Atp6ap2/Gba/Ap1g1/Clcn3/H2-T23/Cyb561/Lamtor3/Lamtor1/Lrrc8a/Chmp3/Arl8b/Hsp90ab1/Flcn/Psen1/Ifitm2/Fnip1/Slc39a8/Atp6v1g1/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009260</t>
@@ -4045,7 +4045,7 @@
     <t xml:space="preserve">ribonucleotide biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Snca/Pkm/Flcn/Gcdh/Ndufa10/Parp1/Adss/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Umps/Cad/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Gart/Npr2/Uprt/Il4/Tgfb1/Nme4/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Uprt/Nme4/Gart/Pfas/Acsl5/Pdha1/Atic/Cad/Pkm/Umps/Il4/Adssl1/Npr2/Adsl/Gmpr/Impdh2/Mthfd1/Papss2/Guk1/Dlat/Flcn/Gcdh/Ak4/Ndufa10/Aprt/Adss/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098852</t>
@@ -4063,7 +4063,7 @@
     <t xml:space="preserve">301/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Washc2/Washc5/Tsc1/Asap3/Rhof/Ssh2/Mlst8/Wasl/Plekhg2/C9orf72/Nckap1/Nck1/Rictor/Swap70/Twf1/Washc4/Arhgap35/Cttn/Taok1/Iqgap1/Was/Flii/Wdr1/Stau2/Hcls1/Sptan1/Flna/Sh3pxd2b/Arpc2/Pdxp/Vangl2/Rac1/Rac2/Capg/Fes/Tgfb1/Vill/Coro1a/Arhgef18/Arhgdib</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Vill/Coro1a/Tmod1/Rac2/Tgfb1/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Arhgdib/Arpc2/Arhgef18/Flna/Mlst8/Sh3pxd2b/Ssh2/Pdxp/Wasl/Fes/Nckap1/Wdr1/Flii/Twf1/Vangl2/Plekhg2/Hcls1/Asap3/Sptan1/Swap70/Washc4/C9orf72/Taok1/Iqgap1/Rhof/Stau2/Arhgap35/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043303</t>
@@ -4075,7 +4075,7 @@
     <t xml:space="preserve">44/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/D6Wsu163e/Gata2/Unc13d/Cplx2/Gab2/Rac2/Il4/Ywhaz/Fes/Cd84/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Ywhaz/Cd84/Gab2/Pld2/Unc13d/D6Wsu163e/Il4/Gata2/Fes/Cplx2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005776</t>
@@ -4084,7 +4084,7 @@
     <t xml:space="preserve">autophagosome</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Wdr81/Rubcnl/Atg9a/Lamp1/Map1lc3b/Uvrag/Trp53inp1/Vps33a/Ftl1/Chmp3/C9orf72/Gabarap/Pip4k2c/Nbr1/Snap29/Sh3glb1/Ubqln4</t>
+    <t xml:space="preserve">Trp53inp2/Lamp1/Wdr81/Map1lc3b/Atg9a/Uvrag/Gabarap/Trp53inp1/Vps33a/Sh3glb1/Ubqln4/Chmp3/Rubcnl/Ftl1/C9orf72/Nbr1/Snap29/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046390</t>
@@ -4096,7 +4096,7 @@
     <t xml:space="preserve">32/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Snca/Pkm/Flcn/Gcdh/Ndufa10/Parp1/Adss/Prps1/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Umps/Cad/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Gart/Npr2/Uprt/Il4/Tgfb1/Nme4/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Uprt/Nme4/Gart/Pfas/Acsl5/Pdha1/Atic/Cad/Pkm/Umps/Il4/Adssl1/Npr2/Adsl/Gmpr/Impdh2/Mthfd1/Papss2/Guk1/Prps1/Dlat/Flcn/Gcdh/Ak4/Ndufa10/Aprt/Adss/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016126</t>
@@ -4105,7 +4105,7 @@
     <t xml:space="preserve">sterol biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Insig1/Abcg1/Mvd/Msmo1/Lss/Sqle/Hmgcr/Lpcat3/Pmvk/Sc5d/Cyb5r3/Scp2/Apoe</t>
+    <t xml:space="preserve">Abcg1/Apoe/Insig1/Sqle/Msmo1/Mvd/Lss/Hmgcr/Lpcat3/Cyb5r3/Sc5d/Scp2/Pmvk</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043539</t>
@@ -4114,7 +4114,7 @@
     <t xml:space="preserve">protein serine/threonine kinase activator activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Als2/Pim1/Mlst8/Map3k12/Ccnt1/Rictor/Stradb/Dbf4/Taok1/Iqgap1/Lgals9/Tgfb1/P2rx7</t>
+    <t xml:space="preserve">Tgfb1/P2rx7/Lgals9/Als2/Mlst8/Ccnt1/Taok1/Iqgap1/Stradb/Map3k12/Dbf4/Pim1/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051494</t>
@@ -4126,7 +4126,7 @@
     <t xml:space="preserve">153/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Snca/Map1a/Mdm1/Ssh2/Cib1/Ttbk2/Dyrk1a/Camsap2/Swap70/Twf1/Taok1/Was/Flii/Sptan1/Arpc2/Kat2a/Capg/Arhgef2/Vill/Coro1a/Arhgef18</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Snca/Arhgef2/Vill/Mid1ip1/Coro1a/Tmod1/Dmtn/Capg/Mdm1/Kat2a/Arpc2/Arhgef18/Dyrk1a/Map1a/Ssh2/Flii/Twf1/Camsap2/Sptan1/Cib1/Swap70/Ttbk2/Taok1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902904</t>
@@ -4135,7 +4135,7 @@
     <t xml:space="preserve">negative regulation of supramolecular fiber organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Snca/Map1a/Ldlr/Ssh2/Cib1/Ttbk2/Dyrk1a/Camsap2/Swap70/Twf1/Taok1/Was/Flii/Sptan1/Arpc2/Capg/Arhgef2/Apoe/Vill/Coro1a/Arhgef18</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Snca/Arhgef2/Vill/Mid1ip1/Coro1a/Tmod1/Dmtn/Capg/Arpc2/Apoe/Ldlr/Arhgef18/Dyrk1a/Map1a/Ssh2/Flii/Twf1/Camsap2/Sptan1/Cib1/Swap70/Ttbk2/Taok1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002768</t>
@@ -4159,7 +4159,7 @@
     <t xml:space="preserve">684/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Phyhip/Pld2/Mst1/Map3k1/Add2/Inka2/Prkar2b/Agtr1a/Tfrc/Pfkfb2/Nedd9/Traf4/Adam10/Ptpn23/Cltc/Ticam1/Cdc25b/Rhof/Dpysl2/Mapre3/Arrb1/Pea15a/Zfyve26/Syn1/Hdac5/Fzd5/Dact3/Smcr8/Map3k12/Cdkn2c/Ccnt1/Fbxo5/Kif13b/Cib1/Tob1/Dvl2/Rara/Nck1/Slc12a7/Bcl2l11/Sorbs1/Rictor/Nbr1/Sirt1/Taok1/Usp37/Qars/Rack1/Iqgap1/Parp1/Ctnnb1/Parn/Tcf3/Was/Nek9/Cbl/Rbck1/Hsp90ab1/Stau2/Tnni3/Syngap1/Hcls1/Traf3/Flna/Prmt1/Itgb2/Prkag2/Rnf138/Tcf7l2/Akap5/Trp53/Irak1/Ptpn6/Plcg2/Spred2/Gab2/Rac1/Rcc2/Pitpnm2/Rac2/Vim/Irf5/Prr7/Ywhaz/Rgs14/Trib2/Cd44/Gdf3/Hdac7/Ptprc/Dok2/Syk</t>
+    <t xml:space="preserve">Hdac7/Add2/Map3k1/Prkar2b/Syk/Ptprc/Rac2/Ywhaz/Cltc/Mst1/Dok2/Phyhip/Cd44/Rac1/Trib2/Rcc2/Pfkfb2/Ptpn23/Gab2/Pitpnm2/Plcg2/Vim/Cdc25b/Adam10/Pld2/Ptpn6/Flna/Irak1/Traf4/Rgs14/Gdf3/Inka2/Trp53/Cdkn2c/Spred2/Dpysl2/Nedd9/Irf5/Traf3/Agtr1a/Ticam1/Rnf138/Fzd5/Prkag2/Prmt1/Ccnt1/Zfyve26/Pea15a/Ctnnb1/Hdac5/Prr7/Smcr8/Nek9/Rbck1/Arrb1/Fbxo5/Dvl2/Tfrc/Hcls1/Tob1/Cib1/Bcl2l11/Itgb2/Tcf3/Hsp90ab1/Dact3/Mapre3/Kif13b/Sirt1/Taok1/Tnni3/Iqgap1/Slc12a7/Rara/Rhof/Stau2/Syngap1/Map3k12/Sorbs1/Nbr1/Nck1/Parp1/Tcf7l2/Cbl/Qars/Usp37/Rack1/Akap5/Parn/Syn1/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001944</t>
@@ -4171,7 +4171,7 @@
     <t xml:space="preserve">588/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Prokr1/Egr3/Egr2/Nfe2/Tal1/Cited2/Agtr1a/Grn/Hipk2/Gab1/Adam10/Pkm/Ldlr/Anxa3/Epor/Hdac5/Epn1/Fzd5/Junb/Sars/Plcd3/Fbxw7/Foxo4/Flcn/Atp7a/Ggnbp2/Cib1/Shb/Pknox1/Bax/Luzp1/Ago2/Brca1/Gna13/Sirt1/Adipor2/Kat6a/Mia3/Nras/Sgpl1/Psen1/Ctnnb1/Nedd4/Ppp3r1/Lrp5/Ndst1/Tnni3/Myh10/Cul7/Prkca/Megf8/Sp100/Flna/Srf/Gtf2i/Itgb2/Tcf7l2/Pik3cd/Vangl2/Sema4a/Pdcd4/Gata2/Zfp36l1/Hk2/Tmem231/Itga5/Hif3a/Pik3r6/Ywhaz/Cxcr4/Apoe/Tgfb1/Col5a1/Spi1/Hdac7/Plxdc1/Vash2/Syk/Eng</t>
+    <t xml:space="preserve">Hdac7/Egr1/Syk/Tgfb1/Ywhaz/Prokr1/Grn/Tal1/Nfe2/Vash2/Gab1/Spi1/Cited2/Eng/Hif3a/Cxcr4/Epn1/Apoe/Cd36/Adam10/Ldlr/Col5a1/Itga5/Hipk2/Gtf2i/Megf8/Flna/Fbxw7/Pkm/Egr3/Plxdc1/Epor/Sars/Agtr1a/Egr2/Pik3cd/Fzd5/Myh10/Gata2/Cul7/Sema4a/Gna13/Pik3r6/Srf/Ggnbp2/Zfp36l1/Pknox1/Ctnnb1/Tmem231/Hdac5/Vangl2/Nedd4/Anxa3/Luzp1/Ndst1/Lrp5/Cib1/Itgb2/Prkca/Atp7a/Adipor2/Hk2/Flcn/Pdcd4/Psen1/Sirt1/Tnni3/Junb/Ppp3r1/Bax/Nras/Brca1/Kat6a/Foxo4/Ago2/Plcd3/Tcf7l2/Mia3/Sgpl1/Sp100/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005247</t>
@@ -4183,7 +4183,7 @@
     <t xml:space="preserve">9/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Clcn6/Clcn7/Clcn5/Clcn3/Ano6</t>
+    <t xml:space="preserve">Ano6/Clcn6/Clcn7/Clcn5/Clcn3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000646</t>
@@ -4192,7 +4192,7 @@
     <t xml:space="preserve">positive regulation of receptor catabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Dtx3l/Pcsk9/Abca2/Apoe/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Abca2/Apoe/Dtx3l/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009165</t>
@@ -4204,7 +4204,7 @@
     <t xml:space="preserve">222/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Snca/Pkm/Nmnat3/Flcn/Gcdh/Ndufa10/Parp1/Adss/Prps1/Dlat/Dut/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Idh2/Umps/Qprt/Cad/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Gart/Npr2/Uprt/Il4/Tgfb1/Nme4/Dctd/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Uprt/Nme4/Dctd/Gart/Pfas/Acsl5/Pdha1/Atic/Cad/Pkm/Umps/Idh2/Il4/Adssl1/Npr2/Adsl/Gmpr/Impdh2/Dut/Mthfd1/Papss2/Guk1/Prps1/Dlat/Qprt/Flcn/Gcdh/Ak4/Ndufa10/Aprt/Adss/Parp1/Nmnat3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008308</t>
@@ -4213,7 +4213,7 @@
     <t xml:space="preserve">voltage-gated anion channel activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Clcn6/Clcn7/Clcn5/Clcn3/Gpr89/Ano6</t>
+    <t xml:space="preserve">Ano6/Clcn6/Clcn7/Clcn5/Clcn3/Gpr89</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032700</t>
@@ -4222,7 +4222,7 @@
     <t xml:space="preserve">negative regulation of interleukin-17 production</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Tusc2/Parp1/Vsir/Il27ra/Tgfb1</t>
+    <t xml:space="preserve">Prnp/Tgfb1/Il27ra/Vsir/Tusc2/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060213</t>
@@ -4240,7 +4240,7 @@
     <t xml:space="preserve">regulation of receptor catabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Mylip/Dtx3l/Pcsk9/Abca2/Apoe/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Abca2/Apoe/Mylip/Dtx3l/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030258</t>
@@ -4252,7 +4252,7 @@
     <t xml:space="preserve">176/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Agtr1a/Pip4p1/Scd1/Aldh1l2/Abcg1/Acox1/Stard4/St3gal2/Lamtor1/Gba/Ppard/Lpcat3/Gcdh/Mtmr3/Adipor2/Mtmr12/Etfb/Scp2/Dgkz/Ilvbl/Mboat7/Plpp2/Abca2/Agk/Hadh/Mtmr9/Acsl5/B4galnt1/Apoe</t>
+    <t xml:space="preserve">Appl2/Abcg1/Pip4p1/Stard4/Abca2/Acsl5/Apoe/Cd36/Mtmr9/Hadh/Acox1/Gba/Agk/Agtr1a/Mtmr3/Scd1/Dgkz/Mboat7/Lamtor1/Ppard/Aldh1l2/B4galnt1/Lpcat3/Adipor2/Plpp2/St3gal2/Gcdh/Scp2/Mtmr12/Etfb/Ilvbl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901617</t>
@@ -4261,7 +4261,7 @@
     <t xml:space="preserve">organic hydroxy compound biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Snca/Agtr1a/Insig1/Abcg1/Mvd/Msmo1/Stard4/Lss/Sqle/Gba/Isyna1/Hmgcr/Lpcat3/Atp7a/Pmvk/Vps35/Sc5d/Ip6k1/Cyb5r3/Sirt1/Ppip5k2/Got1/Scp2/Abca2/H6pd/Plcg2/Nr1d1/Aldh2/Apoe/Sptssa</t>
+    <t xml:space="preserve">Snca/Ctns/Sptssa/Abcg1/Aldh2/Stard4/Abca2/Plcg2/Apoe/Insig1/Sqle/Isyna1/Gba/Msmo1/Agtr1a/Mvd/H6pd/Vps35/Lss/Nr1d1/Ppip5k2/Hmgcr/Lpcat3/Cyb5r3/Atp7a/Sirt1/Sc5d/Ip6k1/Scp2/Got1/Pmvk</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016032</t>
@@ -4273,7 +4273,7 @@
     <t xml:space="preserve">294/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Map3k1/Trim10/Agtr1a/Isg20/Pcx/Uvrag/Pikfyve/Rab43/Epor/Trim56/Igf2r/Ccnt1/Kpna6/Tmem41b/Dag1/Bax/Pkn2/Ddx6/Bcl2l11/Hexim1/Morc2a/Stom/Arl8b/Snx3/Setdb1/Vps4b/Usp6nl/Nedd4/Trim28/Cnot7/Nucks1/Ifitm2/Hsp90ab1/Rrp1b/Sp100/Ifih1/Oasl1/Trp53/Vapa/Apobec3/Tfap4/Cxcr4/Apoe/Mst1r/Lgals1/Oas2</t>
+    <t xml:space="preserve">Lgals1/Map3k1/Oas2/Trim10/Vapa/Cxcr4/Apoe/Mst1r/Igf2r/Pikfyve/Pcx/Tfap4/Uvrag/Apobec3/Rab43/Trp53/Dag1/Epor/Kpna6/Ddx6/Pkn2/Trim56/Agtr1a/Ccnt1/Isg20/Tmem41b/Morc2a/Nedd4/Hexim1/Nucks1/Bcl2l11/Arl8b/Hsp90ab1/Trim28/Ifih1/Ifitm2/Bax/Setdb1/Vps4b/Stom/Cnot7/Oasl1/Sp100/Snx3/Usp6nl/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043648</t>
@@ -4282,7 +4282,7 @@
     <t xml:space="preserve">dicarboxylic acid metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldh1l2/Pcx/Aldh4a1/Gls/Cs/Got1/Got2/Idh3g/Adss/Idh3a/Mthfd1/Mthfd1l/Qprt/Adssl1/Atic/Prodh/Kyat3</t>
+    <t xml:space="preserve">Kyat3/Pcx/Atic/Prodh/Adssl1/Aldh1l2/Idh3a/Cs/Mthfd1/Got2/Mthfd1l/Qprt/Aldh4a1/Idh3g/Got1/Adss/Gls</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000756</t>
@@ -4291,7 +4291,7 @@
     <t xml:space="preserve">regulation of peptidyl-lysine acetylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Nfe2/Snca/Wbp2/Arrb1/Flcn/Dip2b/Brca1/Sirt1/Ctcf/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Kat2a/Gata2/Tgfb1/Spi1</t>
+    <t xml:space="preserve">Snca/Tgfb1/Nfe2/Spi1/Glyr1/Kat2a/Wbp2/Dip2b/Gata2/Mybbp1a/Arrb1/Ruvbl2/Flcn/Sirt1/Brca1/Ctcf/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007032</t>
@@ -4300,7 +4300,7 @@
     <t xml:space="preserve">endosome organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Washc5/Pheta2/Als2/Vps11/Lamtor1/Arfgef2/Tmcc1/Dnajc13/Chmp3/Exoc8/Washc4/Snx3/Vps4b/Aktip/Snx10</t>
+    <t xml:space="preserve">Washc5/Pheta2/Vps11/Als2/Arfgef2/Dnajc13/Tmcc1/Snx10/Lamtor1/Aktip/Chmp3/Exoc8/Washc4/Vps4b/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051051</t>
@@ -4312,7 +4312,7 @@
     <t xml:space="preserve">385/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Cd36/Appl2/Wnk4/Abcg2/Dmtn/Cd47/Snca/Insig1/Kalrn/Slc43a1/Rhbdf1/Picalm/Yod1/Kel/Pea15a/Smcr8/Hmgcr/Atp7a/C9orf72/Vps35/Gnas/Rap1b/Sirt1/Snx3/Vps4b/Rack1/Grk6/Nedd4/Ppp3r1/Gopc/Prkca/Sp100/Idh2/Ppif/Fkbp1b/Pcsk9/Slc43a2/Ankrd13b/Abca2/Akap5/Hadh/Irak1/Zfas1/Ankrd27/Rgs2/Pim3/Lypla1/Gsto1/Lgals9/Apoe/Tgfb1/Sytl4/Spi1/Coro1a/Cd84/Rin3</t>
+    <t xml:space="preserve">Snca/Appl2/Picalm/Wnk4/Coro1a/Slc6a9/Tgfb1/Abcg2/Ankrd27/Dmtn/Cd47/Gsto1/Cd84/Lypla1/Spi1/Rin3/Abca2/Lgals9/Apoe/Cd36/Yod1/Insig1/Pim3/Kalrn/Hadh/Gnas/Irak1/Slc43a1/Idh2/Zfas1/Ankrd13b/Sytl4/Rgs2/Pea15a/Kel/Smcr8/Vps35/Rhbdf1/Ppif/Nedd4/Hmgcr/Prkca/Atp7a/Slc43a2/Rap1b/Sirt1/C9orf72/Ppp3r1/Pcsk9/Fkbp1b/Vps4b/Grk6/Rack1/Akap5/Sp100/Snx3/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016052</t>
@@ -4324,7 +4324,7 @@
     <t xml:space="preserve">132/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Aldh1a1/Pfkfb2/Eno3/Neu1/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Sord/Psen1/Man2b1/Lrp5/Gpi1/Man2c1/Prkag2/Trp53/Khk/Gusb/Hk2/Man2b2/Pgm2/P2rx7</t>
+    <t xml:space="preserve">Aldh1a1/Slc4a1/Pfkfb2/Man2b2/P2rx7/Ddit4/Khk/Gusb/Mtch2/Neu1/Mlst8/Pkm/Trp53/Prkag2/Pgm2/Man2c1/Man2b1/Eno3/Lrp5/Hk2/Psen1/Bpgm/Nupr1/Sord/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019216</t>
@@ -4336,7 +4336,7 @@
     <t xml:space="preserve">295/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Appl2/Mid1ip1/Snca/Agtr1a/Scd1/Insig1/Abcg1/Rubcnl/Ldlr/Stard4/Pcx/Lamtor1/Mlst8/Ppp2r5a/Ppard/Lpcat3/Sorbs1/Mtmr3/Brca1/Pip4k2c/Sirt1/Sh3glb1/Tbl1xr1/Phb2/Scp2/Dgkz/Igf1r/Stat5a/Mboat7/Gk/Prkag2/Tcf7l2/Abca2/Stat5b/Mtmr9/Acsl5/H6pd/Plcg2/Nr1d2/Rac1/Nr1d1/Apoe/Tgfb1/Pik3ip1</t>
+    <t xml:space="preserve">Egr1/Snca/Appl2/Mid1ip1/Tgfb1/Abcg1/Rac1/Ppp2r5a/Pik3ip1/Stard4/Abca2/Plcg2/Acsl5/Apoe/Stat5b/Cd36/Ldlr/Mtmr9/Insig1/Nr1d2/Pcx/Mlst8/Agtr1a/Mtmr3/Scd1/Stat5a/Gk/Prkag2/Dgkz/H6pd/Mboat7/Lamtor1/Ppard/Nr1d1/Sh3glb1/Lpcat3/Rubcnl/Sirt1/Scp2/Brca1/Phb2/Sorbs1/Igf1r/Tbl1xr1/Tcf7l2/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045859</t>
@@ -4351,7 +4351,7 @@
     <t xml:space="preserve">487/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Wnk4/Map3k1/Snca/Prkar2b/Agtr1a/Prnp/Nedd9/Als2/Gab1/Traf4/Tsc1/Uvrag/Stil/Cdc25b/Cdc6/Pim1/Ubash3b/Mapre3/Gba/Fzd5/Smcr8/Map3k12/Cdkn2c/Fbxw7/Hmgcr/Ggnbp2/Cib1/Shb/Dag1/Dvl2/Rap2b/Stradb/Hexim1/Rb1/Sirt1/Abi1/Qars/Psen1/Iqgap1/Phb2/Lrp5/Gtpbp4/Maged1/Cbl/Hsp90ab1/Prkca/Pik3r5/Rap2c/Prkag2/Ccng1/Irak1/Vangl2/Ptpn6/Xrcc5/Rgs2/Mmd/Pik3r6/Tfap4/Il4/Csf1/Rgs14/Apoe/Trib2/Tgfb1/Mst1r/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Egr1/Map3k1/Prkar2b/Snca/Syk/Ptprc/Wnk4/Prnp/Tgfb1/Tsc1/Trib2/Gab1/P2rx7/Als2/Ccng1/Apoe/Cdc25b/Mst1r/Mmd/Ptpn6/Xrcc5/Cdc6/Irak1/Tfap4/Traf4/Uvrag/Fbxw7/Rap2b/Gba/Rgs14/Cdkn2c/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Rgs2/Rap2c/Prkag2/Pik3r6/Ggnbp2/Maged1/Csf1/Smcr8/Rb1/Vangl2/Dvl2/Hmgcr/Hexim1/Lrp5/Cib1/Prkca/Ubash3b/Hsp90ab1/Mapre3/Psen1/Sirt1/Iqgap1/Stradb/Map3k12/Phb2/Gtpbp4/Abi1/Cbl/Qars/Pim1/Shb/Pik3r5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009896</t>
@@ -4363,7 +4363,7 @@
     <t xml:space="preserve">453/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Btg2/Trp53inp2/Scoc/Snca/Dnajb2/Optn/Zswim8/Tnrc6b/Tsc1/Vps11/Nupr1/Ldlr/Sesn1/Mylip/Ticam1/Rchy1/Rnf14/Gba/Trp53inp1/Mlst8/Gigyf2/Smcr8/Rnf139/Tbk1/Fbxw7/Flcn/Tob1/Bax/C9orf72/Sesn3/Gabarap/Vps35/Rnf185/Bcl2l11/Ago2/Bid/Tnrc6c/Pip4k2c/Tut7/Pias1/Sirt1/Clec16a/Sh3glb1/Celf1/Rack1/Psen1/Parn/Nedd4/Cnot7/Mov10/Ulk2/Exosc5/Dtx3l/Pcsk9/Vsir/Abca2/Dapk1/Acsl5/Sh3d19/Zfp36l1/Il4/Apoe/Trib2/Laptm5/P2rx7</t>
+    <t xml:space="preserve">Laptm5/Snca/Btg2/Tsc1/Trp53inp2/Trib2/Gigyf2/Scoc/Tnrc6b/Zswim8/P2rx7/Abca2/Vps11/Acsl5/Optn/Apoe/Ldlr/Rnf14/Sesn1/Fbxw7/Tbk1/Gba/Mlst8/Rchy1/Rnf139/Gabarap/Ticam1/Trp53inp1/Il4/Sh3d19/Zfp36l1/Dnajb2/Mylip/Smcr8/Vps35/Dapk1/Sh3glb1/Nedd4/Celf1/Tob1/Mov10/Dtx3l/Bcl2l11/Flcn/Vsir/Psen1/Bid/Sesn3/Exosc5/Ulk2/Sirt1/C9orf72/Pcsk9/Bax/Nupr1/Rnf185/Pias1/Ago2/Tut7/Tnrc6c/Cnot7/Rack1/Clec16a/Parn/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031346</t>
@@ -4372,7 +4372,7 @@
     <t xml:space="preserve">positive regulation of cell projection organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Grn/Kalrn/Neu1/Washc5/Ache/Picalm/Plek2/Numb/Epor/Tbc1d24/Wasl/Serpini1/Atp7a/Stk25/Pias2/Ppp2r5b/Cdkl5/Ehd1/Nckap1/Ttbk2/Golga4/Nck1/Tapt1/Twf1/Arhgap35/Sirt1/Fbxo38/Sh3glb1/Snx3/Iqgap1/Rpl4/Actr2/Stau2/Def8/Cul7/Igf1r/Megf8/Flna/Srf/Fkbp1b/Akap5/Arpc2/Atp1b2/Kat2a/Ankrd27/Rgs2/Rac1/Plxnc1/Ripor2/Rac2/Fes/Apoe/P2rx7</t>
+    <t xml:space="preserve">Cobl/Picalm/Rac2/Grn/Washc5/Ankrd27/Rac1/Ripor2/P2rx7/Kat2a/Arpc2/Apoe/Tbc1d24/Kalrn/Ache/Megf8/Flna/Ehd1/Neu1/Stk25/Epor/Numb/Pias2/Tapt1/Rgs2/Cul7/Wasl/Srf/Fes/Nckap1/Sh3glb1/Twf1/Atp1b2/Plxnc1/Def8/Atp7a/Ttbk2/Plek2/Fbxo38/Sirt1/Actr2/Iqgap1/Golga4/Cdkl5/Rpl4/Serpini1/Stau2/Arhgap35/Fkbp1b/Igf1r/Nck1/Ppp2r5b/Akap5/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070201</t>
@@ -4384,7 +4384,7 @@
     <t xml:space="preserve">479/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Sh3tc2/Ptp4a3/Rph3al/Dmtn/Ctsd/Insig1/Glrx/Prnp/Pfkfb2/Abcg1/Arntl/Rhbdf1/Picalm/Ptpn23/Yod1/Arrb1/Ppard/Fbxw7/Hmgcr/Cib1/Uhmk1/Birc5/Vps35/Gripap1/Brca1/Exoc1/Stom/Cdk16/Sirt1/Sh3glb1/Snx3/Rack1/Psen1/Dnajc27/Trim28/Ipo5/Cct6a/Ergic3/Gopc/Lrp5/Tm7sf3/Cct2/Hsp90ab1/Myh10/Wipf1/Hcls1/Sp100/Sar1b/Idh2/Flna/Ier3ip1/Fkbp1b/Tcf7l2/Ripor1/Akap5/Arpc2/Hadh/Pmaip1/Pim3/Rac1/Nr1d1/Lypla1/Apoe/Tgfb1/Sytl4/P2rx7/Lcp1</t>
+    <t xml:space="preserve">Sh3tc2/Ctsd/Picalm/Prnp/Tgfb1/Rph3al/Abcg1/Dmtn/Rac1/Lypla1/Pfkfb2/Ptpn23/P2rx7/Lcp1/Ripor1/Glrx/Arpc2/Apoe/Cd36/Yod1/Insig1/Pim3/Hadh/Flna/Pmaip1/Fbxw7/Arntl/Ptp4a3/Idh2/Sytl4/Myh10/Ppard/Vps35/Nr1d1/Uhmk1/Sh3glb1/Rhbdf1/Arrb1/Cct2/Hcls1/Hmgcr/Wipf1/Lrp5/Sar1b/Ergic3/Cib1/Cdk16/Hsp90ab1/Trim28/Ier3ip1/Birc5/Exoc1/Psen1/Sirt1/Tm7sf3/Brca1/Gripap1/Fkbp1b/Ipo5/Cct6a/Tcf7l2/Stom/Rack1/Akap5/Sp100/Snx3/Dnajc27/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030139</t>
@@ -4393,7 +4393,7 @@
     <t xml:space="preserve">endocytic vesicle</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Itsn1/H2-T23/Pip4p1/Vps11/Lamp1/Cltc/Anxa3/Uvrag/Pikfyve/Rab43/Rab22a/Igf2r/Clcn3/Myo6/Rabep1/Ftl1/Ehd1/Ap2m1/Snx3/Was/Sec61a1/Pik3c2b/Anxa11/Ehd3/Capg/Vim/Unc93b1/Coro1a/Dpp4/Syk/Rin3</t>
+    <t xml:space="preserve">Appl2/Syk/Coro1a/Cltc/Lamp1/Pip4p1/Capg/Itsn1/Rin3/Vps11/Vim/Unc93b1/Rabep1/Igf2r/Pikfyve/Dpp4/Uvrag/Ehd1/Rab22a/Rab43/Myo6/Clcn3/H2-T23/Anxa11/Anxa3/Ehd3/Ap2m1/Ftl1/Sec61a1/Snx3/Pik3c2b/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048259</t>
@@ -4405,7 +4405,7 @@
     <t xml:space="preserve">104/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Bmp2k/Picalm/Numb/Arrb1/Wasl/Smap1/Ap2m1/Nedd4/Ppp3r1/Cbl/Atad1/Prkca/Pcsk9/Ankrd13b/Abca2/Akap5/Plcg2/Il4/Syk/Rin3</t>
+    <t xml:space="preserve">Syk/Picalm/Bmp2k/Rin3/Abca2/Plcg2/Pld2/Numb/Ankrd13b/Il4/Atad1/Wasl/Arrb1/Nedd4/Smap1/Prkca/Ap2m1/Ppp3r1/Pcsk9/Cbl/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002833</t>
@@ -4417,7 +4417,7 @@
     <t xml:space="preserve">140/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Lamp1/Trim56/Tbk1/Rnf185/Hexim1/Fbxo38/Usp15/Nono/Matr3/Hspd1/Ap1g1/Prkca/Stat5a/Oasl1/Stat5b/Xrcc5/Plcg2/Vav1/Cadm1/Havcr2/Lgals9/Spi1/Tyrobp/Dpp4/Syk</t>
+    <t xml:space="preserve">Syk/Grn/Lamp1/Spi1/Vav1/Plcg2/Lgals9/Stat5b/Dpp4/Xrcc5/Tbk1/Ap1g1/Trim56/Tyrobp/Stat5a/Nono/Havcr2/Matr3/Hexim1/Prkca/Usp15/Cadm1/Fbxo38/Hspd1/Rnf185/Oasl1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009374</t>
@@ -4432,7 +4432,7 @@
     <t xml:space="preserve">3/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pcx/Acaca/Hlcs</t>
+    <t xml:space="preserve">Hlcs/Pcx/Acaca</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0020016</t>
@@ -4441,7 +4441,7 @@
     <t xml:space="preserve">ciliary pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">Ehd1/Snap29/Ehd3</t>
+    <t xml:space="preserve">Ehd1/Ehd3/Snap29</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0020018</t>
@@ -4456,7 +4456,7 @@
     <t xml:space="preserve">retromer, cargo-selective complex</t>
   </si>
   <si>
-    <t xml:space="preserve">Vps26a/Vps29/Vps35</t>
+    <t xml:space="preserve">Vps26a/Vps35/Vps29</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032805</t>
@@ -4465,7 +4465,7 @@
     <t xml:space="preserve">positive regulation of low-density lipoprotein particle receptor catabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pcsk9/Abca2/Apoe</t>
+    <t xml:space="preserve">Abca2/Apoe/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008652</t>
@@ -4474,7 +4474,7 @@
     <t xml:space="preserve">cellular amino acid biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldh1a1/Pycr1/Gls/Pycr2/Got1/Got2/Enoph1/Mtap/Plod3/Ilvbl/Mthfd1/Cad/Sdsl</t>
+    <t xml:space="preserve">Aldh1a1/Sdsl/Cad/Plod3/Mthfd1/Got2/Pycr1/Mtap/Got1/Enoph1/Ilvbl/Pycr2/Gls</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032613</t>
@@ -4489,7 +4489,7 @@
     <t xml:space="preserve">alpha-amino acid biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pycr1/Gls/Pycr2/Got1/Got2/Enoph1/Mtap/Plod3/Ilvbl/Mthfd1/Cad/Sdsl</t>
+    <t xml:space="preserve">Sdsl/Cad/Plod3/Mthfd1/Got2/Pycr1/Mtap/Got1/Enoph1/Ilvbl/Pycr2/Gls</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902105</t>
@@ -4498,7 +4498,7 @@
     <t xml:space="preserve">regulation of leukocyte differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Egr3/Tal1/Prdx2/Fos/Zbtb7b/Ubash3b/Fbxw7/Ap3d1/Shb/Rara/Gnas/Rb1/Gfi1b/Asxl2/Phf10/Ctnnb1/Hcls1/Prkca/Stat5a/Vsir/Smarcd1/Stat5b/Ptpn6/Kat2a/Gata2/Zfp36l1/Cbfb/Pik3r6/Il4/Csf1/Fes/Lgals9/Mmp14/Tgfb1/Cd44/Tyrobp/Ptprc/Myb/Cdk6/Jak3/Nfam1/Syk</t>
+    <t xml:space="preserve">Car2/Prdx2/Jak3/Nfam1/Syk/Myb/Ptprc/Tgfb1/Cdk6/Tal1/Cd44/Cbfb/Lgals9/Kat2a/Stat5b/Ptpn6/Gnas/Fbxw7/Smarcd1/Egr3/Zbtb7b/Tyrobp/Stat5a/Il4/Gata2/Mmp14/Pik3r6/Fes/Zfp36l1/Csf1/Ctnnb1/Ap3d1/Rb1/Hcls1/Prkca/Ubash3b/Vsir/Fos/Rara/Gfi1b/Asxl2/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010975</t>
@@ -4507,7 +4507,7 @@
     <t xml:space="preserve">regulation of neuron projection development</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Sema4b/Grn/Kalrn/Neu1/Washc5/Ache/Tsc1/Picalm/Adam10/Mylip/Numb/Kel/Dpysl2/Epor/Trak2/Tbc1d24/Serpini1/Kif13b/Xk/Cib1/Stk25/Pias2/Dip2b/Ppp2r5b/Cdkl5/Ehd1/Camsap2/Golga4/Nck1/Acap3/Twf1/Arhgap35/Sirt1/Fbxo38/Sh3glb1/Snx3/Psen1/Iqgap1/Rpl4/Actr2/Nedd4/Itm2c/Stau2/Syngap1/Ulk2/Cul7/Igf1r/Megf8/Flna/Srf/Ptpn9/Fkbp1b/Akap5/Sema4a/Atp1b2/Ankrd27/Rgs2/Plxnc1/Vim/Ptprs/Fes/Apoe/Lgals1</t>
+    <t xml:space="preserve">Lgals1/Cobl/Picalm/Ptprs/Grn/Washc5/Ankrd27/Tsc1/Vim/Apoe/Adam10/Tbc1d24/Kalrn/Ache/Megf8/Flna/Dip2b/Ehd1/Neu1/Stk25/Dpysl2/Epor/Numb/Pias2/Sema4b/Xk/Rgs2/Cul7/Sema4a/Srf/Fes/Ptpn9/Mylip/Kel/Sh3glb1/Twf1/Nedd4/Camsap2/Atp1b2/Plxnc1/Trak2/Cib1/Psen1/Kif13b/Ulk2/Fbxo38/Sirt1/Actr2/Iqgap1/Golga4/Cdkl5/Rpl4/Serpini1/Stau2/Syngap1/Itm2c/Arhgap35/Fkbp1b/Igf1r/Nck1/Ppp2r5b/Akap5/Acap3/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1900407</t>
@@ -4519,7 +4519,7 @@
     <t xml:space="preserve">77/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Glrx/Tsc1/Pycr1/Epor/Tbc1d24/Fbxw7/Rnf146/Mcl1/Sirt1/Rack1/Parp1/Nono/Ctnnb1/Lancl1/Fut8/Trp53</t>
+    <t xml:space="preserve">Tsc1/Glrx/Cd36/Tbc1d24/Fbxw7/Trp53/Fut8/Epor/Rnf146/Nono/Ctnnb1/Mcl1/Lancl1/Sirt1/Pycr1/Parp1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071706</t>
@@ -4537,7 +4537,7 @@
     <t xml:space="preserve">209/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mrm1/Isg20/Pop5/Utp14b/Helq/Ddx27/Rpl35/Ddx18/Snu13/Pa2g4/Ddx21/Ddx49/Gtpbp4/Rcl1/Ebna1bp2/Wdr36/Rrp1b/Urb1/Pwp1/Trmt2b/Exosc1/Lyar/Wdr43/Exosc5/Mdn1/Heatr1/Nat10/Naf1/Rrp12/Rpl10a/Nol6/Wdr46/Tfb2m/Rrp9/Npm3</t>
+    <t xml:space="preserve">Npm3/Nat10/Rpl10a/Rrp9/Wdr46/Utp14b/Trmt2b/Mrm1/Nol6/Pop5/Naf1/Tfb2m/Isg20/Rrp12/Heatr1/Mdn1/Pwp1/Urb1/Wdr43/Exosc5/Ddx18/Rcl1/Exosc1/Snu13/Wdr36/Lyar/Gtpbp4/Ebna1bp2/Ddx21/Helq/Ddx27/Ddx49/Rpl35/Pa2g4/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050867</t>
@@ -4549,7 +4549,7 @@
     <t xml:space="preserve">313/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Pld2/Egr3/Cd47/Tfrc/Lamp1/Ticam1/Zbtb7b/Ap3d1/Shb/Rara/Fcho1/Nck1/Phf10/Tcf3/Hspd1/Ap1g1/Cd320/Shld2/Flna/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Il27ra/Gata2/Gab2/Cbfb/Dock8/Havcr2/Pik3r6/Il4/Lgals9/Spn/Mmp14/Tgfb1/Ccdc88b/Tyrobp/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Il1rl1/Syk</t>
+    <t xml:space="preserve">Lgals1/Spta1/Jak3/Il1rl1/Syk/Slc4a1/Myb/Ptprc/Coro1a/Ccdc88b/Tgfb1/Spn/Lamp1/Cd47/Dock8/Cbfb/Gab2/Lgals9/Stat5b/Pld2/Dpp4/Flna/Ap1g1/Smarcd1/Egr3/Zbtb7b/Ticam1/Tyrobp/Stat5a/Il4/Gata2/Mmp14/Pik3r6/Ap3d1/Il27ra/Havcr2/Tfrc/Itgb2/Tcf3/Vsir/Hspd1/Rara/Cd320/Shld2/Nck1/Fcho1/Shb/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032261</t>
@@ -4570,7 +4570,7 @@
     <t xml:space="preserve">186/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Snca/Pkm/Flcn/Adal/Gcdh/Ndufa10/Parp1/Adss/Prps1/Dlat/Impdh2/Guk1/Pdha1/Mtap/Aprt/Adsl/Mthfd1/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Gart/Npr2/Pgm2/Il4/Tgfb1/Nme4/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Nme4/Gart/Pfas/Acsl5/Pdha1/Atic/Pkm/Il4/Adssl1/Npr2/Adsl/Pgm2/Gmpr/Impdh2/Mthfd1/Papss2/Guk1/Prps1/Dlat/Adal/Flcn/Gcdh/Ak4/Ndufa10/Aprt/Mtap/Adss/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031929</t>
@@ -4579,7 +4579,7 @@
     <t xml:space="preserve">TOR signaling</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Pip4p1/Arntl/Rragc/Ddit4/Tsc1/Sesn1/Lamtor1/Gba/Mlst8/Smcr8/Flcn/Usp9x/Lamtor3/C9orf72/Sesn3/Rictor/Tti1/Sirt1/Rps6kb1/Fnip1/Clec16a/Eif4ebp2</t>
+    <t xml:space="preserve">Rragc/Ctns/Tsc1/Pip4p1/Ddit4/Sesn1/Gba/Eif4ebp2/Arntl/Mlst8/Usp9x/Lamtor3/Lamtor1/Smcr8/Flcn/Sesn3/Sirt1/C9orf72/Tti1/Fnip1/Clec16a/Rps6kb1/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055094</t>
@@ -4591,7 +4591,7 @@
     <t xml:space="preserve">23/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ldlr/Mylip/Ticam1/Mia3/Itgb2/Apoe/Syk</t>
+    <t xml:space="preserve">Syk/Apoe/Cd36/Ldlr/Ticam1/Mylip/Itgb2/Mia3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0003779</t>
@@ -4603,7 +4603,7 @@
     <t xml:space="preserve">363/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cobl/Spta1/Fhdc1/Tmod1/Add2/Dmtn/Sptb/S100a4/Snca/Map1a/Epb41/Micall2/Samd14/Actn1/Mybpc3/Ssh2/Stk38l/Myo6/Wasl/Ppp1r9b/Dag1/Dyrk1a/Myo9a/Twf1/Vcl/Daam1/Cttn/Iqgap1/Actr2/Was/Flii/Wdr1/Tnni3/Parvg/Myh10/Wipf1/Hcls1/Sptan1/Flna/Cap1/Epb41l1/Akap5/Arpc2/Adssl1/Pdlim2/Capg/Cxcr4/Vill/Vash2/Rcsd1/Coro1a/Myo1g/Lcp1</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Snca/Myo1g/Slc4a1/Vill/Coro1a/Tmod1/Dmtn/Capg/Rcsd1/Vash2/Cap1/Actn1/Micall2/Lcp1/Cxcr4/Arpc2/Dyrk1a/Flna/S100a4/Samd14/Stk38l/Epb41/Map1a/Ssh2/Myo6/Dag1/Myh10/Adssl1/Wasl/Ppp1r9b/Wdr1/Flii/Twf1/Hcls1/Wipf1/Sptan1/Pdlim2/Actr2/Tnni3/Epb41l1/Iqgap1/Parvg/Cttn/Akap5/Myo9a/Vcl/Daam1/Mybpc3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0110053</t>
@@ -4615,7 +4615,7 @@
     <t xml:space="preserve">233/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Cd47/Washc2/Washc5/Tsc1/Asap3/Ssh2/Mlst8/Wasl/Plekhg2/C9orf72/Nckap1/Nck1/Rictor/Swap70/Twf1/Washc4/Arhgap35/Cttn/Was/Flii/Wdr1/Hcls1/Sptan1/Flna/Sh3pxd2b/Arpc2/Pdxp/Rac1/Capg/Vill/Coro1a/Arhgef18</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Vill/Coro1a/Tmod1/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Arpc2/Arhgef18/Flna/Mlst8/Sh3pxd2b/Ssh2/Pdxp/Wasl/Nckap1/Wdr1/Flii/Twf1/Plekhg2/Hcls1/Asap3/Sptan1/Swap70/Washc4/C9orf72/Arhgap35/Nck1/Cttn/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0150034</t>
@@ -4627,7 +4627,7 @@
     <t xml:space="preserve">281/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Atp6v0d1/Snca/Itsn1/Mylk2/Prnp/Als2/Tsc1/Dpysl2/Hdac5/Trak2/Clcn3/Map3k12/Usp9x/Polg/Cib1/Ap3d1/Ppp1r9b/C9orf72/Cdkl5/Myo9a/Acap3/Elk1/Cttn/Sirt1/Psen1/Iqgap1/Got1/Cbl/Fkbp1a/Hsp90ab1/Copg2/Myh10/Prkca/Flna/Unc13a/Arpc2/Slc4a8/Atp1a3/Cplx2/Kcnab2/Cxcr4/Tspoap1/P2rx7</t>
+    <t xml:space="preserve">Atp6v0d1/Cobl/Snca/Tspoap1/Prnp/Tsc1/Itsn1/Kcnab2/P2rx7/Cxcr4/Als2/Arpc2/Flna/Polg/Clcn3/Usp9x/Dpysl2/Myh10/Ppp1r9b/Ap3d1/Hdac5/Copg2/Slc4a8/Mylk2/Trak2/Cib1/Cplx2/Prkca/Hsp90ab1/Atp1a3/Elk1/Psen1/Sirt1/Fkbp1a/C9orf72/Iqgap1/Cdkl5/Got1/Map3k12/Unc13a/Cbl/Cttn/Acap3/Myo9a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016301</t>
@@ -4636,7 +4636,7 @@
     <t xml:space="preserve">kinase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Fn3k/Mink1/Wnk4/Map3k1/Bmp2k/Mylk2/Kalrn/Pfkfb2/Hipk2/Dmpk/Pkm/Pim1/Pikfyve/Grk5/Stk38l/Map3k12/Tbk1/Sgk3/Pmvk/Stk25/Ppp1r9b/Cdkl5/Uhmk1/Ttbk2/Pkn2/Dyrk1a/N4bp2/Clk3/Ip6k1/Twf1/Mknk1/Pip4k2c/Dbf4/Cdk16/Mknk2/Rps6kb1/Taok1/Cdc42bpa/Pi4ka/Grk6/Ppip5k2/Trim28/Nek4/Nek9/Prps1/Pik3c2b/Dgkz/Pfkfb3/Guk1/Ulk2/Igf1r/Prkca/Rps6ka2/Adck1/Gk/Prkag2/Map4k1/Map3k15/Agk/Pik3cd/Amhr2/Dapk1/Cad/Irak1/Khk/Ak4/Lrrk1/Papss2/Hk2/Npr2/Pim3/Mmd/Pgm2/Pik3r6/Fes/Map3k6/Trib2/Nme4/Mst1r/Btk/Cdk6/Jak3/Syk/Eng</t>
+    <t xml:space="preserve">Btk/Map3k1/Jak3/Syk/Wnk4/Mink1/Cdk6/Trib2/Pfkfb2/Nme4/Fn3k/Bmp2k/Eng/Mst1r/Pikfyve/Mmd/Khk/Dyrk1a/Pim3/Kalrn/Hipk2/Lrrk1/Irak1/Tbk1/Cad/Stk25/Stk38l/Pkm/Pkn2/Agk/Pik3cd/Gk/Prkag2/Npr2/Dgkz/Map4k1/Map3k6/Ppp1r9b/Pgm2/Pik3r6/Fes/Grk5/Dapk1/Uhmk1/Nek9/Amhr2/Dmpk/Twf1/Ppip5k2/Map3k15/Papss2/Mylk2/Guk1/Prps1/Mknk2/Clk3/Prkca/Cdk16/Trim28/Ttbk2/Hk2/Rps6ka2/Ulk2/Adck1/Ip6k1/Ak4/Taok1/Nek4/Cdkl5/Cdc42bpa/Map3k12/Sgk3/Pfkfb3/N4bp2/Igf1r/Dbf4/Grk6/Pmvk/Mknk1/Pim1/Rps6kb1/Pip4k2c/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901981</t>
@@ -4648,7 +4648,7 @@
     <t xml:space="preserve">156/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Washc2/Rubcnl/Picalm/Plek2/Nrgn/Zfyve26/Chmp3/Atg2b/Ttpal/Twf1/Exoc1/Snx3/Iqgap1/Flii/Snx5/Arhgap9/Fzd7/Sh3pxd2b/Dennd1c/Snx10/Gab2/Capg/Phlda2/Adap1/Vill/Btk/Myo1g/Arap3</t>
+    <t xml:space="preserve">Arap3/Btk/Myo1g/Picalm/Vill/Washc2/Capg/Gab2/Adap1/Sh3pxd2b/Atg2b/Phlda2/Fzd7/Zfyve26/Snx10/Flii/Twf1/Chmp3/Nrgn/Snx5/Arhgap9/Rubcnl/Exoc1/Plek2/Ttpal/Iqgap1/Dennd1c/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001934</t>
@@ -4657,7 +4657,7 @@
     <t xml:space="preserve">positive regulation of protein phosphorylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Wnk4/Map3k1/Snca/Agtr1a/Tfrc/Prnp/Hipk2/Nedd9/Als2/Gab1/Traf4/Fnip2/Gdf11/Stil/Cdc25b/Cdc6/Pim1/Mapre3/Mlst8/Arrb1/Fzd5/Map3k12/Fbxw7/Mob3c/Flcn/Cib1/Dag1/Dvl2/Rap2b/Birc5/Rictor/Stradb/Gnas/Sirt1/Adipor2/Fnip1/Abi1/Rack1/Psen1/Iqgap1/Phb2/Maged1/Pde4d/Hsp90ab1/Hcls1/Prkca/Pik3r5/Rap2c/Prkag2/Akap5/Trp53/Aktip/Irak1/Vangl2/Xrcc5/Plcg2/Lrrk1/Mob3b/Itga5/Rac1/Mmd/Pik3r6/Il4/Csf1/Cxcr4/Lgals9/Arhgef2/Spn/Tgfb1/Cd44/Gdf3/Mst1r/Ptprc/P2rx7/Syk/Eng</t>
+    <t xml:space="preserve">Egr1/Map3k1/Snca/Syk/Arhgef2/Ptprc/Wnk4/Prnp/Tgfb1/Spn/Cd44/Rac1/Fnip2/Gab1/Eng/P2rx7/Plcg2/Lgals9/Cxcr4/Als2/Cdc25b/Mst1r/Cd36/Mmd/Xrcc5/Itga5/Hipk2/Gnas/Lrrk1/Cdc6/Irak1/Traf4/Fbxw7/Rap2b/Mlst8/Gdf3/Gdf11/Mob3b/Trp53/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Rap2c/Prkag2/Pik3r6/Maged1/Csf1/Aktip/Arrb1/Vangl2/Dvl2/Tfrc/Hcls1/Cib1/Prkca/Hsp90ab1/Adipor2/Flcn/Mapre3/Birc5/Psen1/Sirt1/Iqgap1/Fnip1/Stradb/Map3k12/Phb2/Abi1/Mob3c/Rack1/Pim1/Akap5/Pik3r5/Pde4d/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010638</t>
@@ -4669,7 +4669,7 @@
     <t xml:space="preserve">465/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Map3k1/Ank1/Tal1/Cd47/Snca/Ddhd1/Grn/Abcg1/Tsc1/Stil/Slf2/Mlst8/Smcr8/Wasl/Fbxo5/Gpsm2/Ppp1r10/Bax/Nckap1/Ttbk2/Vps35/Nck1/Bcl2l11/Rictor/Bid/Tapt1/Swap70/Rb1/Togaram1/Morc2a/Acd/Pip4k2c/Arhgap35/Cttn/Clec16a/Sh3glb1/Setdb1/Vps4b/Ctnnb1/Parn/Was/Trim28/Cct6a/Lrp5/Cct2/Wdr1/Ruvbl2/Igf1r/Lman1/Slain2/Flna/Adck1/Ppif/Naf1/Sh3pxd2b/Arpc2/Trp53/Pdxp/Terc/Xrcc5/Surf4/Pmaip1/Rac1/Fes/P2rx7/Lcp1</t>
+    <t xml:space="preserve">Map3k1/Snca/Grn/Abcg1/Tal1/Tsc1/Ank1/Rac1/Cd47/Surf4/P2rx7/Lcp1/Slf2/Arpc2/Xrcc5/Ddhd1/Flna/Lman1/Pmaip1/Mlst8/Sh3pxd2b/Trp53/Pdxp/Stil/Tapt1/Wasl/Naf1/Fes/Terc/Ctnnb1/Nckap1/Slain2/Wdr1/Smcr8/Vps35/Rb1/Sh3glb1/Morc2a/Ppif/Togaram1/Fbxo5/Gpsm2/Ruvbl2/Cct2/Lrp5/Ppp1r10/Bcl2l11/Swap70/Trim28/Ttbk2/Bid/Acd/Adck1/Bax/Setdb1/Arhgap35/Igf1r/Cct6a/Nck1/Vps4b/Cttn/Clec16a/Parn/Pip4k2c/Rictor/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032355</t>
@@ -4678,7 +4678,7 @@
     <t xml:space="preserve">response to estradiol</t>
   </si>
   <si>
-    <t xml:space="preserve">Fam210b/Grn/Glrx/Socs2/Ncoa1/Ctnnb1/Ruvbl2/Prkca/Stat5b/Tgfb1</t>
+    <t xml:space="preserve">Fam210b/Tgfb1/Grn/Glrx/Stat5b/Socs2/Ctnnb1/Ruvbl2/Prkca/Ncoa1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901293</t>
@@ -4699,7 +4699,7 @@
     <t xml:space="preserve">315/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Appl2/Wnk4/Tfrc/Rragc/Tsc1/Fos/Ldlr/Sesn1/Map1lc3b/Pim1/Gba/Mlst8/Bhlha15/Alad/Flcn/Bax/Sesn3/Xpr1/Gabarap/Rictor/Mtmr3/Ncoa1/Arhgap35/Sirt1/Rps6kb1/Fnip1/Clec16a/Sh3glb1/Tbl1xr1/Plin2/Pik3c2b/Ulk2/Adsl/Srf/Pcsk9/Mybbp1a/Prkag2/Tcf7l2/Ripor1/Trp53/Pmaip1/Hlcs/Fes/Apoe/Gdf3/Ptprc/P2rx7</t>
+    <t xml:space="preserve">Appl2/Ptprc/Wnk4/Rragc/Tsc1/Cpeb4/P2rx7/Ripor1/Hlcs/Apoe/Map1lc3b/Ldlr/Sesn1/Xpr1/Pmaip1/Gba/Mlst8/Gdf3/Trp53/Gabarap/Mtmr3/Prkag2/Adsl/Srf/Fes/Mybbp1a/Sh3glb1/Tfrc/Flcn/Bhlha15/Sesn3/Ulk2/Sirt1/Fos/Ncoa1/Alad/Fnip1/Pcsk9/Bax/Arhgap35/Tbl1xr1/Tcf7l2/Clec16a/Pim1/Rps6kb1/Plin2/Pik3c2b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042116</t>
@@ -4711,7 +4711,7 @@
     <t xml:space="preserve">78/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Wnk4/Snca/Grn/Ldlr/Ticam1/Ifngr1/Hspd1/Cst7/Plcg2/Nr1d1/Havcr2/Il4/Lgals9/Tyrobp/Il1rl1/Cd84/Syk</t>
+    <t xml:space="preserve">Snca/Il1rl1/Syk/Wnk4/Grn/Cd84/Plcg2/Lgals9/Ldlr/Ticam1/Tyrobp/Il4/Nr1d1/Havcr2/Hspd1/Ifngr1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006189</t>
@@ -4723,7 +4723,7 @@
     <t xml:space="preserve">6/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Adsl/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">Gart/Pfas/Atic/Adsl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032799</t>
@@ -4732,7 +4732,7 @@
     <t xml:space="preserve">low-density lipoprotein receptor particle metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Mylip/Pcsk9/Abca2/Apoe</t>
+    <t xml:space="preserve">Abca2/Apoe/Mylip/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032802</t>
@@ -4753,7 +4753,7 @@
     <t xml:space="preserve">tetrahydrofolate biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Mthfd1/Mthfd1l/Atic/Gart</t>
+    <t xml:space="preserve">Gart/Atic/Mthfd1/Mthfd1l</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016469</t>
@@ -4777,7 +4777,7 @@
     <t xml:space="preserve">positive regulation of TOR signaling</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Pip4p1/Rragc/Lamtor1/Mlst8/Smcr8/Flcn/Usp9x/Lamtor3/Rictor/Fnip1/Clec16a</t>
+    <t xml:space="preserve">Rragc/Ctns/Pip4p1/Mlst8/Usp9x/Lamtor3/Lamtor1/Smcr8/Flcn/Fnip1/Clec16a/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045471</t>
@@ -4786,7 +4786,7 @@
     <t xml:space="preserve">response to ethanol</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldh1a1/Trp53inp1/Alad/Rara/Sirt1/Got2/Igf1r/Prkca/Eef1b2/Gk/Aldh2/Adcy7</t>
+    <t xml:space="preserve">Adcy7/Aldh1a1/Aldh2/Trp53inp1/Gk/Eef1b2/Got2/Prkca/Sirt1/Alad/Rara/Igf1r</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010256</t>
@@ -4798,7 +4798,7 @@
     <t xml:space="preserve">67/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Fhdc1/Sh3tc2/Sptb/Optn/Abcg1/Washc5/Pheta2/Als2/Dmpk/Vps11/Cltc/Rab43/Lamtor1/Arfgef2/Bhlha15/Retreg2/Tmcc1/Wasl/Hace1/Dnajc13/Rfx2/Lpcat3/Ap3d1/Stk25/Chmp3/Camsap2/Exoc8/Nemp1/Trappc8/Washc4/Reep5/Arl8b/Cog4/Tor1aip2/Snap29/Mia3/Sh3glb1/Uso1/Snx3/Vps4b/Usp6nl/Sec61a1/Gorasp2/Esyt1/Myh10/Use1/Ap1g1/Lman1/Tmed5/Ehd3/Ugcg/Srgn/Tmed3/Aktip/Surf4/Snx10/Ano6/Cplx2/Ywhaz/Cxcr4/Col5a1/Sytl4/Emc4/Ptprc/P2rx7</t>
+    <t xml:space="preserve">Spta1/Sh3tc2/Fhdc1/Sptb/Slc4a1/Ptprc/Ano6/Emc4/Ywhaz/Cltc/Washc5/Abcg1/Surf4/P2rx7/Pheta2/Vps11/Optn/Cxcr4/Als2/Arfgef2/Ugcg/Col5a1/Lman1/Tmed3/Dnajc13/Stk25/Rab43/Ap1g1/Tmcc1/Retreg2/Hace1/Sytl4/Myh10/Wasl/Snx10/Lamtor1/Ap3d1/Aktip/Trappc8/Sh3glb1/Dmpk/Gorasp2/Camsap2/Rfx2/Esyt1/Chmp3/Exoc8/Srgn/Lpcat3/Reep5/Cplx2/Arl8b/Ehd3/Washc4/Bhlha15/Tmed5/Sec61a1/Cog4/Tor1aip2/Vps4b/Mia3/Use1/Snx3/Snap29/Usp6nl/Uso1/Nemp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901216</t>
@@ -4810,7 +4810,7 @@
     <t xml:space="preserve">113/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Snca/Optn/Grn/Prnp/Ddit4/Picalm/Fos/Nupr1/Fbxw7/Bax/Bcl2l11/Elk1/Mcl1/Parp1/Ctnnb1/Ncf2/Pcsk9/Trp53/Pmaip1/Apoe/Tyrobp</t>
+    <t xml:space="preserve">Egr1/Snca/Picalm/Prnp/Grn/Ddit4/Optn/Apoe/Pmaip1/Fbxw7/Trp53/Tyrobp/Ctnnb1/Mcl1/Bcl2l11/Ncf2/Elk1/Fos/Pcsk9/Bax/Nupr1/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031669</t>
@@ -4819,7 +4819,7 @@
     <t xml:space="preserve">cellular response to nutrient levels</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Rragc/Tsc1/Sesn1/Map1lc3b/Pim1/Gba/Mlst8/Bhlha15/Flcn/Sesn3/Xpr1/Gabarap/Rictor/Mtmr3/Ncoa1/Sirt1/Fnip1/Clec16a/Sh3glb1/Plin2/Pik3c2b/Srf/Pcsk9/Mybbp1a/Prkag2/Tcf7l2/Ripor1/Trp53/Pmaip1/Fes</t>
+    <t xml:space="preserve">Rragc/Tsc1/Cpeb4/Ripor1/Map1lc3b/Sesn1/Xpr1/Pmaip1/Gba/Mlst8/Trp53/Gabarap/Mtmr3/Prkag2/Srf/Fes/Mybbp1a/Sh3glb1/Flcn/Bhlha15/Sesn3/Sirt1/Ncoa1/Fnip1/Pcsk9/Tcf7l2/Clec16a/Pim1/Plin2/Pik3c2b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042626</t>
@@ -4828,7 +4828,7 @@
     <t xml:space="preserve">ATPase-coupled transmembrane transporter activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Abcb10/Abcg2/Atp6v1d/Abcb6/Abcg1/Atp6v1c1/Atp6v1e1/Atp2b1/Atp6v1a/Atp6v1b2/Atp7a/Atp6v0b/Atp6v1g1/Abca2/Abcb8/Atp1b2/Atp1a3</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Abcb6/Abcb10/Abcg2/Atp6v1c1/Atp6v1e1/Abcg1/Abca2/Atp2b1/Atp6v1b2/Atp6v1a/Abcb8/Atp6v0b/Atp1b2/Atp1a3/Atp7a/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030101</t>
@@ -4837,7 +4837,7 @@
     <t xml:space="preserve">natural killer cell activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Ticam1/Tusc2/Elf4/Tcf3/Ap1g1/Stat5a/Itgb2/Stat5b/Unc13d/Havcr2/Lgals9/Tyrobp/Ptprc/Coro1a</t>
+    <t xml:space="preserve">Ptprc/Coro1a/Lamp1/Lgals9/Stat5b/Unc13d/Ap1g1/Ticam1/Tyrobp/Stat5a/Havcr2/Itgb2/Tcf3/Tusc2/Elf4</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901657</t>
@@ -4846,7 +4846,7 @@
     <t xml:space="preserve">glycosyl compound metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Abcg2/Oard1/Gba/Adal/Prps1/Tyw1/Mtap/Aprt/Gla/Umps/Macrod1/Atic/Gusb/Pgm2/Uprt</t>
+    <t xml:space="preserve">Abcg2/Uprt/Gusb/Atic/Gba/Umps/Pgm2/Oard1/Prps1/Adal/Tyw1/Gla/Aprt/Mtap/Macrod1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034248</t>
@@ -4855,7 +4855,7 @@
     <t xml:space="preserve">regulation of cellular amide metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Btg2/Snca/Fech/Prnp/Tnrc6b/Abcg1/Tsc1/Picalm/Pkm/Ppp1r15b/Mlst8/Gigyf2/Rnf139/Habp4/Tob1/Rara/Uhmk1/Nck1/Ddx6/Aco1/Ago2/Tnrc6c/Mknk1/Tut7/Mknk2/Rps6kb1/Celf1/Rack1/Parn/Cnot7/Pa2g4/Ifngr1/Pus7/Zfp706/Eif4g2/Mov10/Tcof1/Cnbp/Trnau1ap/Prkca/Exosc5/Dph6/Eif4ebp2/Otud6b/Nat10/Mrps27/Abca2/Trp53/Dapk1/Bzw2/Ogfod1/Zfp36l1/Msi1/Rgs2/Ago4/Vim/Apoe</t>
+    <t xml:space="preserve">Snca/Btg2/Picalm/Prnp/Fech/Abcg1/Tsc1/Cpeb4/Gigyf2/Tnrc6b/Abca2/Vim/Apoe/Ago4/Eif4ebp2/Bzw2/Mlst8/Nat10/Pkm/Tcof1/Trp53/Rnf139/Ddx6/Habp4/Ogfod1/Mrps27/Rgs2/Ppp1r15b/Aco1/Zfp36l1/Msi1/Otud6b/Dapk1/Uhmk1/Celf1/Cnbp/Tob1/Mov10/Pus7/Mknk2/Prkca/Zfp706/Dph6/Exosc5/Eif4g2/Ifngr1/Rara/Ago2/Tut7/Trnau1ap/Tnrc6c/Nck1/Cnot7/Mknk1/Rack1/Parn/Pa2g4/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060249</t>
@@ -4867,7 +4867,7 @@
     <t xml:space="preserve">267/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldh1a1/Car2/Mink1/Trp53inp2/Map1a/Tfrc/Tpp1/Ubash3b/Gigyf2/Clcn3/Cln8/Atp7a/Bax/Gnas/Rb1/Slc39a8/Homer1/Acaca/Taok1/Psen1/Ctnnb1/Wdr36/Def8/Ldb1/Prkca/Slc22a5/P2rx1/Srf/Atp1b2/Gata2/Lrrk1/Snx10/Tjp3/Rac1/Rac2/Col11a2/Csf1/Tgfb1/Coro1a/P2rx7/Syk/Muc13</t>
+    <t xml:space="preserve">Car2/Aldh1a1/Syk/Mink1/Coro1a/Tpp1/Rac2/Tgfb1/Trp53inp2/Rac1/Gigyf2/P2rx7/Muc13/Gnas/Lrrk1/Map1a/Clcn3/Ldb1/Col11a2/Gata2/Srf/Csf1/Snx10/Ctnnb1/Tjp3/Rb1/Atp1b2/Tfrc/Def8/Prkca/Ubash3b/Acaca/Atp7a/Psen1/Taok1/Bax/Slc22a5/Wdr36/Slc39a8/Homer1/P2rx1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051607</t>
@@ -4876,7 +4876,7 @@
     <t xml:space="preserve">defense response to virus</t>
   </si>
   <si>
-    <t xml:space="preserve">Ddit4/Isg20/Ticam1/Trim56/Tbk1/Elmod2/Rnf185/Serinc5/Irf2/Ppm1b/Usp15/Serinc3/Trim28/Cnot7/Phb2/Ifitm2/Ddx21/Trim35/Ifngr1/Mov10/Traf3/Exosc5/Dtx3l/Polr3e/Ifih1/Oasl1/Traf3ip2/Unc13d/Apobec3/Pmaip1/Cd37/Irf5/Il4/Rnf125/Spn/Unc93b1/Ptprc/Oas2</t>
+    <t xml:space="preserve">Ptprc/Spn/Oas2/Ddit4/Unc93b1/Rnf125/Unc13d/Pmaip1/Tbk1/Apobec3/Irf5/Trim56/Traf3/Ticam1/Il4/Cd37/Isg20/Polr3e/Mov10/Dtx3l/Usp15/Trim28/Ifih1/Serinc5/Exosc5/Ifitm2/Traf3ip2/Ifngr1/Serinc3/Rnf185/Trim35/Phb2/Irf2/Ddx21/Cnot7/Oasl1/Elmod2/Ppm1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002695</t>
@@ -4885,7 +4885,7 @@
     <t xml:space="preserve">negative regulation of leukocyte activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Prdx2/Grn/Prnp/Ldlr/Zbtb7b/Samsn1/Vsir/Cst7/Ptpn6/Cd37/Nr1d1/Cbfb/Ripor2/Havcr2/Il4/Lgals9/Spn/Lgals7/Tgfb1/Cd44/Laptm5/Spi1/Tyrobp/Btk/Jak3/Tbc1d10c/Cd84</t>
+    <t xml:space="preserve">Prdx2/Btk/Jak3/Laptm5/Prnp/Tgfb1/Grn/Spn/Cd44/Cd84/Ripor2/Cbfb/Spi1/Tbc1d10c/Lgals9/Ldlr/Ptpn6/Zbtb7b/Tyrobp/Il4/Lgals7/Cd37/Nr1d1/Havcr2/Vsir/Samsn1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002705</t>
@@ -4894,7 +4894,7 @@
     <t xml:space="preserve">positive regulation of leukocyte mediated immunity</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Tfrc/Lamp1/Ticam1/Fzd5/Fbxo38/Ddx21/Hspd1/Ap1g1/Shld2/Stat5a/Itgb2/Stat5b/Fcgr3/Plcg2/Vav1/Cadm1/Il4/Tgfb1/Spi1/Tyrobp/Ptprc/Dpp4/P2rx7</t>
+    <t xml:space="preserve">Ptprc/Tgfb1/Lamp1/Spi1/Vav1/P2rx7/Plcg2/Stat5b/Dpp4/Ap1g1/H2-T23/Ticam1/Tyrobp/Stat5a/Fzd5/Il4/Fcgr3/Tfrc/Itgb2/Cadm1/Fbxo38/Hspd1/Shld2/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903203</t>
@@ -4903,7 +4903,7 @@
     <t xml:space="preserve">regulation of oxidative stress-induced neuron death</t>
   </si>
   <si>
-    <t xml:space="preserve">Tsc1/Tbc1d24/Fbxw7/Mcl1/Rack1/Parp1/Nono/Ctnnb1/Lancl1</t>
+    <t xml:space="preserve">Tsc1/Tbc1d24/Fbxw7/Nono/Ctnnb1/Mcl1/Lancl1/Parp1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042625</t>
@@ -4912,7 +4912,7 @@
     <t xml:space="preserve">ATPase-coupled ion transmembrane transporter activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp6v1a/Atp6v1b2/Atp6v1g1</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp6v1b2/Atp6v1a/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044769</t>
@@ -4927,7 +4927,7 @@
     <t xml:space="preserve">positive regulation by host of viral process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pcx/Igf2r/Stom/Nucks1/Vapa/Apoe</t>
+    <t xml:space="preserve">Vapa/Apoe/Igf2r/Pcx/Nucks1/Stom</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045651</t>
@@ -4936,7 +4936,7 @@
     <t xml:space="preserve">positive regulation of macrophage differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Rb1/Asxl2/Hcls1/Prkca/Csf1/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Csf1/Rb1/Hcls1/Prkca/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046961</t>
@@ -4975,7 +4975,7 @@
     <t xml:space="preserve">309/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Btnl10/Cd47/Prnp/Ermap/Ticam1/Wdfy1/Usp9x/Shb/Elf1/Bax/Fcho1/Usp15/Nras/Otud4/Psen1/Phb2/Pde4d/Rbck1/Dgkz/Hspd1/Traf3/Ifih1/Lpxn/Oasl1/Irak1/Ptpn6/Plcg2/Ubash3a/Pde4b/Nr1d1/Havcr2/Ptprs/Rnf125/Lgals9/Lcp2/Laptm5/Fyb/Tyrobp/Unc93b1/Btk/Ptprc/Myo1g/Rftn1/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Laptm5/Nfam1/Myo1g/Appl2/Rftn1/Syk/Ptprs/Ptprc/Prnp/Btnl10/Ermap/Fyb/Cd47/Plcg2/Lgals9/Unc93b1/Cd36/Rnf125/Ptpn6/Wdfy1/Irak1/Usp9x/Lcp2/Ubash3a/Traf3/Ticam1/Tyrobp/Elf1/Dgkz/Nr1d1/Rbck1/Havcr2/Otud4/Usp15/Pde4b/Psen1/Ifih1/Hspd1/Bax/Nras/Phb2/Oasl1/Fcho1/Shb/Pde4d/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032386</t>
@@ -4984,7 +4984,7 @@
     <t xml:space="preserve">regulation of intracellular transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Sh3tc2/Dmtn/Insig1/Mylk2/Prnp/Vps11/Lamp1/Ptpn23/Yod1/Rnf139/Fbxw7/Dnajc13/Cib1/Ehd1/Uhmk1/Vps35/Gripap1/Brca1/Stom/Sh3glb1/Snx3/Psen1/Dnajc27/Nedd4/Trim28/Ipo5/Ergic3/Scp2/Hsp90ab1/Wipf1/Use1/Hcls1/Sp100/Sar1b/Flna/Mdn1/Pcsk9/Tcf7l2/Abca2/Ripor1/Akap5/Arpc2/Pmaip1/Tgfb1/Lcp1</t>
+    <t xml:space="preserve">Sh3tc2/Prnp/Tgfb1/Dmtn/Lamp1/Ptpn23/Abca2/Lcp1/Ripor1/Vps11/Arpc2/Cd36/Yod1/Insig1/Flna/Pmaip1/Dnajc13/Fbxw7/Ehd1/Rnf139/Vps35/Uhmk1/Sh3glb1/Nedd4/Mdn1/Hcls1/Wipf1/Mylk2/Sar1b/Ergic3/Cib1/Hsp90ab1/Trim28/Psen1/Pcsk9/Scp2/Brca1/Gripap1/Ipo5/Tcf7l2/Use1/Stom/Akap5/Sp100/Snx3/Dnajc27</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051223</t>
@@ -4996,7 +4996,7 @@
     <t xml:space="preserve">452/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Sh3tc2/Rph3al/Dmtn/Insig1/Glrx/Prnp/Pfkfb2/Abcg1/Arntl/Rhbdf1/Picalm/Ptpn23/Yod1/Arrb1/Ppard/Fbxw7/Hmgcr/Cib1/Uhmk1/Birc5/Vps35/Gripap1/Brca1/Exoc1/Stom/Cdk16/Sirt1/Sh3glb1/Snx3/Rack1/Psen1/Dnajc27/Trim28/Ipo5/Ergic3/Gopc/Lrp5/Tm7sf3/Hsp90ab1/Myh10/Wipf1/Hcls1/Sp100/Sar1b/Idh2/Flna/Ier3ip1/Fkbp1b/Tcf7l2/Ripor1/Akap5/Arpc2/Hadh/Pmaip1/Pim3/Rac1/Nr1d1/Lypla1/Apoe/Tgfb1/Sytl4/P2rx7/Lcp1</t>
+    <t xml:space="preserve">Sh3tc2/Picalm/Prnp/Tgfb1/Rph3al/Abcg1/Dmtn/Rac1/Lypla1/Pfkfb2/Ptpn23/P2rx7/Lcp1/Ripor1/Glrx/Arpc2/Apoe/Cd36/Yod1/Insig1/Pim3/Hadh/Flna/Pmaip1/Fbxw7/Arntl/Idh2/Sytl4/Myh10/Ppard/Vps35/Nr1d1/Uhmk1/Sh3glb1/Rhbdf1/Arrb1/Hcls1/Hmgcr/Wipf1/Lrp5/Sar1b/Ergic3/Cib1/Cdk16/Hsp90ab1/Trim28/Ier3ip1/Birc5/Exoc1/Psen1/Sirt1/Tm7sf3/Brca1/Gripap1/Fkbp1b/Ipo5/Tcf7l2/Stom/Rack1/Akap5/Sp100/Snx3/Dnajc27/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031341</t>
@@ -5008,7 +5008,7 @@
     <t xml:space="preserve">93/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Lamp1/Bcl2l11/Hsp90ab1/Ap1g1/Stat5a/Stat5b/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Il4/Lgals9/Spi1/Tyrobp/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Syk/Ptprc/Lamp1/Spi1/Vav1/P2rx7/Lgals9/Stat5b/Ap1g1/H2-T23/Tyrobp/Stat5a/Il4/Pik3r6/Havcr2/Serpinb9/Bcl2l11/Hsp90ab1/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031647</t>
@@ -5020,7 +5020,7 @@
     <t xml:space="preserve">269/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Wdr81/Mfsd1/Grn/Prnp/Glmp/Tsc1/Lamp1/Mylip/Lss/Pim1/Rnf139/Fbxw7/Usp9x/Nckap1/Vps35/Ctsa/Mosmo/Ipo9/Siah1b/Sirt1/Sav1/Usp47/Fbxw11/Pex6/Tcf3/Cct6a/Phb2/Cct2/Gtpbp4/Ncln/Hsp90ab1/Crtap/Hspd1/Flna/Trp53/Mtmr9/Atp1b2/Cmtm6/Kat2a/Nr1d1/Tyrobp</t>
+    <t xml:space="preserve">Snca/Mfsd1/Prnp/Grn/Tsc1/Lamp1/Glmp/Wdr81/Kat2a/Mtmr9/Cmtm6/Flna/Fbxw7/Trp53/Rnf139/Usp9x/Ipo9/Tyrobp/Ctsa/Mylip/Nckap1/Vps35/Lss/Nr1d1/Atp1b2/Cct2/Tcf3/Hsp90ab1/Sirt1/Sav1/Hspd1/Ncln/Crtap/Phb2/Gtpbp4/Siah1b/Pex6/Cct6a/Fbxw11/Usp47/Pim1/Mosmo</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001919</t>
@@ -5029,7 +5029,7 @@
     <t xml:space="preserve">regulation of receptor recycling</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Agtr1a/Optn/Ache/Ldlr/Lamtor1/Psen1/Pcsk9</t>
+    <t xml:space="preserve">Snca/Optn/Ldlr/Ache/Agtr1a/Lamtor1/Psen1/Pcsk9</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903201</t>
@@ -5041,7 +5041,7 @@
     <t xml:space="preserve">66/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Glrx/Tsc1/Pycr1/Epor/Tbc1d24/Fbxw7/Rnf146/Mcl1/Sirt1/Rack1/Parp1/Nono/Ctnnb1/Lancl1/Trp53</t>
+    <t xml:space="preserve">Tsc1/Glrx/Tbc1d24/Fbxw7/Trp53/Epor/Rnf146/Nono/Ctnnb1/Mcl1/Lancl1/Sirt1/Pycr1/Parp1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005975</t>
@@ -5050,7 +5050,7 @@
     <t xml:space="preserve">carbohydrate metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Aldh1a1/Amdhd2/Abcg2/Renbp/Snca/St3gal6/Pfkfb2/Eno3/Rubcnl/Neu1/Ddit4/Gdpgp1/Pkm/Nupr1/Cltc/Bpgm/Hagh/Pcx/St3gal2/Mlst8/Gnpda1/Isyna1/Hexa/Ppp1r3f/Mtch2/Man1c1/Sord/Ip6k1/Sorbs1/Sirt1/Ppip5k2/Psen1/Cs/Got1/Man2b1/Lrp5/Gpi1/Dlat/Ndst1/Lancl1/St6galnac4/Pdha1/Gla/Idh2/Gk/Man2c1/Prkag2/Tcf7l2/Trp53/Khk/H6pd/Kat2a/Gusb/Pmaip1/Hk2/Man2b2/Ydjc/Fut4/G6pc3/Nr1d1/Pgm2/Gsto1/Phlda2/Tgfb1/P2rx7/Igfbp4</t>
+    <t xml:space="preserve">Aldh1a1/Snca/Slc4a1/Igfbp4/Tgfb1/Renbp/Cltc/Abcg2/Gsto1/Amdhd2/Pfkfb2/Man2b2/P2rx7/Ddit4/Kat2a/Cd36/Khk/Pdha1/Gusb/Pcx/Mtch2/Isyna1/Hagh/Pmaip1/Neu1/Mlst8/Pkm/Trp53/Phlda2/G6pc3/Idh2/Fut4/Gk/Prkag2/Gnpda1/Pgm2/Ydjc/H6pd/Gdpgp1/Man2c1/Nr1d1/Cs/Ppip5k2/Ndst1/Man2b1/Eno3/Lrp5/Dlat/St3gal6/Hk2/Rubcnl/Gla/Lancl1/Psen1/Hexa/St3gal2/Sirt1/Bpgm/Ip6k1/Man1c1/Nupr1/Ppp1r3f/Got1/St6galnac4/Sorbs1/Tcf7l2/Sord/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0018108</t>
@@ -5065,7 +5065,7 @@
     <t xml:space="preserve">253/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Dmtn/Agtr1a/Prnp/Nedd9/Mlst8/Fbxw7/Ggnbp2/Ppp2r5b/Dvl2/Dyrk1a/Rap2b/Clk3/Rictor/Abi1/Psen1/Iqgap1/Cnot7/Cbl/Igf1r/Hcls1/Prkca/Stat5a/Samsn1/Itgb2/Rap2c/Trp53/Ptpn6/Plcg2/Lrrk1/Itga5/Il4/Fes/Arhgef2/Tgfb1/Cd44/Btk/Ptprc/Jak3/Syk</t>
+    <t xml:space="preserve">Btk/Jak3/Syk/Arhgef2/Ptprc/Prnp/Tgfb1/Dmtn/Cd44/Plcg2/Cd36/Ptpn6/Dyrk1a/Itga5/Lrrk1/Fbxw7/Rap2b/Mlst8/Trp53/Nedd9/Agtr1a/Stat5a/Il4/Rap2c/Fes/Ggnbp2/Dvl2/Hcls1/Clk3/Itgb2/Prkca/Psen1/Iqgap1/Samsn1/Abi1/Igf1r/Cbl/Ppp2r5b/Cnot7/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006695</t>
@@ -5074,7 +5074,7 @@
     <t xml:space="preserve">cholesterol biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Insig1/Abcg1/Mvd/Msmo1/Lss/Hmgcr/Lpcat3/Pmvk/Sc5d/Cyb5r3/Scp2/Apoe</t>
+    <t xml:space="preserve">Abcg1/Apoe/Insig1/Msmo1/Mvd/Lss/Hmgcr/Lpcat3/Cyb5r3/Sc5d/Scp2/Pmvk</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902653</t>
@@ -5089,7 +5089,7 @@
     <t xml:space="preserve">retromer complex</t>
   </si>
   <si>
-    <t xml:space="preserve">Snx8/Vps26a/Vps29/Vps35/Snx2/Snx3/Snx5</t>
+    <t xml:space="preserve">Vps26a/Snx8/Vps35/Vps29/Snx5/Snx2/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045649</t>
@@ -5098,7 +5098,7 @@
     <t xml:space="preserve">regulation of macrophage differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Rb1/Asxl2/Hcls1/Prkca/Gata2/Csf1/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Gata2/Csf1/Rb1/Hcls1/Prkca/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097237</t>
@@ -5122,7 +5122,7 @@
     <t xml:space="preserve">development of secondary sexual characteristics</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Phb2/Stat5a/Stat5b/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Stat5b/Stat5a/Bax/Phb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045647</t>
@@ -5131,7 +5131,7 @@
     <t xml:space="preserve">negative regulation of erythrocyte differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Ldb1/Stat5a/Lmo2/Stat5b/Zfp36l1</t>
+    <t xml:space="preserve">Stat5b/Ldb1/Stat5a/Lmo2/Zfp36l1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042254</t>
@@ -5143,7 +5143,7 @@
     <t xml:space="preserve">286/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mrm1/Tsc1/Isg20/Pop5/Utp14b/Ipo9/Helq/Ddx27/Rpl35/Ddx18/Snu13/Pa2g4/Ddx21/Ddx49/Gtpbp4/Rcl1/Rsl24d1/Ebna1bp2/Wdr36/Sdad1/Rrp1b/Urb1/Pwp1/Gtf3a/Trmt2b/Exosc1/Lyar/Wdr43/Exosc5/Mdn1/Nop16/Heatr1/Mybbp1a/Nat10/Naf1/Rrp12/Rpl10a/Nol6/Wdr46/Xrcc5/Tfb2m/Rrp9/Npm3/Ltv1</t>
+    <t xml:space="preserve">Tsc1/Npm3/Ltv1/Xrcc5/Nat10/Rpl10a/Rrp9/Wdr46/Utp14b/Trmt2b/Mrm1/Nol6/Ipo9/Pop5/Naf1/Tfb2m/Isg20/Mybbp1a/Rrp12/Heatr1/Mdn1/Pwp1/Nop16/Urb1/Sdad1/Wdr43/Exosc5/Ddx18/Gtf3a/Rcl1/Exosc1/Snu13/Rsl24d1/Wdr36/Lyar/Gtpbp4/Ebna1bp2/Ddx21/Helq/Ddx27/Ddx49/Rpl35/Pa2g4/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006886</t>
@@ -5158,7 +5158,7 @@
     <t xml:space="preserve">743/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Sh3tc2/Appl2/Egr2/Rph3al/Dmtn/Map1a/Insig1/Prnp/Arntl/Snx8/Vps26a/Vps11/Ptpn23/Yod1/Cltc/Gga2/Pikfyve/Rab43/Rab22a/Rab3ip/Arl4a/Trak2/Vps33a/Myo6/Fbxw7/Kpna6/Cib1/Ap3d1/Tom1/Bax/Ehd1/Uhmk1/Vps29/Nup50/Vps35/Gripap1/Stradb/Bid/Brca1/Acd/Ipo9/Stom/Zfand6/Cttn/Snx2/Ap2m1/Sh3glb1/Uso1/Sec62/Snx3/Pex6/Psen1/Dnajc27/Nedd4/Trim28/Ipo5/Ppp3r1/Sec61a1/Ergic3/Phb2/Tnpo1/Hsp90ab1/Copg2/Wipf1/Hspd1/Ap1g1/Hcls1/Tmed5/Sp100/Sar1b/Flna/Snx5/Timm50/Xpo5/Zdhhc23/Tcf7l2/Agk/Ripor1/Akap5/Arpc2/Trp53/Tmed3/Traf3ip2/Pmaip1/Snx10/Zdhhc21/Rangrf/Bcap29/Ywhaz/Tgfb1/Laptm5/Sytl4/Unc93b1/Rftn1/Syk/Lcp1</t>
+    <t xml:space="preserve">Sh3tc2/Laptm5/Appl2/Rftn1/Syk/Prnp/Vps26a/Tgfb1/Ywhaz/Cltc/Rph3al/Dmtn/Gga2/Bcap29/Ptpn23/Lcp1/Ripor1/Vps11/Snx8/Zdhhc21/Unc93b1/Arpc2/Xpo5/Cd36/Yod1/Pikfyve/Insig1/Flna/Tmed3/Pmaip1/Fbxw7/Ehd1/Arntl/Rab22a/Rab43/Ap1g1/Trp53/Map1a/Myo6/Arl4a/Kpna6/Agk/Egr2/Rangrf/Tnpo1/Rab3ip/Ipo9/Timm50/Sytl4/Nup50/Snx10/Ap3d1/Vps33a/Vps35/Copg2/Uhmk1/Sh3glb1/Nedd4/Vps29/Hcls1/Wipf1/Trak2/Snx5/Sar1b/Ergic3/Cib1/Hsp90ab1/Trim28/Ap2m1/Psen1/Bid/Tmed5/Snx2/Sec61a1/Acd/Zfand6/Ppp3r1/Traf3ip2/Hspd1/Bax/Stradb/Brca1/Phb2/Gripap1/Pex6/Ipo5/Tcf7l2/Sec62/Cttn/Stom/Akap5/Sp100/Tom1/Snx3/Dnajc27/Uso1/Zdhhc23</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051347</t>
@@ -5167,7 +5167,7 @@
     <t xml:space="preserve">positive regulation of transferase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Wnk4/Map3k1/Snca/Agtr1a/Prnp/Pfkfb2/Nedd9/Als2/Gab1/Traf4/Stil/Cdc25b/Cdc6/Pim1/Mapre3/Fzd5/Map3k12/Fbxw7/Dcun1d3/Cib1/Dag1/Dvl2/Serinc5/Stradb/Acd/Sirt1/Dcun1d1/Sh3glb1/Abi1/Psen1/Iqgap1/Ctnnb1/Rfc2/Parn/Phb2/Cct2/Maged1/Dgkz/Hsp90ab1/Ube2s/Igf1r/Dtx3l/Pik3r5/Prkag2/Naf1/Irak1/Vangl2/Xrcc5/Rac1/Mmd/Pik3r6/Il4/Csf1/Trib2/Tgfb1/Mst1r/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Egr1/Map3k1/Snca/Syk/Ptprc/Wnk4/Prnp/Tgfb1/Rac1/Trib2/Pfkfb2/Gab1/P2rx7/Als2/Cdc25b/Mst1r/Mmd/Xrcc5/Cdc6/Irak1/Traf4/Fbxw7/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Prkag2/Dgkz/Pik3r6/Naf1/Maged1/Csf1/Ctnnb1/Sh3glb1/Vangl2/Dvl2/Cct2/Ube2s/Dtx3l/Cib1/Rfc2/Hsp90ab1/Mapre3/Psen1/Serinc5/Sirt1/Acd/Iqgap1/Dcun1d1/Stradb/Map3k12/Phb2/Dcun1d3/Abi1/Igf1r/Pim1/Parn/Pik3r5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0140352</t>
@@ -5179,7 +5179,7 @@
     <t xml:space="preserve">735/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Slc6a9/Pld2/Wnk4/Exoc3l4/Rph3al/Abcg2/Dmtn/Snca/Itsn1/Agtr1a/Glrx/Kalrn/Pfkfb2/Abcg1/Arntl/Washc5/Slc16a10/Rhbdf1/Vps11/Lamp1/Ptpn23/D6Wsu163e/Anxa3/Dpysl2/Rab3ip/Arrb1/Arfgef2/Syn1/Myo6/Smcr8/Ppard/Atp2b1/Hmgcr/Ccdc186/C9orf72/Birc5/Exoc8/Vps35/Tmem167b/Gnas/Rap1b/Exoc1/Arl8b/Cdk16/Sirt1/Snap29/Mia3/Vps4b/Mia2/Psen1/Lrp5/Tm7sf3/Selenot/Copg2/Myh10/Ap1g1/Prkca/P2rx1/Idh2/Ier3ip1/Fkbp1b/Itgb2/Tcf7l2/Lin7c/Unc13a/Akap5/Tfr2/Hadh/Slc4a8/Fcgr3/Slc22a18/Atp1b2/Gata2/Unc13d/Atp1a3/Cplx2/Gab2/Pim3/Rac1/Nr1d1/Rac2/Il4/Ywhaz/Fes/Lgals9/Ltbp4/Apoe/Tgfb1/Sytl4/Spi1/Coro1a/Myo1g/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Rab3il1/Snca/Myo1g/Syk/Wnk4/Coro1a/Slc6a9/Rac2/Tgfb1/Ywhaz/Rph3al/Abcg2/Washc5/Abcg1/Dmtn/Lamp1/Rac1/Cd84/Itsn1/Pfkfb2/Ptpn23/Spi1/Gab2/P2rx7/Vps11/Slc16a10/Lgals9/Arfgef2/Glrx/Atp2b1/Apoe/Lin7c/Pld2/Ltbp4/Pim3/Kalrn/Hadh/Gnas/Unc13d/Arntl/Ap1g1/Myo6/Dpysl2/Tfr2/D6Wsu163e/Agtr1a/Exoc3l4/Idh2/Rab3ip/Sytl4/Il4/Myh10/Gata2/Fes/Selenot/Ppard/Smcr8/Vps35/Copg2/Nr1d1/Rhbdf1/Arrb1/Fcgr3/Slc4a8/Atp1b2/Anxa3/Hmgcr/Exoc8/Mia2/Lrp5/Tmem167b/Cplx2/Itgb2/Prkca/Arl8b/Cdk16/Atp1a3/Ier3ip1/Birc5/Exoc1/Rap1b/Psen1/Sirt1/C9orf72/Slc22a18/Tm7sf3/Unc13a/Fkbp1b/Tcf7l2/Ccdc186/Vps4b/Mia3/P2rx1/Akap5/Snap29/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051219</t>
@@ -5188,7 +5188,7 @@
     <t xml:space="preserve">phosphoprotein binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Grap2/Snca/Epb41/Ubash3b/Arrb1/Igf2r/Tbk1/Fbxw7/Shb/Rb1/Scaf4/Nedd4/Cbl/Samsn1/Ptpn6/Plcg2/Vav1/Cd44/Syk</t>
+    <t xml:space="preserve">Snca/Syk/Cd44/Vav1/Plcg2/Igf2r/Ptpn6/Grap2/Fbxw7/Tbk1/Epb41/Rb1/Arrb1/Nedd4/Ubash3b/Samsn1/Scaf4/Cbl/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0035239</t>
@@ -5200,7 +5200,7 @@
     <t xml:space="preserve">691/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Cd36/Egr3/Mst1/Wnk4/Tal1/Cited2/Agtr1a/Grn/Hipk2/Gab1/Tsc1/Pkm/Ldlr/Anxa3/Stil/Epor/Hdac5/Epn1/Fzd5/Junb/Sars/Plcd3/Fbxw7/Foxo4/Flcn/Cib1/Shb/Pknox1/Dag1/Bax/Dvl2/Rara/Nckap1/Kdm2a/Luzp1/Nup50/Bcl2l11/Ago2/Brca1/Gna13/Arhgap35/Sirt1/Adipor2/Kat6a/Mia3/Nras/Sgpl1/Psen1/Ctnnb1/Nedd4/Ppp3r1/Phb2/Lrp5/Maged1/Tnni3/Cul7/Ift172/Prkca/Megf8/Mthfd1/Sp100/Flna/Srf/Gtf2i/Itgb2/Tcf7l2/Pik3cd/Mthfd1l/Vangl2/Sema4a/Kat2a/Gata2/Zfp36l1/Hk2/Itga5/Hif3a/Pik3r6/Csf1/Ywhaz/Cxcr4/Mmp14/Apoe/Tgfb1/Cd44/Spi1/Hdac7/Plxdc1/Vash2/Syk/Eng</t>
+    <t xml:space="preserve">Hdac7/Cobl/Syk/Wnk4/Tgfb1/Ywhaz/Mst1/Grn/Tal1/Tsc1/Cd44/Vash2/Gab1/Spi1/Cited2/Eng/Hif3a/Cxcr4/Kat2a/Epn1/Apoe/Cd36/Ldlr/Itga5/Hipk2/Gtf2i/Megf8/Flna/Fbxw7/Pkm/Kdm2a/Dag1/Egr3/Plxdc1/Epor/Sars/Agtr1a/Pik3cd/Nup50/Fzd5/Stil/Gata2/Cul7/Mmp14/Sema4a/Gna13/Pik3r6/Srf/Zfp36l1/Maged1/Csf1/Pknox1/Ctnnb1/Nckap1/Hdac5/Ift172/Vangl2/Nedd4/Mthfd1/Dvl2/Anxa3/Mthfd1l/Luzp1/Lrp5/Cib1/Bcl2l11/Itgb2/Prkca/Adipor2/Hk2/Flcn/Psen1/Sirt1/Tnni3/Junb/Ppp3r1/Rara/Bax/Nras/Brca1/Kat6a/Phb2/Foxo4/Ago2/Plcd3/Arhgap35/Tcf7l2/Mia3/Sgpl1/Sp100/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050866</t>
@@ -5209,7 +5209,7 @@
     <t xml:space="preserve">negative regulation of cell activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Prdx2/Grn/Prnp/Ldlr/Zbtb7b/Ubash3b/Samsn1/Vsir/Cst7/Ptpn6/Cd37/Nr1d1/Cbfb/Ripor2/Havcr2/Il4/Lgals9/Spn/Apoe/Lgals7/Tgfb1/Cd44/Laptm5/Spi1/Tyrobp/Btk/Jak3/Tbc1d10c/Cd84</t>
+    <t xml:space="preserve">Prdx2/Btk/Jak3/Laptm5/Prnp/Tgfb1/Grn/Spn/Cd44/Cd84/Ripor2/Cbfb/Spi1/Tbc1d10c/Lgals9/Apoe/Ldlr/Ptpn6/Zbtb7b/Tyrobp/Il4/Lgals7/Cd37/Nr1d1/Havcr2/Ubash3b/Vsir/Samsn1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0018212</t>
@@ -5227,7 +5227,7 @@
     <t xml:space="preserve">54/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Nfe2/Arntl/Wbp2/Arrb1/Dip2b/Brca1/Taok1/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Kat2a/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Nfe2/Glyr1/Kat2a/Wbp2/Dip2b/Arntl/Mybbp1a/Arrb1/Ruvbl2/Taok1/Brca1/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0035065</t>
@@ -5239,7 +5239,7 @@
     <t xml:space="preserve">67/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Wbp2/Arrb1/Flcn/Brca1/Sirt1/Ctcf/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Kat2a/Gata2/Tgfb1/Spi1</t>
+    <t xml:space="preserve">Snca/Tgfb1/Spi1/Glyr1/Kat2a/Wbp2/Gata2/Mybbp1a/Arrb1/Ruvbl2/Flcn/Sirt1/Brca1/Ctcf/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000108</t>
@@ -5248,7 +5248,7 @@
     <t xml:space="preserve">positive regulation of leukocyte apoptotic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Bcl2l11/Sirt1/Fnip1/Pik3cd/Trp53/Cd44/Jak3/P2rx7</t>
+    <t xml:space="preserve">Jak3/Cd44/P2rx7/Trp53/Pik3cd/Bcl2l11/Sirt1/Fnip1/Bax</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008203</t>
@@ -5260,7 +5260,7 @@
     <t xml:space="preserve">116/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Fech/Pip4p1/Insig1/Abcg1/Mvd/Ldlr/Msmo1/Lss/Sqle/Gba/Cln8/Hmgcr/Lpcat3/Pmvk/Sc5d/Cyb5r3/Lrp5/Scp2/Pcsk9/Abca2/Il4/Apoe</t>
+    <t xml:space="preserve">Fech/Abcg1/Pip4p1/Abca2/Apoe/Ldlr/Insig1/Sqle/Gba/Msmo1/Mvd/Il4/Lss/Hmgcr/Lpcat3/Lrp5/Cyb5r3/Sc5d/Pcsk9/Scp2/Pmvk/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009132</t>
@@ -5269,7 +5269,7 @@
     <t xml:space="preserve">nucleoside diphosphate metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Entpd6/Guk1/Umps/Prkag2/Cad/Khk/Ak4/Hk2/Nme4/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Slc4a1/Pfkfb2/Nme4/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Cad/Pkm/Umps/Prkag2/Guk1/Eno3/Hk2/Psen1/Bpgm/Ak4/Nupr1/Gpi1/Entpd6</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046165</t>
@@ -5278,7 +5278,7 @@
     <t xml:space="preserve">alcohol biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Insig1/Abcg1/Mvd/Msmo1/Lss/Gba/Isyna1/Hmgcr/Lpcat3/Pmvk/Sc5d/Ip6k1/Cyb5r3/Ppip5k2/Got1/Scp2/Abca2/H6pd/Plcg2/Apoe/Sptssa</t>
+    <t xml:space="preserve">Snca/Sptssa/Abcg1/Abca2/Plcg2/Apoe/Insig1/Isyna1/Gba/Msmo1/Mvd/H6pd/Lss/Ppip5k2/Hmgcr/Lpcat3/Cyb5r3/Sc5d/Ip6k1/Scp2/Got1/Pmvk</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043087</t>
@@ -5287,7 +5287,7 @@
     <t xml:space="preserve">regulation of GTPase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalrn/Nedd9/Als2/Tsc1/Picalm/Asap3/Fgd6/Prex1/Arhgap12/Rgl1/Mlst8/Arrb1/Smcr8/Arhgap15/Flcn/Elmod2/Dvl2/C9orf72/Cdkl5/Myo9a/Rabgap1/Rictor/Gnas/Arhgap35/Rack1/Usp6nl/Iqgap1/Rrp1b/Syngap1/Arhgap9/Ripor1/Vav1/Gmip/Rgl2/Rcc2/Plxnc1/Ripor2/Dock8/Rgs1/Rgs14/Adap1/Arhgap27/Tbc1d10c/Arap3</t>
+    <t xml:space="preserve">Arap3/Picalm/Tsc1/Dock8/Arhgap27/Ripor2/Rcc2/Tbc1d10c/Vav1/Ripor1/Als2/Rgl2/Prex1/Kalrn/Gnas/Gmip/Mlst8/Adap1/Rgs14/Nedd9/Rabgap1/Fgd6/Rgs1/Smcr8/Arhgap12/Arrb1/Dvl2/Plxnc1/Asap3/Rgl1/Arhgap9/Flcn/C9orf72/Iqgap1/Cdkl5/Syngap1/Arhgap15/Arhgap35/Rack1/Elmod2/Myo9a/Usp6nl/Rictor/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010769</t>
@@ -5296,7 +5296,7 @@
     <t xml:space="preserve">regulation of cell morphogenesis involved in differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Kalrn/Nedd9/Ache/Prex1/Numb/Tbc1d24/Cib1/Pias2/Cdkl5/Sh3glb1/Actr2/Stau2/Cul7/Flna/Akap5/Arpc2/Unc13d/Ankrd27/Rac1/Rcc2</t>
+    <t xml:space="preserve">Ankrd27/Dmtn/Rac1/Rcc2/Arpc2/Prex1/Tbc1d24/Kalrn/Ache/Unc13d/Flna/Numb/Nedd9/Pias2/Cul7/Sh3glb1/Cib1/Actr2/Cdkl5/Stau2/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031623</t>
@@ -5305,7 +5305,7 @@
     <t xml:space="preserve">receptor internalization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Snca/Tfrc/Ache/Picalm/Cltc/Numb/Arrb1/Myo6/Ap2m1/Nedd4/Ppp3r1/Atad1/Pcsk9/Itgb2/Ankrd13b/Akap5/Plcg2/Syk/Rin3</t>
+    <t xml:space="preserve">Snca/Syk/Picalm/Cltc/Rin3/Plcg2/Cd36/Pld2/Ache/Myo6/Numb/Ankrd13b/Atad1/Arrb1/Nedd4/Tfrc/Itgb2/Ap2m1/Ppp3r1/Pcsk9/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006644</t>
@@ -5314,7 +5314,7 @@
     <t xml:space="preserve">phospholipid metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Snca/Pip4p1/Serac1/Gpcpd1/Mvd/Pcyt1b/Ldlr/Pcx/Uvrag/Pikfyve/Isyna1/Ppard/Socs2/Cln8/Lpcat3/Pmvk/Serinc5/Ip6k1/Mtmr3/Pip4k2c/Sh3glb1/Mtmr12/Pi4ka/Serinc3/Phb2/Ttc7b/Scp2/Pik3c2b/Abhd16a/Dgkz/Pigt/Mboat7/Pcsk9/Plpp2/Pla2g12a/Abca2/Pik3cd/Mtmr9/Prdx6/Acsl5/Plcg2/Vapa/Pgap2/Plcb2/Pla2g1b/Lpcat2</t>
+    <t xml:space="preserve">Snca/Pip4p1/Plcb2/Serac1/Abca2/Vapa/Plcg2/Acsl5/Pld2/Ldlr/Mtmr9/Pikfyve/Pcx/Isyna1/Uvrag/Pgap2/Prdx6/Socs2/Mtmr3/Mvd/Lpcat2/Pik3cd/Pla2g12a/Pcyt1b/Dgkz/Pla2g1b/Mboat7/Ppard/Sh3glb1/Gpcpd1/Lpcat3/Pigt/Abhd16a/Plpp2/Serinc5/Ip6k1/Pcsk9/Scp2/Serinc3/Mtmr12/Ttc7b/Phb2/Pmvk/Cln8/Pip4k2c/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043198</t>
@@ -5323,7 +5323,7 @@
     <t xml:space="preserve">dendritic shaft</t>
   </si>
   <si>
-    <t xml:space="preserve">Prkar2b/Map1a/Mpp2/Homer1/Psen1/Ctnnb1/Stau2/Syngap1/Flna/Akap5/Arpc2/Arhgef2</t>
+    <t xml:space="preserve">Prkar2b/Arhgef2/Mpp2/Arpc2/Flna/Map1a/Ctnnb1/Psen1/Stau2/Syngap1/Homer1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007565</t>
@@ -5332,7 +5332,7 @@
     <t xml:space="preserve">female pregnancy</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Abcg2/Cited2/Grn/Epor/Epn1/Junb/Ppard/Kpna6/Ash1l/Ago2/Exoc1/Dedd/Trim28/Stat5a/Stat5b/Polr1b/Havcr2/Lgals9/Arhgdib</t>
+    <t xml:space="preserve">Mst1/Grn/Abcg2/Cited2/Lgals9/Arhgdib/Epn1/Stat5b/Epor/Kpna6/Polr1b/Stat5a/Ppard/Havcr2/Trim28/Exoc1/Ash1l/Junb/Ago2/Dedd</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042269</t>
@@ -5341,7 +5341,7 @@
     <t xml:space="preserve">regulation of natural killer cell mediated cytotoxicity</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Ap1g1/Stat5a/Stat5b/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9</t>
+    <t xml:space="preserve">Lamp1/Vav1/Lgals9/Stat5b/Ap1g1/Stat5a/Pik3r6/Havcr2/Serpinb9/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043069</t>
@@ -5353,7 +5353,7 @@
     <t xml:space="preserve">99/1492</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Prokr1/Btg2/Egr3/Mst1/St3gal1/Slc30a10/Snca/Prdx2/Itsn1/Cited2/Agtr1a/Optn/Tfrc/Grn/Glrx/Prnp/Hipk2/Nupr1/Stil/Pim1/Gba/Mlst8/Arrb1/Epor/Pea15a/Grk5/Map3k12/Ppard/Grina/Cln8/Sgk3/Hmgcr/Atp7a/Cib1/Ppp1r10/Bax/Kdm2a/Tsc22d1/Birc5/Rictor/Stradb/Bid/Brca1/Mcl1/Rb1/Tsc22d3/Zfand6/Cttn/Sirt1/Rps6kb1/Fnip1/Sh3glb1/Usp47/Qars/Psen1/Nono/Ctnnb1/Kifap3/Pa2g4/Phb2/Gpi1/Tm7sf3/Armc10/Cbl/Rbck1/Hsp90ab1/Set/Syngap1/Hspd1/Igf1r/Hcls1/Mnt/Prkca/Flna/Stat5a/Ppif/Ccng1/Trp53/Stat5b/Dapk1/Il27ra/Pcgf2/Pdcd4/Gata2/Plcg2/Rgl2/Ago4/Serpinb9/Pim3/Itga5/Dock8/Aldh2/Il4/Apoe/Cd44/Laptm5/Coro1a/Jak3</t>
+    <t xml:space="preserve">Prdx2/Jak3/Laptm5/Snca/Btg2/Coro1a/Prnp/Slc30a10/Prokr1/Mst1/Grn/Aldh2/St3gal1/Cd44/Cpeb4/Dock8/Itsn1/Cited2/Plcg2/Optn/Glrx/Ccng1/Rgl2/Apoe/Stat5b/Itga5/Pim3/Hipk2/Flna/Ago4/Gba/Mlst8/Kdm2a/Trp53/Egr3/Epor/Agtr1a/Stat5a/Pcgf2/Il4/Stil/Gata2/Pea15a/Grk5/Nono/Ctnnb1/Il27ra/Ppard/Dapk1/Rb1/Rbck1/Sh3glb1/Ppif/Arrb1/Mcl1/Armc10/Serpinb9/Tfrc/Hcls1/Hmgcr/Ppp1r10/Cib1/Prkca/Hsp90ab1/Atp7a/Birc5/Pdcd4/Psen1/Bid/Set/Sirt1/Grina/Zfand6/Hspd1/Fnip1/Bax/Nupr1/Tm7sf3/Stradb/Brca1/Syngap1/Tsc22d1/Map3k12/Phb2/Mnt/Sgk3/Igf1r/Usp47/Tsc22d3/Cbl/Cttn/Qars/Kifap3/Pim1/Cln8/Pa2g4/Rps6kb1/Rictor/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030295</t>
@@ -5365,7 +5365,7 @@
     <t xml:space="preserve">95/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Als2/Pim1/Mlst8/Map3k12/Mob3c/Ccnt1/Rictor/Stradb/Dbf4/Taok1/Abi1/Iqgap1/Tcf3/Prkag2/Mob3b/Lgals9/Tgfb1/P2rx7</t>
+    <t xml:space="preserve">Tgfb1/Tal1/P2rx7/Lgals9/Als2/Mlst8/Mob3b/Prkag2/Ccnt1/Tcf3/Taok1/Iqgap1/Stradb/Map3k12/Abi1/Mob3c/Dbf4/Pim1/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019829</t>
@@ -5374,7 +5374,7 @@
     <t xml:space="preserve">ATPase-coupled cation transmembrane transporter activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp2b1/Atp6v1a/Atp6v1b2/Atp7a/Atp6v0b/Atp6v1g1/Atp1b2/Atp1a3</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp2b1/Atp6v1b2/Atp6v1a/Atp6v0b/Atp1b2/Atp1a3/Atp7a/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043030</t>
@@ -5383,7 +5383,7 @@
     <t xml:space="preserve">regulation of macrophage activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Grn/Ldlr/Hspd1/Cst7/Nr1d1/Havcr2/Il4/Lgals9/Il1rl1/Cd84</t>
+    <t xml:space="preserve">Snca/Il1rl1/Grn/Cd84/Lgals9/Ldlr/Il4/Nr1d1/Havcr2/Hspd1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006892</t>
@@ -5392,7 +5392,7 @@
     <t xml:space="preserve">post-Golgi vesicle-mediated transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Optn/Lamp1/Gga2/Arfgef2/Rabep1/Ccdc93/Ap3d1/Vps29/Exoc8/Golga4/Exoc1/Rack1/Gopc/Ap1g1/Ehd3/Vamp5/Lypla1/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Lamp1/Gga2/Lypla1/Optn/Arfgef2/Vamp5/Rabep1/Ap1g1/Ap3d1/Vps29/Ccdc93/Exoc8/Ehd3/Exoc1/Golga4/Rack1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005905</t>
@@ -5404,7 +5404,7 @@
     <t xml:space="preserve">61/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Itsn1/Tfrc/Picalm/Ldlr/Cltc/Numb/Arrb1/Epn1/Myo6/Fcho1/Cttn/Itsn2/Ap2m1/Hspd1</t>
+    <t xml:space="preserve">Picalm/Cltc/Itsn1/Epn1/Ldlr/Myo6/Numb/Arrb1/Tfrc/Ap2m1/Hspd1/Cttn/Fcho1/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032271</t>
@@ -5413,7 +5413,7 @@
     <t xml:space="preserve">regulation of protein polymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Snca/Mapre3/Ssh2/Mlst8/Plekhg2/Nckap1/Dyrk1a/Camsap2/Nck1/Rictor/Twf1/Togaram1/Cttn/Flii/Hcls1/Sptan1/Slain2/Arpc2/Rangrf/Rac1/Capg/Fes/Vill/Coro1a</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Snca/Vill/Coro1a/Tmod1/Dmtn/Rac1/Capg/Arpc2/Dyrk1a/Mlst8/Ssh2/Rangrf/Fes/Nckap1/Slain2/Flii/Twf1/Togaram1/Camsap2/Plekhg2/Hcls1/Sptan1/Mapre3/Nck1/Cttn/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032940</t>
@@ -5425,7 +5425,7 @@
     <t xml:space="preserve">694/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Slc6a9/Pld2/Wnk4/Exoc3l4/Rph3al/Dmtn/Snca/Itsn1/Agtr1a/Glrx/Kalrn/Pfkfb2/Abcg1/Arntl/Washc5/Slc16a10/Rhbdf1/Vps11/Lamp1/Ptpn23/D6Wsu163e/Anxa3/Dpysl2/Rab3ip/Arrb1/Arfgef2/Syn1/Myo6/Smcr8/Ppard/Hmgcr/Ccdc186/C9orf72/Birc5/Exoc8/Vps35/Tmem167b/Gnas/Rap1b/Exoc1/Arl8b/Cdk16/Sirt1/Snap29/Mia3/Vps4b/Mia2/Psen1/Lrp5/Tm7sf3/Selenot/Copg2/Myh10/Ap1g1/Prkca/P2rx1/Idh2/Ier3ip1/Fkbp1b/Itgb2/Tcf7l2/Lin7c/Unc13a/Akap5/Tfr2/Hadh/Slc4a8/Fcgr3/Gata2/Unc13d/Cplx2/Gab2/Pim3/Rac1/Nr1d1/Rac2/Il4/Ywhaz/Fes/Lgals9/Ltbp4/Apoe/Tgfb1/Sytl4/Spi1/Coro1a/Myo1g/P2rx7/Cd84/Syk</t>
+    <t xml:space="preserve">Rab3il1/Snca/Myo1g/Syk/Wnk4/Coro1a/Slc6a9/Rac2/Tgfb1/Ywhaz/Rph3al/Washc5/Abcg1/Dmtn/Lamp1/Rac1/Cd84/Itsn1/Pfkfb2/Ptpn23/Spi1/Gab2/P2rx7/Vps11/Slc16a10/Lgals9/Arfgef2/Glrx/Apoe/Lin7c/Pld2/Ltbp4/Pim3/Kalrn/Hadh/Gnas/Unc13d/Arntl/Ap1g1/Myo6/Dpysl2/Tfr2/D6Wsu163e/Agtr1a/Exoc3l4/Idh2/Rab3ip/Sytl4/Il4/Myh10/Gata2/Fes/Selenot/Ppard/Smcr8/Vps35/Copg2/Nr1d1/Rhbdf1/Arrb1/Fcgr3/Slc4a8/Anxa3/Hmgcr/Exoc8/Mia2/Lrp5/Tmem167b/Cplx2/Itgb2/Prkca/Arl8b/Cdk16/Ier3ip1/Birc5/Exoc1/Rap1b/Psen1/Sirt1/C9orf72/Tm7sf3/Unc13a/Fkbp1b/Tcf7l2/Ccdc186/Vps4b/Mia3/P2rx1/Akap5/Snap29/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050900</t>
@@ -5434,7 +5434,7 @@
     <t xml:space="preserve">leukocyte migration</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Add2/Cd47/Adam10/Prex1/Pikfyve/Gba/Mospd2/Wasl/Mpp1/Swap70/Mia3/Pde4d/Wdr1/Prkca/Itgb2/Trp53/Stat5b/Fcgr3/Il27ra/Vav1/Ano6/Cadm1/Pde4b/Fut4/Plvap/Rac1/Ripor2/Dock8/Rac2/Il4/Csf1/Lgals9/Spn/Mmp14/Selplg/Tgfb1/Spi1/Coro1a/Dpp4/Myo1g/Syk/Rin3</t>
+    <t xml:space="preserve">Add2/Myo1g/Syk/Coro1a/Ano6/Rac2/Tgfb1/Mst1/Spn/Rac1/Cd47/Dock8/Ripor2/Spi1/Vav1/Rin3/Lgals9/Stat5b/Prex1/Adam10/Pikfyve/Dpp4/Gba/Trp53/Selplg/Fut4/Il4/Mmp14/Wasl/Csf1/Wdr1/Il27ra/Mospd2/Fcgr3/Plvap/Mpp1/Itgb2/Prkca/Pde4b/Swap70/Cadm1/Mia3/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032279</t>
@@ -5446,7 +5446,7 @@
     <t xml:space="preserve">314/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Slc6a9/Add2/Dmtn/Map1a/Mpp2/Mylk2/Prnp/Kalrn/Als2/Tsc1/Picalm/Adam10/Samd14/Numb/Nrgn/Arrb1/Arfgef2/Syn1/Myo6/Ppp1r9b/Rnf10/Cdkl5/Vps35/Homer1/Abi1/Rpl4/Actr2/Ctnnb1/Phb2/Ifngr1/Dgkz/Eif4g2/Syngap1/Rpl10a/Epb41l1/Akap5/Slc4a8/Grin2d/Cadm1/Pde4b/Kcnab2/Prr7/Ptprs/Ywhaz/Rgs14/Arhgef2</t>
+    <t xml:space="preserve">Add2/Picalm/Arhgef2/Ptprs/Slc6a9/Prnp/Ywhaz/Tsc1/Dmtn/Cpeb4/Kcnab2/Mpp2/Als2/Arfgef2/Adam10/Kalrn/Samd14/Rgs14/Rpl10a/Map1a/Myo6/Numb/Dgkz/Ppp1r9b/Ctnnb1/Rnf10/Prr7/Vps35/Arrb1/Slc4a8/Nrgn/Mylk2/Pde4b/Cadm1/Grin2d/Actr2/Epb41l1/Eif4g2/Ifngr1/Cdkl5/Rpl4/Syngap1/Phb2/Homer1/Abi1/Akap5/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032367</t>
@@ -5455,7 +5455,7 @@
     <t xml:space="preserve">intracellular cholesterol transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Serac1/Abcg1/Ldlr/Stard4/Arl8b/Scp2/Pcsk9/Abca2</t>
+    <t xml:space="preserve">Abcg1/Serac1/Stard4/Abca2/Ldlr/Arl8b/Pcsk9/Scp2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019915</t>
@@ -5467,7 +5467,7 @@
     <t xml:space="preserve">68/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Abcg1/Stard4/Sqle/Gba/Ppard/Hexa/Ehd1/Asxl2/Sirt1/Plin2/Stat5a/Stat5b/B4galnt1/Apoe</t>
+    <t xml:space="preserve">Abcg1/Stard4/Apoe/Stat5b/Cd36/Sqle/Gba/Ehd1/Stat5a/Ppard/B4galnt1/Hexa/Sirt1/Asxl2/Plin2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032456</t>
@@ -5476,7 +5476,7 @@
     <t xml:space="preserve">endocytic recycling</t>
   </si>
   <si>
-    <t xml:space="preserve">Vps26a/Ptpn23/Micall2/Ccdc93/Ehd1/Vps29/Vps35/Gripap1/Snx3/Ehd3/Akap5/Dennd1c/Cmtm6/Vps53/Ankrd27</t>
+    <t xml:space="preserve">Vps26a/Ankrd27/Ptpn23/Vps53/Micall2/Cmtm6/Ehd1/Vps35/Vps29/Ccdc93/Ehd3/Dennd1c/Gripap1/Akap5/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001909</t>
@@ -5485,7 +5485,7 @@
     <t xml:space="preserve">leukocyte mediated cytotoxicity</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Lamp1/Tusc2/Arl8b/Ap1g1/Stat5a/Stat5b/Fcgr3/Ptpn6/Unc13d/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9/Spi1/Tyrobp/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Ptprc/Coro1a/Lamp1/Spi1/Vav1/P2rx7/Lgals9/Stat5b/Ptpn6/Unc13d/Ap1g1/H2-T23/Tyrobp/Stat5a/Pik3r6/Havcr2/Fcgr3/Serpinb9/Arl8b/Cadm1/Tusc2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030029</t>
@@ -5497,7 +5497,7 @@
     <t xml:space="preserve">660/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Fhdc1/Mink1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Specc1/Cd47/Mylk2/Washc2/Nedd9/Epb41/Washc5/Gab1/Tsc1/Asap3/Plek2/Micall2/Frmd6/Samd14/Rhof/Actn1/Arhgap12/Mybpc3/Ssh2/Mlst8/Arrb1/Myo6/Wasl/Plekhg2/Ppp1r9b/C9orf72/Nckap1/Nck1/Sorbs1/Rictor/Swap70/Twf1/Washc4/Arhgap35/Daam1/Cttn/Taok1/Cdc42bpa/Abi1/Iqgap1/Actr2/Was/Flii/Pde4d/Wdr1/Sdad1/Stau2/Parvg/Myh10/Wipf1/Hcls1/Sptan1/Flna/Srf/Cap1/Sh3pxd2b/Epb41l1/Arpc2/Pdxp/Vangl2/Pdlim2/Rangrf/Pde4b/Rac1/Rac2/Capg/Fes/Arhgef2/Dock2/Tgfb1/Vill/Tyrobp/Coro1a/Arhgef18/Myo1g/Elmo1/Lcp1/Arhgdib</t>
+    <t xml:space="preserve">Spta1/Fhdc1/Add2/Cobl/Sptb/Dock2/Map3k1/Myo1g/Arhgef2/Vill/Mink1/Coro1a/Tmod1/Rac2/Tgfb1/Washc5/Washc2/Tsc1/Dmtn/Rac1/Cd47/Capg/Elmo1/Gab1/Cap1/Actn1/Micall2/Lcp1/Arhgdib/Arpc2/Arhgef18/Specc1/Flna/Frmd6/Samd14/Mlst8/Epb41/Sh3pxd2b/Ssh2/Myo6/Nedd9/Pdxp/Rangrf/Tyrobp/Myh10/Wasl/Ppp1r9b/Srf/Fes/Nckap1/Wdr1/Flii/Arhgap12/Arrb1/Twf1/Vangl2/Plekhg2/Hcls1/Asap3/Wipf1/Sptan1/Mylk2/Pde4b/Swap70/Washc4/Sdad1/Pdlim2/Plek2/C9orf72/Actr2/Taok1/Epb41l1/Iqgap1/Parvg/Rhof/Stau2/Cdc42bpa/Sorbs1/Abi1/Arhgap35/Nck1/Cttn/Pde4d/Daam1/Rictor/Mybpc3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0018205</t>
@@ -5506,7 +5506,7 @@
     <t xml:space="preserve">peptidyl-lysine modification</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Egr2/Nfe2/Snca/Tollip/Wbp2/Arrb1/Rlf/Flcn/Atp7a/Kmt2c/Pias2/Dip2b/Jade3/Taf6l/Kdm4c/Ash1l/Brca1/Ncoa1/Arnt/Gfi1b/Asxl2/Pias1/Nsd3/Sirt1/Kat6a/Ctcf/Setdb1/Ctnnb1/Msl3/Tcf3/Trim28/Ddx21/Smyd2/Pwp1/Jade2/Ldb1/Ruvbl2/Sgf29/Plod3/Mllt6/Ifih1/Glyr1/Mybbp1a/Dnmt3b/Jade1/Pcgf2/Kat2a/Gata2/Smyd5/Tgfb1/Spi1/Myb</t>
+    <t xml:space="preserve">Egr1/Snca/Myb/Tgfb1/Nfe2/Smyd5/Spi1/Tollip/Glyr1/Kat2a/Wbp2/Jade1/Jade3/Arnt/Dip2b/Dnmt3b/Rlf/Ldb1/Pias2/Egr2/Mllt6/Pcgf2/Gata2/Ctnnb1/Mybbp1a/Plod3/Arrb1/Ruvbl2/Pwp1/Tcf3/Atp7a/Trim28/Flcn/Kmt2c/Ifih1/Sirt1/Kdm4c/Sgf29/Ash1l/Nsd3/Ncoa1/Setdb1/Brca1/Kat6a/Pias1/Gfi1b/Smyd2/Taf6l/Msl3/Ctcf/Asxl2/Ddx21/Jade2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002281</t>
@@ -5515,7 +5515,7 @@
     <t xml:space="preserve">macrophage activation involved in immune response</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Ticam1/Plcg2/Havcr2/Tyrobp/Syk</t>
+    <t xml:space="preserve">Syk/Grn/Plcg2/Ticam1/Tyrobp/Havcr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009067</t>
@@ -5524,7 +5524,7 @@
     <t xml:space="preserve">aspartate family amino acid biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Got1/Got2/Enoph1/Mtap/Plod3/Mthfd1</t>
+    <t xml:space="preserve">Plod3/Mthfd1/Got2/Mtap/Got1/Enoph1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1900153</t>
@@ -5533,7 +5533,7 @@
     <t xml:space="preserve">positive regulation of nuclear-transcribed mRNA catabolic process, deadenylation-dependent decay</t>
   </si>
   <si>
-    <t xml:space="preserve">Tnrc6b/Tob1/Ago2/Tnrc6c/Cnot7/Zfp36l1</t>
+    <t xml:space="preserve">Tnrc6b/Zfp36l1/Tob1/Ago2/Tnrc6c/Cnot7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042327</t>
@@ -5545,7 +5545,7 @@
     <t xml:space="preserve">625/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Wnk4/Map3k1/Snca/Agtr1a/Tfrc/Prnp/Pfkfb2/Hipk2/Nedd9/Als2/Gab1/Traf4/Fnip2/Gdf11/Stil/Cdc25b/Cdc6/Pim1/Mapre3/Mlst8/Arrb1/Fzd5/Map3k12/Fbxw7/Mob3c/Flcn/Cib1/Dag1/Dvl2/Rap2b/Birc5/Rictor/Stradb/Gnas/Sirt1/Adipor2/Fnip1/Sh3glb1/Abi1/Rack1/Psen1/Iqgap1/Phb2/Maged1/Pde4d/Dgkz/Hsp90ab1/Igf1r/Hcls1/Prkca/Pik3r5/Rap2c/Prkag2/Fzd7/Akap5/Trp53/Aktip/Irak1/Vangl2/Xrcc5/Plcg2/Lrrk1/Mob3b/Itga5/Rac1/Mmd/Pik3r6/Il4/Csf1/Cxcr4/Lgals9/Arhgef2/Spn/Tgfb1/Cd44/Gdf3/Mst1r/Ptprc/P2rx7/Syk/Eng</t>
+    <t xml:space="preserve">Egr1/Map3k1/Snca/Syk/Arhgef2/Ptprc/Wnk4/Prnp/Tgfb1/Spn/Cd44/Rac1/Fnip2/Pfkfb2/Gab1/Eng/P2rx7/Plcg2/Lgals9/Cxcr4/Als2/Cdc25b/Mst1r/Cd36/Mmd/Xrcc5/Itga5/Hipk2/Gnas/Lrrk1/Cdc6/Irak1/Traf4/Fbxw7/Rap2b/Mlst8/Gdf3/Gdf11/Mob3b/Trp53/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Rap2c/Prkag2/Dgkz/Fzd7/Pik3r6/Maged1/Csf1/Aktip/Sh3glb1/Arrb1/Vangl2/Dvl2/Tfrc/Hcls1/Cib1/Prkca/Hsp90ab1/Adipor2/Flcn/Mapre3/Birc5/Psen1/Sirt1/Iqgap1/Fnip1/Stradb/Map3k12/Phb2/Abi1/Igf1r/Mob3c/Rack1/Pim1/Akap5/Pik3r5/Pde4d/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030220</t>
@@ -5554,7 +5554,7 @@
     <t xml:space="preserve">platelet formation</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Actn1/Vps33a/Cib1/Wdr1/Srf/Ptpn6</t>
+    <t xml:space="preserve">Tal1/Actn1/Ptpn6/Srf/Vps33a/Wdr1/Cib1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070064</t>
@@ -5563,7 +5563,7 @@
     <t xml:space="preserve">proline-rich region binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Itsn1/Gigyf2/Garem1/Cttn/Nedd4/Rabac1/Sh3d19</t>
+    <t xml:space="preserve">Gigyf2/Itsn1/Sh3d19/Rabac1/Nedd4/Garem1/Cttn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009152</t>
@@ -5572,7 +5572,7 @@
     <t xml:space="preserve">purine ribonucleotide biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Snca/Pkm/Flcn/Gcdh/Ndufa10/Parp1/Adss/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Gart/Npr2/Il4/Tgfb1/Nme4/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Nme4/Gart/Pfas/Acsl5/Pdha1/Atic/Pkm/Il4/Adssl1/Npr2/Adsl/Gmpr/Impdh2/Mthfd1/Papss2/Guk1/Dlat/Flcn/Gcdh/Ak4/Ndufa10/Aprt/Adss/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001819</t>
@@ -5584,7 +5584,7 @@
     <t xml:space="preserve">383/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Agtr1a/Optn/Ticam1/Zbtb7b/Arfgef2/Trim56/Atp6ap2/Fzd5/Akap12/Tbk1/1810058I24Rik/Kpna6/Rara/Brca1/Tusc2/Arnt/Sirt1/Nras/Psen1/Ddx21/Pde4d/Ifngr1/Dhx33/Hspd1/Ifih1/Stat5a/Stat5b/Irak1/Fcgr3/Il27ra/Kat2a/Plcg2/Cadm1/Pde4b/Havcr2/Irf5/Il4/Lgals9/Arhgef2/Spn/Tgfb1/Ccdc88b/Laptm5/Tyrobp/Unc93b1/Ptprc/Rftn1/P2rx7/Il1rl1/Cd84/Nfam1/Syk/Oas2</t>
+    <t xml:space="preserve">Egr1/Laptm5/Nfam1/Il1rl1/Rftn1/Syk/Arhgef2/Ptprc/Ccdc88b/Tgfb1/Spn/Oas2/Cd84/P2rx7/Plcg2/Lgals9/Optn/Kat2a/Arfgef2/Unc93b1/Stat5b/Cd36/Atp6ap2/Arnt/Irak1/Tbk1/Zbtb7b/Irf5/Kpna6/Trim56/Agtr1a/Ticam1/Tyrobp/1810058I24Rik/Stat5a/Fzd5/Il4/Il27ra/Havcr2/Fcgr3/Pde4b/Cadm1/Dhx33/Psen1/Ifih1/Tusc2/Sirt1/Hspd1/Ifngr1/Rara/Nras/Brca1/Akap12/Ddx21/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031965</t>
@@ -5593,7 +5593,7 @@
     <t xml:space="preserve">nuclear membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Smox/Tmem120b/Snca/Dnajb2/Prnp/Dmpk/Mlx/Grk5/Myo6/Apeh/Habp4/C9orf72/Nup50/Cpne1/Sirt1/Psen1/Ctnnb1/Dpy19l3/Gtpbp4/Rcc1/Stau2/Tmem97/P2rx1/Tmem109/Spin1/Mfsd10/Vapa/Surf4/Retsat/Alox5ap/Cenpv/Lypla1/Nrm/Dnajc2/Gsto1/P2rx7</t>
+    <t xml:space="preserve">Snca/Prnp/Dnajc2/Tmem120b/Gsto1/Lypla1/Surf4/P2rx7/Alox5ap/Vapa/Nrm/Smox/Retsat/Cenpv/Mlx/Mfsd10/Apeh/Myo6/Spin1/Habp4/Nup50/Grk5/Ctnnb1/Dnajb2/Dmpk/Tmem109/Psen1/Rcc1/Cpne1/Sirt1/C9orf72/Stau2/Gtpbp4/Tmem97/Dpy19l3/P2rx1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050864</t>
@@ -5605,7 +5605,7 @@
     <t xml:space="preserve">118/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tfrc/Aplf/Ticam1/Tcf3/Cd320/Shld2/Stat5a/Samsn1/Stat5b/Ptpn6/Il27ra/Zfp36l1/Il4/Mmp14/Tgfb1/Laptm5/Tyrobp/Btk/Ptprc/Tbc1d10c/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Laptm5/Nfam1/Syk/Ptprc/Tgfb1/Tbc1d10c/Stat5b/Ptpn6/Aplf/Ticam1/Tyrobp/Stat5a/Il4/Mmp14/Zfp36l1/Il27ra/Tfrc/Tcf3/Samsn1/Cd320/Shld2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006911</t>
@@ -5614,7 +5614,7 @@
     <t xml:space="preserve">phagocytosis, engulfment</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Arhgap12/Clcn3/Itgb2/Fcgr3/Gata2/Plcg2/Ano6/Rac1/Rac2/Elmo1</t>
+    <t xml:space="preserve">Appl2/Ano6/Rac2/Rac1/Elmo1/Plcg2/Cd36/Clcn3/Gata2/Arhgap12/Fcgr3/Itgb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0036475</t>
@@ -5629,7 +5629,7 @@
     <t xml:space="preserve">hematopoietic stem cell differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Chd2/N4bp2l2/Pus7/Srf/Trp53/Terc/Xrcc5/Cdk6</t>
+    <t xml:space="preserve">Cdk6/Tal1/Xrcc5/Chd2/Trp53/Srf/Terc/Pus7/N4bp2l2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006091</t>
@@ -5644,7 +5644,7 @@
     <t xml:space="preserve">392/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Snca/Aldh1l2/Pfkfb2/Eno3/Rubcnl/Ddit4/Pkm/Nupr1/Coq10a/Acox1/Bpgm/Gba/Mlst8/Gnpda1/Flcn/Atp7a/Ppp1r3f/Mtch2/Bax/Aco1/Sorbs1/Gnas/Bid/Cox6a1/Ndufa10/Psen1/Cs/Etfb/Idh3g/Phb2/Gpi1/Prps1/Dlat/Idh3a/Pdha1/Adsl/Idh2/Ppif/Suclg2/Mybbp1a/Prkag2/Tcf7l2/Trp53/Cyb561/Khk/H6pd/Cox10/Ak4/Hk2/Nr1d1/Pgm2/Il4/Phlda2/P2rx7</t>
+    <t xml:space="preserve">Snca/Slc4a1/Pfkfb2/P2rx7/Ddit4/Cd36/Khk/Gnas/Pdha1/Mtch2/Acox1/Gba/Mlst8/Pkm/Trp53/Phlda2/Cyb561/Idh2/Coq10a/Il4/Prkag2/Adsl/Gnpda1/Pgm2/Aco1/H6pd/Mybbp1a/Cox10/Aldh1l2/Nr1d1/Idh3a/Ppif/Cs/Suclg2/Prps1/Eno3/Dlat/Atp7a/Hk2/Rubcnl/Flcn/Psen1/Bid/Bpgm/Ak4/Ndufa10/Idh3g/Bax/Nupr1/Ppp1r3f/Cox6a1/Phb2/Etfb/Sorbs1/Tcf7l2/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045121</t>
@@ -5656,7 +5656,7 @@
     <t xml:space="preserve">300/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Add2/Abcg2/Prkar2b/Ctsd/Prnp/Tpp1/Ldlr/Pikfyve/Lamtor1/Atp2b1/Tuba1a/Atp7a/Lamtor3/Dag1/Rap2b/Sorbs1/Gnas/Stom/Vcl/Psen1/Iqgap1/Ctnnb1/Nedd4/Cbl/Hspd1/Igf1r/Prkca/P2rx1/Tnfrsf26/Itgb2/Plpp2/Akap5/Rangrf/Plvap/Cd48/Selplg/Lcp2/Cd44/Btk/Ptprc/Rftn1/P2rx7/Nfam1</t>
+    <t xml:space="preserve">Btk/Add2/Ctsd/Prkar2b/Nfam1/Rftn1/Ptprc/Tpp1/Prnp/Abcg2/Cd44/P2rx7/Atp2b1/Cd36/Pld2/Ldlr/Pikfyve/Gnas/Cd48/Rap2b/Dag1/Lcp2/Selplg/Rangrf/Tuba1a/Lamtor3/Lamtor1/Ctnnb1/Nedd4/Plvap/Itgb2/Prkca/Atp7a/Plpp2/Psen1/Iqgap1/Hspd1/Sorbs1/Igf1r/Cbl/P2rx1/Tnfrsf26/Stom/Akap5/Vcl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000758</t>
@@ -5665,7 +5665,7 @@
     <t xml:space="preserve">positive regulation of peptidyl-lysine acetylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Nfe2/Wbp2/Arrb1/Dip2b/Brca1/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Kat2a/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Nfe2/Glyr1/Kat2a/Wbp2/Dip2b/Mybbp1a/Arrb1/Ruvbl2/Brca1/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051015</t>
@@ -5674,7 +5674,7 @@
     <t xml:space="preserve">actin filament binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Add2/Dmtn/Sptb/Micall2/Samd14/Actn1/Myo6/Ppp1r9b/Myo9a/Twf1/Vcl/Cttn/Iqgap1/Actr2/Flii/Wdr1/Tnni3/Myh10/Hcls1/Sptan1/Flna/Arpc2/Adssl1/Capg/Vill/Rcsd1/Coro1a/Myo1g/Lcp1</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Myo1g/Vill/Coro1a/Tmod1/Dmtn/Capg/Rcsd1/Actn1/Micall2/Lcp1/Arpc2/Flna/Samd14/Myo6/Myh10/Adssl1/Ppp1r9b/Wdr1/Flii/Twf1/Hcls1/Sptan1/Actr2/Tnni3/Iqgap1/Cttn/Myo9a/Vcl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005635</t>
@@ -5686,7 +5686,7 @@
     <t xml:space="preserve">384/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mgst3/Smox/Tmem120b/Snca/Itsn1/Dnajb2/Prnp/Ache/Dmpk/Mlx/Grk5/Igf2r/Myo6/Apeh/Habp4/Chmp3/Bax/C9orf72/Nup50/Ccar1/Nemp1/Ipo9/Cpne1/Sirt1/Bnip2/Vps4b/Fbxw11/Psen1/Parp1/Ctnnb1/Dpy19l3/Gtpbp4/Rcc1/Stau2/Tmem97/Nup210/Anxa11/P2rx1/Tmem109/Spin1/Mfsd10/Slc22a18/Vapa/Surf4/Retsat/Clic1/Alox5ap/Cenpv/Lypla1/Rac2/Nrm/Dnajc2/Gsto1/Apoe/P2rx7</t>
+    <t xml:space="preserve">Snca/Mgst3/Prnp/Rac2/Dnajc2/Tmem120b/Gsto1/Lypla1/Itsn1/Surf4/Clic1/P2rx7/Alox5ap/Vapa/Nrm/Smox/Apoe/Igf2r/Retsat/Cenpv/Ache/Mlx/Mfsd10/Apeh/Myo6/Spin1/Habp4/Ipo9/Nup50/Grk5/Ctnnb1/Dnajb2/Anxa11/Dmpk/Ccar1/Chmp3/Nup210/Tmem109/Psen1/Rcc1/Cpne1/Sirt1/C9orf72/Slc22a18/Bax/Stau2/Gtpbp4/Tmem97/Bnip2/Dpy19l3/Parp1/Fbxw11/Vps4b/P2rx1/Nemp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007034</t>
@@ -5695,7 +5695,7 @@
     <t xml:space="preserve">vacuolar transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Grn/Als2/Vps11/Lamp1/Ptpn23/Igf2r/Trak2/Vps33a/Ap3d1/Chmp3/C9orf72/Vps29/Vps35/Arl8b/Clec16a/Vps4b/Nedd4/Ap1g1/Dtx3l/Ehd3/Pcsk9/Aktip/Vps53/Laptm5</t>
+    <t xml:space="preserve">Atp6v0d1/Laptm5/Grn/Lamp1/Ptpn23/Vps53/Vps11/Als2/Igf2r/Ap1g1/Ap3d1/Vps33a/Vps35/Aktip/Nedd4/Vps29/Chmp3/Trak2/Dtx3l/Arl8b/Ehd3/C9orf72/Pcsk9/Vps4b/Clec16a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002706</t>
@@ -5704,7 +5704,7 @@
     <t xml:space="preserve">regulation of lymphocyte mediated immunity</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Tfrc/Aplf/Lamp1/Fzd5/Fbxo38/Was/Hspd1/Ap1g1/Shld2/Stat5a/Vsir/Stat5b/Fcgr3/Ptpn6/Il27ra/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Il4/Lgals9/Spn/Tgfb1/Ptprc/Dpp4/P2rx7</t>
+    <t xml:space="preserve">Ptprc/Tgfb1/Spn/Lamp1/Vav1/P2rx7/Lgals9/Stat5b/Ptpn6/Dpp4/Ap1g1/Aplf/H2-T23/Stat5a/Fzd5/Il4/Pik3r6/Il27ra/Havcr2/Fcgr3/Serpinb9/Tfrc/Cadm1/Vsir/Fbxo38/Hspd1/Shld2/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098984</t>
@@ -5713,7 +5713,7 @@
     <t xml:space="preserve">neuron to neuron synapse</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Slc6a9/Add2/Dmtn/Map1a/Mpp2/Mylk2/Prnp/Kalrn/Als2/Tsc1/Picalm/Adam10/Samd14/Numb/Nrgn/Arrb1/Arfgef2/Syn1/Myo6/Ppp1r9b/Rnf10/Cdkl5/Vps35/Homer1/Abi1/Rpl4/Actr2/Ctnnb1/Phb2/Ifngr1/Dgkz/Eif4g2/Syngap1/Rpl10a/Epb41l1/Akap5/Slc4a8/Atp1b2/Atp1a3/Grin2d/Cadm1/Pde4b/Kcnab2/Prr7/Ptprs/Ywhaz/Rgs14/Arhgef2</t>
+    <t xml:space="preserve">Add2/Picalm/Arhgef2/Ptprs/Slc6a9/Prnp/Ywhaz/Tsc1/Dmtn/Cpeb4/Kcnab2/Mpp2/Als2/Arfgef2/Adam10/Kalrn/Samd14/Rgs14/Rpl10a/Map1a/Myo6/Numb/Dgkz/Ppp1r9b/Ctnnb1/Rnf10/Prr7/Vps35/Arrb1/Slc4a8/Atp1b2/Nrgn/Mylk2/Pde4b/Atp1a3/Cadm1/Grin2d/Actr2/Epb41l1/Eif4g2/Ifngr1/Cdkl5/Rpl4/Syngap1/Phb2/Homer1/Abi1/Akap5/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098857</t>
@@ -5731,7 +5731,7 @@
     <t xml:space="preserve">56/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctns/Pip4p1/Rragc/Sesn1/Lamtor1/Mlst8/Smcr8/Flcn/Lamtor3/C9orf72/Sesn3/Rps6kb1/Clec16a</t>
+    <t xml:space="preserve">Rragc/Ctns/Pip4p1/Sesn1/Mlst8/Lamtor3/Lamtor1/Smcr8/Flcn/Sesn3/C9orf72/Clec16a/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001667</t>
@@ -5743,7 +5743,7 @@
     <t xml:space="preserve">343/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Egr3/Ptp4a3/Dmtn/Sema4b/Grn/Ptpn23/Anxa3/Hdac5/Ppard/Akap12/Fbxw7/Cib1/Glipr2/Nckap1/Pkn2/Ago2/Gna13/Sirt1/Adipor2/Mia3/Sgpl1/Iqgap1/Lrp5/Gpi1/Prkca/Megf8/Sp100/Srf/Stat5a/Itgb2/Cap1/Lpxn/Pik3cd/Fut8/Sema4a/Gata2/Plcg2/Gab2/Rac1/Rcc2/Cenpv/Il4/Cxcr4/Apoe/Tgfb1/Hdac7/Coro1a/Dpp4/Arhgdib</t>
+    <t xml:space="preserve">Hdac7/Appl2/Coro1a/Tgfb1/Grn/Dmtn/Rac1/Rcc2/Ptpn23/Gab2/Cap1/Plcg2/Arhgdib/Cxcr4/Apoe/Dpp4/Cenpv/Megf8/Fbxw7/Ptp4a3/Fut8/Egr3/Pkn2/Sema4b/Pik3cd/Stat5a/Il4/Gata2/Sema4a/Gna13/Srf/Nckap1/Ppard/Hdac5/Anxa3/Lrp5/Cib1/Itgb2/Prkca/Adipor2/Sirt1/Iqgap1/Ago2/Akap12/Mia3/Sgpl1/Sp100/Glipr2/Gpi1/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031253</t>
@@ -5755,7 +5755,7 @@
     <t xml:space="preserve">244/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Ank1/Abcg2/Dmtn/Mpp2/Slc11a2/Myo6/Atp2b1/Atp7a/Ppp1r9b/Cdkl5/Ehd1/Mosmo/Twf1/Gna13/Snap29/Ctnnb1/Gpi1/Hsp90ab1/Slc22a5/Iqce/Ehd3/Mfsd10/Akap5/Arpc2/Pdxp/Atp1b2/Plcg2/Tmem231/Itga5/Rac1/Ripor2/Slc19a1/Arhgef2/Cd44/Tbc1d10c</t>
+    <t xml:space="preserve">Appl2/Arhgef2/Slc11a2/Abcg2/Dmtn/Ank1/Cd44/Rac1/Ripor2/Tbc1d10c/Plcg2/Mpp2/Arpc2/Atp2b1/Cd36/Pld2/Itga5/Ehd1/Mfsd10/Myo6/Slc19a1/Pdxp/Gna13/Ppp1r9b/Ctnnb1/Tmem231/Iqce/Twf1/Atp1b2/Hsp90ab1/Ehd3/Atp7a/Cdkl5/Slc22a5/Akap5/Snap29/Mosmo/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045860</t>
@@ -5767,7 +5767,7 @@
     <t xml:space="preserve">285/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Wnk4/Map3k1/Snca/Agtr1a/Prnp/Nedd9/Als2/Gab1/Traf4/Stil/Cdc25b/Cdc6/Pim1/Mapre3/Fzd5/Map3k12/Fbxw7/Cib1/Dag1/Dvl2/Stradb/Sirt1/Abi1/Psen1/Iqgap1/Phb2/Maged1/Hsp90ab1/Pik3r5/Prkag2/Irak1/Vangl2/Xrcc5/Mmd/Pik3r6/Il4/Csf1/Tgfb1/Mst1r/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Egr1/Map3k1/Snca/Syk/Ptprc/Wnk4/Prnp/Tgfb1/Gab1/P2rx7/Als2/Cdc25b/Mst1r/Mmd/Xrcc5/Cdc6/Irak1/Traf4/Fbxw7/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Prkag2/Pik3r6/Maged1/Csf1/Vangl2/Dvl2/Cib1/Hsp90ab1/Mapre3/Psen1/Sirt1/Iqgap1/Stradb/Map3k12/Phb2/Abi1/Pim1/Pik3r5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006888</t>
@@ -5776,7 +5776,7 @@
     <t xml:space="preserve">endoplasmic reticulum to Golgi vesicle-mediated transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Ank1/Insig1/Trappc2l/Rnf139/Trappc8/Ergic2/Mia3/Uso1/Mia2/Ergic3/Copg2/Use1/Lman1/Tmed5/Sar1b/Ier3ip1/Tmed3/Vapa/Rangrf/Ergic1/Bcap29</t>
+    <t xml:space="preserve">Ank1/Bcap29/Vapa/Ergic1/Insig1/Lman1/Tmed3/Rnf139/Rangrf/Trappc2l/Copg2/Trappc8/Mia2/Sar1b/Ergic3/Ier3ip1/Tmed5/Mia3/Use1/Ergic2/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002069</t>
@@ -5788,7 +5788,7 @@
     <t xml:space="preserve">11/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Gdf11/Fzd5/Bhlha15/Gata2/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Gdf11/Fzd5/Gata2/Bhlha15</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043031</t>
@@ -5797,7 +5797,7 @@
     <t xml:space="preserve">negative regulation of macrophage activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Ldlr/Cst7/Nr1d1/Il4</t>
+    <t xml:space="preserve">Grn/Ldlr/Il4/Nr1d1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045586</t>
@@ -5806,7 +5806,7 @@
     <t xml:space="preserve">regulation of gamma-delta T cell differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr3/Stat5a/Stat5b/Ptprc/Syk</t>
+    <t xml:space="preserve">Syk/Ptprc/Stat5b/Egr3/Stat5a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046643</t>
@@ -5824,7 +5824,7 @@
     <t xml:space="preserve">220/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slfn14/Fam210b/Epb42/Tal1/Washc5/Gdf11/Klf1/Cdc25b/Gba/Atp6ap2/Fzd5/Bhlha15/Ppard/Fbxo5/Shb/Dag1/Tusc2/Rb1/Tut7/Asxl2/Psen1/Ctnnb1/Wdr77/Mbtps2/Rps6ka2/Akap5/Ppp2r1a/Gata2/Snx10/Ano6/Npr2/Rac1/Cbfb/Tgfb1/Btk</t>
+    <t xml:space="preserve">Btk/Fam210b/Ano6/Tgfb1/Slfn14/Washc5/Tal1/Rac1/Epb42/Cbfb/Klf1/Ppp2r1a/Cdc25b/Atp6ap2/Gba/Gdf11/Dag1/Fzd5/Gata2/Npr2/Snx10/Ctnnb1/Ppard/Rb1/Fbxo5/Rps6ka2/Psen1/Bhlha15/Tusc2/Mbtps2/Tut7/Wdr77/Asxl2/Akap5/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019904</t>
@@ -5836,7 +5836,7 @@
     <t xml:space="preserve">683/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr2/Nfe2/Rph3al/Snca/Prkar2b/Cited2/Mpp2/Tceal8/Traf4/Picalm/Adam10/Vps11/Lamp1/Tceal9/Cltc/Acox1/Map1lc3b/Klf1/Uvrag/Actn1/Trak2/Clcn3/Rabep1/Atp2b1/Tuba1a/Gpsm2/Dag1/Pias2/Bax/Dvl2/Rara/Rap2b/Nck1/Ddx6/Gnas/Mcl1/Rb1/Sirt1/Rps6kb1/Ap2m1/Abi1/Usp47/Rack1/Psen1/Iqgap1/Ctnnb1/Tcf3/Was/Nedd4/Trim28/Ppp3r1/Cct6a/Armc10/Cbl/Hsp90ab1/Lancl1/Tnni3/Ldb1/Wipf1/Syngap1/Hcls1/Slc22a5/Sp100/Sh3bgrl/Etv6/Plekha2/Fzd7/Sh3pxd2b/Tcf7l2/Lin7c/Unc13a/Akap5/Fut8/Trp53/Ptpn6/Gusb/Gata2/Vapa/Cadm1/Gab2/Rcc2/Capg/Vim/Ywhaz/Spn/Myb/Arhgap27/Elmo1/Syk</t>
+    <t xml:space="preserve">Prkar2b/Snca/Syk/Picalm/Myb/Ywhaz/Cltc/Rph3al/Spn/Lamp1/Nfe2/Capg/Arhgap27/Rcc2/Elmo1/Gab2/Klf1/Cited2/Actn1/Vapa/Vps11/Vim/Mpp2/Atp2b1/Map1lc3b/Rabep1/Adam10/Lin7c/Ptpn6/Gnas/Gusb/Tceal9/Tceal8/Traf4/Uvrag/Acox1/Rap2b/Sh3pxd2b/Trp53/Fut8/Clcn3/Dag1/Ldb1/Ddx6/Pias2/Egr2/Tuba1a/Gata2/Fzd7/Ctnnb1/Rb1/Etv6/Mcl1/Nedd4/Armc10/Dvl2/Gpsm2/Hcls1/Sh3bgrl/Wipf1/Trak2/Tcf3/Hsp90ab1/Trim28/Ap2m1/Cadm1/Lancl1/Psen1/Plekha2/Sirt1/Tnni3/Iqgap1/Ppp3r1/Rara/Bax/Syngap1/Slc22a5/Abi1/Unc13a/Cct6a/Nck1/Tcf7l2/Usp47/Cbl/Rack1/Akap5/Sp100/Rps6kb1/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010873</t>
@@ -5845,7 +5845,7 @@
     <t xml:space="preserve">positive regulation of cholesterol esterification</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Scd1/Stard4/Apoe</t>
+    <t xml:space="preserve">Stard4/Apoe/Agtr1a/Scd1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0014731</t>
@@ -5854,7 +5854,7 @@
     <t xml:space="preserve">spectrin-associated cytoskeleton</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Ank1/Dmtn/Sptb</t>
+    <t xml:space="preserve">Spta1/Sptb/Dmtn/Ank1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903979</t>
@@ -5863,7 +5863,7 @@
     <t xml:space="preserve">negative regulation of microglial cell activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Ldlr/Cst7/Nr1d1</t>
+    <t xml:space="preserve">Grn/Ldlr/Nr1d1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034470</t>
@@ -5875,7 +5875,7 @@
     <t xml:space="preserve">386/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mrm1/Isg20/Pop5/Trmt12/Utp14b/Nr2f1/Ago2/Trmt1l/Tut7/Helq/Ints8/Zc3h7b/Ddx27/Parn/Elp3/Rpl35/Ddx18/Snu13/Pa2g4/Ddx21/Ddx49/Gtpbp4/Pus7/Rcl1/Ebna1bp2/Wdr36/Rrp1b/Urb1/Pwp1/Tyw1/Trmt2b/Exosc1/Lyar/Wdr43/Exosc5/Tarbp1/Wdr4/Mdn1/Heatr1/Nat10/Naf1/Rrp12/Rpl10a/Mettl1/Nol6/Trp53/Wdr46/Tfb2m/Trub1/Rrp9/Tsen15/Npm3/Ago4/2210016F16Rik/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Npm3/Ago4/Trub1/Nat10/Rpl10a/Tsen15/Rrp9/Wdr46/Trp53/Utp14b/Trmt2b/Mrm1/Nol6/Pop5/Naf1/Tfb2m/Isg20/2210016F16Rik/Rrp12/Heatr1/Mdn1/Wdr4/Pwp1/Pus7/Urb1/Tyw1/Ints8/Wdr43/Exosc5/Ddx18/Rcl1/Exosc1/Nr2f1/Tarbp1/Mettl1/Trmt12/Snu13/Wdr36/Lyar/Trmt1l/Ago2/Tut7/Gtpbp4/Ebna1bp2/Ddx21/Helq/Zc3h7b/Ddx27/Ddx49/Parn/Rpl35/Pa2g4/Elp3/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033137</t>
@@ -5884,7 +5884,7 @@
     <t xml:space="preserve">negative regulation of peptidyl-serine phosphorylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Ddit4/Ggnbp2/Bax/Nck1/Rack1/Pde4d/Pwp1</t>
+    <t xml:space="preserve">Dmtn/Ddit4/Ggnbp2/Pwp1/Bax/Nck1/Rack1/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016773</t>
@@ -5896,7 +5896,7 @@
     <t xml:space="preserve">577/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Fn3k/Mink1/Wnk4/Map3k1/Bmp2k/Mylk2/Kalrn/Pfkfb2/Hipk2/Dmpk/Pkm/Pim1/Pikfyve/Grk5/Stk38l/Map3k12/Tbk1/Sgk3/Stk25/Ppp1r9b/Cdkl5/Uhmk1/Ttbk2/Pkn2/Dyrk1a/N4bp2/Clk3/Twf1/Mknk1/Pip4k2c/Dbf4/Cdk16/Mknk2/Rps6kb1/Taok1/Cdc42bpa/Pi4ka/Grk6/Trim28/Nek4/Nek9/Pik3c2b/Dgkz/Pfkfb3/Ulk2/Igf1r/Prkca/Rps6ka2/Adck1/Gk/Prkag2/Map4k1/Map3k15/Agk/Pik3cd/Amhr2/Dapk1/Cad/Irak1/Khk/Lrrk1/Papss2/Hk2/Npr2/Pim3/Mmd/Pgm2/Pik3r6/Fes/Map3k6/Trib2/Mst1r/Btk/Cdk6/Jak3/Syk/Eng</t>
+    <t xml:space="preserve">Btk/Map3k1/Jak3/Syk/Wnk4/Mink1/Cdk6/Trib2/Pfkfb2/Fn3k/Bmp2k/Eng/Mst1r/Pikfyve/Mmd/Khk/Dyrk1a/Pim3/Kalrn/Hipk2/Lrrk1/Irak1/Tbk1/Cad/Stk25/Stk38l/Pkm/Pkn2/Agk/Pik3cd/Gk/Prkag2/Npr2/Dgkz/Map4k1/Map3k6/Ppp1r9b/Pgm2/Pik3r6/Fes/Grk5/Dapk1/Uhmk1/Nek9/Amhr2/Dmpk/Twf1/Map3k15/Papss2/Mylk2/Mknk2/Clk3/Prkca/Cdk16/Trim28/Ttbk2/Hk2/Rps6ka2/Ulk2/Adck1/Taok1/Nek4/Cdkl5/Cdc42bpa/Map3k12/Sgk3/Pfkfb3/N4bp2/Igf1r/Dbf4/Grk6/Mknk1/Pim1/Rps6kb1/Pip4k2c/Pi4ka/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042149</t>
@@ -5905,7 +5905,7 @@
     <t xml:space="preserve">cellular response to glucose starvation</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Sesn1/Bhlha15/Sesn3/Mtmr3/Sirt1/Sh3glb1/Plin2/Mybbp1a/Prkag2/Trp53/Pmaip1</t>
+    <t xml:space="preserve">Cpeb4/Sesn1/Pmaip1/Trp53/Mtmr3/Prkag2/Mybbp1a/Sh3glb1/Bhlha15/Sesn3/Sirt1/Plin2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016050</t>
@@ -5914,7 +5914,7 @@
     <t xml:space="preserve">vesicle organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Abcb6/Snca/Insig1/Abcg1/Trappc2l/Rubcnl/Washc5/Pheta2/Als2/Picalm/Vps11/Uvrag/Pikfyve/Lamtor1/Arfgef2/Clcn3/Tmcc1/Wasl/Dnajc13/Rfx2/Fbxo5/Ap3d1/Chmp3/Exoc8/Trappc8/Washc4/Arl8b/Snap29/Ap2m1/Mia3/Uso1/Snx3/Vps4b/Ap1g1/Sar1b/Srgn/Unc13a/Aktip/Vapa/Snx10/Cplx2/Ankrd27/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Snca/Picalm/Coro1a/Abcb6/Washc5/Abcg1/Ankrd27/P2rx7/Pheta2/Vapa/Vps11/Als2/Arfgef2/Pikfyve/Insig1/Uvrag/Dnajc13/Ap1g1/Tmcc1/Clcn3/Wasl/Snx10/Lamtor1/Trappc2l/Ap3d1/Aktip/Trappc8/Fbxo5/Rfx2/Chmp3/Exoc8/Srgn/Sar1b/Cplx2/Arl8b/Ap2m1/Rubcnl/Washc4/Unc13a/Vps4b/Mia3/Snx3/Snap29/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990778</t>
@@ -5923,7 +5923,7 @@
     <t xml:space="preserve">protein localization to cell periphery</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ank1/Tspan33/Optn/Prnp/Kalrn/Epb41/Picalm/Adam10/Cltc/Gga2/Numb/Ppp2r5a/Rabep1/Gpsm2/Cib1/Ppp1r9b/Dag1/Ehd1/Golga4/Vps35/Gripap1/Sorbs1/Pacs2/Ap2m1/Rack1/Gorasp2/Gopc/Ttc7b/Scp2/Lztfl1/Pgrmc1/Flna/Ptpn9/Ehd3/Zdhhc23/Lin7c/Abca2/Akap5/Pgap2/Rangrf/Vamp5/Rac1/Lypla1/Mmp14/Tgfb1/Fyb</t>
+    <t xml:space="preserve">Picalm/Slc4a1/Prnp/Tgfb1/Cltc/Ank1/Fyb/Tspan33/Rac1/Gga2/Lypla1/Ppp2r5a/Abca2/Optn/Vamp5/Rabep1/Adam10/Lin7c/Kalrn/Flna/Pgap2/Ehd1/Pacs2/Epb41/Dag1/Numb/Rangrf/Mmp14/Ppp1r9b/Ptpn9/Vps35/Gorasp2/Gpsm2/Cib1/Ehd3/Ap2m1/Pgrmc1/Golga4/Scp2/Ttc7b/Lztfl1/Sorbs1/Gripap1/Rack1/Akap5/Gopc/Zdhhc23</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002449</t>
@@ -5932,7 +5932,7 @@
     <t xml:space="preserve">lymphocyte mediated immunity</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Tfrc/Aplf/Lamp1/Gba/Fzd5/Rnf168/Swap70/Arl8b/Fbxo38/Was/Hspd1/Ap1g1/Shld2/Stat5a/Vsir/Stat5b/Fcgr3/Ptpn6/Il27ra/Traf3ip2/Unc13d/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Il4/Lgals9/Spn/Tgfb1/Unc93b1/Btk/Ptprc/Coro1a/Dpp4/Myo1g/Rftn1/P2rx7</t>
+    <t xml:space="preserve">Btk/Myo1g/Rftn1/Ptprc/Coro1a/Tgfb1/Spn/Lamp1/Vav1/P2rx7/Lgals9/Unc93b1/Stat5b/Ptpn6/Dpp4/Unc13d/Gba/Ap1g1/Aplf/H2-T23/Stat5a/Fzd5/Il4/Pik3r6/Il27ra/Rnf168/Havcr2/Fcgr3/Serpinb9/Tfrc/Arl8b/Swap70/Cadm1/Vsir/Fbxo38/Traf3ip2/Hspd1/Shld2/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030593</t>
@@ -5944,7 +5944,7 @@
     <t xml:space="preserve">70/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Prex1/Pikfyve/Mospd2/Mpp1/Pde4d/Prkca/Itgb2/Fcgr3/Vav1/Pde4b/Rac1/Ripor2/Rac2/Dpp4/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Rac1/Ripor2/Vav1/Prex1/Pikfyve/Dpp4/Mospd2/Fcgr3/Mpp1/Itgb2/Prkca/Pde4b/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019218</t>
@@ -5956,7 +5956,7 @@
     <t xml:space="preserve">91/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Agtr1a/Scd1/Insig1/Abcg1/Ldlr/Stard4/Lamtor1/Lpcat3/Sirt1/Scp2/Igf1r/Stat5a/Abca2/Stat5b/H6pd/Nr1d1/Apoe</t>
+    <t xml:space="preserve">Egr1/Abcg1/Stard4/Abca2/Apoe/Stat5b/Ldlr/Insig1/Agtr1a/Scd1/Stat5a/H6pd/Lamtor1/Nr1d1/Lpcat3/Sirt1/Scp2/Igf1r</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098927</t>
@@ -5968,7 +5968,7 @@
     <t xml:space="preserve">38/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Wdr81/Vps11/Ptpn23/Dnajc13/Sh3glb1/Snx3/Flna/Aktip/Ankrd27/Coro1a</t>
+    <t xml:space="preserve">Coro1a/Ankrd27/Ptpn23/Vps11/Wdr81/Flna/Dnajc13/Aktip/Sh3glb1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0035914</t>
@@ -5980,7 +5980,7 @@
     <t xml:space="preserve">57/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Btg2/Egr2/Cited2/Hlf/Mylk2/Arntl/Fos/Nupr1/Hdac5/Rb1/Med20/Nr1d2</t>
+    <t xml:space="preserve">Egr1/Btg2/Cited2/Hlf/Nr1d2/Arntl/Egr2/Hdac5/Rb1/Mylk2/Fos/Nupr1/Med20</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006869</t>
@@ -5992,7 +5992,7 @@
     <t xml:space="preserve">312/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Wnk4/Abcg2/Slc43a3/Agtr1a/Serac1/Abcg1/Atg9a/Ldlr/Stard4/Lamtor1/Ppard/Lpcat3/Tex2/Tmem41b/Atg2b/Arl8b/Sirt1/Rps6kb1/Vps4b/Plin2/Got2/Scp2/Esyt1/Mfsd2b/Pdzd8/Sar1b/Pcsk9/Ugcg/Pla2g12a/Abca2/Irak1/Acsl5/Prelid2/Vapa/Surf4/Ano6/Rft1/Pitpnm2/Spns3/Pla2g1b/Apoe/Nme4/P2rx7/Syk</t>
+    <t xml:space="preserve">Syk/Slc43a3/Slc4a1/Wnk4/Ano6/Abcg2/Abcg1/Surf4/Nme4/Pitpnm2/Serac1/P2rx7/Stard4/Abca2/Vapa/Acsl5/Apoe/Cd36/Ugcg/Ldlr/Irak1/Atg9a/Atg2b/Pdzd8/Rft1/Agtr1a/Pla2g12a/Pla2g1b/Tex2/Lamtor1/Tmem41b/Ppard/Spns3/Got2/Esyt1/Lpcat3/Sar1b/Arl8b/Sirt1/Prelid2/Pcsk9/Scp2/Vps4b/Rps6kb1/Plin2/Mfsd2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002717</t>
@@ -6001,7 +6001,7 @@
     <t xml:space="preserve">positive regulation of natural killer cell mediated immunity</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Ap1g1/Stat5a/Stat5b/Vav1/Cadm1/Dpp4</t>
+    <t xml:space="preserve">Lamp1/Vav1/Stat5b/Dpp4/Ap1g1/Stat5a/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009678</t>
@@ -6010,7 +6010,7 @@
     <t xml:space="preserve">pyrophosphate hydrolysis-driven proton transmembrane transporter activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp6v1a/Atp6v1b2/Atp6v0b/Atp6v1g1</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1c1/Atp6v1e1/Atp6v1b2/Atp6v1a/Atp6v0b/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016645</t>
@@ -6019,7 +6019,7 @@
     <t xml:space="preserve">oxidoreductase activity, acting on the CH-NH group of donors</t>
   </si>
   <si>
-    <t xml:space="preserve">Smox/Aldh1l2/Pycr1/Pycr2/Mthfd1/Mthfd1l/Prodh</t>
+    <t xml:space="preserve">Smox/Prodh/Aldh1l2/Mthfd1/Mthfd1l/Pycr1/Pycr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046037</t>
@@ -6028,7 +6028,7 @@
     <t xml:space="preserve">GMP metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Impdh2/Guk1/Aprt/Adsl/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">Gart/Pfas/Atic/Adsl/Impdh2/Guk1/Aprt</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045089</t>
@@ -6040,7 +6040,7 @@
     <t xml:space="preserve">106/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Trim56/Tbk1/Rnf185/Hexim1/Nono/Matr3/Ap1g1/Stat5a/Stat5b/Xrcc5/Plcg2/Vav1/Cadm1/Havcr2/Lgals9/Spi1/Tyrobp/Dpp4/Syk</t>
+    <t xml:space="preserve">Syk/Lamp1/Spi1/Vav1/Plcg2/Lgals9/Stat5b/Dpp4/Xrcc5/Tbk1/Ap1g1/Trim56/Tyrobp/Stat5a/Nono/Havcr2/Matr3/Hexim1/Cadm1/Rnf185</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006177</t>
@@ -6049,7 +6049,7 @@
     <t xml:space="preserve">GMP biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Impdh2/Aprt/Adsl/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">Gart/Pfas/Atic/Adsl/Impdh2/Aprt</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1905146</t>
@@ -6058,7 +6058,7 @@
     <t xml:space="preserve">lysosomal protein catabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Dpp7/Grn/Tpp1/Ldlr/Tmem199/Vps35</t>
+    <t xml:space="preserve">Tpp1/Grn/Dpp7/Ldlr/Vps35/Tmem199</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044389</t>
@@ -6067,7 +6067,7 @@
     <t xml:space="preserve">ubiquitin-like protein ligase binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr2/Prkar2b/Dnajb2/Ube2l6/Traf4/Yod1/Tollip/Map1lc3b/Slf2/Ubash3b/Arrb1/Fzd5/Fbxw7/Usp9x/Pias2/Gabarap/Polr2a/Usp25/Sorbs1/Bid/Brca1/Rb1/Vcl/Pias1/Trim28/Pa2g4/Gpi1/Cct2/Hsp90ab1/Hspd1/Cul7/Traf3/Dtx3l/Trp53/Prdx6/Pdlim2/Slc22a18/Xrcc5/Prr7/Ywhaz/Cxcr4/Trib2/Laptm5/Syk</t>
+    <t xml:space="preserve">Prkar2b/Laptm5/Syk/Ywhaz/Trib2/Tollip/Slf2/Cxcr4/Map1lc3b/Yod1/Xrcc5/Traf4/Fbxw7/Polr2a/Trp53/Prdx6/Usp9x/Gabarap/Pias2/Traf3/Egr2/Ube2l6/Fzd5/Cul7/Dnajb2/Prr7/Rb1/Arrb1/Cct2/Dtx3l/Ubash3b/Hsp90ab1/Usp25/Trim28/Bid/Pdlim2/Slc22a18/Hspd1/Brca1/Pias1/Sorbs1/Vcl/Pa2g4/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030425</t>
@@ -6079,7 +6079,7 @@
     <t xml:space="preserve">545/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Cpeb4/Prkar2b/Itsn1/Agtr1a/Map1a/Mpp2/Mylk2/Glrx/Prnp/Als2/Ache/Adam10/Slc38a2/Lamp1/Map1lc3b/Anxa3/Samd14/Numb/Nrgn/Actn1/Dpysl2/Rab3ip/Arrb1/Arfgef2/Syn1/Gigyf2/Trak2/Atp2b1/Cnnm4/Atp7a/Cib1/Ppp1r9b/Glrx5/Dip2b/C9orf72/Cdkl5/Rara/Uhmk1/Dyrk1a/Ago2/Gnas/Elk1/Homer1/Sav1/Rack1/Psen1/Ctnnb1/Nedd4/Ifngr1/Hsp90ab1/Stau2/Myh10/Syngap1/Prkca/Flna/Kif1c/Ccng1/Akap5/Arpc2/Slc4a8/Atp1a3/Cplx2/Cadm1/Pde4b/Rac1/Nr1d1/Rgs14/Arhgef2/Apoe/Plxdc1/Sla/Rin3</t>
+    <t xml:space="preserve">Cobl/Prkar2b/Arhgef2/Prnp/Sla/Lamp1/Cpeb4/Rac1/Gigyf2/Itsn1/Actn1/Rin3/Mpp2/Als2/Arfgef2/Glrx/Arpc2/Atp2b1/Ccng1/Apoe/Map1lc3b/Adam10/Dyrk1a/Gnas/Ache/Flna/Samd14/Dip2b/Slc38a2/Kif1c/Rgs14/Map1a/Plxdc1/Dpysl2/Numb/Agtr1a/Rab3ip/Myh10/Cnnm4/Ppp1r9b/Ctnnb1/Nr1d1/Uhmk1/Glrx5/Arrb1/Nedd4/Slc4a8/Anxa3/Nrgn/Mylk2/Trak2/Cib1/Cplx2/Prkca/Pde4b/Hsp90ab1/Atp1a3/Atp7a/Cadm1/Elk1/Psen1/C9orf72/Sav1/Ifngr1/Rara/Cdkl5/Stau2/Syngap1/Ago2/Homer1/Rack1/Akap5/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030833</t>
@@ -6091,7 +6091,7 @@
     <t xml:space="preserve">121/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Map3k1/Add2/Dmtn/Sptb/Ssh2/Mlst8/Plekhg2/Nckap1/Nck1/Rictor/Twf1/Cttn/Flii/Hcls1/Sptan1/Arpc2/Rac1/Capg/Vill/Coro1a</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Map3k1/Vill/Coro1a/Tmod1/Dmtn/Rac1/Capg/Arpc2/Mlst8/Ssh2/Nckap1/Flii/Twf1/Plekhg2/Hcls1/Sptan1/Nck1/Cttn/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045335</t>
@@ -6100,7 +6100,7 @@
     <t xml:space="preserve">phagocytic vesicle</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/H2-T23/Pip4p1/Lamp1/Anxa3/Uvrag/Pikfyve/Rab43/Rab22a/Clcn3/Snx3/Was/Sec61a1/Anxa11/Capg/Vim/Unc93b1/Coro1a/Syk</t>
+    <t xml:space="preserve">Appl2/Syk/Coro1a/Lamp1/Pip4p1/Capg/Vim/Unc93b1/Pikfyve/Uvrag/Rab22a/Rab43/Clcn3/H2-T23/Anxa11/Anxa3/Sec61a1/Snx3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903076</t>
@@ -6109,7 +6109,7 @@
     <t xml:space="preserve">regulation of protein localization to plasma membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Picalm/Cltc/Numb/Ppp2r5a/Cib1/Ppp1r9b/Gripap1/Sorbs1/Ap2m1/Rack1/Gopc/Pgrmc1/Ptpn9/Akap5/Rangrf/Lypla1/Mmp14/Tgfb1</t>
+    <t xml:space="preserve">Picalm/Prnp/Tgfb1/Cltc/Lypla1/Ppp2r5a/Numb/Rangrf/Mmp14/Ppp1r9b/Ptpn9/Cib1/Ap2m1/Pgrmc1/Sorbs1/Gripap1/Rack1/Akap5/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031667</t>
@@ -6118,7 +6118,7 @@
     <t xml:space="preserve">response to nutrient levels</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Appl2/Wnk4/Rragc/Tsc1/Ldlr/Sesn1/Map1lc3b/Pim1/Gba/Mlst8/Bhlha15/Alad/Flcn/Bax/Sesn3/Xpr1/Gabarap/Rictor/Mtmr3/Ncoa1/Sirt1/Rps6kb1/Fnip1/Clec16a/Sh3glb1/Tbl1xr1/Plin2/Pik3c2b/Ulk2/Adsl/Srf/Pcsk9/Mybbp1a/Prkag2/Tcf7l2/Ripor1/Trp53/Pmaip1/Hlcs/Fes/Apoe/Gdf3</t>
+    <t xml:space="preserve">Appl2/Wnk4/Rragc/Tsc1/Cpeb4/Ripor1/Hlcs/Apoe/Map1lc3b/Ldlr/Sesn1/Xpr1/Pmaip1/Gba/Mlst8/Gdf3/Trp53/Gabarap/Mtmr3/Prkag2/Adsl/Srf/Fes/Mybbp1a/Sh3glb1/Flcn/Bhlha15/Sesn3/Ulk2/Sirt1/Ncoa1/Alad/Fnip1/Pcsk9/Bax/Tbl1xr1/Tcf7l2/Clec16a/Pim1/Rps6kb1/Plin2/Pik3c2b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001906</t>
@@ -6127,7 +6127,7 @@
     <t xml:space="preserve">cell killing</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Lamp1/Bcl2l11/Tusc2/Arl8b/Hsp90ab1/Ap1g1/Stat5a/Stat5b/Fcgr3/Ptpn6/Unc13d/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Il4/Lgals9/Spi1/Tyrobp/Ptprc/Coro1a/P2rx7/Syk</t>
+    <t xml:space="preserve">Syk/Ptprc/Coro1a/Lamp1/Spi1/Vav1/P2rx7/Lgals9/Stat5b/Ptpn6/Unc13d/Ap1g1/H2-T23/Tyrobp/Stat5a/Il4/Pik3r6/Havcr2/Fcgr3/Serpinb9/Bcl2l11/Arl8b/Hsp90ab1/Cadm1/Tusc2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031625</t>
@@ -6136,7 +6136,7 @@
     <t xml:space="preserve">ubiquitin protein ligase binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr2/Prkar2b/Dnajb2/Ube2l6/Traf4/Yod1/Tollip/Map1lc3b/Slf2/Ubash3b/Arrb1/Fzd5/Fbxw7/Usp9x/Pias2/Gabarap/Polr2a/Usp25/Sorbs1/Bid/Brca1/Rb1/Vcl/Pias1/Trim28/Pa2g4/Gpi1/Cct2/Hsp90ab1/Hspd1/Cul7/Traf3/Trp53/Prdx6/Pdlim2/Slc22a18/Xrcc5/Ywhaz/Cxcr4/Trib2/Laptm5/Syk</t>
+    <t xml:space="preserve">Prkar2b/Laptm5/Syk/Ywhaz/Trib2/Tollip/Slf2/Cxcr4/Map1lc3b/Yod1/Xrcc5/Traf4/Fbxw7/Polr2a/Trp53/Prdx6/Usp9x/Gabarap/Pias2/Traf3/Egr2/Ube2l6/Fzd5/Cul7/Dnajb2/Rb1/Arrb1/Cct2/Ubash3b/Hsp90ab1/Usp25/Trim28/Bid/Pdlim2/Slc22a18/Hspd1/Brca1/Pias1/Sorbs1/Vcl/Pa2g4/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032945</t>
@@ -6145,7 +6145,7 @@
     <t xml:space="preserve">negative regulation of mononuclear cell proliferation</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Zbtb7b/Vsir/Ptpn6/Cd37/Ripor2/Havcr2/Lgals9/Spn/Lgals7/Tgfb1/Cd44/Laptm5/Tyrobp/Btk</t>
+    <t xml:space="preserve">Btk/Laptm5/Prnp/Tgfb1/Spn/Cd44/Ripor2/Lgals9/Ptpn6/Zbtb7b/Tyrobp/Lgals7/Cd37/Havcr2/Vsir</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050672</t>
@@ -6163,7 +6163,7 @@
     <t xml:space="preserve">191/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Prdx2/Pea15a/Sgk3/Bax/Bex3/Gabarap/Bcl2l11/Stradb/Bid/Brca1/Mcl1/Mknk1/Dedd/Mknk2/Cttn/Rps6kb1/Rbck1/Itm2c/Sp100/Tnfrsf26/Dapk1/Acsl5/Ppp2r1a/Pmaip1/Casp7/Il4/Tgfb1/Spi1/Ptprc/Jak3/P2rx7</t>
+    <t xml:space="preserve">Prdx2/Jak3/Ptprc/Tgfb1/Casp7/Spi1/Ppp2r1a/P2rx7/Acsl5/Pmaip1/Gabarap/Il4/Pea15a/Dapk1/Rbck1/Mcl1/Mknk2/Bcl2l11/Bid/Bax/Bex3/Stradb/Brca1/Itm2c/Sgk3/Cttn/Tnfrsf26/Dedd/Mknk1/Sp100/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048469</t>
@@ -6175,7 +6175,7 @@
     <t xml:space="preserve">160/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slfn14/Fam210b/Epb42/Tal1/Washc5/Gdf11/Klf1/Cdc25b/Gba/Fzd5/Bhlha15/Fbxo5/Shb/Tusc2/Rb1/Tut7/Ctnnb1/Wdr77/Rps6ka2/Akap5/Ppp2r1a/Gata2/Npr2/Rac1/Cbfb/Tgfb1/Btk</t>
+    <t xml:space="preserve">Btk/Fam210b/Tgfb1/Slfn14/Washc5/Tal1/Rac1/Epb42/Cbfb/Klf1/Ppp2r1a/Cdc25b/Gba/Gdf11/Fzd5/Gata2/Npr2/Ctnnb1/Rb1/Fbxo5/Rps6ka2/Bhlha15/Tusc2/Tut7/Wdr77/Akap5/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097447</t>
@@ -6190,7 +6190,7 @@
     <t xml:space="preserve">T cell homeostasis</t>
   </si>
   <si>
-    <t xml:space="preserve">Prdx2/Bax/Bcl2l11/Tsc22d3/Stat5a/Stat5b/Pmaip1/Tgfb1/Coro1a/Jak3/P2rx7</t>
+    <t xml:space="preserve">Prdx2/Jak3/Coro1a/Tgfb1/P2rx7/Stat5b/Pmaip1/Stat5a/Bcl2l11/Bax/Tsc22d3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1905475</t>
@@ -6199,7 +6199,7 @@
     <t xml:space="preserve">regulation of protein localization to membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Prnp/Kalrn/Picalm/Adam10/Cltc/Numb/Ppp2r5a/Cib1/Ppp1r9b/Dag1/Gripap1/Sorbs1/Stom/Ap2m1/Sh3glb1/Rack1/Gopc/Lztfl1/Pgrmc1/Ptpn9/Akap5/Arpc2/Pmaip1/Rangrf/Lypla1/Mmp14/Tgfb1</t>
+    <t xml:space="preserve">Picalm/Prnp/Tgfb1/Cltc/Dmtn/Lypla1/Ppp2r5a/Arpc2/Adam10/Kalrn/Pmaip1/Dag1/Numb/Rangrf/Mmp14/Ppp1r9b/Ptpn9/Sh3glb1/Cib1/Ap2m1/Pgrmc1/Lztfl1/Sorbs1/Gripap1/Stom/Rack1/Akap5/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031329</t>
@@ -6211,7 +6211,7 @@
     <t xml:space="preserve">645/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Btg2/Trp53inp2/Scoc/Snca/Dnajb2/Map1a/Optn/Zswim8/Tnrc6b/Hipk2/Rragc/Tsc1/Nupr1/Ldlr/Sesn1/Mylip/Atp6v0a1/Ticam1/Uvrag/Rchy1/Carhsp1/Rnf14/Gba/Trp53inp1/Mlst8/Gigyf2/Smcr8/Rnf139/Tbk1/Fbxw7/Flcn/Tent5c/Usp9x/Tob1/Bax/C9orf72/Sesn3/Gabarap/Bcl2l11/Ago2/Ctsa/Mtmr3/Bid/Tnrc6c/Mcl1/Rmc1/Pip4k2c/Tut7/Pias1/Cttn/Sirt1/Clec16a/Sh3glb1/Celf1/Rack1/Psen1/Parn/Cnot7/Ubqln4/Ddx49/Hsp90ab1/Eif4g2/Mov10/Pabpc4/Ulk2/Exosc5/Dtx3l/Pcsk9/Naf1/Abca2/Trp53/Dapk1/Mtmr9/Acsl5/Fastkd1/Traf3ip2/Sh3d19/Zfp36l1/Vim/Il4/Apoe/Trib2/Laptm5/P2rx7</t>
+    <t xml:space="preserve">Laptm5/Snca/Btg2/Rragc/Tsc1/Trp53inp2/Trib2/Gigyf2/Scoc/Tnrc6b/Zswim8/P2rx7/Abca2/Acsl5/Vim/Optn/Apoe/Ldlr/Mtmr9/Rnf14/Pabpc4/Hipk2/Sesn1/Uvrag/Fbxw7/Tbk1/Carhsp1/Gba/Mlst8/Rchy1/Trp53/Map1a/Rnf139/Usp9x/Gabarap/Atp6v0a1/Ticam1/Trp53inp1/Mtmr3/Il4/Ctsa/Sh3d19/Naf1/Zfp36l1/Dnajb2/Mylip/Smcr8/Dapk1/Sh3glb1/Fastkd1/Mcl1/Ubqln4/Celf1/Tob1/Mov10/Dtx3l/Bcl2l11/Hsp90ab1/Tent5c/Flcn/Psen1/Bid/Sesn3/Exosc5/Rmc1/Ulk2/Sirt1/C9orf72/Traf3ip2/Eif4g2/Pcsk9/Bax/Nupr1/Pias1/Ago2/Tut7/Tnrc6c/Cttn/Ddx49/Cnot7/Rack1/Clec16a/Parn/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001556</t>
@@ -6223,7 +6223,7 @@
     <t xml:space="preserve">27/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Washc5/Cdc25b/Fbxo5/Shb/Tut7/Rps6ka2/Ppp2r1a/Npr2</t>
+    <t xml:space="preserve">Washc5/Ppp2r1a/Cdc25b/Npr2/Fbxo5/Rps6ka2/Tut7/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032366</t>
@@ -6238,7 +6238,7 @@
     <t xml:space="preserve">response to interleukin-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Fasn/Alad/Hsp90ab1/Impdh2/Rpl3/Stat5b/Coro1a/Jak3</t>
+    <t xml:space="preserve">Jak3/Coro1a/Stat5b/Fasn/Rpl3/Impdh2/Hsp90ab1/Alad</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019787</t>
@@ -6250,7 +6250,7 @@
     <t xml:space="preserve">391/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Map3k1/Egr2/Trim10/Neurl1b/Trim2/Uba7/Herc6/Ube2l6/Rnf145/Cnot4/Vps11/Mylip/Rchy1/Rnf14/Rnf115/Trim56/Rnf139/Fbxw7/Hace1/Rnf146/Rnf38/Med7/Fbxo11/Pias2/Rnf10/Hectd3/Rnf168/Rnf185/Mkrn1/Rnf167/Brca1/Fbxo30/Med20/Siah1b/Trip12/Pias1/Klhl9/Ltn1/Fbxw11/Prpf19/Nedd4/Trim28/Ube2e1/Trim35/Cbl/Rbck1/Jade2/Ube2s/Dtx4/Dtx3l/Rnf138/Mex3c/Aktip/Traf3ip2/Rnf125</t>
+    <t xml:space="preserve">Map3k1/Trim2/Rnf145/Rnf115/Uba7/Trim10/Vps11/Cnot4/Rnf125/Rnf14/Mex3c/Herc6/Fbxw7/Rnf38/Rchy1/Rnf139/Pias2/Trim56/Hace1/Egr2/Fbxo11/Rnf146/Ube2l6/Neurl1b/Rnf138/Fbxo30/Mylip/Rnf10/Rnf168/Aktip/Rbck1/Nedd4/Trip12/Med7/Ltn1/Rnf167/Ube2s/Dtx3l/Dtx4/Prpf19/Trim28/Traf3ip2/Hectd3/Rnf185/Trim35/Brca1/Pias1/Ube2e1/Med20/Siah1b/Klhl9/Fbxw11/Cbl/Jade2/Mkrn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009185</t>
@@ -6262,7 +6262,7 @@
     <t xml:space="preserve">100/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Guk1/Umps/Prkag2/Cad/Khk/Hk2/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Slc4a1/Pfkfb2/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Cad/Pkm/Umps/Prkag2/Guk1/Eno3/Hk2/Psen1/Bpgm/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045596</t>
@@ -6274,7 +6274,7 @@
     <t xml:space="preserve">539/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Dmtn/Prdx2/Sema4b/Insig1/Sox6/Abcg1/Arntl/Ldlr/Gdf11/Zbtb7b/Ubash3b/Trp53inp1/Hdac5/Trak2/Bhlha15/Dact3/Ppard/Fbxw7/Foxo4/Flcn/Tent5c/Cib1/Shb/Tob1/Dip2b/Rnf10/Rara/Ddx6/Rb1/Nbr1/Sirt1/N4bp2l2/Psen1/Ctnnb1/Kifap3/Lrp5/Ldb1/Syngap1/Ulk2/Idh2/Prmt1/Stat5a/Smarcd1/Fzd7/Ss18/Lmo2/Tcf7l2/Trp53/Stat5b/Sema4a/Pdcd4/Gata2/Spred2/Zfp36l1/Npr2/Rgs2/Rcc2/Nr1d1/Cbfb/Il4/Ptprs/Arhgef2/Trib2/Tgfb1/Col5a1/Cd44/Gdf3/Hdac7/Myb/Cdk6/Jak3</t>
+    <t xml:space="preserve">Prdx2/Hdac7/Jak3/Appl2/Arhgef2/Myb/Ptprs/Tgfb1/Cdk6/Abcg1/Dmtn/Cd44/Trib2/Rcc2/Cbfb/Ss18/Stat5b/Ldlr/Insig1/Col5a1/Dip2b/Fbxw7/Arntl/Gdf3/Gdf11/Smarcd1/Trp53/Spred2/Zbtb7b/Ldb1/Ddx6/Sema4b/Idh2/Trp53inp1/Stat5a/Il4/Gata2/Rgs2/Npr2/Lmo2/Fzd7/Sema4a/Prmt1/Zfp36l1/Ctnnb1/Rnf10/Ppard/Hdac5/Rb1/Nr1d1/Tob1/Trak2/Lrp5/Sox6/Cib1/Ubash3b/Tent5c/Flcn/Dact3/Pdcd4/Psen1/Bhlha15/Ulk2/Sirt1/Rara/Syngap1/N4bp2l2/Foxo4/Nbr1/Tcf7l2/Kifap3/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060560</t>
@@ -6283,7 +6283,7 @@
     <t xml:space="preserve">developmental growth involved in morphogenesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Mst1/Sema4b/Picalm/Dpysl2/Usp9x/Dip2b/C9orf72/Cdkl5/Golga4/Cpne1/Vcl/Cttn/Itsn2/Sh3glb1/Iqgap1/Rpl4/Ctnnb1/Trim28/Hsp90ab1/Wdr36/Jade2/Ulk2/Megf8/Srf/Unc13a/Vangl2/Sema4a/Cadm1/Csf1/Ptprs/Cxcr4/Apoe/Tgfb1</t>
+    <t xml:space="preserve">Cobl/Picalm/Ptprs/Tgfb1/Mst1/Cxcr4/Apoe/Megf8/Dip2b/Usp9x/Dpysl2/Sema4b/Sema4a/Srf/Csf1/Ctnnb1/Sh3glb1/Vangl2/Hsp90ab1/Trim28/Cadm1/Cpne1/Ulk2/C9orf72/Iqgap1/Golga4/Cdkl5/Rpl4/Wdr36/Unc13a/Jade2/Cttn/Vcl/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0022613</t>
@@ -6295,7 +6295,7 @@
     <t xml:space="preserve">400/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mrm1/Tsc1/Isg20/Pop5/Utp14b/Rbm5/Ago2/Ipo9/Prpf3/Helq/Prpf18/Celf1/Ddx27/Prpf19/Rpl35/Ddx18/Wdr77/Snu13/Pa2g4/Ddx21/Ddx49/Gtpbp4/Rcl1/Rsl24d1/Hsp90ab1/Ebna1bp2/Wdr36/Sdad1/Rrp1b/Urb1/Pwp1/Gtf3a/Ruvbl2/Trmt2b/Exosc1/Lyar/Wdr43/Exosc5/Mdn1/Nop16/Heatr1/Mybbp1a/Nat10/Naf1/Rrp12/Rpl10a/Prmt7/Nol6/Wdr46/Xrcc5/Tfb2m/Rrp9/Npm3/Ltv1/Ago4/Celf2</t>
+    <t xml:space="preserve">Celf2/Tsc1/Npm3/Ltv1/Xrcc5/Ago4/Nat10/Rpl10a/Rrp9/Wdr46/Prmt7/Utp14b/Rbm5/Trmt2b/Mrm1/Nol6/Ipo9/Pop5/Naf1/Tfb2m/Isg20/Mybbp1a/Rrp12/Heatr1/Celf1/Ruvbl2/Mdn1/Pwp1/Nop16/Prpf3/Prpf19/Hsp90ab1/Urb1/Sdad1/Wdr43/Exosc5/Ddx18/Gtf3a/Rcl1/Exosc1/Snu13/Rsl24d1/Prpf18/Wdr36/Lyar/Ago2/Gtpbp4/Wdr77/Ebna1bp2/Ddx21/Helq/Ddx27/Ddx49/Rpl35/Pa2g4/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010324</t>
@@ -6304,7 +6304,7 @@
     <t xml:space="preserve">membrane invagination</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Arhgap12/Clcn3/Wasl/Snx3/Itgb2/Fcgr3/Gata2/Plcg2/Ano6/Rac1/Rac2/Elmo1</t>
+    <t xml:space="preserve">Appl2/Ano6/Rac2/Rac1/Elmo1/Plcg2/Cd36/Clcn3/Gata2/Wasl/Arhgap12/Fcgr3/Itgb2/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001920</t>
@@ -6325,7 +6325,7 @@
     <t xml:space="preserve">B cell selection</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Traf3ip2/Btk</t>
+    <t xml:space="preserve">Btk/Traf3ip2/Bax</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0004427</t>
@@ -6334,7 +6334,7 @@
     <t xml:space="preserve">inorganic diphosphate phosphatase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Ppa1/Ppa2/Lhpp</t>
+    <t xml:space="preserve">Lhpp/Ppa1/Ppa2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032020</t>
@@ -6352,7 +6352,7 @@
     <t xml:space="preserve">regulation of natural killer cell degranulation</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Ap1g1/Lgals9</t>
+    <t xml:space="preserve">Lamp1/Lgals9/Ap1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904761</t>
@@ -6370,7 +6370,7 @@
     <t xml:space="preserve">spermatoproteasome complex</t>
   </si>
   <si>
-    <t xml:space="preserve">Psme4/Psmb10/Psmb8</t>
+    <t xml:space="preserve">Psme4/Psmb8/Psmb10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0036473</t>
@@ -6379,7 +6379,7 @@
     <t xml:space="preserve">cell death in response to oxidative stress</t>
   </si>
   <si>
-    <t xml:space="preserve">Glrx/Tsc1/Pycr1/Epor/Tbc1d24/Fbxw7/Rnf146/Stk25/Mcl1/Sirt1/Rack1/Parp1/Nono/Ctnnb1/Lancl1/Trp53/Aldh2</t>
+    <t xml:space="preserve">Tsc1/Aldh2/Glrx/Tbc1d24/Fbxw7/Stk25/Trp53/Epor/Rnf146/Nono/Ctnnb1/Mcl1/Lancl1/Sirt1/Pycr1/Parp1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0003725</t>
@@ -6391,7 +6391,7 @@
     <t xml:space="preserve">72/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Tfrc/Cltc/Actn1/Ago2/Ddx21/Hsp90ab1/Stau2/Dhx33/Hspd1/Ifih1/Oasl1/Ago4/Vim/Rftn1/Oas2</t>
+    <t xml:space="preserve">Rftn1/Cltc/Oas2/Actn1/Vim/Ago4/Tfrc/Hsp90ab1/Dhx33/Ifih1/Hspd1/Stau2/Ago2/Ddx21/Oasl1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030864</t>
@@ -6400,7 +6400,7 @@
     <t xml:space="preserve">cortical actin cytoskeleton</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Spta1/Sptb/Actn1/Wasl/Ppp1r9b/Cttn/Iqgap1/Actr2/Wdr1/Hcls1/Sptan1/Cap1/Pdlim2/Coro1a</t>
+    <t xml:space="preserve">Spta1/Cobl/Sptb/Coro1a/Cap1/Actn1/Wasl/Ppp1r9b/Wdr1/Hcls1/Sptan1/Pdlim2/Actr2/Iqgap1/Cttn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042632</t>
@@ -6412,7 +6412,7 @@
     <t xml:space="preserve">79/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Insig1/Abcg1/Washc5/Ldlr/Mylip/Acox1/Lamtor1/Ehd1/Med13/Sirt1/Mia2/Lrp5/Tmem97/Pcsk9/Nr1d1/Apoe</t>
+    <t xml:space="preserve">Washc5/Abcg1/Apoe/Ldlr/Insig1/Acox1/Ehd1/Med13/Lamtor1/Mylip/Nr1d1/Mia2/Lrp5/Sirt1/Pcsk9/Tmem97</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034765</t>
@@ -6421,7 +6421,7 @@
     <t xml:space="preserve">regulation of ion transmembrane transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Mink1/Wnk4/Scn10a/Snca/Agtr1a/Glrx/Prnp/Slc43a1/Kel/Ubash3b/Atp7a/Fgf11/Bax/Stom/Homer1/Grk6/Gpr89/Psen1/Nedd4/Ppp3r1/Gopc/Phb2/Pde4d/Ifngr1/Fkbp1a/Prkca/P2rx1/Flna/Tmem109/Ppif/Fkbp1b/Ehd3/Pcsk9/Slc43a2/Akap5/Dapk1/Ptpn6/Atp1b2/Plcg2/Ano6/Zfas1/Grin2d/Rangrf/Pde4b/Rgs2/Clic1/Kcnab2/Il4/Gsto1/Tgfb1/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Snca/Wnk4/Mink1/Coro1a/Ano6/Slc6a9/Prnp/Tgfb1/Gsto1/Kcnab2/Clic1/P2rx7/Plcg2/Glrx/Ptpn6/Flna/Scn10a/Slc43a1/Agtr1a/Zfas1/Rangrf/Il4/Rgs2/Kel/Dapk1/Ppif/Nedd4/Atp1b2/Fgf11/Prkca/Ubash3b/Pde4b/Ehd3/Atp7a/Slc43a2/Tmem109/Grin2d/Psen1/Fkbp1a/Ppp3r1/Ifngr1/Pcsk9/Bax/Phb2/Homer1/Fkbp1b/P2rx1/Grk6/Stom/Gpr89/Akap5/Gopc/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032101</t>
@@ -6436,7 +6436,7 @@
     <t xml:space="preserve">728/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Mst1/Dmtn/Cd47/Snca/Prdx2/Optn/Sema4b/Grn/Serpinb1a/Adam10/Lamp1/Nupr1/Ldlr/Ubash3b/Mospd2/Trim56/Ppard/Tbk1/Wasl/Hmgcr/Lpcat3/Bax/Elmod2/Mpp1/Vps35/Rnf185/Ash1l/Rictor/Hexim1/Swap70/Rb1/Cttn/Ppm1b/Celf1/Usp15/Nono/Cnot7/Matr3/Hspd1/Ap1g1/Igf1r/Lyar/Prkca/Megf8/Traf3/Flna/Dtx3l/Stat5a/Fkbp1b/Cst7/Oasl1/Stat5b/Fcgr3/Sema4a/Xrcc5/Pdcd4/Plcg2/Traf3ip2/Vav1/Apobec3/Ano6/Nr1d2/Cadm1/Cd37/Serpinb9/Alox5ap/Rac1/Nr1d1/Ripor2/Rac2/Havcr2/Aldh2/Pik3r6/Il4/Csf1/Ptprs/Rnf125/Cxcr4/Lgals9/Spn/Apoe/Tgfb1/Cd44/Spi1/Tyrobp/Lgals1/Dpp4/Il1rl1/Cd84/Syk/Rin3</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Snca/Appl2/Il1rl1/Syk/Ptprs/Ano6/Rac2/Tgfb1/Mst1/Grn/Spn/Dmtn/Aldh2/Lamp1/Cd44/Rac1/Cd47/Cd84/Ripor2/Spi1/Vav1/Rin3/Alox5ap/Plcg2/Lgals9/Optn/Cxcr4/Apoe/Stat5b/Cd36/Adam10/Ldlr/Rnf125/Dpp4/Nr1d2/Xrcc5/Megf8/Serpinb1a/Flna/Tbk1/Apobec3/Ap1g1/Trim56/Sema4b/Traf3/Tyrobp/Stat5a/Il4/Wasl/Sema4a/Cd37/Pik3r6/Csf1/Nono/Ppard/Vps35/Rb1/Mospd2/Nr1d1/Havcr2/Matr3/Fcgr3/Celf1/Serpinb9/Hmgcr/Hexim1/Mpp1/Lpcat3/Dtx3l/Prkca/Ubash3b/Usp15/Swap70/Cadm1/Pdcd4/Ash1l/Traf3ip2/Hspd1/Bax/Nupr1/Rnf185/Lyar/Fkbp1b/Igf1r/Cttn/Cst7/Cnot7/Oasl1/Elmod2/Ppm1b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002253</t>
@@ -6448,7 +6448,7 @@
     <t xml:space="preserve">225/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Btnl10/Cd47/Prnp/Ermap/Tbk1/Usp9x/Shb/Elf1/Bax/Fcho1/Hexim1/Nras/Psen1/Nono/Pde4d/Rbck1/Dgkz/Matr3/Lpxn/Ptpn6/Xrcc5/Plcg2/Ubash3a/Pde4b/Lcp2/Laptm5/Fyb/Tyrobp/Btk/Ptprc/Myo1g/Rftn1/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Laptm5/Nfam1/Myo1g/Appl2/Rftn1/Syk/Ptprc/Prnp/Btnl10/Ermap/Fyb/Cd47/Plcg2/Ptpn6/Xrcc5/Tbk1/Usp9x/Lcp2/Ubash3a/Tyrobp/Elf1/Dgkz/Nono/Rbck1/Matr3/Hexim1/Pde4b/Psen1/Bax/Nras/Fcho1/Shb/Pde4d/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0150076</t>
@@ -6457,7 +6457,7 @@
     <t xml:space="preserve">neuroinflammatory response</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Grn/Nupr1/Ldlr/Bpgm/Psen1/Ifngr1/Cst7/Plcg2/Nr1d1/Il4/Tyrobp</t>
+    <t xml:space="preserve">Snca/Grn/Plcg2/Ldlr/Tyrobp/Il4/Nr1d1/Psen1/Bpgm/Ifngr1/Nupr1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016125</t>
@@ -6475,7 +6475,7 @@
     <t xml:space="preserve">postsynaptic density</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Slc6a9/Add2/Dmtn/Map1a/Mpp2/Mylk2/Prnp/Kalrn/Als2/Tsc1/Picalm/Adam10/Samd14/Numb/Nrgn/Arrb1/Syn1/Myo6/Ppp1r9b/Rnf10/Cdkl5/Vps35/Homer1/Abi1/Rpl4/Actr2/Ctnnb1/Phb2/Ifngr1/Dgkz/Eif4g2/Syngap1/Rpl10a/Epb41l1/Akap5/Grin2d/Cadm1/Pde4b/Kcnab2/Prr7/Ptprs/Ywhaz/Rgs14/Arhgef2</t>
+    <t xml:space="preserve">Add2/Picalm/Arhgef2/Ptprs/Slc6a9/Prnp/Ywhaz/Tsc1/Dmtn/Cpeb4/Kcnab2/Mpp2/Als2/Adam10/Kalrn/Samd14/Rgs14/Rpl10a/Map1a/Myo6/Numb/Dgkz/Ppp1r9b/Ctnnb1/Rnf10/Prr7/Vps35/Arrb1/Nrgn/Mylk2/Pde4b/Cadm1/Grin2d/Actr2/Epb41l1/Eif4g2/Ifngr1/Cdkl5/Rpl4/Syngap1/Phb2/Homer1/Abi1/Akap5/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006643</t>
@@ -6487,7 +6487,7 @@
     <t xml:space="preserve">154/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/St3gal6/Neu1/St3gal2/Gba/Cln8/Hexa/Bax/Serinc5/Sgpl1/Serinc3/Cers5/Pigt/St6galnac4/Gla/P2rx1/Ugcg/Plpp2/Abca2/Agk/Vapa/B4galnt1/Pgap2/Fut4/Sptssa/P2rx7</t>
+    <t xml:space="preserve">Sptssa/St3gal1/P2rx7/Abca2/Vapa/Ugcg/Pgap2/Gba/Neu1/Agk/Fut4/B4galnt1/St3gal6/Pigt/Gla/Plpp2/Hexa/Serinc5/St3gal2/Bax/Serinc3/St6galnac4/Cers5/P2rx1/Sgpl1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001573</t>
@@ -6496,7 +6496,7 @@
     <t xml:space="preserve">ganglioside metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/Neu1/St3gal2/Hexa/St6galnac4/Abca2/B4galnt1</t>
+    <t xml:space="preserve">St3gal1/Abca2/Neu1/B4galnt1/Hexa/St3gal2/St6galnac4</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030670</t>
@@ -6505,7 +6505,7 @@
     <t xml:space="preserve">phagocytic vesicle membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/H2-T23/Pip4p1/Lamp1/Anxa3/Pikfyve/Sec61a1</t>
+    <t xml:space="preserve">Appl2/Lamp1/Pip4p1/Pikfyve/H2-T23/Anxa3/Sec61a1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0036344</t>
@@ -6520,7 +6520,7 @@
     <t xml:space="preserve">glutamatergic synapse</t>
   </si>
   <si>
-    <t xml:space="preserve">Add2/Scn10a/Prkar2b/Itsn1/Mpp2/Kalrn/Adam10/Numb/Nrgn/Actn1/Fzd5/Clcn3/Myo6/Atp2b1/Wasl/Ap3d1/Dag1/Rnf10/Cdkl5/Vps35/Gripap1/Cttn/Homer1/Ap2m1/Abi1/Nedd4/Ppp3r1/Phb2/Dgkz/Atad1/Myh10/Syngap1/P2rx1/Flna/Srgn/Lin7c/Unc13a/Akap5/Arpc2/Slc4a8/Ppp2r1a/Cplx2/Grin2d/Cadm1/Ppm1h/Rac1/Prr7/Ptprs/Ywhaz/Rgs14/Arhgef2/Apoe/Coro1a/Tspoap1</t>
+    <t xml:space="preserve">Add2/Prkar2b/Arhgef2/Ptprs/Coro1a/Tspoap1/Ywhaz/Rac1/Itsn1/Ppp2r1a/Actn1/Mpp2/Arpc2/Atp2b1/Apoe/Adam10/Lin7c/Kalrn/Flna/Scn10a/Rgs14/Myo6/Clcn3/Dag1/Numb/Fzd5/Myh10/Atad1/Dgkz/Wasl/Ap3d1/Rnf10/Ppm1h/Prr7/Vps35/Nedd4/Slc4a8/Nrgn/Srgn/Cplx2/Ap2m1/Cadm1/Grin2d/Ppp3r1/Cdkl5/Syngap1/Phb2/Homer1/Gripap1/Abi1/Unc13a/Cttn/P2rx1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051050</t>
@@ -6532,7 +6532,7 @@
     <t xml:space="preserve">784/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Car2/Wnk4/Rph3al/Cd47/Snca/Itsn1/Agtr1a/Glrx/Prnp/Pfkfb2/Abcg1/Picalm/Vps11/Lamp1/Ptpn23/Map1lc3b/Dpysl2/Arrb1/Ppard/Atp2b1/Wasl/Fbxw7/Lpcat3/Atp7a/Cib1/Bax/Ehd1/Vps35/Sorbs1/Gnas/Brca1/Exoc1/Stom/Homer1/Sirt1/Adipor2/Ap2m1/Sh3glb1/Vps4b/Rack1/Psen1/Nedd4/Trim28/Ipo5/Ppp3r1/Ergic3/Tm7sf3/Scp2/Ifngr1/Cbl/Selenot/Atad1/Hsp90ab1/Myh10/Wipf1/Ap1g1/Hcls1/Lyar/Mllt6/Prkca/P2rx1/Sar1b/Flna/Snx5/Ier3ip1/Ehd3/Pcsk9/Itgb2/Tcf7l2/Unc13a/Ripor1/Akap5/Tfr2/Arpc2/Slc4a8/Fcgr3/Acsl5/Atp1b2/Gata2/Plcg2/Unc13d/Pmaip1/Ano6/Gab2/Rac1/Il4/Gsto1/Cxcr4/Dock2/Apoe/Tgfb1/Sytl4/Ptprc/Jak3/P2rx7/Syk</t>
+    <t xml:space="preserve">Car2/Dock2/Jak3/Snca/Appl2/Syk/Picalm/Ptprc/Wnk4/Ano6/Prnp/Tgfb1/Rph3al/Abcg1/Lamp1/Rac1/Cd47/Gsto1/Itsn1/Pfkfb2/Ptpn23/Gab2/P2rx7/Ripor1/Vps11/Plcg2/Acsl5/Cxcr4/Glrx/Arpc2/Atp2b1/Apoe/Map1lc3b/Cd36/Pld2/Gnas/Unc13d/Flna/Pmaip1/Fbxw7/Ehd1/Ap1g1/Dpysl2/Tfr2/Agtr1a/Mllt6/Sytl4/Il4/Myh10/Gata2/Atad1/Wasl/Selenot/Ppard/Vps35/Sh3glb1/Arrb1/Nedd4/Fcgr3/Slc4a8/Atp1b2/Hcls1/Wipf1/Lpcat3/Snx5/Sar1b/Ergic3/Cib1/Itgb2/Prkca/Hsp90ab1/Ehd3/Atp7a/Adipor2/Trim28/Ap2m1/Ier3ip1/Exoc1/Psen1/Sirt1/Ppp3r1/Ifngr1/Pcsk9/Bax/Scp2/Tm7sf3/Brca1/Lyar/Homer1/Sorbs1/Unc13a/Ipo5/Tcf7l2/Vps4b/Cbl/P2rx1/Stom/Rack1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032606</t>
@@ -6541,7 +6541,7 @@
     <t xml:space="preserve">type I interferon production</t>
   </si>
   <si>
-    <t xml:space="preserve">Atg9a/Ticam1/Trim56/Tbk1/Ap3d1/Ppm1b/Dhx33/Hspd1/Traf3/Ifih1/Irak1/Plcg2/Havcr2/Irf5/Ptprs/Rnf125/Syk/Oas2</t>
+    <t xml:space="preserve">Syk/Ptprs/Oas2/Plcg2/Rnf125/Irak1/Atg9a/Tbk1/Irf5/Trim56/Traf3/Ticam1/Ap3d1/Havcr2/Dhx33/Ifih1/Hspd1/Ppm1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005916</t>
@@ -6553,7 +6553,7 @@
     <t xml:space="preserve">12/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Actn1/Vcl/Ctnnb1/Sptan1/Des</t>
+    <t xml:space="preserve">Actn1/Des/Ctnnb1/Sptan1/Vcl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016717</t>
@@ -6562,7 +6562,7 @@
     <t xml:space="preserve">oxidoreductase activity, acting on paired donors, with oxidation of a pair of donors resulting in the reduction of molecular oxygen to two molecules of water</t>
   </si>
   <si>
-    <t xml:space="preserve">Fads3/Scd1/Scd2/Cyb5a/Sc5d</t>
+    <t xml:space="preserve">Fads3/Cyb5a/Scd1/Scd2/Sc5d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016846</t>
@@ -6571,7 +6571,7 @@
     <t xml:space="preserve">carbon-sulfur lyase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Mgst3/Hccs/Alox5ap/Cenpv/Kyat3</t>
+    <t xml:space="preserve">Mgst3/Kyat3/Alox5ap/Cenpv/Hccs</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031748</t>
@@ -6580,7 +6580,7 @@
     <t xml:space="preserve">D1 dopamine receptor binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Vps35/Gnas/Snx5/Atp1a3</t>
+    <t xml:space="preserve">Gnas/Agtr1a/Vps35/Snx5/Atp1a3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043650</t>
@@ -6589,7 +6589,7 @@
     <t xml:space="preserve">dicarboxylic acid biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Gls/Got1/Got2/Mthfd1/Mthfd1l</t>
+    <t xml:space="preserve">Mthfd1/Got2/Mthfd1l/Got1/Gls</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097531</t>
@@ -6598,7 +6598,7 @@
     <t xml:space="preserve">mast cell migration</t>
   </si>
   <si>
-    <t xml:space="preserve">Swap70/Stat5b/Rac1/Rac2/Rin3</t>
+    <t xml:space="preserve">Rac2/Rac1/Rin3/Stat5b/Swap70</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1905664</t>
@@ -6607,7 +6607,7 @@
     <t xml:space="preserve">regulation of calcium ion import across plasma membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Prnp/Ppp3r1/P2rx1/Akap5</t>
+    <t xml:space="preserve">Prnp/Agtr1a/Ppp3r1/P2rx1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006164</t>
@@ -6619,7 +6619,7 @@
     <t xml:space="preserve">178/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampd3/Snca/Pkm/Flcn/Gcdh/Ndufa10/Parp1/Adss/Prps1/Dlat/Impdh2/Guk1/Pdha1/Aprt/Adsl/Mthfd1/Adssl1/Acsl5/Atic/Ak4/Pfas/Papss2/Gmpr/Gart/Npr2/Il4/Tgfb1/Nme4/Adcy7</t>
+    <t xml:space="preserve">Ampd3/Adcy7/Snca/Tgfb1/Nme4/Gart/Pfas/Acsl5/Pdha1/Atic/Pkm/Il4/Adssl1/Npr2/Adsl/Gmpr/Impdh2/Mthfd1/Papss2/Guk1/Prps1/Dlat/Flcn/Gcdh/Ak4/Ndufa10/Aprt/Adss/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045088</t>
@@ -6628,7 +6628,7 @@
     <t xml:space="preserve">regulation of innate immune response</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Grn/Serpinb1a/Lamp1/Trim56/Tbk1/Rnf185/Hexim1/Usp15/Nono/Cnot7/Matr3/Ap1g1/Lyar/Stat5a/Stat5b/Xrcc5/Plcg2/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9/Apoe/Spi1/Tyrobp/Dpp4/Syk</t>
+    <t xml:space="preserve">Appl2/Syk/Grn/Lamp1/Spi1/Vav1/Plcg2/Lgals9/Apoe/Stat5b/Dpp4/Xrcc5/Serpinb1a/Tbk1/Ap1g1/Trim56/Tyrobp/Stat5a/Pik3r6/Nono/Havcr2/Matr3/Serpinb9/Hexim1/Usp15/Cadm1/Rnf185/Lyar/Cnot7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030219</t>
@@ -6637,7 +6637,7 @@
     <t xml:space="preserve">megakaryocyte differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Mturn/Cnot4/Cib1/Abi1/Flna/Srf/Prmt1/Ptpn6/Gata2/Fli1</t>
+    <t xml:space="preserve">Tal1/Fli1/Cnot4/Ptpn6/Flna/Mturn/Gata2/Prmt1/Srf/Cib1/Abi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033003</t>
@@ -6652,7 +6652,7 @@
     <t xml:space="preserve">bone development</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Cited2/Insig1/Atg9a/Fbxw7/Rara/Gnas/Asxl2/Abi1/Setdb1/Lrp5/Mbtps2/Ift172/Megf8/Flna/Srf/Sh3pxd2b/Trp53/Ptpn6/Kat2a/Lrrk1/Papss2/Snx10/Ano6/Cadm1/Npr2/Fli1/Mmp14/Tyrobp/Ptprc</t>
+    <t xml:space="preserve">Ptprc/Ano6/Tal1/Cited2/Fli1/Kat2a/Insig1/Ptpn6/Gnas/Lrrk1/Megf8/Flna/Atg9a/Fbxw7/Sh3pxd2b/Trp53/Tyrobp/Npr2/Mmp14/Srf/Snx10/Ift172/Papss2/Lrp5/Cadm1/Mbtps2/Rara/Setdb1/Abi1/Asxl2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055092</t>
@@ -6670,7 +6670,7 @@
     <t xml:space="preserve">438/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Btg2/Dpf3/Cited2/Mier3/Hipk2/Dcaf6/Nupr1/Wbp2/Actn1/Hcfc2/Arrb1/Hdac5/Slc30a9/Tle2/Med17/Med7/Kmt2c/Tob1/Pias2/Kdm2a/Dyrk1a/Npat/Taf6l/Ccar1/Med13/Brca1/Elk1/Ncoa1/Med20/Pias1/Sirt1/Kat6a/N4bp2l2/Phf10/Tbl1xr1/Ctnnb1/Trim28/Cnot7/Wdr77/Nucks1/Pa2g4/Maged1/Rbck1/Rrp1b/Ldb1/Ruvbl2/Irf2bp2/Smarcd1/Rap2c/Mybbp1a/Ss18/Lpxn/Lmo2/Zbtb32/Dnmt3b/Jade1/Kat2a/Tfb2m/Cbfb/Hdac7</t>
+    <t xml:space="preserve">Hdac7/Btg2/Mier3/Dpf3/Cbfb/Cited2/Actn1/Slc30a9/Kat2a/Wbp2/Ss18/Jade1/Dyrk1a/Hipk2/Dnmt3b/Irf2bp2/Smarcd1/Kdm2a/Dcaf6/Ldb1/Pias2/Rap2c/Lmo2/Med13/Med17/Maged1/Tfb2m/Ctnnb1/Mybbp1a/Hdac5/Npat/Rbck1/Hcfc2/Arrb1/Ccar1/Ruvbl2/Tob1/Med7/Nucks1/Trim28/Elk1/Kmt2c/Sirt1/Ncoa1/Nupr1/Brca1/Kat6a/Pias1/N4bp2l2/Taf6l/Med20/Zbtb32/Wdr77/Tbl1xr1/Cnot7/Tle2/Pa2g4/Phf10/Rrp1b/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0004842</t>
@@ -6679,7 +6679,7 @@
     <t xml:space="preserve">ubiquitin-protein transferase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Map3k1/Trim10/Neurl1b/Trim2/Uba7/Herc6/Ube2l6/Rnf145/Cnot4/Vps11/Mylip/Rchy1/Rnf14/Rnf115/Trim56/Rnf139/Fbxw7/Hace1/Rnf146/Rnf38/Med7/Fbxo11/Rnf10/Hectd3/Rnf168/Rnf185/Mkrn1/Rnf167/Brca1/Fbxo30/Med20/Siah1b/Trip12/Klhl9/Ltn1/Fbxw11/Prpf19/Nedd4/Trim28/Ube2e1/Trim35/Cbl/Rbck1/Jade2/Ube2s/Dtx4/Dtx3l/Rnf138/Mex3c/Aktip/Traf3ip2/Rnf125</t>
+    <t xml:space="preserve">Map3k1/Trim2/Rnf145/Rnf115/Uba7/Trim10/Vps11/Cnot4/Rnf125/Rnf14/Mex3c/Herc6/Fbxw7/Rnf38/Rchy1/Rnf139/Trim56/Hace1/Fbxo11/Rnf146/Ube2l6/Neurl1b/Rnf138/Fbxo30/Mylip/Rnf10/Rnf168/Aktip/Rbck1/Nedd4/Trip12/Med7/Ltn1/Rnf167/Ube2s/Dtx3l/Dtx4/Prpf19/Trim28/Traf3ip2/Hectd3/Rnf185/Trim35/Brca1/Ube2e1/Med20/Siah1b/Klhl9/Fbxw11/Cbl/Jade2/Mkrn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051640</t>
@@ -6691,7 +6691,7 @@
     <t xml:space="preserve">517/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Snca/Pip4p1/Mylk2/Trappc2l/Mis12/Picalm/Vps11/Lamp1/D6Wsu163e/Uvrag/Dpysl2/Lamtor1/Syn1/Trak2/Bhlha15/Vps33a/Myo6/Wasl/Armcx3/Gpsm2/Flcn/Ap3d1/Stk25/Ccdc186/Birc5/Exoc8/Trappc8/Pacs2/Exoc1/Arl8b/Snap29/Cdc42bpa/Uso1/Vps4b/Fbxw11/Psen1/Actr2/Ctnnb1/Esyt1/Pdzd8/Sdad1/Copg2/Def8/Myh10/Sar1b/Mdn1/Kif1c/Tcf7l2/Unc13a/Ripor1/Tmem230/Cluh/Kat2a/Gata2/Unc13d/Cplx2/Ltv1/Gab2/Rac2/Il4/Ywhaz/Fes/Arhgef2/Iffo1/Sytl4/Myo1g/Cd84/Syk</t>
+    <t xml:space="preserve">Snca/Myo1g/Syk/Picalm/Arhgef2/Rac2/Ywhaz/Lamp1/Pip4p1/Cd84/Gab2/Iffo1/Ripor1/Vps11/Kat2a/Ltv1/Pld2/Unc13d/Uvrag/Kif1c/Stk25/Pacs2/Pdzd8/Myo6/Mis12/Cluh/Dpysl2/D6Wsu163e/Sytl4/Il4/Myh10/Gata2/Wasl/Fes/Lamtor1/Trappc2l/Ctnnb1/Ap3d1/Vps33a/Copg2/Trappc8/Gpsm2/Esyt1/Mdn1/Mylk2/Exoc8/Trak2/Sar1b/Def8/Cplx2/Arl8b/Tmem230/Flcn/Sdad1/Birc5/Exoc1/Psen1/Bhlha15/Actr2/Armcx3/Cdc42bpa/Unc13a/Fbxw11/Tcf7l2/Ccdc186/Vps4b/Snap29/Syn1/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000679</t>
@@ -6703,7 +6703,7 @@
     <t xml:space="preserve">17/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">H1f0/Rb1/Parp1/Ctnnb1/Lgals9/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Lgals9/H1f0/Ctnnb1/Rb1/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2001235</t>
@@ -6712,7 +6712,7 @@
     <t xml:space="preserve">positive regulation of apoptotic signaling pathway</t>
   </si>
   <si>
-    <t xml:space="preserve">Nupr1/Pea15a/Fbxw7/Flcn/Mtch2/Bax/Nck1/Bcl2l11/Bid/Mcl1/Siah1b/Sirt1/Sh3glb1/Rack1/Serinc3/Maged1/Rbck1/Itm2c/Trp53/Ppp2r1a/Pmaip1/Ptprc/Jak3</t>
+    <t xml:space="preserve">Jak3/Ptprc/Ppp2r1a/Mtch2/Pmaip1/Fbxw7/Trp53/Maged1/Pea15a/Rbck1/Sh3glb1/Mcl1/Bcl2l11/Flcn/Bid/Sirt1/Bax/Nupr1/Serinc3/Itm2c/Siah1b/Nck1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034762</t>
@@ -6724,7 +6724,7 @@
     <t xml:space="preserve">456/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Appl2/Car2/Mink1/Wnk4/Scn10a/Snca/Agtr1a/Glrx/Prnp/Slc43a1/Pim1/Kel/Ubash3b/Pea15a/Atp7a/Fgf11/Bax/Sorbs1/Stom/Homer1/Rps6kb1/Adipor2/Grk6/Gpr89/Psen1/Nedd4/Ppp3r1/Gopc/Phb2/Pde4d/Ifngr1/Fkbp1a/Prkca/P2rx1/Flna/Tmem109/Ppif/Fkbp1b/Ehd3/Pcsk9/Slc43a2/Akap5/Dapk1/Ptpn6/Acsl5/Atp1b2/Plcg2/Hk2/Ano6/Zfas1/Grin2d/Rangrf/Pde4b/Rgs2/Clic1/Kcnab2/Il4/Gsto1/Tgfb1/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Car2/Snca/Appl2/Wnk4/Mink1/Coro1a/Ano6/Slc6a9/Prnp/Tgfb1/Gsto1/Kcnab2/Clic1/P2rx7/Plcg2/Acsl5/Glrx/Ptpn6/Flna/Scn10a/Slc43a1/Agtr1a/Zfas1/Rangrf/Il4/Rgs2/Pea15a/Kel/Dapk1/Ppif/Nedd4/Atp1b2/Fgf11/Prkca/Ubash3b/Pde4b/Ehd3/Atp7a/Slc43a2/Adipor2/Hk2/Tmem109/Grin2d/Psen1/Fkbp1a/Ppp3r1/Ifngr1/Pcsk9/Bax/Phb2/Homer1/Sorbs1/Fkbp1b/P2rx1/Grk6/Stom/Gpr89/Pim1/Akap5/Rps6kb1/Gopc/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031589</t>
@@ -6733,7 +6733,7 @@
     <t xml:space="preserve">cell-substrate adhesion</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Mink1/Dmtn/Nedd9/Tsc1/Micall2/Prex1/Actn1/Ppard/Megf9/Cib1/Dag1/Atrnl1/Bcl2l11/Sorbs1/Lamc1/Vcl/Cttn/Iqgap1/Ctnnb1/Ldb1/Parvg/Flna/Srf/Plekha2/Itgb2/Fzd7/Lpxn/Arpc2/Atp1b2/Unc13d/Itga5/Rac1/Rcc2/Rac2/Fermt3/Csf1/Mmp14/Cdk6/Coro1a/Lgals1/Myo1g</t>
+    <t xml:space="preserve">Lgals1/Myo1g/Mink1/Coro1a/Rac2/Cdk6/Tsc1/Dmtn/Rac1/Rcc2/Fermt3/Actn1/Micall2/Arpc2/Cd36/Prex1/Itga5/Unc13d/Flna/Dag1/Ldb1/Nedd9/Mmp14/Fzd7/Srf/Csf1/Ctnnb1/Megf9/Ppard/Atp1b2/Cib1/Bcl2l11/Itgb2/Lamc1/Plekha2/Iqgap1/Parvg/Sorbs1/Cttn/Atrnl1/Vcl/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002068</t>
@@ -6745,7 +6745,7 @@
     <t xml:space="preserve">28/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Arntl/Gdf11/Fasn/Fzd5/Bhlha15/Rara/Gata2/Cdk6</t>
+    <t xml:space="preserve">Cdk6/Fasn/Arntl/Gdf11/Fzd5/Gata2/Bhlha15/Rara</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030507</t>
@@ -6754,7 +6754,7 @@
     <t xml:space="preserve">spectrin binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Ank1/Add2/Dmtn/Epb41/Camsap2/Sptan1/Unc13a/Ptprc</t>
+    <t xml:space="preserve">Add2/Ptprc/Dmtn/Ank1/Epb41/Camsap2/Sptan1/Unc13a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043302</t>
@@ -6763,7 +6763,7 @@
     <t xml:space="preserve">positive regulation of leukocyte degranulation</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Lamp1/Ap1g1/Itgb2/Gata2/Gab2/Il4/Syk</t>
+    <t xml:space="preserve">Syk/Lamp1/Gab2/Pld2/Ap1g1/Il4/Gata2/Itgb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044346</t>
@@ -6772,7 +6772,7 @@
     <t xml:space="preserve">fibroblast apoptotic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Nupr1/Bcl2l11/Bid/Sirt1/Ier3ip1/Trp53/Pmaip1/Casp7</t>
+    <t xml:space="preserve">Casp7/Pmaip1/Trp53/Bcl2l11/Ier3ip1/Bid/Sirt1/Nupr1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903959</t>
@@ -6781,7 +6781,7 @@
     <t xml:space="preserve">regulation of anion transmembrane transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Slc43a1/Grk6/Psen1/Gopc/Prkca/Slc43a2/Rgs2</t>
+    <t xml:space="preserve">Prnp/Slc43a1/Rgs2/Prkca/Slc43a2/Psen1/Grk6/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002687</t>
@@ -6793,7 +6793,7 @@
     <t xml:space="preserve">117/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd47/Adam10/Mospd2/Swap70/Mia3/Trp53/Ano6/Fut4/Plvap/Rac1/Ripor2/Dock8/Rac2/Il4/Csf1/Lgals9/Spn/Mmp14/Tgfb1/Spi1/Coro1a</t>
+    <t xml:space="preserve">Coro1a/Ano6/Rac2/Tgfb1/Spn/Rac1/Cd47/Dock8/Ripor2/Spi1/Lgals9/Adam10/Trp53/Fut4/Il4/Mmp14/Csf1/Mospd2/Plvap/Swap70/Mia3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033157</t>
@@ -6802,7 +6802,7 @@
     <t xml:space="preserve">regulation of intracellular protein transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Sh3tc2/Dmtn/Insig1/Prnp/Yod1/Fbxw7/Cib1/Uhmk1/Gripap1/Brca1/Stom/Sh3glb1/Snx3/Psen1/Dnajc27/Trim28/Ipo5/Ergic3/Hsp90ab1/Wipf1/Hcls1/Sp100/Sar1b/Flna/Tcf7l2/Ripor1/Akap5/Arpc2/Pmaip1/Tgfb1/Lcp1</t>
+    <t xml:space="preserve">Sh3tc2/Prnp/Tgfb1/Dmtn/Lcp1/Ripor1/Arpc2/Cd36/Yod1/Insig1/Flna/Pmaip1/Fbxw7/Uhmk1/Sh3glb1/Hcls1/Wipf1/Sar1b/Ergic3/Cib1/Hsp90ab1/Trim28/Psen1/Brca1/Gripap1/Ipo5/Tcf7l2/Stom/Akap5/Sp100/Snx3/Dnajc27</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010608</t>
@@ -6811,7 +6811,7 @@
     <t xml:space="preserve">post-transcriptional regulation of gene expression</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Btg2/Fech/Tnrc6b/Tsc1/Pkm/Marf1/Carhsp1/Ppp1r15b/Nr2f1/Gigyf2/Rnf139/Habp4/Tent5c/Tob1/Rara/Uhmk1/Nck1/Ddx6/Aco1/Ago2/Tnrc6c/Mknk1/Tut7/Mknk2/Rps6kb1/Celf1/Rack1/Zc3h7b/Parn/Cnot7/Pa2g4/Ddx49/Pus7/Zfp706/Eif4g2/Mov10/Tcof1/Pabpc4/Matr3/Cnbp/Trnau1ap/Prkca/Exosc5/Dph6/Eif4ebp2/Xpo5/Otud6b/Nat10/Naf1/Mrps27/Trp53/Dapk1/Bzw2/Ogfod1/Fastkd1/Traf3ip2/Zfp36l1/Msi1/Rgs2/Ago4/Vim/Tgfb1/Celf2</t>
+    <t xml:space="preserve">Btg2/Celf2/Tgfb1/Fech/Tsc1/Cpeb4/Gigyf2/Marf1/Tnrc6b/Vim/Xpo5/Pabpc4/Carhsp1/Ago4/Eif4ebp2/Bzw2/Nat10/Pkm/Tcof1/Trp53/Rnf139/Ddx6/Habp4/Ogfod1/Mrps27/Rgs2/Ppp1r15b/Aco1/Naf1/Zfp36l1/Msi1/Otud6b/Dapk1/Uhmk1/Fastkd1/Matr3/Celf1/Cnbp/Tob1/Mov10/Pus7/Mknk2/Prkca/Tent5c/Zfp706/Dph6/Exosc5/Traf3ip2/Eif4g2/Nr2f1/Rara/Ago2/Tut7/Trnau1ap/Tnrc6c/Nck1/Zc3h7b/Ddx49/Cnot7/Mknk1/Rack1/Parn/Pa2g4/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009792</t>
@@ -6823,7 +6823,7 @@
     <t xml:space="preserve">661/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Nfe2/Abcg2/Specc1/Cited2/Grn/Nsrp1/Sox6/Gab1/Tsc1/Adam10/Zfat/Klf1/Stil/Atp6ap2/Epn1/Fzd5/Junb/Coprs/Plcd3/Mxi1/Flcn/Tent5c/Ggnbp2/Usp9x/Dvl2/Rara/Nckap1/Kdm2a/Ttbk2/Luzp1/Nup50/Npat/Mafg/Kdm4c/Bcl2l11/4933434E20Rik/Otud7b/Rictor/Gnas/Brca1/Tapt1/Ncoa1/Arnt/Gna13/Asxl2/Arhgap35/Nxn/Bnip2/N4bp2l2/Abi1/Setdb1/Tbl1xr1/Psen1/Ctnnb1/Trim28/Gpi1/Dhx35/Ndst1/Myh10/Tcof1/Matr3/Plod3/Ift172/Megf8/Mthfd1/Srf/Prmt1/Tcf7l2/Mthfd1l/Trp53/Vangl2/Pcgf2/Kat2a/Gata2/Ptpn18/Zfp36l1/Tmem231/Arhgdig/Phlda2/Mmp14/Tgfb1/Gdf3/Vash2/Myb</t>
+    <t xml:space="preserve">Cobl/Myb/Tgfb1/Grn/Abcg2/Tsc1/Nfe2/Vash2/Gab1/Klf1/Cited2/Kat2a/Epn1/Adam10/Atp6ap2/Specc1/Gnas/Arnt/Megf8/Arhgdig/Gdf3/Tcof1/Kdm2a/Trp53/Phlda2/Usp9x/Nsrp1/Pcgf2/Nup50/Fzd5/Stil/Myh10/Tapt1/Mxi1/Gata2/Mmp14/Prmt1/Gna13/4933434E20Rik/Srf/Ptpn18/Ggnbp2/Zfp36l1/Ctnnb1/Nckap1/Zfat/Tmem231/Plod3/Npat/Ift172/Vangl2/Matr3/Mthfd1/Dvl2/Mthfd1l/Luzp1/Coprs/Ndst1/Otud7b/Sox6/Bcl2l11/Tent5c/Trim28/Ttbk2/Flcn/Psen1/Kdm4c/Dhx35/Junb/Ncoa1/Rara/Setdb1/Brca1/N4bp2l2/Plcd3/Abi1/Arhgap35/Bnip2/Asxl2/Tbl1xr1/Tcf7l2/Nxn/Mafg/Rictor/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071621</t>
@@ -6832,7 +6832,7 @@
     <t xml:space="preserve">granulocyte chemotaxis</t>
   </si>
   <si>
-    <t xml:space="preserve">Prex1/Pikfyve/Mospd2/Mpp1/Pde4d/Prkca/Itgb2/Fcgr3/Vav1/Pde4b/Rac1/Ripor2/Rac2/Il4/Csf1/Dpp4/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Rac1/Ripor2/Vav1/Prex1/Pikfyve/Dpp4/Il4/Csf1/Mospd2/Fcgr3/Mpp1/Itgb2/Prkca/Pde4b/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0004860</t>
@@ -6844,7 +6844,7 @@
     <t xml:space="preserve">60/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Inka2/Prkar2b/Smcr8/Cdkn2c/Cib1/Nck1/Hexim1/Qars/Rack1/Parp1/Prkag2/Spred2/Trib2</t>
+    <t xml:space="preserve">Prkar2b/Trib2/Inka2/Cdkn2c/Spred2/Prkag2/Smcr8/Hexim1/Cib1/Nck1/Parp1/Qars/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042130</t>
@@ -6853,7 +6853,7 @@
     <t xml:space="preserve">negative regulation of T cell proliferation</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Zbtb7b/Vsir/Ptpn6/Cd37/Ripor2/Havcr2/Lgals9/Spn/Lgals7/Tgfb1/Cd44/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Prnp/Tgfb1/Spn/Cd44/Ripor2/Lgals9/Ptpn6/Zbtb7b/Lgals7/Cd37/Havcr2/Vsir</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045453</t>
@@ -6862,7 +6862,7 @@
     <t xml:space="preserve">bone resorption</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Tfrc/Tpp1/Ubash3b/Ctnnb1/Def8/Prkca/Lrrk1/Snx10/Rac1/Rac2/P2rx7/Syk</t>
+    <t xml:space="preserve">Car2/Syk/Tpp1/Rac2/Rac1/P2rx7/Lrrk1/Snx10/Ctnnb1/Tfrc/Def8/Prkca/Ubash3b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030027</t>
@@ -6871,7 +6871,7 @@
     <t xml:space="preserve">lamellipodium</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Itsn1/Als2/Tsc1/Wasl/Cib1/Ppp1r9b/Dag1/Nckap1/Pkn2/Cttn/Cdc42bpa/Abi1/Actr2/Ctnnb1/Dgkz/Myh10/Arpc2/Pdxp/Arhgef6/Rac1/Rac2/Cd44/Coro1a/Dpp4/Myo1g</t>
+    <t xml:space="preserve">Myo1g/Coro1a/Rac2/Tsc1/Cd44/Rac1/Itsn1/Als2/Arpc2/Pld2/Dpp4/Arhgef6/Dag1/Pdxp/Pkn2/Myh10/Dgkz/Wasl/Ppp1r9b/Ctnnb1/Nckap1/Cib1/Actr2/Cdc42bpa/Abi1/Cttn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904062</t>
@@ -6883,7 +6883,7 @@
     <t xml:space="preserve">303/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Mink1/Wnk4/Snca/Agtr1a/Glrx/Prnp/Slc43a1/Kel/Ubash3b/Atp7a/Fgf11/Bax/Stom/Homer1/Nedd4/Ppp3r1/Phb2/Pde4d/Ifngr1/Fkbp1a/P2rx1/Flna/Ppif/Fkbp1b/Ehd3/Pcsk9/Slc43a2/Akap5/Dapk1/Ptpn6/Atp1b2/Plcg2/Zfas1/Grin2d/Rangrf/Pde4b/Rgs2/Kcnab2/Il4/Gsto1/Tgfb1/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Snca/Wnk4/Mink1/Coro1a/Slc6a9/Prnp/Tgfb1/Gsto1/Kcnab2/P2rx7/Plcg2/Glrx/Ptpn6/Flna/Slc43a1/Agtr1a/Zfas1/Rangrf/Il4/Rgs2/Kel/Dapk1/Ppif/Nedd4/Atp1b2/Fgf11/Ubash3b/Pde4b/Ehd3/Atp7a/Slc43a2/Grin2d/Fkbp1a/Ppp3r1/Ifngr1/Pcsk9/Bax/Phb2/Homer1/Fkbp1b/P2rx1/Stom/Akap5/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016788</t>
@@ -6895,7 +6895,7 @@
     <t xml:space="preserve">617/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slfn14/Pld2/Car2/Ptp4a3/Lrrc39/Ddhd1/Pip4p1/Gpcpd1/Pfkfb2/Dusp6/Ache/Aplf/Ptpn23/Mus81/Isg20/Pop5/Hagh/Cdc25b/Fasn/Ubash3b/Ssh2/Apex2/Dnase2a/Ppp2r5a/Plcd3/Acot13/Abhd15/Polg/Nt5dc2/N4bp2/Ago2/Mtmr3/Gnas/Fancm/Ppm1b/Mtmr12/Vars2/Parn/Cnot7/Ppp3r1/Pde4d/Rcl1/Abhd16a/Ptpru/Ppa2/Pfkfb3/Ndst1/Enoph1/Cpsf3/Tars2/Nt5m/Timm50/Ptpn9/Ssu72/Arsk/Faah/Lhpp/Plpp2/Pla2g12a/Pdxp/Mtmr9/Prdx6/Ptpn6/H6pd/Ppp2r1a/Plcg2/Ptpn18/Tsen15/Pde4b/Ppm1h/Ago4/Meiob/G6pc3/Plcb2/Lypla1/Aldh2/Ptprs/Pla2g1b/Ptprc/Ces2g</t>
+    <t xml:space="preserve">Car2/Ces2g/Ptprs/Ptprc/Slfn14/Aldh2/Pip4p1/Lypla1/Pfkfb2/Ptpn23/Ppp2r5a/Plcb2/Ppp2r1a/Plcg2/Cdc25b/Pld2/Mtmr9/Ptpn6/Fasn/Ddhd1/Gnas/Ache/Tars2/Hagh/Mus81/Ago4/Ptp4a3/Tsen15/Polg/Ssh2/Prdx6/Aplf/Dnase2a/Pdxp/G6pc3/Dusp6/Mtmr3/Timm50/Pla2g12a/Lhpp/Pop5/Pla2g1b/Lrrc39/H6pd/Ptpn18/Ptpn9/Isg20/Ppm1h/Ssu72/Faah/Gpcpd1/Apex2/Cpsf3/Nt5dc2/Ndst1/Meiob/Ubash3b/Pde4b/Abhd16a/Plpp2/Acot13/Rcl1/Fancm/Ppp3r1/Mtmr12/Arsk/Enoph1/Ago2/Plcd3/Ptpru/Vars2/Pfkfb3/N4bp2/Abhd15/Cnot7/Parn/Ppa2/Ppm1b/Nt5m/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097581</t>
@@ -6907,7 +6907,7 @@
     <t xml:space="preserve">81/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Atp7a/Nckap1/Nck1/Twf1/Vcl/Cttn/Snx2/Abi1/Actr2/Was/Arpc2/Arhgef6/Rac1/Rac2/Cd44</t>
+    <t xml:space="preserve">Rac2/Dmtn/Cd44/Rac1/Arpc2/Arhgef6/Nckap1/Twf1/Atp7a/Snx2/Actr2/Abi1/Nck1/Cttn/Vcl/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098562</t>
@@ -6925,7 +6925,7 @@
     <t xml:space="preserve">glandular epithelial cell maturation</t>
   </si>
   <si>
-    <t xml:space="preserve">Gdf11/Fzd5/Bhlha15/Gata2</t>
+    <t xml:space="preserve">Gdf11/Fzd5/Gata2/Bhlha15</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002433</t>
@@ -6934,7 +6934,7 @@
     <t xml:space="preserve">immune response-regulating cell surface receptor signaling pathway involved in phagocytosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Cd47/Ptprc/Myo1g</t>
+    <t xml:space="preserve">Myo1g/Appl2/Ptprc/Cd47</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031698</t>
@@ -6943,7 +6943,7 @@
     <t xml:space="preserve">beta-2 adrenergic receptor binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Gnas/Nedd4/Pde4d/Akap5</t>
+    <t xml:space="preserve">Gnas/Nedd4/Akap5/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0038096</t>
@@ -6958,7 +6958,7 @@
     <t xml:space="preserve">AMP salvage</t>
   </si>
   <si>
-    <t xml:space="preserve">Adss/Aprt/Adsl/Adssl1</t>
+    <t xml:space="preserve">Adssl1/Adsl/Aprt/Adss</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045588</t>
@@ -6967,7 +6967,7 @@
     <t xml:space="preserve">positive regulation of gamma-delta T cell differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Stat5a/Stat5b/Ptprc/Syk</t>
+    <t xml:space="preserve">Syk/Ptprc/Stat5b/Stat5a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046543</t>
@@ -6976,7 +6976,7 @@
     <t xml:space="preserve">development of secondary female sexual characteristics</t>
   </si>
   <si>
-    <t xml:space="preserve">Phb2/Stat5a/Stat5b/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Stat5b/Stat5a/Phb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046645</t>
@@ -6997,7 +6997,7 @@
     <t xml:space="preserve">retromer complex binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Washc2/Slc11a2/Igf2r/Snx3</t>
+    <t xml:space="preserve">Slc11a2/Washc2/Igf2r/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990535</t>
@@ -7006,7 +7006,7 @@
     <t xml:space="preserve">neuron projection maintenance</t>
   </si>
   <si>
-    <t xml:space="preserve">Map1a/Prnp/Psen1/Atp1a3</t>
+    <t xml:space="preserve">Prnp/Map1a/Atp1a3/Psen1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030544</t>
@@ -7015,7 +7015,7 @@
     <t xml:space="preserve">Hsp70 protein binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Dnajb2/Tfrc/Tsc1/Mvd/Dnajc10/Bax/Fkbp1a/Stau2/Dnajc2/Spn</t>
+    <t xml:space="preserve">Snca/Spn/Dnajc2/Tsc1/Dnajc10/Mvd/Dnajb2/Tfrc/Fkbp1a/Bax/Stau2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050435</t>
@@ -7024,7 +7024,7 @@
     <t xml:space="preserve">amyloid-beta metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Abcg1/Picalm/Adam10/Apeh/Dyrk1a/Psen1/Ifngr1/Abca2/Unc13a/Apoe</t>
+    <t xml:space="preserve">Picalm/Prnp/Abcg1/Abca2/Apoe/Adam10/Dyrk1a/Apeh/Psen1/Ifngr1/Unc13a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050879</t>
@@ -7033,7 +7033,7 @@
     <t xml:space="preserve">multicellular organismal movement</t>
   </si>
   <si>
-    <t xml:space="preserve">Map1a/Mylk2/Hipk2/Dmpk/Gigyf2/Cln8/Vps35/Homer1/Parp1/Tnni3/Rcsd1</t>
+    <t xml:space="preserve">Rcsd1/Gigyf2/Hipk2/Map1a/Vps35/Dmpk/Mylk2/Tnni3/Homer1/Parp1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050881</t>
@@ -7051,7 +7051,7 @@
     <t xml:space="preserve">726/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cpeb4/Cd36/Pld2/Appl2/Car2/Egr2/Dmtn/Slc30a10/Snca/Dnajb2/Agtr1a/Insig1/Prnp/Rragc/Ache/Tsc1/Pkm/Yod1/Ldlr/Sesn1/Mylip/Ticam1/Zbtb7b/Lamtor1/Hdac5/Rnf139/Atp2b1/Socs2/Foxo4/Dnajc10/Atp7a/Lamtor3/Ppp1r9b/Sesn3/Vps35/Nck1/Rnf185/Usp25/Sorbs1/Gnas/Brca1/Rap1b/Rb1/Ncoa1/Pip4k2c/Ubxn4/Homer1/Sirt1/Rps6kb1/Mia3/Uso1/Psen1/Parp1/Ctnnb1/Ipo5/Nucks1/Gpi1/Mat2a/Pde4d/Fkbp1a/Igf1r/Prkca/P2rx1/Flna/Snx5/Stat5a/Eif4ebp2/Pcsk9/Itgb2/Dnmt3b/Arpc2/Trp53/Pdxp/Stat5b/Irak1/Khk/Plcg2/Zfp36l1/Atp1a3/Pde4b/Nrros/Hlcs/Rac1/Casp7/Vim/Irf5/Arhgef2/Apoe/Jak3/P2rx7/Syk</t>
+    <t xml:space="preserve">Car2/Egr1/Jak3/Snca/Appl2/Syk/Arhgef2/Prnp/Rragc/Casp7/Slc30a10/Tsc1/Dmtn/Cpeb4/Rac1/P2rx7/Plcg2/Vim/Arpc2/Atp2b1/Hlcs/Apoe/Stat5b/Cd36/Pld2/Yod1/Ldlr/Insig1/Khk/Gnas/Sesn1/Ache/Flna/Irak1/Dnmt3b/Eif4ebp2/Pkm/Trp53/Nrros/Rnf139/Dnajc10/Zbtb7b/Irf5/Pdxp/Agtr1a/Egr2/Socs2/Ticam1/Stat5a/Ppp1r9b/Zfp36l1/Lamtor3/Lamtor1/Ctnnb1/Dnajb2/Mylip/Hdac5/Vps35/Rb1/Ubxn4/Snx5/Nucks1/Itgb2/Prkca/Pde4b/Atp1a3/Atp7a/Usp25/Rap1b/Psen1/Sesn3/Sirt1/Fkbp1a/Ncoa1/Pcsk9/Rnf185/Brca1/Foxo4/Homer1/Sorbs1/Ipo5/Igf1r/Nck1/Parp1/Mia3/P2rx1/Mat2a/Rps6kb1/Pip4k2c/Pde4d/Uso1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048514</t>
@@ -7063,7 +7063,7 @@
     <t xml:space="preserve">485/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Egr3/Tal1/Cited2/Agtr1a/Grn/Hipk2/Gab1/Pkm/Ldlr/Anxa3/Epor/Hdac5/Epn1/Fzd5/Junb/Sars/Plcd3/Fbxw7/Foxo4/Flcn/Cib1/Shb/Pknox1/Bax/Ago2/Brca1/Gna13/Sirt1/Adipor2/Kat6a/Mia3/Nras/Sgpl1/Ctnnb1/Nedd4/Ppp3r1/Lrp5/Tnni3/Cul7/Prkca/Sp100/Flna/Srf/Gtf2i/Itgb2/Pik3cd/Vangl2/Sema4a/Gata2/Zfp36l1/Hk2/Itga5/Hif3a/Pik3r6/Ywhaz/Cxcr4/Apoe/Tgfb1/Spi1/Hdac7/Plxdc1/Vash2/Syk/Eng</t>
+    <t xml:space="preserve">Hdac7/Syk/Tgfb1/Ywhaz/Grn/Tal1/Vash2/Gab1/Spi1/Cited2/Eng/Hif3a/Cxcr4/Epn1/Apoe/Cd36/Ldlr/Itga5/Hipk2/Gtf2i/Flna/Fbxw7/Pkm/Egr3/Plxdc1/Epor/Sars/Agtr1a/Pik3cd/Fzd5/Gata2/Cul7/Sema4a/Gna13/Pik3r6/Srf/Zfp36l1/Pknox1/Ctnnb1/Hdac5/Vangl2/Nedd4/Anxa3/Lrp5/Cib1/Itgb2/Prkca/Adipor2/Hk2/Flcn/Sirt1/Tnni3/Junb/Ppp3r1/Bax/Nras/Brca1/Kat6a/Foxo4/Ago2/Plcd3/Mia3/Sgpl1/Sp100/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071900</t>
@@ -7072,7 +7072,7 @@
     <t xml:space="preserve">regulation of protein serine/threonine kinase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Map3k1/Snca/Prkar2b/Gab1/Uvrag/Stil/Cdc6/Pim1/Mapre3/Gba/Fzd5/Map3k12/Cdkn2c/Hmgcr/Cib1/Dvl2/Hexim1/Rb1/Sirt1/Psen1/Iqgap1/Lrp5/Gtpbp4/Maged1/Hsp90ab1/Pik3r5/Prkag2/Ccng1/Irak1/Vangl2/Ptpn6/Rgs2/Pik3r6/Tfap4/Rgs14/Apoe/Trib2/Tgfb1/Mst1r/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Map3k1/Prkar2b/Snca/Syk/Ptprc/Tgfb1/Trib2/Gab1/P2rx7/Ccng1/Apoe/Mst1r/Ptpn6/Cdc6/Irak1/Tfap4/Uvrag/Gba/Rgs14/Cdkn2c/Fzd5/Stil/Rgs2/Prkag2/Pik3r6/Maged1/Rb1/Vangl2/Dvl2/Hmgcr/Hexim1/Lrp5/Cib1/Hsp90ab1/Mapre3/Psen1/Sirt1/Iqgap1/Map3k12/Gtpbp4/Pim1/Pik3r5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046939</t>
@@ -7084,7 +7084,7 @@
     <t xml:space="preserve">96/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Guk1/Prkag2/Khk/Ak4/Hk2/Nme4/P2rx7</t>
+    <t xml:space="preserve">Slc4a1/Pfkfb2/Nme4/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Pkm/Prkag2/Guk1/Eno3/Hk2/Psen1/Bpgm/Ak4/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098655</t>
@@ -7096,7 +7096,7 @@
     <t xml:space="preserve">592/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Mink1/Wnk4/Ank1/Slc25a37/Atp6v0d1/Rhag/Slc30a10/Abcb6/Scn10a/Snca/Agtr1a/Slc36a1/Asic4/Mcoln1/Glrx/Prnp/Slc43a1/Atp6v1e1/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Clcn3/Bhlha15/Atp2b1/Smdt1/Atp6v1a/Atp6v1b2/Atp7a/Slc38a5/Fgf11/Bax/Atp6v0b/Slc12a7/Stom/Atp6v1g1/Slc39a8/Homer1/Nedd4/Ppp3r1/Phb2/Pde4d/Ifngr1/Fkbp1a/Slc22a5/P2rx1/Flna/Ppif/Fkbp1b/Ehd3/Pcsk9/Slc43a2/Akap5/Dapk1/Abcb8/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Ano6/Zfas1/Grin2d/Rangrf/Pde4b/Rgs2/Slc39a11/Kcnab2/Il4/Gsto1/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Atp6v0d1/Snca/Ptprc/Wnk4/Mink1/Coro1a/Ano6/Abcb6/Slc6a9/Prnp/Tgfb1/Slc30a10/Slc11a2/Atp6v1e1/Ank1/Gsto1/Kcnab2/Rhag/P2rx7/Mcoln1/Slc36a1/Plcg2/Glrx/Atp2b1/Ptpn6/Micu1/Flna/Scn10a/Atp6v1b2/Slc39a11/Atp6v1a/Abcb8/Slc43a1/Clcn3/Atp6v0a1/Slc25a37/Agtr1a/Rhd/Zfas1/Rangrf/Smdt1/Il4/Rgs2/Atp6v0b/Kel/Dapk1/Ppif/Nedd4/Slc4a8/Atp1b2/Slc38a5/Asic4/Fgf11/Ubash3b/Pde4b/Atp1a3/Ehd3/Atp7a/Slc43a2/Grin2d/Bhlha15/Fkbp1a/Slc12a7/Ppp3r1/Ifngr1/Pcsk9/Bax/Slc22a5/Phb2/Slc39a8/Homer1/Fkbp1b/Atp6v1g1/P2rx1/Stom/Akap5/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050767</t>
@@ -7108,7 +7108,7 @@
     <t xml:space="preserve">364/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Egr2/Sema4b/Kalrn/Arntl/Ache/Picalm/Ldlr/Numb/Trak2/Tbc1d24/Stk25/Dag1/Pias2/Dip2b/Rnf10/Cdkl5/Plag1/Golga4/Rb1/Sh3glb1/Nap1l1/Psen1/Rpl4/Actr2/Ctnnb1/Prpf19/Kifap3/Stau2/Jade2/Syngap1/Ulk2/Cul7/Megf8/Idh2/Srf/Akap5/Trp53/Sema4a/Xrcc5/Ankrd27/Nr1d1/Plxnc1/Vim/Ptprs/Tenm4/Rgs14/Cxcr4/Arhgef2/Apoe/Tgfb1</t>
+    <t xml:space="preserve">Appl2/Picalm/Arhgef2/Ptprs/Tgfb1/Ankrd27/Vim/Cxcr4/Apoe/Tbc1d24/Ldlr/Xrcc5/Kalrn/Ache/Megf8/Dip2b/Arntl/Stk25/Rgs14/Tenm4/Trp53/Dag1/Numb/Pias2/Sema4b/Egr2/Idh2/Cul7/Sema4a/Srf/Ctnnb1/Rnf10/Rb1/Nr1d1/Sh3glb1/Plxnc1/Trak2/Prpf19/Plag1/Psen1/Ulk2/Actr2/Golga4/Cdkl5/Rpl4/Stau2/Syngap1/Jade2/Nap1l1/Kifap3/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0061024</t>
@@ -7120,7 +7120,7 @@
     <t xml:space="preserve">637/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Cd36/Sh3tc2/Appl2/Sptb/Snca/Insig1/Trappc2l/Rubcnl/Dmpk/Picalm/Vps11/Uvrag/Pikfyve/Arhgap12/Epn1/Clcn3/Tmcc1/Wasl/Hace1/Cln8/Lpcat3/Mtch2/Ap3d1/Chmp3/Bax/Exoc8/Bcl2l11/Sorbs1/Bid/Nemp1/Trappc8/Exoc1/Reep5/Arl8b/Tor1aip2/Snap29/Ap2m1/Mia3/Sh3glb1/Uso1/Snx3/Vps4b/Sec61a1/Myh10/Sar1b/Adck1/Timm50/Ppif/Ugcg/Itgb2/Cep55/Abca2/Agk/Akap5/Trp53/Fcgr3/Gata2/Plcg2/Vapa/Pmaip1/Hk2/Ano6/Cplx2/Ankrd27/Rft1/Rac1/Rac2/Cxcr4/Lpcat2/Dock2/Apoe/Col5a1/Laptm5/Sytl4/Emc4/Ptprc/Coro1a/Rftn1/Elmo1/P2rx7</t>
+    <t xml:space="preserve">Spta1/Sh3tc2/Sptb/Dock2/Laptm5/Snca/Appl2/Rftn1/Picalm/Slc4a1/Ptprc/Coro1a/Ano6/Rac2/Emc4/Ankrd27/Rac1/Elmo1/P2rx7/Abca2/Vapa/Vps11/Plcg2/Cxcr4/Epn1/Apoe/Cd36/Ugcg/Pikfyve/Insig1/Col5a1/Mtch2/Pmaip1/Uvrag/Tmcc1/Trp53/Clcn3/Rft1/Hace1/Agk/Lpcat2/Timm50/Sytl4/Myh10/Gata2/Wasl/Trappc2l/Ap3d1/Trappc8/Sh3glb1/Ppif/Dmpk/Arhgap12/Fcgr3/Chmp3/Exoc8/Lpcat3/Reep5/Sar1b/Cep55/Cplx2/Bcl2l11/Itgb2/Arl8b/Ap2m1/Hk2/Rubcnl/Exoc1/Bid/Sec61a1/Adck1/Bax/Sorbs1/Tor1aip2/Vps4b/Mia3/Cln8/Akap5/Snx3/Snap29/Uso1/Nemp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050821</t>
@@ -7129,7 +7129,7 @@
     <t xml:space="preserve">protein stabilization</t>
   </si>
   <si>
-    <t xml:space="preserve">Wdr81/Mfsd1/Grn/Glmp/Tsc1/Lamp1/Pim1/Fbxw7/Usp9x/Nckap1/Ipo9/Sav1/Pex6/Tcf3/Cct6a/Phb2/Cct2/Gtpbp4/Ncln/Hsp90ab1/Crtap/Hspd1/Flna/Trp53/Mtmr9/Atp1b2/Tyrobp</t>
+    <t xml:space="preserve">Mfsd1/Grn/Tsc1/Lamp1/Glmp/Wdr81/Mtmr9/Flna/Fbxw7/Trp53/Usp9x/Ipo9/Tyrobp/Nckap1/Atp1b2/Cct2/Tcf3/Hsp90ab1/Sav1/Hspd1/Ncln/Crtap/Phb2/Gtpbp4/Pex6/Cct6a/Pim1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990138</t>
@@ -7138,7 +7138,7 @@
     <t xml:space="preserve">neuron projection extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Sema4b/Picalm/Dpysl2/Usp9x/Dip2b/C9orf72/Cdkl5/Golga4/Cpne1/Vcl/Cttn/Itsn2/Sh3glb1/Iqgap1/Rpl4/Ctnnb1/Hsp90ab1/Wdr36/Jade2/Ulk2/Megf8/Srf/Unc13a/Sema4a/Ptprs/Cxcr4/Apoe</t>
+    <t xml:space="preserve">Picalm/Ptprs/Cxcr4/Apoe/Megf8/Dip2b/Usp9x/Dpysl2/Sema4b/Sema4a/Srf/Ctnnb1/Sh3glb1/Hsp90ab1/Cpne1/Ulk2/C9orf72/Iqgap1/Golga4/Cdkl5/Rpl4/Wdr36/Unc13a/Jade2/Cttn/Vcl/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043173</t>
@@ -7153,7 +7153,7 @@
     <t xml:space="preserve">regulation of fibroblast apoptotic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Nupr1/Bcl2l11/Bid/Sirt1/Ier3ip1/Trp53/Pmaip1</t>
+    <t xml:space="preserve">Pmaip1/Trp53/Bcl2l11/Ier3ip1/Bid/Sirt1/Nupr1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050775</t>
@@ -7162,7 +7162,7 @@
     <t xml:space="preserve">positive regulation of dendrite morphogenesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalrn/Ache/Numb/Tbc1d24/Pias2/Cdkl5/Sh3glb1/Actr2/Stau2/Cul7/Akap5/Ankrd27</t>
+    <t xml:space="preserve">Ankrd27/Tbc1d24/Kalrn/Ache/Numb/Pias2/Cul7/Sh3glb1/Actr2/Cdkl5/Stau2/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009135</t>
@@ -7174,7 +7174,7 @@
     <t xml:space="preserve">89/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Guk1/Prkag2/Khk/Hk2/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Slc4a1/Pfkfb2/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Pkm/Prkag2/Guk1/Eno3/Hk2/Psen1/Bpgm/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009179</t>
@@ -7189,7 +7189,7 @@
     <t xml:space="preserve">negative regulation of oxidative stress-induced cell death</t>
   </si>
   <si>
-    <t xml:space="preserve">Glrx/Tsc1/Pycr1/Epor/Tbc1d24/Rnf146/Sirt1/Rack1/Nono/Ctnnb1</t>
+    <t xml:space="preserve">Tsc1/Glrx/Tbc1d24/Epor/Rnf146/Nono/Ctnnb1/Sirt1/Pycr1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043066</t>
@@ -7201,7 +7201,7 @@
     <t xml:space="preserve">746/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Prokr1/Btg2/Egr3/Mst1/St3gal1/Slc30a10/Snca/Prdx2/Itsn1/Cited2/Agtr1a/Optn/Tfrc/Grn/Prnp/Hipk2/Nupr1/Stil/Pim1/Gba/Mlst8/Arrb1/Epor/Pea15a/Grk5/Map3k12/Ppard/Grina/Cln8/Sgk3/Hmgcr/Atp7a/Cib1/Ppp1r10/Bax/Kdm2a/Tsc22d1/Birc5/Rictor/Stradb/Bid/Brca1/Mcl1/Rb1/Tsc22d3/Zfand6/Cttn/Sirt1/Rps6kb1/Fnip1/Sh3glb1/Usp47/Qars/Psen1/Nono/Ctnnb1/Kifap3/Pa2g4/Phb2/Gpi1/Armc10/Cbl/Hsp90ab1/Set/Syngap1/Hspd1/Igf1r/Hcls1/Mnt/Prkca/Flna/Stat5a/Ppif/Ccng1/Trp53/Stat5b/Dapk1/Il27ra/Pcgf2/Pdcd4/Gata2/Rgl2/Ago4/Serpinb9/Pim3/Itga5/Dock8/Aldh2/Il4/Apoe/Cd44/Coro1a/Jak3</t>
+    <t xml:space="preserve">Prdx2/Jak3/Snca/Btg2/Coro1a/Prnp/Slc30a10/Prokr1/Mst1/Grn/Aldh2/St3gal1/Cd44/Cpeb4/Dock8/Itsn1/Cited2/Optn/Ccng1/Rgl2/Apoe/Stat5b/Itga5/Pim3/Hipk2/Flna/Ago4/Gba/Mlst8/Kdm2a/Trp53/Egr3/Epor/Agtr1a/Stat5a/Pcgf2/Il4/Stil/Gata2/Pea15a/Grk5/Nono/Ctnnb1/Il27ra/Ppard/Dapk1/Rb1/Sh3glb1/Ppif/Arrb1/Mcl1/Armc10/Serpinb9/Tfrc/Hcls1/Hmgcr/Ppp1r10/Cib1/Prkca/Hsp90ab1/Atp7a/Birc5/Pdcd4/Psen1/Bid/Set/Sirt1/Grina/Zfand6/Hspd1/Fnip1/Bax/Nupr1/Stradb/Brca1/Syngap1/Tsc22d1/Map3k12/Phb2/Mnt/Sgk3/Igf1r/Usp47/Tsc22d3/Cbl/Cttn/Qars/Kifap3/Pim1/Cln8/Pa2g4/Rps6kb1/Rictor/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033674</t>
@@ -7213,7 +7213,7 @@
     <t xml:space="preserve">339/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Wnk4/Map3k1/Snca/Agtr1a/Prnp/Pfkfb2/Nedd9/Als2/Gab1/Traf4/Stil/Cdc25b/Cdc6/Pim1/Mapre3/Fzd5/Map3k12/Fbxw7/Cib1/Dag1/Dvl2/Stradb/Sirt1/Sh3glb1/Abi1/Psen1/Iqgap1/Phb2/Maged1/Dgkz/Hsp90ab1/Igf1r/Pik3r5/Prkag2/Irak1/Vangl2/Xrcc5/Rac1/Mmd/Pik3r6/Il4/Csf1/Tgfb1/Mst1r/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Egr1/Map3k1/Snca/Syk/Ptprc/Wnk4/Prnp/Tgfb1/Rac1/Pfkfb2/Gab1/P2rx7/Als2/Cdc25b/Mst1r/Mmd/Xrcc5/Cdc6/Irak1/Traf4/Fbxw7/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Prkag2/Dgkz/Pik3r6/Maged1/Csf1/Sh3glb1/Vangl2/Dvl2/Cib1/Hsp90ab1/Mapre3/Psen1/Sirt1/Iqgap1/Stradb/Map3k12/Phb2/Abi1/Igf1r/Pim1/Pik3r5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043009</t>
@@ -7225,7 +7225,7 @@
     <t xml:space="preserve">647/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Nfe2/Specc1/Cited2/Grn/Nsrp1/Sox6/Gab1/Tsc1/Adam10/Zfat/Klf1/Stil/Atp6ap2/Epn1/Fzd5/Junb/Coprs/Plcd3/Mxi1/Flcn/Tent5c/Ggnbp2/Usp9x/Dvl2/Rara/Nckap1/Kdm2a/Ttbk2/Luzp1/Nup50/Npat/Mafg/Kdm4c/Bcl2l11/4933434E20Rik/Otud7b/Gnas/Brca1/Tapt1/Ncoa1/Arnt/Gna13/Asxl2/Arhgap35/Nxn/Bnip2/N4bp2l2/Abi1/Setdb1/Tbl1xr1/Psen1/Ctnnb1/Trim28/Gpi1/Dhx35/Ndst1/Myh10/Tcof1/Matr3/Plod3/Ift172/Megf8/Mthfd1/Srf/Prmt1/Tcf7l2/Mthfd1l/Trp53/Vangl2/Pcgf2/Kat2a/Gata2/Ptpn18/Zfp36l1/Tmem231/Arhgdig/Phlda2/Mmp14/Tgfb1/Gdf3/Vash2/Myb</t>
+    <t xml:space="preserve">Cobl/Myb/Tgfb1/Grn/Tsc1/Nfe2/Vash2/Gab1/Klf1/Cited2/Kat2a/Epn1/Adam10/Atp6ap2/Specc1/Gnas/Arnt/Megf8/Arhgdig/Gdf3/Tcof1/Kdm2a/Trp53/Phlda2/Usp9x/Nsrp1/Pcgf2/Nup50/Fzd5/Stil/Myh10/Tapt1/Mxi1/Gata2/Mmp14/Prmt1/Gna13/4933434E20Rik/Srf/Ptpn18/Ggnbp2/Zfp36l1/Ctnnb1/Nckap1/Zfat/Tmem231/Plod3/Npat/Ift172/Vangl2/Matr3/Mthfd1/Dvl2/Mthfd1l/Luzp1/Coprs/Ndst1/Otud7b/Sox6/Bcl2l11/Tent5c/Trim28/Ttbk2/Flcn/Psen1/Kdm4c/Dhx35/Junb/Ncoa1/Rara/Setdb1/Brca1/N4bp2l2/Plcd3/Abi1/Arhgap35/Bnip2/Asxl2/Tbl1xr1/Tcf7l2/Nxn/Mafg/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904951</t>
@@ -7234,7 +7234,7 @@
     <t xml:space="preserve">positive regulation of establishment of protein localization</t>
   </si>
   <si>
-    <t xml:space="preserve">Ptp4a3/Rph3al/Glrx/Prnp/Pfkfb2/Abcg1/Ptpn23/Arrb1/Ppard/Fbxw7/Cib1/Vps35/Brca1/Exoc1/Stom/Sirt1/Sh3glb1/Rack1/Psen1/Trim28/Ipo5/Cct6a/Ergic3/Tm7sf3/Cct2/Hsp90ab1/Myh10/Wipf1/Hcls1/Sar1b/Flna/Ier3ip1/Tcf7l2/Ripor1/Akap5/Arpc2/Pmaip1/Rac1/Tgfb1/Sytl4/P2rx7</t>
+    <t xml:space="preserve">Prnp/Tgfb1/Rph3al/Abcg1/Rac1/Pfkfb2/Ptpn23/P2rx7/Ripor1/Glrx/Arpc2/Flna/Pmaip1/Fbxw7/Ptp4a3/Sytl4/Myh10/Ppard/Vps35/Sh3glb1/Arrb1/Cct2/Hcls1/Wipf1/Sar1b/Ergic3/Cib1/Hsp90ab1/Trim28/Ier3ip1/Exoc1/Psen1/Sirt1/Tm7sf3/Brca1/Ipo5/Cct6a/Tcf7l2/Stom/Rack1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001558</t>
@@ -7243,7 +7243,7 @@
     <t xml:space="preserve">regulation of cell growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Extl3/Dnajb2/Dcbld2/Sema4b/Picalm/Adam10/Sesn1/Dpysl2/Lamtor1/Mlst8/Dact3/Cdkn2c/Cgrrf1/Ppard/Socs2/Dcun1d3/Flcn/Cib1/Ppp1r9b/Dip2b/Cdkl5/Golga4/Rictor/Rb1/Cttn/Sirt1/Adipor2/Itsn2/Sh3glb1/Usp47/Rack1/Rpl4/Ddx49/Wdr36/Eif4g2/Ulk2/Megf8/Srf/Unc13a/Jade1/Trp53/Sema4a/Rgs2/Dnajc2/Ptprs/Cxcr4/Mmp14/Apoe/Tgfb1/Cd44/Igfbp4</t>
+    <t xml:space="preserve">Picalm/Ptprs/Extl3/Igfbp4/Tgfb1/Dcbld2/Dnajc2/Cd44/Cxcr4/Apoe/Jade1/Adam10/Sesn1/Megf8/Dip2b/Mlst8/Trp53/Cdkn2c/Dpysl2/Sema4b/Socs2/Rgs2/Mmp14/Sema4a/Ppp1r9b/Srf/Lamtor1/Dnajb2/Ppard/Rb1/Sh3glb1/Cgrrf1/Cib1/Adipor2/Flcn/Dact3/Ulk2/Sirt1/Golga4/Eif4g2/Cdkl5/Rpl4/Wdr36/Dcun1d3/Unc13a/Usp47/Cttn/Ddx49/Rack1/Rictor/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008285</t>
@@ -7255,7 +7255,7 @@
     <t xml:space="preserve">540/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Btg2/Appl2/Nfe2/Dnajb2/Cited2/Optn/Prnp/Tsc1/Fnip2/Nupr1/Gdf11/Zbtb7b/Trp53inp1/Fzd5/Rnf139/Cdkn2c/Ppard/Foxo4/Flcn/Ggnbp2/Cib1/Tob1/Bax/Rnf10/Rara/Rb1/Gna13/Sav1/Fnip1/Celf1/Ctcf/Ctnnb1/Cnot7/Wdr77/Kifap3/Phb2/Trim35/Gtpbp4/Maged1/Smyd2/Ptpru/Ift172/Prkca/Prdx4/Rps6ka2/Idh2/Srf/Vsir/Trp53/Ptpn6/Pdcd4/Gata2/Pmaip1/Zfas1/Cd37/Ripor2/Havcr2/Tfap4/Il4/Lgals9/Spn/Apoe/Lgals7/Tgfb1/Cd44/Laptm5/Tyrobp/Btk/Cdk6/Il1rl1/Eng</t>
+    <t xml:space="preserve">Btk/Laptm5/Appl2/Il1rl1/Btg2/Prnp/Tgfb1/Cdk6/Spn/Tsc1/Nfe2/Cd44/Ripor2/Fnip2/Cited2/Eng/Lgals9/Optn/Apoe/Ptpn6/Tfap4/Pmaip1/Gdf11/Trp53/Cdkn2c/Rnf139/Zbtb7b/Idh2/Zfas1/Trp53inp1/Tyrobp/Fzd5/Il4/Gata2/Lgals7/Cd37/Gna13/Srf/Ggnbp2/Maged1/Ctnnb1/Dnajb2/Rnf10/Ppard/Rb1/Ift172/Havcr2/Celf1/Tob1/Cib1/Prkca/Prdx4/Rps6ka2/Flcn/Pdcd4/Vsir/Sav1/Fnip1/Rara/Bax/Nupr1/Trim35/Phb2/Foxo4/Gtpbp4/Smyd2/Ptpru/Wdr77/Ctcf/Cnot7/Kifap3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070664</t>
@@ -7270,7 +7270,7 @@
     <t xml:space="preserve">negative regulation of myeloid cell differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Ubash3b/Fbxw7/Cib1/Rara/Ctnnb1/Ldb1/Prmt1/Stat5a/Lmo2/Stat5b/Gata2/Zfp36l1/Il4/Cdk6</t>
+    <t xml:space="preserve">Cdk6/Stat5b/Fbxw7/Ldb1/Stat5a/Il4/Gata2/Lmo2/Prmt1/Zfp36l1/Ctnnb1/Cib1/Ubash3b/Rara</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009311</t>
@@ -7279,7 +7279,7 @@
     <t xml:space="preserve">oligosaccharide metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal6/Neu1/St3gal2/Man2b1/St6galnac4/Gla/Man2c1/Man2b2/Fut4</t>
+    <t xml:space="preserve">Man2b2/Neu1/Fut4/Man2c1/Man2b1/St3gal6/Gla/St3gal2/St6galnac4</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034220</t>
@@ -7294,7 +7294,7 @@
     <t xml:space="preserve">711/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Mink1/Wnk4/Ank1/Slc25a37/Atp6v0d1/Rhag/Slc30a10/Abcb6/Scn10a/Snca/Agtr1a/Slc36a1/Asic4/Mcoln1/Glrx/Prnp/Slc43a1/Atp6v1e1/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Clcn3/Bhlha15/Atp2b1/Smdt1/Atp6v1a/Cln8/Atp6v1b2/Atp7a/Slc38a5/Fgf11/Bax/Xpr1/Atp6v0b/Slc12a7/Lrrc8a/Stom/Atp6v1g1/Slc39a8/Slc25a11/Homer1/Grk6/Gpr89/Psen1/Nedd4/Ppp3r1/Gopc/Phb2/Slc25a30/Pde4d/Ifngr1/Fkbp1a/Prkca/Slc22a5/P2rx1/Flna/Tmem109/Ppif/Fkbp1b/Ehd3/Pcsk9/Slc43a2/Akap5/Dapk1/Abcb8/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Ano6/Zfas1/Grin2d/Rangrf/Pde4b/Rgs2/Clic1/Slc39a11/Kcnab2/Slc19a1/Il4/Gsto1/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Atp6v0d1/Snca/Ptprc/Wnk4/Mink1/Coro1a/Ano6/Abcb6/Slc6a9/Prnp/Tgfb1/Slc30a10/Slc11a2/Atp6v1e1/Ank1/Gsto1/Kcnab2/Clic1/Rhag/P2rx7/Mcoln1/Slc36a1/Plcg2/Glrx/Atp2b1/Ptpn6/Micu1/Flna/Xpr1/Scn10a/Atp6v1b2/Slc39a11/Atp6v1a/Abcb8/Slc43a1/Clcn3/Atp6v0a1/Slc25a37/Slc19a1/Agtr1a/Rhd/Zfas1/Rangrf/Smdt1/Il4/Rgs2/Atp6v0b/Kel/Dapk1/Lrrc8a/Ppif/Nedd4/Slc4a8/Atp1b2/Slc38a5/Asic4/Fgf11/Prkca/Ubash3b/Pde4b/Atp1a3/Ehd3/Atp7a/Slc43a2/Tmem109/Grin2d/Psen1/Bhlha15/Slc25a30/Fkbp1a/Slc12a7/Ppp3r1/Ifngr1/Pcsk9/Bax/Slc22a5/Phb2/Slc39a8/Homer1/Fkbp1b/Slc25a11/Atp6v1g1/P2rx1/Grk6/Stom/Gpr89/Cln8/Akap5/Gopc/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050730</t>
@@ -7303,7 +7303,7 @@
     <t xml:space="preserve">regulation of peptidyl-tyrosine phosphorylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Dmtn/Prnp/Nedd9/Mlst8/Fbxw7/Ggnbp2/Ppp2r5b/Dvl2/Rap2b/Rictor/Abi1/Psen1/Iqgap1/Cnot7/Cbl/Hcls1/Prkca/Samsn1/Itgb2/Rap2c/Trp53/Ptpn6/Plcg2/Lrrk1/Itga5/Il4/Arhgef2/Tgfb1/Cd44/Ptprc/Syk</t>
+    <t xml:space="preserve">Syk/Arhgef2/Ptprc/Prnp/Tgfb1/Dmtn/Cd44/Plcg2/Cd36/Ptpn6/Itga5/Lrrk1/Fbxw7/Rap2b/Mlst8/Trp53/Nedd9/Il4/Rap2c/Ggnbp2/Dvl2/Hcls1/Itgb2/Prkca/Psen1/Iqgap1/Samsn1/Abi1/Cbl/Ppp2r5b/Cnot7/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032689</t>
@@ -7312,7 +7312,7 @@
     <t xml:space="preserve">negative regulation of interferon-gamma production</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Rara/Vsir/Havcr2/Lgals9/Lgals7/Laptm5/Il1rl1</t>
+    <t xml:space="preserve">Laptm5/Il1rl1/Prnp/Lgals9/Lgals7/Havcr2/Vsir/Rara</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051099</t>
@@ -7321,7 +7321,7 @@
     <t xml:space="preserve">positive regulation of binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Add2/Hipk2/Epb41/H1f0/Map1lc3b/Ticam1/Mapre3/Arrb1/Usp9x/Rara/Rb1/Acd/Psen1/Parp1/Ctnnb1/Trim28/Hsp90ab1/Dtx3l/Tcf7l2/Ripor1/Aktip/Ripor2/Lgals9/Apoe/Tgfb1</t>
+    <t xml:space="preserve">Spta1/Add2/Tgfb1/Ripor2/Ripor1/Lgals9/Apoe/Map1lc3b/Hipk2/H1f0/Epb41/Usp9x/Ticam1/Ctnnb1/Rb1/Aktip/Arrb1/Dtx3l/Hsp90ab1/Trim28/Mapre3/Psen1/Acd/Rara/Parp1/Tcf7l2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030879</t>
@@ -7333,7 +7333,7 @@
     <t xml:space="preserve">97/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Kalrn/Fasn/Zbtb7b/Socs2/Bax/Bcl2l11/Arhgap35/Phb2/Lrp5/Aprt/Igf1r/Stat5a/Stat5b/Zfas1/Csf1/Tgfb1/Oas2</t>
+    <t xml:space="preserve">Tgfb1/Mst1/Oas2/Stat5b/Fasn/Kalrn/Zbtb7b/Socs2/Zfas1/Stat5a/Csf1/Lrp5/Bcl2l11/Bax/Aprt/Phb2/Arhgap35/Igf1r</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0003682</t>
@@ -7345,7 +7345,7 @@
     <t xml:space="preserve">541/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Egr2/Tal1/Ttc39aos1/Cited2/Chd2/H1f0/Fos/Nupr1/Wbp2/Zfp143/Cdc6/Mbd6/Slc30a9/Foxo4/Ccnt1/Polg/Pknox1/Rara/Rnf168/Polr2a/Phc3/Mkrn1/Ash1l/Orc1/Brca1/Elk1/Ncoa1/Fancm/Morc2a/Ticrr/Asxl2/Atad2b/Sirt1/Kat6a/Ctcf/Setdb1/Brd3/Nap1l1/Parp1/Nono/Ctnnb1/Tcf3/Trim28/Nucks1/Rcc1/Set/Ldb1/Ruvbl2/Polr1a/Mllt6/Mnt/Srf/Glyr1/Smarcd1/Lmo2/Tcf7l2/Dnmt3b/Trp53/Stat5b/Hp1bp3/Pcgf2/Kat2a/Nfia/Gata2/Npm3/Fli1/Meiob/Dnajc2/Spi1/Hdac7</t>
+    <t xml:space="preserve">Hdac7/Egr1/Dnajc2/Tal1/Spi1/Hp1bp3/Cited2/Fli1/Glyr1/Slc30a9/Npm3/Kat2a/Wbp2/Stat5b/Nfia/Cdc6/H1f0/Chd2/Dnmt3b/Polr2a/Smarcd1/Polg/Trp53/Ttc39aos1/Zfp143/Mbd6/Ldb1/Egr2/Mllt6/Pcgf2/Gata2/Lmo2/Ccnt1/Srf/Pknox1/Nono/Ctnnb1/Rnf168/Morc2a/Ruvbl2/Polr1a/Ticrr/Meiob/Nucks1/Tcf3/Trim28/Atad2b/Elk1/Orc1/Set/Rcc1/Sirt1/Fos/Ash1l/Brd3/Fancm/Ncoa1/Rara/Nupr1/Setdb1/Brca1/Kat6a/Mnt/Foxo4/Ctcf/Asxl2/Parp1/Tcf7l2/Mkrn1/Nap1l1/Phc3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0120039</t>
@@ -7354,7 +7354,7 @@
     <t xml:space="preserve">plasma membrane bounded cell projection morphogenesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Mink1/Egr2/Map1a/Sema4b/Kalrn/Als2/Ache/Picalm/Adam10/Slc11a2/Numb/Kel/Dpysl2/Trak2/Tbc1d24/Wasl/Kif13b/Atp7a/Xk/Usp9x/Stk25/Dag1/Pias2/Dip2b/C9orf72/Cdkl5/Nckap1/Golga4/Myo9a/Arhgap35/Cpne1/Vcl/Cttn/Snx2/Itsn2/Taok1/Sh3glb1/Abi1/Psen1/Iqgap1/Rpl4/Actr2/Ctnnb1/Nedd4/Hsp90ab1/Wdr36/Stau2/Jade2/Myh10/Mov10/Syngap1/Ulk2/Cul7/Igf1r/Prkca/Megf8/Srf/Unc13a/Akap5/Vangl2/Sema4a/Ankrd27/Rac1/Plxnc1/Rac2/Vim/Ptprs/Cxcr4/Apoe/Cd44</t>
+    <t xml:space="preserve">Cobl/Picalm/Ptprs/Mink1/Rac2/Slc11a2/Ankrd27/Cd44/Rac1/Vim/Cxcr4/Als2/Apoe/Adam10/Tbc1d24/Kalrn/Ache/Megf8/Dip2b/Stk25/Map1a/Usp9x/Dag1/Dpysl2/Numb/Pias2/Sema4b/Egr2/Xk/Myh10/Cul7/Wasl/Sema4a/Srf/Ctnnb1/Nckap1/Kel/Sh3glb1/Vangl2/Nedd4/Plxnc1/Mov10/Trak2/Prkca/Hsp90ab1/Atp7a/Psen1/Kif13b/Cpne1/Snx2/Ulk2/C9orf72/Actr2/Taok1/Iqgap1/Golga4/Cdkl5/Rpl4/Stau2/Syngap1/Wdr36/Abi1/Arhgap35/Unc13a/Igf1r/Jade2/Cttn/Akap5/Myo9a/Vcl/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010562</t>
@@ -7363,7 +7363,7 @@
     <t xml:space="preserve">positive regulation of phosphorus metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Cd36/Wnk4/Map3k1/Snca/Agtr1a/Tfrc/Prnp/Pfkfb2/Hipk2/Nedd9/Als2/Gab1/Traf4/Fnip2/Gdf11/Pcx/Stil/Cdc25b/Cdc6/Pim1/Ppp1r15b/Mapre3/Gba/Mlst8/Arrb1/Fzd5/Ppp2r5a/Map3k12/Fbxw7/Mob3c/Flcn/Cib1/Dag1/Dvl2/Rap2b/Birc5/Rictor/Stradb/Gnas/Sirt1/Adipor2/Fnip1/Sh3glb1/Abi1/Rack1/Psen1/Iqgap1/Phb2/Maged1/Pde4d/Dgkz/Hsp90ab1/Igf1r/Hcls1/Prkca/Pik3r5/Rap2c/Prkag2/Fzd7/Akap5/Trp53/Aktip/Irak1/Mtmr9/Vangl2/Xrcc5/Plcg2/Lrrk1/Mob3b/Itga5/Rac1/Mmd/Pik3r6/Il4/Csf1/Cxcr4/Lgals9/Arhgef2/Spn/Tgfb1/Cd44/Gdf3/Mst1r/Ptprc/P2rx7/Syk/Eng</t>
+    <t xml:space="preserve">Egr1/Map3k1/Snca/Syk/Arhgef2/Ptprc/Wnk4/Prnp/Tgfb1/Spn/Cd44/Rac1/Fnip2/Pfkfb2/Gab1/Ppp2r5a/Eng/P2rx7/Plcg2/Lgals9/Cxcr4/Als2/Cdc25b/Mst1r/Cd36/Mtmr9/Mmd/Xrcc5/Itga5/Hipk2/Gnas/Lrrk1/Cdc6/Pcx/Irak1/Traf4/Fbxw7/Rap2b/Gba/Mlst8/Gdf3/Gdf11/Mob3b/Trp53/Dag1/Nedd9/Agtr1a/Fzd5/Il4/Stil/Rap2c/Prkag2/Dgkz/Fzd7/Ppp1r15b/Pik3r6/Maged1/Csf1/Aktip/Sh3glb1/Arrb1/Vangl2/Dvl2/Tfrc/Hcls1/Cib1/Prkca/Hsp90ab1/Adipor2/Flcn/Mapre3/Birc5/Psen1/Sirt1/Iqgap1/Fnip1/Stradb/Map3k12/Phb2/Abi1/Igf1r/Mob3c/Rack1/Pim1/Akap5/Pik3r5/Pde4d/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045937</t>
@@ -7378,7 +7378,7 @@
     <t xml:space="preserve">negative regulation of adaptive immune response</t>
   </si>
   <si>
-    <t xml:space="preserve">Zbtb7b/Samsn1/Vsir/Ptpn6/Il27ra/Havcr2/Il4/Spn/Ptprc/Jak3/Il1rl1</t>
+    <t xml:space="preserve">Jak3/Il1rl1/Ptprc/Spn/Ptpn6/Zbtb7b/Il4/Il27ra/Havcr2/Vsir/Samsn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055038</t>
@@ -7387,7 +7387,7 @@
     <t xml:space="preserve">recycling endosome membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Tfrc/Atg9a/Ldlr/Clcn3/Ehd1/Rap2b/Ehd3/Rap2c/Fzd7/Cmtm6/Rac1</t>
+    <t xml:space="preserve">Rac1/Ldlr/Cmtm6/Atg9a/Rap2b/Ehd1/Clcn3/Rap2c/Fzd7/Tfrc/Ehd3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032479</t>
@@ -7396,7 +7396,7 @@
     <t xml:space="preserve">regulation of type I interferon production</t>
   </si>
   <si>
-    <t xml:space="preserve">Atg9a/Ticam1/Trim56/Tbk1/Ppm1b/Dhx33/Hspd1/Traf3/Ifih1/Irak1/Plcg2/Havcr2/Irf5/Ptprs/Rnf125/Syk/Oas2</t>
+    <t xml:space="preserve">Syk/Ptprs/Oas2/Plcg2/Rnf125/Irak1/Atg9a/Tbk1/Irf5/Trim56/Traf3/Ticam1/Havcr2/Dhx33/Ifih1/Hspd1/Ppm1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002888</t>
@@ -7405,7 +7405,7 @@
     <t xml:space="preserve">positive regulation of myeloid leukocyte mediated immunity</t>
   </si>
   <si>
-    <t xml:space="preserve">Ticam1/Ddx21/Itgb2/Fcgr3/Spi1/Tyrobp</t>
+    <t xml:space="preserve">Spi1/Ticam1/Tyrobp/Fcgr3/Itgb2/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007039</t>
@@ -7420,7 +7420,7 @@
     <t xml:space="preserve">calyx of Held</t>
   </si>
   <si>
-    <t xml:space="preserve">Itsn1/Prkca/Unc13a/Atp1a3/Cplx2/Tspoap1</t>
+    <t xml:space="preserve">Tspoap1/Itsn1/Cplx2/Prkca/Atp1a3/Unc13a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0099512</t>
@@ -7432,7 +7432,7 @@
     <t xml:space="preserve">722/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cobl/Fhdc1/Mid1ip1/Narf/Tmod1/Map3k1/Ank1/Dmtn/Specc1/Snca/Map1a/Mdm1/Tsc1/Ninl/Vps11/Cltc/Map1lc3b/Actn1/Dpysl2/Mybpc3/Mapre3/Arfgef2/Ppp2r5a/Myo6/Wasl/Tuba1a/Kif13b/Habp4/Ska2/Chmp3/Dag1/Nckap1/Dyrk1a/Gabarap/Birc5/Camsap2/Myo9a/Ddx6/Bcl2l11/Twf1/Cep57/Togaram1/Vcl/Cttn/Homer1/Fbxw11/Psen1/Iqgap1/Rpl4/Ctnnb1/Was/Cct6a/Kifap3/Cct2/Pde4d/Haus4/Fkbp1a/Stau2/Tnni3/Myh10/Wipf1/Hcls1/Lman1/Sptan1/Slain2/Flna/Fkbp1b/Kif1c/Arpc2/Pdlim2/Lrrc49/Pde4b/Kif21b/Des/Rac1/Rcc2/Rac2/Col11a2/Kcnab2/Vim/Rgs14/Arhgef2/Ltbp4/Apoe/Iffo1/Col5a1/Adamts10/Coro1a/Dnah8/Lcp1</t>
+    <t xml:space="preserve">Narf/Fhdc1/Cobl/Map3k1/Snca/Dnah8/Arhgef2/Slc4a1/Mid1ip1/Coro1a/Tmod1/Rac2/Cltc/Tsc1/Dmtn/Ank1/Rac1/Ninl/Kcnab2/Rcc2/Ppp2r5a/Iffo1/Actn1/Mdm1/Kif21b/Lcp1/Vps11/Vim/Arfgef2/Arpc2/Adamts10/Apoe/Map1lc3b/Ltbp4/Col5a1/Dyrk1a/Specc1/Flna/Des/Lman1/Kif1c/Rgs14/Map1a/Myo6/Dag1/Gabarap/Dpysl2/Ddx6/Habp4/Col11a2/Tuba1a/Myh10/Wasl/Ctnnb1/Nckap1/Slain2/Twf1/Togaram1/Lrrc49/Camsap2/Chmp3/Cct2/Hcls1/Wipf1/Sptan1/Cep57/Bcl2l11/Pde4b/Mapre3/Birc5/Psen1/Kif13b/Pdlim2/Fkbp1a/Tnni3/Iqgap1/Rpl4/Stau2/Homer1/Fkbp1b/Cct6a/Fbxw11/Cttn/Kifap3/Myo9a/Haus4/Ska2/Vcl/Pde4d/Mybpc3/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002323</t>
@@ -7447,7 +7447,7 @@
     <t xml:space="preserve">oxidoreductase activity, acting on the CH-NH group of donors, NAD or NADP as acceptor</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldh1l2/Pycr1/Pycr2/Mthfd1/Mthfd1l</t>
+    <t xml:space="preserve">Aldh1l2/Mthfd1/Mthfd1l/Pycr1/Pycr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048143</t>
@@ -7456,7 +7456,7 @@
     <t xml:space="preserve">astrocyte activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Grn/Ldlr/Psen1/Ifngr1/Nr1d1</t>
+    <t xml:space="preserve">Grn/Ldlr/Nr1d1/Psen1/Ifngr1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070508</t>
@@ -7465,7 +7465,7 @@
     <t xml:space="preserve">cholesterol import</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ldlr/Stard4/Lamtor1/Scp2</t>
+    <t xml:space="preserve">Stard4/Cd36/Ldlr/Lamtor1/Scp2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0140036</t>
@@ -7474,7 +7474,7 @@
     <t xml:space="preserve">ubiquitin-dependent protein binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Dnajb2/Usp15/Ankrd13b/Dnajc2/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Dnajc2/Ankrd13b/Dnajb2/Usp15</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005798</t>
@@ -7483,7 +7483,7 @@
     <t xml:space="preserve">Golgi-associated vesicle</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam10/Cltc/Nrgn/Igf2r/Tmem199/Atp7a/Gnas/Pi4ka/Gpr89/Actr1a/Gopc/Copg2/Use1/Ap1g1/Unc13a/Tmed3</t>
+    <t xml:space="preserve">Cltc/Adam10/Igf2r/Gnas/Tmed3/Ap1g1/Copg2/Nrgn/Actr1a/Tmem199/Atp7a/Unc13a/Use1/Gpr89/Gopc/Pi4ka</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031110</t>
@@ -7492,7 +7492,7 @@
     <t xml:space="preserve">regulation of microtubule polymerization or depolymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid1ip1/Snca/Map1a/Mapre3/Ska2/Cib1/Ttbk2/Dyrk1a/Camsap2/Togaram1/Taok1/Slain2/Rangrf/Rac1/Fes/Arhgef2</t>
+    <t xml:space="preserve">Snca/Arhgef2/Mid1ip1/Rac1/Dyrk1a/Map1a/Rangrf/Fes/Slain2/Togaram1/Camsap2/Cib1/Ttbk2/Mapre3/Taok1/Ska2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006893</t>
@@ -7501,7 +7501,7 @@
     <t xml:space="preserve">Golgi to plasma membrane transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Optn/Gga2/Arfgef2/Rabep1/Ccdc93/Exoc8/Golga4/Exoc1/Rack1/Gopc/Vamp5/Lypla1</t>
+    <t xml:space="preserve">Gga2/Lypla1/Optn/Arfgef2/Vamp5/Rabep1/Ccdc93/Exoc8/Exoc1/Golga4/Rack1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045309</t>
@@ -7510,7 +7510,7 @@
     <t xml:space="preserve">protein phosphorylated amino acid binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Grap2/Arrb1/Fbxw7/Shb/Scaf4/Nedd4/Cbl/Samsn1/Ptpn6/Plcg2/Vav1/Syk</t>
+    <t xml:space="preserve">Syk/Vav1/Plcg2/Ptpn6/Grap2/Fbxw7/Arrb1/Nedd4/Samsn1/Scaf4/Cbl/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0055067</t>
@@ -7519,7 +7519,7 @@
     <t xml:space="preserve">monovalent inorganic cation homeostasis</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Car2/Atp6v0d1/Rhag/Agtr1a/Grn/Atp6v0a1/Rhd/Atp6ap2/Vps33a/Tmem199/Atp6v1b2/Mafg/Slc12a7/Gnas/Gpr89/Mllt6/Snx5/Trp53/Slc4a8/Atp1b2/Atp1a3</t>
+    <t xml:space="preserve">Car2/Atp6v0d1/Slc4a1/Grn/Rhag/Atp6ap2/Gnas/Atp6v1b2/Trp53/Atp6v0a1/Agtr1a/Rhd/Mllt6/Vps33a/Slc4a8/Atp1b2/Snx5/Tmem199/Atp1a3/Slc12a7/Gpr89/Mafg</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010586</t>
@@ -7528,7 +7528,7 @@
     <t xml:space="preserve">miRNA metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Zswim8/Fos/Ppard/Rara/Ago2/Tut7/Ctcf/Parn/Srf/Trp53/Gata2/Ago4/Tgfb1/Spi1</t>
+    <t xml:space="preserve">Egr1/Tgfb1/Spi1/Zswim8/Ago4/Trp53/Gata2/Srf/Ppard/Fos/Rara/Ago2/Tut7/Ctcf/Parn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031343</t>
@@ -7540,7 +7540,7 @@
     <t xml:space="preserve">62/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Lamp1/Bcl2l11/Ap1g1/Stat5a/Stat5b/Vav1/Cadm1/Spi1/Tyrobp/Ptprc/P2rx7/Syk</t>
+    <t xml:space="preserve">Syk/Ptprc/Lamp1/Spi1/Vav1/P2rx7/Stat5b/Ap1g1/H2-T23/Tyrobp/Stat5a/Bcl2l11/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034394</t>
@@ -7549,7 +7549,7 @@
     <t xml:space="preserve">protein localization to cell surface</t>
   </si>
   <si>
-    <t xml:space="preserve">Map1a/Picalm/Gga2/Vcl/Ctnnb1/Gopc/Ptpru/Hsp90ab1/Flna/Abca2/Rangrf/Kcnab2/Tyrobp</t>
+    <t xml:space="preserve">Picalm/Gga2/Kcnab2/Abca2/Flna/Map1a/Rangrf/Tyrobp/Ctnnb1/Hsp90ab1/Ptpru/Vcl/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042982</t>
@@ -7558,7 +7558,7 @@
     <t xml:space="preserve">amyloid precursor protein metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Abcg1/Tmcc2/Picalm/Adam10/Dyrk1a/Ago2/Psen1/Ifngr1/Itm2c/Abca2/Unc13a/Apoe</t>
+    <t xml:space="preserve">Picalm/Prnp/Abcg1/Abca2/Apoe/Adam10/Dyrk1a/Tmcc2/Psen1/Ifngr1/Itm2c/Ago2/Unc13a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048598</t>
@@ -7567,7 +7567,7 @@
     <t xml:space="preserve">embryonic morphogenesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Aldh1a1/Tal1/Cited2/Insig1/Hipk2/Tsc1/Stil/Fzd5/Myo6/Dag1/Bax/Dvl2/Rara/Nckap1/Kdm2a/Ttbk2/Luzp1/Nup50/Bcl2l11/Gnas/Tnrc6c/Ncoa1/Acd/Asxl2/Arhgap35/Rack1/Psen1/Ctnnb1/Tcf3/Trim28/Lrp5/Gpi1/Ndst1/Ldb1/Ift172/Megf8/Mthfd1/Tshz1/Srf/Fzd7/Tcf7l2/Mthfd1l/Trp53/Vangl2/Pcgf2/Kat2a/Gata2/Zfp36l1/Tmem231/Itga5/Rac1/Ripor2/Tenm4/Mmp14/Aff3/Tgfb1/Col5a1/Gdf3/Eng</t>
+    <t xml:space="preserve">Cobl/Aldh1a1/Tgfb1/Tal1/Tsc1/Rac1/Ripor2/Cited2/Eng/Kat2a/Aff3/Insig1/Col5a1/Itga5/Hipk2/Gnas/Megf8/Gdf3/Tenm4/Kdm2a/Trp53/Myo6/Dag1/Ldb1/Pcgf2/Nup50/Fzd5/Stil/Gata2/Tshz1/Mmp14/Fzd7/Srf/Zfp36l1/Ctnnb1/Nckap1/Tmem231/Ift172/Vangl2/Mthfd1/Dvl2/Mthfd1l/Luzp1/Ndst1/Lrp5/Bcl2l11/Tcf3/Trim28/Ttbk2/Psen1/Acd/Ncoa1/Rara/Bax/Arhgap35/Asxl2/Tnrc6c/Tcf7l2/Rack1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902600</t>
@@ -7579,7 +7579,7 @@
     <t xml:space="preserve">69/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Slc36a1/Atp6v1e1/Atp6v0a1/Clcn3/Atp6v1a/Atp6v1b2/Atp7a/Atp6v0b/Atp6v1g1/Phb2/Ppif/Atp1a3/Il4</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1e1/Slc36a1/Atp6v1b2/Atp6v1a/Clcn3/Atp6v0a1/Il4/Atp6v0b/Ppif/Atp1a3/Atp7a/Phb2/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0072657</t>
@@ -7588,7 +7588,7 @@
     <t xml:space="preserve">protein localization to membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ank1/Dmtn/Tspan33/Optn/Prnp/Kalrn/Picalm/Adam10/Cltc/Gga2/Numb/Pikfyve/Rab3ip/Ppp2r5a/Rabep1/Cib1/Mtch2/Ap3d1/Ppp1r9b/Dag1/Bax/Ehd1/Golga4/Vps35/Gripap1/Sorbs1/Bid/Pacs2/Stom/Ap2m1/Sav1/Sh3glb1/Sec62/Rack1/Sec61a1/Gorasp2/Gopc/Ttc7b/Scp2/Lztfl1/Pgrmc1/Atad1/Syngap1/Flna/Ptpn9/Ehd3/Itgb2/Zdhhc23/Sh3pxd2b/Lin7c/Agk/Akap5/Arpc2/Pmaip1/Pgap2/Zdhhc21/Rangrf/Frmpd1/Vamp5/Rac1/Lypla1/Mmp14/Apoe/Tgfb1/Fyb/Emc4/Rftn1</t>
+    <t xml:space="preserve">Rftn1/Picalm/Slc4a1/Prnp/Tgfb1/Emc4/Cltc/Dmtn/Ank1/Fyb/Tspan33/Rac1/Gga2/Lypla1/Ppp2r5a/Zdhhc21/Optn/Vamp5/Arpc2/Apoe/Rabep1/Adam10/Lin7c/Pikfyve/Kalrn/Flna/Mtch2/Pmaip1/Pgap2/Ehd1/Pacs2/Sh3pxd2b/Dag1/Numb/Agk/Rangrf/Rab3ip/Atad1/Mmp14/Ppp1r9b/Ptpn9/Ap3d1/Vps35/Sh3glb1/Gorasp2/Frmpd1/Cib1/Itgb2/Ehd3/Ap2m1/Bid/Sec61a1/Sav1/Pgrmc1/Golga4/Bax/Scp2/Ttc7b/Syngap1/Lztfl1/Sorbs1/Gripap1/Sec62/Stom/Rack1/Akap5/Gopc/Zdhhc23</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098662</t>
@@ -7597,7 +7597,7 @@
     <t xml:space="preserve">inorganic cation transmembrane transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Wnk4/Ank1/Slc25a37/Atp6v0d1/Rhag/Slc30a10/Abcb6/Scn10a/Snca/Agtr1a/Slc36a1/Asic4/Mcoln1/Glrx/Prnp/Atp6v1e1/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Clcn3/Bhlha15/Atp2b1/Smdt1/Atp6v1a/Atp6v1b2/Atp7a/Fgf11/Bax/Atp6v0b/Slc12a7/Stom/Atp6v1g1/Slc39a8/Nedd4/Ppp3r1/Phb2/Pde4d/Fkbp1a/P2rx1/Flna/Ppif/Fkbp1b/Ehd3/Pcsk9/Akap5/Abcb8/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Ano6/Zfas1/Grin2d/Rangrf/Pde4b/Slc39a11/Kcnab2/Il4/Gsto1/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Atp6v0d1/Snca/Ptprc/Wnk4/Coro1a/Ano6/Abcb6/Slc6a9/Prnp/Tgfb1/Slc30a10/Slc11a2/Atp6v1e1/Ank1/Gsto1/Kcnab2/Rhag/P2rx7/Mcoln1/Slc36a1/Plcg2/Glrx/Atp2b1/Ptpn6/Micu1/Flna/Scn10a/Atp6v1b2/Slc39a11/Atp6v1a/Abcb8/Clcn3/Atp6v0a1/Slc25a37/Agtr1a/Rhd/Zfas1/Rangrf/Smdt1/Il4/Atp6v0b/Kel/Ppif/Nedd4/Slc4a8/Atp1b2/Asic4/Fgf11/Ubash3b/Pde4b/Atp1a3/Ehd3/Atp7a/Grin2d/Bhlha15/Fkbp1a/Slc12a7/Ppp3r1/Pcsk9/Bax/Phb2/Slc39a8/Fkbp1b/Atp6v1g1/P2rx1/Stom/Akap5/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008202</t>
@@ -7606,7 +7606,7 @@
     <t xml:space="preserve">steroid metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Dhrs11/Fech/Agtr1a/Pip4p1/Scd1/Insig1/Abcg1/Mvd/Ldlr/Msmo1/Stard4/Lss/Sqle/Lamtor1/Gba/Cln8/Hmgcr/Lpcat3/Pmvk/Sc5d/Cyb5r3/Sirt1/Sgpl1/Lrp5/Scp2/Igf1r/Stat5a/Pcsk9/Abca2/Stat5b/H6pd/Hsd17b11/Nr1d1/Il4/Apoe</t>
+    <t xml:space="preserve">Egr1/Fech/Abcg1/Pip4p1/Dhrs11/Stard4/Abca2/Apoe/Stat5b/Ldlr/Insig1/Sqle/Gba/Msmo1/Agtr1a/Scd1/Mvd/Stat5a/Il4/H6pd/Hsd17b11/Lamtor1/Lss/Nr1d1/Hmgcr/Lpcat3/Lrp5/Cyb5r3/Sirt1/Sc5d/Pcsk9/Scp2/Igf1r/Pmvk/Sgpl1/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098660</t>
@@ -7618,7 +7618,7 @@
     <t xml:space="preserve">553/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Wnk4/Ank1/Slc25a37/Atp6v0d1/Rhag/Slc30a10/Abcb6/Scn10a/Snca/Agtr1a/Slc36a1/Asic4/Mcoln1/Glrx/Prnp/Atp6v1e1/Slc11a2/Atp6v0a1/Rhd/Kel/Ubash3b/Micu1/Clcn3/Bhlha15/Atp2b1/Smdt1/Atp6v1a/Atp6v1b2/Atp7a/Fgf11/Bax/Xpr1/Atp6v0b/Slc12a7/Lrrc8a/Stom/Atp6v1g1/Slc39a8/Slc25a11/Nedd4/Ppp3r1/Phb2/Slc25a30/Pde4d/Fkbp1a/P2rx1/Flna/Ppif/Fkbp1b/Ehd3/Pcsk9/Akap5/Abcb8/Slc4a8/Ptpn6/Atp1b2/Plcg2/Atp1a3/Ano6/Zfas1/Grin2d/Rangrf/Pde4b/Slc39a11/Kcnab2/Il4/Gsto1/Tgfb1/Ptprc/Coro1a/P2rx7</t>
+    <t xml:space="preserve">Atp6v0d1/Snca/Ptprc/Wnk4/Coro1a/Ano6/Abcb6/Slc6a9/Prnp/Tgfb1/Slc30a10/Slc11a2/Atp6v1e1/Ank1/Gsto1/Kcnab2/Rhag/P2rx7/Mcoln1/Slc36a1/Plcg2/Glrx/Atp2b1/Ptpn6/Micu1/Flna/Xpr1/Scn10a/Atp6v1b2/Slc39a11/Atp6v1a/Abcb8/Clcn3/Atp6v0a1/Slc25a37/Agtr1a/Rhd/Zfas1/Rangrf/Smdt1/Il4/Atp6v0b/Kel/Lrrc8a/Ppif/Nedd4/Slc4a8/Atp1b2/Asic4/Fgf11/Ubash3b/Pde4b/Atp1a3/Ehd3/Atp7a/Grin2d/Bhlha15/Slc25a30/Fkbp1a/Slc12a7/Ppp3r1/Pcsk9/Bax/Phb2/Slc39a8/Fkbp1b/Slc25a11/Atp6v1g1/P2rx1/Stom/Akap5/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098609</t>
@@ -7627,7 +7627,7 @@
     <t xml:space="preserve">cell-cell adhesion</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Spta1/Mink1/Egr3/Add2/Dmtn/Cd47/Prdx2/Cited2/Tfrc/Prnp/Ptpn23/Zbtb7b/Ubash3b/Icam5/Ap3d1/Shb/Rara/Fcho1/Rap2b/Nck1/Gnas/Swap70/Slc39a8/Vcl/Mia3/Phf10/Psen1/Ctnnb1/Kifap3/Gtpbp4/Pde4d/Ptpru/Mfsd2b/Hspd1/Prkca/Srf/Stat5a/Vsir/Itgb2/Smarcd1/Stat5b/Irak1/Ptpn6/Il27ra/Atp1b2/Icam2/Tcam1/Zfp36l1/Zdhhc21/Cadm1/Cd37/Fut4/Tjp3/Itga5/Cbfb/Ripor2/Dock8/Rac2/Havcr2/Pik3r6/Fermt3/Il4/Ptprs/Tenm4/Lgals9/Spn/Selplg/Lgals7/Tgfb1/Ccdc88b/Cd44/Laptm5/Spi1/Ptprc/Myb/Coro1a/Jak3/Lgals1/Dpp4/Syk</t>
+    <t xml:space="preserve">Prdx2/Lgals1/Spta1/Add2/Jak3/Laptm5/Syk/Slc4a1/Myb/Ptprs/Ptprc/Mink1/Coro1a/Prnp/Ccdc88b/Rac2/Tgfb1/Spn/Dmtn/Cd44/Cd47/Dock8/Ripor2/Cbfb/Ptpn23/Spi1/Fermt3/Cited2/Lgals9/Zdhhc21/Stat5b/Ptpn6/Dpp4/Itga5/Gnas/Irak1/Rap2b/Tenm4/Smarcd1/Egr3/Zbtb7b/Selplg/Fut4/Stat5a/Il4/Lgals7/Cd37/Pik3r6/Srf/Zfp36l1/Ctnnb1/Ap3d1/Il27ra/Tjp3/Havcr2/Atp1b2/Tfrc/Itgb2/Prkca/Ubash3b/Swap70/Cadm1/Vsir/Psen1/Tcam1/Icam5/Icam2/Hspd1/Rara/Slc39a8/Gtpbp4/Ptpru/Nck1/Mia3/Kifap3/Fcho1/Shb/Vcl/Mfsd2b/Pde4d/Phf10</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002009</t>
@@ -7636,7 +7636,7 @@
     <t xml:space="preserve">morphogenesis of an epithelium</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Aldh1a1/Car2/Mst1/Wnk4/Map3k1/Cited2/Agtr1a/Tsc1/Stil/Numb/Arhgap12/Hdac5/Fzd5/Atp7a/Dag1/Dvl2/Rara/Nckap1/Kdm2a/Luzp1/Nup50/Myo9a/Gna13/Lamc1/Arhgap35/Vcl/Psen1/Ctnnb1/Trim28/Ppp3r1/Phb2/Lrp5/Maged1/Wdr1/Igf1r/Plod3/Ift172/Megf8/Mthfd1/Flna/Srf/Stat5a/Lin7c/Pik3cd/Mthfd1l/Vangl2/Kat2a/Rac1/Csf1/Cxcr4/Mmp14/Tgfb1/Col5a1/Cd44/Eng</t>
+    <t xml:space="preserve">Car2/Cobl/Map3k1/Aldh1a1/Wnk4/Tgfb1/Mst1/Tsc1/Cd44/Rac1/Cited2/Eng/Cxcr4/Kat2a/Lin7c/Col5a1/Megf8/Flna/Kdm2a/Dag1/Numb/Agtr1a/Pik3cd/Stat5a/Nup50/Fzd5/Stil/Mmp14/Gna13/Srf/Maged1/Csf1/Ctnnb1/Nckap1/Wdr1/Hdac5/Plod3/Ift172/Arhgap12/Vangl2/Mthfd1/Dvl2/Mthfd1l/Luzp1/Lrp5/Atp7a/Trim28/Lamc1/Psen1/Ppp3r1/Rara/Phb2/Arhgap35/Igf1r/Myo9a/Vcl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097529</t>
@@ -7645,7 +7645,7 @@
     <t xml:space="preserve">myeloid leukocyte migration</t>
   </si>
   <si>
-    <t xml:space="preserve">Mst1/Cd47/Prex1/Pikfyve/Mospd2/Mpp1/Swap70/Pde4d/Wdr1/Prkca/Itgb2/Stat5b/Fcgr3/Vav1/Ano6/Pde4b/Fut4/Rac1/Ripor2/Rac2/Il4/Csf1/Mmp14/Spi1/Dpp4/Syk/Rin3</t>
+    <t xml:space="preserve">Syk/Ano6/Rac2/Mst1/Rac1/Cd47/Ripor2/Spi1/Vav1/Rin3/Stat5b/Prex1/Pikfyve/Dpp4/Fut4/Il4/Mmp14/Csf1/Wdr1/Mospd2/Fcgr3/Mpp1/Itgb2/Prkca/Pde4b/Swap70/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033077</t>
@@ -7654,7 +7654,7 @@
     <t xml:space="preserve">T cell differentiation in thymus</t>
   </si>
   <si>
-    <t xml:space="preserve">Mink1/Egr3/Gba/Fzd5/Ctnnb1/Tcf3/Srf/Stat5a/Fzd7/Trp53/Stat5b/Zfp36l1/Prr7/Dock2/Spn/Ptprc/Cdk6</t>
+    <t xml:space="preserve">Dock2/Ptprc/Mink1/Cdk6/Spn/Stat5b/Gba/Trp53/Egr3/Stat5a/Fzd5/Fzd7/Srf/Zfp36l1/Ctnnb1/Prr7/Tcf3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034766</t>
@@ -7663,7 +7663,7 @@
     <t xml:space="preserve">negative regulation of ion transmembrane transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc6a9/Slc43a1/Kel/Atp7a/Grk6/Nedd4/Ppp3r1/Gopc/Prkca/Ppif/Fkbp1b/Pcsk9/Slc43a2/Zfas1/Rgs2/Gsto1/Tgfb1</t>
+    <t xml:space="preserve">Slc6a9/Tgfb1/Gsto1/Slc43a1/Zfas1/Rgs2/Kel/Ppif/Nedd4/Prkca/Atp7a/Slc43a2/Ppp3r1/Pcsk9/Fkbp1b/Grk6/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045807</t>
@@ -7672,7 +7672,7 @@
     <t xml:space="preserve">positive regulation of endocytosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Pld2/Appl2/Snca/Itsn1/Picalm/Arrb1/Wasl/Ap2m1/Cbl/Atad1/Pcsk9/Tfr2/Gata2/Plcg2/Ano6/Il4/Apoe/Syk</t>
+    <t xml:space="preserve">Snca/Appl2/Syk/Picalm/Ano6/Itsn1/Plcg2/Apoe/Cd36/Pld2/Tfr2/Il4/Gata2/Atad1/Wasl/Arrb1/Ap2m1/Pcsk9/Cbl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048812</t>
@@ -7684,7 +7684,7 @@
     <t xml:space="preserve">527/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Mink1/Egr2/Map1a/Sema4b/Kalrn/Als2/Ache/Picalm/Adam10/Slc11a2/Numb/Kel/Dpysl2/Trak2/Tbc1d24/Wasl/Kif13b/Atp7a/Xk/Usp9x/Stk25/Dag1/Pias2/Dip2b/C9orf72/Cdkl5/Nckap1/Golga4/Myo9a/Arhgap35/Cpne1/Vcl/Cttn/Itsn2/Taok1/Sh3glb1/Abi1/Psen1/Iqgap1/Rpl4/Actr2/Ctnnb1/Nedd4/Hsp90ab1/Wdr36/Stau2/Jade2/Myh10/Mov10/Syngap1/Ulk2/Cul7/Igf1r/Prkca/Megf8/Srf/Unc13a/Akap5/Vangl2/Sema4a/Ankrd27/Rac1/Plxnc1/Rac2/Vim/Ptprs/Cxcr4/Apoe</t>
+    <t xml:space="preserve">Cobl/Picalm/Ptprs/Mink1/Rac2/Slc11a2/Ankrd27/Rac1/Vim/Cxcr4/Als2/Apoe/Adam10/Tbc1d24/Kalrn/Ache/Megf8/Dip2b/Stk25/Map1a/Usp9x/Dag1/Dpysl2/Numb/Pias2/Sema4b/Egr2/Xk/Myh10/Cul7/Wasl/Sema4a/Srf/Ctnnb1/Nckap1/Kel/Sh3glb1/Vangl2/Nedd4/Plxnc1/Mov10/Trak2/Prkca/Hsp90ab1/Atp7a/Psen1/Kif13b/Cpne1/Ulk2/C9orf72/Actr2/Taok1/Iqgap1/Golga4/Cdkl5/Rpl4/Stau2/Syngap1/Wdr36/Abi1/Arhgap35/Unc13a/Igf1r/Jade2/Cttn/Akap5/Myo9a/Vcl/Itsn2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032365</t>
@@ -7693,7 +7693,7 @@
     <t xml:space="preserve">intracellular lipid transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Serac1/Abcg1/Ldlr/Stard4/Tmem41b/Arl8b/Scp2/Pcsk9/Abca2</t>
+    <t xml:space="preserve">Abcg1/Serac1/Stard4/Abca2/Ldlr/Tmem41b/Arl8b/Pcsk9/Scp2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034205</t>
@@ -7702,7 +7702,7 @@
     <t xml:space="preserve">amyloid-beta formation</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Abcg1/Picalm/Adam10/Dyrk1a/Psen1/Ifngr1/Abca2/Apoe</t>
+    <t xml:space="preserve">Picalm/Prnp/Abcg1/Abca2/Apoe/Adam10/Dyrk1a/Psen1/Ifngr1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901031</t>
@@ -7711,7 +7711,7 @@
     <t xml:space="preserve">regulation of response to reactive oxygen species</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Glrx/Pycr1/Sesn1/Epor/Rnf146/Sesn3/Rack1/Trp53</t>
+    <t xml:space="preserve">Glrx/Cd36/Sesn1/Trp53/Epor/Rnf146/Sesn3/Pycr1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045980</t>
@@ -7720,7 +7720,7 @@
     <t xml:space="preserve">negative regulation of nucleotide metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ddit4/Nupr1/Flcn/Mtch2/Parp1/Trp53</t>
+    <t xml:space="preserve">Slc4a1/Ddit4/Mtch2/Trp53/Flcn/Nupr1/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050858</t>
@@ -7729,7 +7729,7 @@
     <t xml:space="preserve">negative regulation of antigen receptor-mediated signaling pathway</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Elf1/Dgkz/Lpxn/Ptpn6/Ubash3a/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Prnp/Ptpn6/Ubash3a/Elf1/Dgkz/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071677</t>
@@ -7738,7 +7738,7 @@
     <t xml:space="preserve">positive regulation of mononuclear cell migration</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd47/Adam10/Mospd2/Ano6/Dock8/Il4/Lgals9/Spn/Tgfb1/Spi1/Coro1a</t>
+    <t xml:space="preserve">Coro1a/Ano6/Tgfb1/Spn/Cd47/Dock8/Spi1/Lgals9/Adam10/Il4/Mospd2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006099</t>
@@ -7747,7 +7747,7 @@
     <t xml:space="preserve">tricarboxylic acid cycle</t>
   </si>
   <si>
-    <t xml:space="preserve">Aco1/Cs/Idh3g/Dlat/Idh3a/Pdha1/Idh2/Suclg2</t>
+    <t xml:space="preserve">Pdha1/Idh2/Aco1/Idh3a/Cs/Suclg2/Dlat/Idh3g</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009267</t>
@@ -7756,7 +7756,7 @@
     <t xml:space="preserve">cellular response to starvation</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Rragc/Sesn1/Map1lc3b/Gba/Bhlha15/Flcn/Sesn3/Xpr1/Gabarap/Mtmr3/Sirt1/Fnip1/Clec16a/Sh3glb1/Plin2/Pik3c2b/Pcsk9/Mybbp1a/Prkag2/Tcf7l2/Ripor1/Trp53/Pmaip1</t>
+    <t xml:space="preserve">Rragc/Cpeb4/Ripor1/Map1lc3b/Sesn1/Xpr1/Pmaip1/Gba/Trp53/Gabarap/Mtmr3/Prkag2/Mybbp1a/Sh3glb1/Flcn/Bhlha15/Sesn3/Sirt1/Fnip1/Pcsk9/Tcf7l2/Clec16a/Plin2/Pik3c2b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0061061</t>
@@ -7765,7 +7765,7 @@
     <t xml:space="preserve">muscle structure development</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Btg2/Dpf3/Tmod1/Egr2/Cited2/Hlf/Gpcpd1/Mylk2/Sox6/Arntl/Chd2/Mylpf/Dmpk/Tsc1/Fos/Nupr1/Kel/Actn1/Mybpc3/Epor/Hdac5/Coprs/Bhlha15/Ppard/Foxo4/Hmgcr/Xk/Dag1/Rara/Ehd1/Rb1/Med20/Lamc1/Homer1/Sirt1/Bnip2/Rps6kb1/Phf10/Nras/Ctnnb1/Flii/Wdr1/Fkbp1a/Tnni3/Myh10/Srf/Smarcd1/Fzd7/Tcf7l2/Vangl2/Pdlim2/Kat2a/Popdc2/Pdcd4/Zfp36l1/Nr1d2/Rgs2/Vamp5/Des/Ripor2/Il4/Dock2/Mmp14/Tgfb1/Gdf3/Hdac7/Lgals1/Eng/Cd53</t>
+    <t xml:space="preserve">Lgals1/Hdac7/Egr1/Dock2/Btg2/Tmod1/Tgfb1/Tsc1/Dpf3/Ripor2/Cited2/Eng/Actn1/Cd53/Hlf/Kat2a/Vamp5/Nr1d2/Des/Chd2/Ehd1/Arntl/Gdf3/Smarcd1/Dag1/Epor/Egr2/Xk/Il4/Myh10/Rgs2/Mmp14/Fzd7/Srf/Zfp36l1/Ctnnb1/Wdr1/Ppard/Hdac5/Kel/Rb1/Flii/Dmpk/Vangl2/Gpcpd1/Hmgcr/Mylpf/Coprs/Mylk2/Sox6/Lamc1/Pdcd4/Pdlim2/Bhlha15/Sirt1/Fkbp1a/Fos/Tnni3/Rara/Nupr1/Nras/Popdc2/Foxo4/Homer1/Med20/Bnip2/Tcf7l2/Rps6kb1/Phf10/Mybpc3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001910</t>
@@ -7774,7 +7774,7 @@
     <t xml:space="preserve">regulation of leukocyte mediated cytotoxicity</t>
   </si>
   <si>
-    <t xml:space="preserve">H2-T23/Lamp1/Ap1g1/Stat5a/Stat5b/Vav1/Cadm1/Serpinb9/Havcr2/Pik3r6/Lgals9/Spi1/Tyrobp/Ptprc/P2rx7</t>
+    <t xml:space="preserve">Ptprc/Lamp1/Spi1/Vav1/P2rx7/Lgals9/Stat5b/Ap1g1/H2-T23/Tyrobp/Stat5a/Pik3r6/Havcr2/Serpinb9/Cadm1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0048858</t>
@@ -7795,7 +7795,7 @@
     <t xml:space="preserve">431/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cldn13/Snca/Agtr1a/Ctsd/Grn/Kalrn/Nedd9/Als2/Tsc1/Picalm/Asap3/Slc11a2/Prex1/Ppp1r15b/Rgl1/Arrb1/Smcr8/Flcn/Mtch2/Bax/Elmod2/Dvl2/C9orf72/Cdkl5/Myo9a/Bcl2l11/Rabgap1/Gnas/Bid/Gna13/Arhgap35/Sirt1/Rack1/Usp6nl/Phb2/Hsp90ab1/Hspd1/Psme1/P2rx1/Vsir/Dapk1/Mtmr9/Vav1/Pmaip1/Gmip/Rgl2/Rcc2/Dock8/Prr7/Rgs1/Tfap4/Rgs14/Laptm5/Ptprc/Arhgap27/Tbc1d10c/Arap3/Syk</t>
+    <t xml:space="preserve">Arap3/Ctsd/Cldn13/Laptm5/Snca/Syk/Picalm/Ptprc/Slc11a2/Grn/Tsc1/Dock8/Arhgap27/Rcc2/Tbc1d10c/Vav1/Als2/Rgl2/Prex1/Mtmr9/Kalrn/Gnas/Gmip/Mtch2/Tfap4/Pmaip1/Rgs14/Nedd9/Agtr1a/Rabgap1/Ppp1r15b/Gna13/Rgs1/Prr7/Smcr8/Dapk1/Arrb1/Dvl2/Psme1/Asap3/Rgl1/Bcl2l11/Hsp90ab1/Flcn/Vsir/Bid/Sirt1/C9orf72/Hspd1/Bax/Cdkl5/Phb2/Arhgap35/P2rx1/Rack1/Elmod2/Myo9a/Usp6nl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030837</t>
@@ -7804,7 +7804,7 @@
     <t xml:space="preserve">negative regulation of actin filament polymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Add2/Dmtn/Sptb/Ssh2/Twf1/Flii/Sptan1/Arpc2/Capg/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Vill/Tmod1/Dmtn/Capg/Arpc2/Ssh2/Flii/Twf1/Sptan1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019867</t>
@@ -7813,7 +7813,7 @@
     <t xml:space="preserve">outer membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Fam210b/Abcb6/Snca/Agtr1a/Prnp/Dmpk/Slc11a2/1810058I24Rik/Armcx3/Mtch2/Bax/Rnf185/Bid/Mcl1/Cyb5r3/Rps6kb1/Sh3glb1/Psen1/Phb2/Scp2/Pgrmc1/Atad1/Mtx3/Gk/Acsl5/Bri3bp/Hk2/Retsat</t>
+    <t xml:space="preserve">Fam210b/Snca/Abcb6/Prnp/Slc11a2/Acsl5/Retsat/Mtch2/Bri3bp/Agtr1a/1810058I24Rik/Gk/Atad1/Sh3glb1/Dmpk/Mcl1/Cyb5r3/Hk2/Psen1/Bid/Mtx3/Pgrmc1/Bax/Scp2/Rnf185/Armcx3/Phb2/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031968</t>
@@ -7828,7 +7828,7 @@
     <t xml:space="preserve">regulation of translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Btg2/Fech/Tnrc6b/Tsc1/Pkm/Ppp1r15b/Gigyf2/Rnf139/Habp4/Tob1/Rara/Uhmk1/Nck1/Ddx6/Aco1/Ago2/Tnrc6c/Mknk1/Tut7/Mknk2/Rps6kb1/Celf1/Rack1/Parn/Cnot7/Pa2g4/Pus7/Zfp706/Eif4g2/Mov10/Tcof1/Cnbp/Trnau1ap/Prkca/Exosc5/Dph6/Eif4ebp2/Otud6b/Nat10/Mrps27/Dapk1/Bzw2/Ogfod1/Zfp36l1/Msi1/Rgs2/Ago4/Vim</t>
+    <t xml:space="preserve">Btg2/Fech/Tsc1/Cpeb4/Gigyf2/Tnrc6b/Vim/Ago4/Eif4ebp2/Bzw2/Nat10/Pkm/Tcof1/Rnf139/Ddx6/Habp4/Ogfod1/Mrps27/Rgs2/Ppp1r15b/Aco1/Zfp36l1/Msi1/Otud6b/Dapk1/Uhmk1/Celf1/Cnbp/Tob1/Mov10/Pus7/Mknk2/Prkca/Zfp706/Dph6/Exosc5/Eif4g2/Rara/Ago2/Tut7/Trnau1ap/Tnrc6c/Nck1/Cnot7/Mknk1/Rack1/Parn/Pa2g4/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031349</t>
@@ -7837,7 +7837,7 @@
     <t xml:space="preserve">positive regulation of defense response</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd47/Snca/Optn/Grn/Lamp1/Nupr1/Ldlr/Trim56/Tbk1/Rnf185/Hexim1/Nono/Matr3/Hspd1/Ap1g1/Prkca/Stat5a/Stat5b/Fcgr3/Xrcc5/Pdcd4/Plcg2/Vav1/Cadm1/Alox5ap/Havcr2/Lgals9/Spi1/Tyrobp/Lgals1/Dpp4/Il1rl1/Syk</t>
+    <t xml:space="preserve">Lgals1/Snca/Il1rl1/Syk/Grn/Lamp1/Cd47/Spi1/Vav1/Alox5ap/Plcg2/Lgals9/Optn/Stat5b/Ldlr/Dpp4/Xrcc5/Tbk1/Ap1g1/Trim56/Tyrobp/Stat5a/Nono/Havcr2/Matr3/Fcgr3/Hexim1/Prkca/Cadm1/Pdcd4/Hspd1/Nupr1/Rnf185</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006165</t>
@@ -7849,7 +7849,7 @@
     <t xml:space="preserve">92/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Prkag2/Khk/Ak4/Hk2/Nme4/P2rx7</t>
+    <t xml:space="preserve">Slc4a1/Pfkfb2/Nme4/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Pkm/Prkag2/Eno3/Hk2/Psen1/Bpgm/Ak4/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0034446</t>
@@ -7858,7 +7858,7 @@
     <t xml:space="preserve">substrate adhesion-dependent cell spreading</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Nedd9/Micall2/Prex1/Megf9/Cib1/Atrnl1/Lamc1/Parvg/Flna/Fzd7/Lpxn/Arpc2/Unc13d/Rac1/Rcc2/Fermt3</t>
+    <t xml:space="preserve">Dmtn/Rac1/Rcc2/Fermt3/Micall2/Arpc2/Prex1/Unc13d/Flna/Nedd9/Fzd7/Megf9/Cib1/Lamc1/Parvg/Atrnl1/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019058</t>
@@ -7867,7 +7867,7 @@
     <t xml:space="preserve">viral life cycle</t>
   </si>
   <si>
-    <t xml:space="preserve">Trim10/Agtr1a/Isg20/Pcx/Uvrag/Pikfyve/Rab43/Trim56/Kpna6/Tmem41b/Pkn2/Ddx6/Morc2a/Stom/Arl8b/Snx3/Setdb1/Vps4b/Usp6nl/Nedd4/Trim28/Cnot7/Nucks1/Ifitm2/Hsp90ab1/Ifih1/Oasl1/Vapa/Apobec3/Apoe/Lgals1/Oas2</t>
+    <t xml:space="preserve">Lgals1/Oas2/Trim10/Vapa/Apoe/Pikfyve/Pcx/Uvrag/Apobec3/Rab43/Kpna6/Ddx6/Pkn2/Trim56/Agtr1a/Isg20/Tmem41b/Morc2a/Nedd4/Nucks1/Arl8b/Hsp90ab1/Trim28/Ifih1/Ifitm2/Setdb1/Vps4b/Stom/Cnot7/Oasl1/Snx3/Usp6nl</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046777</t>
@@ -7876,7 +7876,7 @@
     <t xml:space="preserve">protein autophosphorylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Mink1/Map3k1/Mylk2/Pim1/Pikfyve/Grk5/Map3k12/Stk25/Ppp2r5b/Cdkl5/Uhmk1/Dyrk1a/Rap2b/Clk3/Mknk1/Mknk2/Taok1/Iqgap1/Trim28/Ulk2/Igf1r/Prkca/Rap2c/Map4k1/Dapk1/Cad/Irak1/Pim3/Fes/Ptprc/Syk/Eng</t>
+    <t xml:space="preserve">Map3k1/Syk/Ptprc/Mink1/Eng/Pikfyve/Dyrk1a/Pim3/Irak1/Rap2b/Cad/Stk25/Rap2c/Map4k1/Fes/Grk5/Dapk1/Uhmk1/Mylk2/Mknk2/Clk3/Prkca/Trim28/Ulk2/Taok1/Iqgap1/Cdkl5/Map3k12/Igf1r/Ppp2r5b/Mknk1/Pim1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043550</t>
@@ -7885,7 +7885,7 @@
     <t xml:space="preserve">regulation of lipid kinase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Wdr81/Ppp2r5a/Rb1/Pip4k2c/Sh3glb1/Dgkz/Pik3r5/Rac1/Tgfb1/Pik3ip1</t>
+    <t xml:space="preserve">Tgfb1/Rac1/Ppp2r5a/Pik3ip1/Wdr81/Dgkz/Rb1/Sh3glb1/Pik3r5/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903426</t>
@@ -7894,7 +7894,7 @@
     <t xml:space="preserve">regulation of reactive oxygen species biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ctns/Slc30a10/Pikfyve/Clcn3/Sirt1/Ncf2/Hspd1/Plcg2/Il4</t>
+    <t xml:space="preserve">Slc30a10/Ctns/Plcg2/Cd36/Pikfyve/Clcn3/Il4/Ncf2/Sirt1/Hspd1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010506</t>
@@ -7903,7 +7903,7 @@
     <t xml:space="preserve">regulation of autophagy</t>
   </si>
   <si>
-    <t xml:space="preserve">Trp53inp2/Scoc/Snca/Optn/Rragc/Tsc1/Nupr1/Sesn1/Atp6v0a1/Ticam1/Uvrag/Trp53inp1/Mlst8/Smcr8/Tbk1/Fbxw7/Flcn/C9orf72/Sesn3/Bcl2l11/Ctsa/Mtmr3/Bid/Mcl1/Rmc1/Pip4k2c/Cttn/Sirt1/Clec16a/Sh3glb1/Ubqln4/Eif4g2/Ulk2/Trp53/Dapk1/Mtmr9/Il4</t>
+    <t xml:space="preserve">Snca/Rragc/Tsc1/Trp53inp2/Scoc/Optn/Mtmr9/Sesn1/Uvrag/Fbxw7/Tbk1/Mlst8/Trp53/Atp6v0a1/Ticam1/Trp53inp1/Mtmr3/Il4/Ctsa/Smcr8/Dapk1/Sh3glb1/Mcl1/Ubqln4/Bcl2l11/Flcn/Bid/Sesn3/Rmc1/Ulk2/Sirt1/C9orf72/Eif4g2/Nupr1/Cttn/Clec16a/Pip4k2c</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031256</t>
@@ -7912,7 +7912,7 @@
     <t xml:space="preserve">leading edge membrane</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Ank1/Mpp2/Myo6/Atp2b1/Ppp1r9b/Cdkl5/Twf1/Akap5/Arpc2/Pdxp/Plcg2/Itga5/Rac1/Ripor2/Dock8/Arhgef2/Adgre5/Cd44/Myo1g</t>
+    <t xml:space="preserve">Myo1g/Appl2/Arhgef2/Ank1/Cd44/Rac1/Dock8/Adgre5/Ripor2/Plcg2/Mpp2/Arpc2/Atp2b1/Itga5/Myo6/Pdxp/Ppp1r9b/Twf1/Cdkl5/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0099081</t>
@@ -7930,7 +7930,7 @@
     <t xml:space="preserve">phosphoric ester hydrolase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Pld2/Ptp4a3/Lrrc39/Pip4p1/Gpcpd1/Pfkfb2/Dusp6/Ptpn23/Cdc25b/Ubash3b/Ssh2/Apex2/Ppp2r5a/Plcd3/Nt5dc2/Mtmr3/Gnas/Ppm1b/Mtmr12/Ppp3r1/Pde4d/Ptpru/Ppa2/Pfkfb3/Enoph1/Nt5m/Timm50/Ptpn9/Ssu72/Lhpp/Plpp2/Pdxp/Mtmr9/Ptpn6/Ppp2r1a/Plcg2/Ptpn18/Pde4b/Ppm1h/G6pc3/Plcb2/Ptprs/Ptprc</t>
+    <t xml:space="preserve">Ptprs/Ptprc/Pip4p1/Pfkfb2/Ptpn23/Ppp2r5a/Plcb2/Ppp2r1a/Plcg2/Cdc25b/Pld2/Mtmr9/Ptpn6/Gnas/Ptp4a3/Ssh2/Pdxp/G6pc3/Dusp6/Mtmr3/Timm50/Lhpp/Lrrc39/Ptpn18/Ptpn9/Ppm1h/Ssu72/Gpcpd1/Apex2/Nt5dc2/Ubash3b/Pde4b/Plpp2/Ppp3r1/Mtmr12/Enoph1/Plcd3/Ptpru/Pfkfb3/Ppa2/Ppm1b/Nt5m/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006090</t>
@@ -7939,7 +7939,7 @@
     <t xml:space="preserve">pyruvate metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Pcx/Mlst8/Mtch2/Psen1/Gpi1/Dlat/Pdha1/Prkag2/Khk/Hk2/P2rx7</t>
+    <t xml:space="preserve">Slc4a1/Pfkfb2/P2rx7/Ddit4/Khk/Pdha1/Pcx/Mtch2/Mlst8/Pkm/Prkag2/Eno3/Dlat/Hk2/Psen1/Bpgm/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031690</t>
@@ -7948,7 +7948,7 @@
     <t xml:space="preserve">adrenergic receptor binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Arrb1/Gnas/Sav1/Nedd4/Pde4d/Akap5</t>
+    <t xml:space="preserve">Gnas/Arrb1/Nedd4/Sav1/Akap5/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050860</t>
@@ -7957,7 +7957,7 @@
     <t xml:space="preserve">negative regulation of T cell receptor signaling pathway</t>
   </si>
   <si>
-    <t xml:space="preserve">Prnp/Elf1/Dgkz/Ptpn6/Ubash3a/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Prnp/Ptpn6/Ubash3a/Elf1/Dgkz</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071548</t>
@@ -7966,7 +7966,7 @@
     <t xml:space="preserve">response to dexamethasone</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Ddit4/Gba/Rps6kb1/Tfap4/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Ddit4/Tfap4/Gba/Agtr1a/Rps6kb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097494</t>
@@ -7975,7 +7975,7 @@
     <t xml:space="preserve">regulation of vesicle size</t>
   </si>
   <si>
-    <t xml:space="preserve">Washc5/Picalm/Rab22a/Chmp3/Ap2m1/Rin3</t>
+    <t xml:space="preserve">Picalm/Washc5/Rin3/Rab22a/Chmp3/Ap2m1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903792</t>
@@ -7990,7 +7990,7 @@
     <t xml:space="preserve">glycolytic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Prkag2/Khk/Hk2/P2rx7</t>
+    <t xml:space="preserve">Slc4a1/Pfkfb2/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Pkm/Prkag2/Eno3/Hk2/Psen1/Bpgm/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006757</t>
@@ -8005,7 +8005,7 @@
     <t xml:space="preserve">iron ion transmembrane transporter activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc25a37/Tfrc/Slc11a2/Slc39a8</t>
+    <t xml:space="preserve">Slc11a2/Slc25a37/Tfrc/Slc39a8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006107</t>
@@ -8014,7 +8014,7 @@
     <t xml:space="preserve">oxaloacetate metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pcx/Cs/Got1/Got2</t>
+    <t xml:space="preserve">Pcx/Cs/Got2/Got1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006560</t>
@@ -8023,7 +8023,7 @@
     <t xml:space="preserve">proline metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pycr1/Aldh4a1/Pycr2/Prodh</t>
+    <t xml:space="preserve">Prodh/Aldh4a1/Pycr1/Pycr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009396</t>
@@ -8038,7 +8038,7 @@
     <t xml:space="preserve">bleb assembly</t>
   </si>
   <si>
-    <t xml:space="preserve">Prdx6/Ano6/Emp3/P2rx7</t>
+    <t xml:space="preserve">Ano6/P2rx7/Emp3/Prdx6</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0033572</t>
@@ -8047,7 +8047,7 @@
     <t xml:space="preserve">transferrin transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Tfrc/Cltc/Snx3/Tfr2</t>
+    <t xml:space="preserve">Cltc/Tfr2/Tfrc/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0036466</t>
@@ -8065,7 +8065,7 @@
     <t xml:space="preserve">neuron intrinsic apoptotic signaling pathway in response to oxidative stress</t>
   </si>
   <si>
-    <t xml:space="preserve">Fbxw7/Mcl1/Parp1/Nono</t>
+    <t xml:space="preserve">Fbxw7/Nono/Mcl1/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043983</t>
@@ -8074,7 +8074,7 @@
     <t xml:space="preserve">histone H4-K12 acetylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Jade3/Jade2/Jade1/Kat2a</t>
+    <t xml:space="preserve">Kat2a/Jade1/Jade3/Jade2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050882</t>
@@ -8083,7 +8083,7 @@
     <t xml:space="preserve">voluntary musculoskeletal movement</t>
   </si>
   <si>
-    <t xml:space="preserve">Map1a/Hipk2/Vps35/Parp1</t>
+    <t xml:space="preserve">Hipk2/Map1a/Vps35/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051574</t>
@@ -8092,7 +8092,7 @@
     <t xml:space="preserve">positive regulation of histone H3-K9 methylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Brca1/Gfi1b/Sirt1/Myb</t>
+    <t xml:space="preserve">Myb/Sirt1/Brca1/Gfi1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0097136</t>
@@ -8101,7 +8101,7 @@
     <t xml:space="preserve">Bcl-2 family protein complex</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Bcl2l11/Mcl1/Pmaip1</t>
+    <t xml:space="preserve">Pmaip1/Mcl1/Bcl2l11/Bax</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903376</t>
@@ -8116,7 +8116,7 @@
     <t xml:space="preserve">negative regulation of lymphocyte migration</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasl/Mia3/Il27ra/Ripor2</t>
+    <t xml:space="preserve">Ripor2/Wasl/Il27ra/Mia3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030133</t>
@@ -8128,7 +8128,7 @@
     <t xml:space="preserve">278/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rab3il1/Slc6a9/Atp6v0d1/Snca/Mylk2/Clcn5/Picalm/Adam10/Atg9a/Lamp1/Cltc/Atp6v0a1/Wdr7/Yipf2/Nrgn/Rab3ip/Syn1/Igf2r/Clcn3/Atp2b1/Atp7a/Gnas/Cdk16/Sh3glb1/Uso1/Psen1/Gopc/Ap1g1/Sar1b/Lin7c/Unc13a/Tmem230/Slc4a8/Unc13d/Cadm1/Pde4b/Ankrd27/Ptprs/Laptm5/Sytl4</t>
+    <t xml:space="preserve">Rab3il1/Atp6v0d1/Laptm5/Snca/Picalm/Ptprs/Slc6a9/Cltc/Ankrd27/Lamp1/Atp2b1/Clcn5/Adam10/Lin7c/Igf2r/Gnas/Unc13d/Atg9a/Ap1g1/Wdr7/Clcn3/Atp6v0a1/Rab3ip/Yipf2/Sytl4/Sh3glb1/Slc4a8/Nrgn/Mylk2/Sar1b/Cdk16/Pde4b/Atp7a/Tmem230/Cadm1/Psen1/Unc13a/Syn1/Gopc/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031406</t>
@@ -8140,7 +8140,7 @@
     <t xml:space="preserve">131/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ogfod2/Snca/Hmbs/Acox1/Pcx/Igf2r/Ppard/Rara/Acaca/Sh3glb1/Got1/Got2/Scp2/Plod3/Ogfod1/Grin2d/Hlcs/Alox5ap/Slc19a1/Prr7/P4ha3</t>
+    <t xml:space="preserve">Snca/Ogfod2/Hmbs/Alox5ap/Hlcs/Cd36/Igf2r/P4ha3/Pcx/Acox1/Slc19a1/Ogfod1/Ppard/Prr7/Plod3/Sh3glb1/Got2/Acaca/Grin2d/Rara/Scp2/Got1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002269</t>
@@ -8149,7 +8149,7 @@
     <t xml:space="preserve">leukocyte activation involved in inflammatory response</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Grn/Ldlr/Ifngr1/Cst7/Traf3ip2/Nr1d1/Il4/Tyrobp</t>
+    <t xml:space="preserve">Snca/Grn/Ldlr/Tyrobp/Il4/Nr1d1/Traf3ip2/Ifngr1/Cst7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006356</t>
@@ -8158,7 +8158,7 @@
     <t xml:space="preserve">regulation of transcription by RNA polymerase I</t>
   </si>
   <si>
-    <t xml:space="preserve">Dedd/Ddx21/Pwp1/Dhx33/Lyar/Wdr43/Flna/Heatr1/Mybbp1a</t>
+    <t xml:space="preserve">Flna/Mybbp1a/Heatr1/Pwp1/Dhx33/Wdr43/Lyar/Ddx21/Dedd</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0010591</t>
@@ -8167,7 +8167,7 @@
     <t xml:space="preserve">regulation of lamellipodium assembly</t>
   </si>
   <si>
-    <t xml:space="preserve">Dmtn/Atp7a/Nckap1/Twf1/Actr2/Was/Arpc2/Rac1/Rac2</t>
+    <t xml:space="preserve">Rac2/Dmtn/Rac1/Arpc2/Nckap1/Twf1/Atp7a/Actr2/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0035066</t>
@@ -8176,7 +8176,7 @@
     <t xml:space="preserve">positive regulation of histone acetylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Wbp2/Arrb1/Brca1/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Kat2a/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Glyr1/Kat2a/Wbp2/Mybbp1a/Arrb1/Ruvbl2/Brca1/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045022</t>
@@ -8185,7 +8185,7 @@
     <t xml:space="preserve">early endosome to late endosome transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Wdr81/Vps11/Ptpn23/Dnajc13/Sh3glb1/Snx3/Flna/Aktip/Ankrd27</t>
+    <t xml:space="preserve">Ankrd27/Ptpn23/Vps11/Wdr81/Flna/Dnajc13/Aktip/Sh3glb1/Snx3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901532</t>
@@ -8194,7 +8194,7 @@
     <t xml:space="preserve">regulation of hematopoietic progenitor cell differentiation</t>
   </si>
   <si>
-    <t xml:space="preserve">Flcn/Rara/Fnip1/N4bp2l2/Pus7/Gata2/Spi1/Myb/Cdk6</t>
+    <t xml:space="preserve">Myb/Cdk6/Spi1/Gata2/Pus7/Flcn/Fnip1/Rara/N4bp2l2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006970</t>
@@ -8203,7 +8203,7 @@
     <t xml:space="preserve">response to osmotic stress</t>
   </si>
   <si>
-    <t xml:space="preserve">Gypa/Map3k1/Micu1/Mlst8/Bax/Lrrc8a/Tsc22d3/Mknk1/Prkca/Trp53/Xrcc5/Zfp36l1/Rac1/Rcsd1</t>
+    <t xml:space="preserve">Gypa/Map3k1/Rac1/Rcsd1/Xrcc5/Micu1/Mlst8/Trp53/Zfp36l1/Lrrc8a/Prkca/Bax/Tsc22d3/Mknk1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016570</t>
@@ -8215,7 +8215,7 @@
     <t xml:space="preserve">434/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Wbp2/Zbtb7b/Arrb1/Hdac5/Coprs/Rlf/Flcn/Kmt2c/Jade3/Kdm2a/Rnf168/Taf6l/Kdm4c/Pcgf3/Ash1l/Brca1/Ncoa1/Gfi1b/Trip12/Asxl2/Nsd3/Sirt1/Kat6a/Ctcf/Usp15/Setdb1/Tbl1xr1/Ctnnb1/Msl3/Tcf3/Wdr77/Ube2e1/Ddx21/Smyd2/Pwp1/Jade2/Ldb1/Ruvbl2/Sgf29/Mllt6/Dtx3l/Prmt1/Glyr1/Mybbp1a/Prmt7/Dnmt3b/Jade1/Trp53/Pcgf2/Kat2a/Gata2/Hlcs/Smyd5/Tgfb1/Spi1/Hdac7/Myb</t>
+    <t xml:space="preserve">Hdac7/Snca/Myb/Tgfb1/Smyd5/Spi1/Glyr1/Kat2a/Wbp2/Hlcs/Jade1/Jade3/Dnmt3b/Rlf/Kdm2a/Trp53/Prmt7/Zbtb7b/Ldb1/Mllt6/Pcgf2/Gata2/Prmt1/Ctnnb1/Mybbp1a/Hdac5/Rnf168/Arrb1/Ruvbl2/Pwp1/Pcgf3/Trip12/Coprs/Dtx3l/Tcf3/Usp15/Flcn/Kmt2c/Sirt1/Kdm4c/Sgf29/Ash1l/Nsd3/Ncoa1/Setdb1/Brca1/Kat6a/Gfi1b/Smyd2/Taf6l/Ube2e1/Msl3/Wdr77/Ctcf/Asxl2/Ddx21/Tbl1xr1/Jade2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0005925</t>
@@ -8224,7 +8224,7 @@
     <t xml:space="preserve">focal adhesion</t>
   </si>
   <si>
-    <t xml:space="preserve">Nedd9/Dcaf6/Asap3/Actn1/Tle2/Dag1/Sorbs1/Irf2/Vcl/Cttn/Iqgap1/Cbl/Parvg/Focad/Itgb2/Lpxn/Arpc2/Itga5/Fes/Ptprc/Sla/Il1rl1/Lcp1</t>
+    <t xml:space="preserve">Il1rl1/Ptprc/Sla/Actn1/Lcp1/Arpc2/Itga5/Dag1/Dcaf6/Nedd9/Fes/Focad/Asap3/Itgb2/Iqgap1/Parvg/Irf2/Sorbs1/Cbl/Cttn/Tle2/Vcl/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0019210</t>
@@ -8239,7 +8239,7 @@
     <t xml:space="preserve">monocarboxylic acid binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Snca/Acox1/Pcx/Igf2r/Ppard/Rara/Acaca/Sh3glb1/Scp2/Hlcs/Alox5ap/Prr7</t>
+    <t xml:space="preserve">Snca/Alox5ap/Hlcs/Cd36/Igf2r/Pcx/Acox1/Ppard/Prr7/Sh3glb1/Acaca/Rara/Scp2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031056</t>
@@ -8248,7 +8248,7 @@
     <t xml:space="preserve">regulation of histone modification</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Wbp2/Zbtb7b/Arrb1/Flcn/Kdm2a/Kdm4c/Brca1/Gfi1b/Trip12/Asxl2/Nsd3/Sirt1/Ctcf/Ctnnb1/Ddx21/Ruvbl2/Sgf29/Mllt6/Glyr1/Mybbp1a/Dnmt3b/Trp53/Kat2a/Gata2/Tgfb1/Spi1/Myb</t>
+    <t xml:space="preserve">Snca/Myb/Tgfb1/Spi1/Glyr1/Kat2a/Wbp2/Dnmt3b/Kdm2a/Trp53/Zbtb7b/Mllt6/Gata2/Ctnnb1/Mybbp1a/Arrb1/Ruvbl2/Trip12/Flcn/Sirt1/Kdm4c/Sgf29/Nsd3/Brca1/Gfi1b/Ctcf/Asxl2/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0099572</t>
@@ -8257,7 +8257,7 @@
     <t xml:space="preserve">postsynaptic specialization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpeb4/Slc6a9/Add2/Dmtn/Map1a/Mpp2/Mylk2/Prnp/Kalrn/Als2/Tsc1/Picalm/Adam10/Samd14/Numb/Nrgn/Arrb1/Syn1/Myo6/Ppp1r9b/Rnf10/Cdkl5/Vps35/Homer1/Abi1/Rpl4/Actr2/Ctnnb1/Phb2/Ifngr1/Dgkz/Eif4g2/Syngap1/Srgn/Rpl10a/Epb41l1/Akap5/Grin2d/Cadm1/Pde4b/Kcnab2/Prr7/Ptprs/Ywhaz/Rgs14/Arhgef2</t>
+    <t xml:space="preserve">Add2/Picalm/Arhgef2/Ptprs/Slc6a9/Prnp/Ywhaz/Tsc1/Dmtn/Cpeb4/Kcnab2/Mpp2/Als2/Adam10/Kalrn/Samd14/Rgs14/Rpl10a/Map1a/Myo6/Numb/Dgkz/Ppp1r9b/Ctnnb1/Rnf10/Prr7/Vps35/Arrb1/Nrgn/Mylk2/Srgn/Pde4b/Cadm1/Grin2d/Actr2/Epb41l1/Eif4g2/Ifngr1/Cdkl5/Rpl4/Syngap1/Phb2/Homer1/Abi1/Akap5/Syn1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001844</t>
@@ -8266,7 +8266,7 @@
     <t xml:space="preserve">protein insertion into mitochondrial membrane involved in apoptotic signaling pathway</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Sh3glb1/Pmaip1</t>
+    <t xml:space="preserve">Pmaip1/Sh3glb1/Bax</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002826</t>
@@ -8275,7 +8275,7 @@
     <t xml:space="preserve">negative regulation of T-helper 1 type immune response</t>
   </si>
   <si>
-    <t xml:space="preserve">Havcr2/Jak3/Il1rl1</t>
+    <t xml:space="preserve">Jak3/Il1rl1/Havcr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0004448</t>
@@ -8284,7 +8284,7 @@
     <t xml:space="preserve">isocitrate dehydrogenase [NAD(P)+] activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Idh3g/Idh3a/Idh2</t>
+    <t xml:space="preserve">Idh2/Idh3a/Idh3g</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0004768</t>
@@ -8293,7 +8293,7 @@
     <t xml:space="preserve">stearoyl-CoA 9-desaturase activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Scd1/Scd2/Cyb5a</t>
+    <t xml:space="preserve">Cyb5a/Scd1/Scd2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009256</t>
@@ -8311,7 +8311,7 @@
     <t xml:space="preserve">negative regulation of anion channel activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Grk6/Gopc/Prkca</t>
+    <t xml:space="preserve">Prkca/Grk6/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0015194</t>
@@ -8320,7 +8320,7 @@
     <t xml:space="preserve">L-serine transmembrane transporter activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc38a2/Slc38a7/Slc38a5</t>
+    <t xml:space="preserve">Slc38a2/Slc38a5/Slc38a7</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031536</t>
@@ -8329,7 +8329,7 @@
     <t xml:space="preserve">positive regulation of exit from mitosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Birc5/Phb2/Tgfb1</t>
+    <t xml:space="preserve">Tgfb1/Birc5/Phb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043985</t>
@@ -8338,7 +8338,7 @@
     <t xml:space="preserve">histone H4-R3 methylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Coprs/Wdr77/Prmt1</t>
+    <t xml:space="preserve">Prmt1/Coprs/Wdr77</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0051725</t>
@@ -8356,7 +8356,7 @@
     <t xml:space="preserve">WD40-repeat domain binding</t>
   </si>
   <si>
-    <t xml:space="preserve">Usp47/Cct6a/Myb</t>
+    <t xml:space="preserve">Myb/Cct6a/Usp47</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0090370</t>
@@ -8365,7 +8365,7 @@
     <t xml:space="preserve">negative regulation of cholesterol efflux</t>
   </si>
   <si>
-    <t xml:space="preserve">Abca2/Irak1/Apoe</t>
+    <t xml:space="preserve">Abca2/Apoe/Irak1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901873</t>
@@ -8374,7 +8374,7 @@
     <t xml:space="preserve">regulation of post-translational protein modification</t>
   </si>
   <si>
-    <t xml:space="preserve">Flcn/Crtap/Abca2</t>
+    <t xml:space="preserve">Abca2/Flcn/Crtap</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902262</t>
@@ -8383,7 +8383,7 @@
     <t xml:space="preserve">apoptotic process involved in blood vessel morphogenesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Lrp5/Spi1</t>
+    <t xml:space="preserve">Spi1/Lrp5/Bax</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1904778</t>
@@ -8392,7 +8392,7 @@
     <t xml:space="preserve">positive regulation of protein localization to cell cortex</t>
   </si>
   <si>
-    <t xml:space="preserve">Epb41/Gpsm2/Ppp1r9b</t>
+    <t xml:space="preserve">Epb41/Ppp1r9b/Gpsm2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031347</t>
@@ -8401,7 +8401,7 @@
     <t xml:space="preserve">regulation of defense response</t>
   </si>
   <si>
-    <t xml:space="preserve">Appl2/Cd47/Snca/Optn/Grn/Serpinb1a/Lamp1/Nupr1/Ldlr/Trim56/Ppard/Tbk1/Lpcat3/Elmod2/Vps35/Rnf185/Ash1l/Rictor/Hexim1/Rb1/Ppm1b/Celf1/Usp15/Nono/Cnot7/Matr3/Hspd1/Ap1g1/Lyar/Prkca/Traf3/Dtx3l/Stat5a/Cst7/Stat5b/Fcgr3/Xrcc5/Pdcd4/Plcg2/Traf3ip2/Vav1/Apobec3/Nr1d2/Cadm1/Cd37/Serpinb9/Alox5ap/Nr1d1/Havcr2/Aldh2/Pik3r6/Il4/Rnf125/Lgals9/Spn/Apoe/Cd44/Spi1/Tyrobp/Lgals1/Dpp4/Il1rl1/Syk</t>
+    <t xml:space="preserve">Lgals1/Snca/Appl2/Il1rl1/Syk/Grn/Spn/Aldh2/Lamp1/Cd44/Cd47/Spi1/Vav1/Alox5ap/Plcg2/Lgals9/Optn/Apoe/Stat5b/Ldlr/Rnf125/Dpp4/Nr1d2/Xrcc5/Serpinb1a/Tbk1/Apobec3/Ap1g1/Trim56/Traf3/Tyrobp/Stat5a/Il4/Cd37/Pik3r6/Nono/Ppard/Vps35/Rb1/Nr1d1/Havcr2/Matr3/Fcgr3/Celf1/Serpinb9/Hexim1/Lpcat3/Dtx3l/Prkca/Usp15/Cadm1/Pdcd4/Ash1l/Traf3ip2/Hspd1/Nupr1/Rnf185/Lyar/Cst7/Cnot7/Elmod2/Ppm1b/Rictor</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0009303</t>
@@ -8410,7 +8410,7 @@
     <t xml:space="preserve">rRNA transcription</t>
   </si>
   <si>
-    <t xml:space="preserve">Dedd/Pwp1/Polr1a/Tcof1/Spin1/Trp53/Polr1b/Npm3</t>
+    <t xml:space="preserve">Npm3/Tcof1/Trp53/Spin1/Polr1b/Pwp1/Polr1a/Dedd</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030291</t>
@@ -8419,7 +8419,7 @@
     <t xml:space="preserve">protein serine/threonine kinase inhibitor activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Inka2/Prkar2b/Cdkn2c/Cib1/Hexim1/Parp1/Prkag2/Spred2</t>
+    <t xml:space="preserve">Prkar2b/Inka2/Cdkn2c/Spred2/Prkag2/Hexim1/Cib1/Parp1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0045920</t>
@@ -8428,7 +8428,7 @@
     <t xml:space="preserve">negative regulation of exocytosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Snca/Smcr8/C9orf72/Rap1b/Vps4b/Lgals9/Spi1/Cd84</t>
+    <t xml:space="preserve">Snca/Cd84/Spi1/Lgals9/Smcr8/Rap1b/C9orf72/Vps4b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000515</t>
@@ -8437,7 +8437,7 @@
     <t xml:space="preserve">negative regulation of CD4-positive, alpha-beta T cell activation</t>
   </si>
   <si>
-    <t xml:space="preserve">Zbtb7b/Vsir/Cbfb/Il4/Lgals9/Lgals7/Cd44/Jak3</t>
+    <t xml:space="preserve">Jak3/Cd44/Cbfb/Lgals9/Zbtb7b/Il4/Lgals7/Vsir</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0001702</t>
@@ -8446,7 +8446,7 @@
     <t xml:space="preserve">gastrulation with mouth forming second</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctnnb1/Lrp5/Ldb1/Megf8/Srf/Tenm4/Gdf3</t>
+    <t xml:space="preserve">Megf8/Gdf3/Tenm4/Ldb1/Srf/Ctnnb1/Lrp5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0044788</t>
@@ -8455,7 +8455,7 @@
     <t xml:space="preserve">modulation by host of viral process</t>
   </si>
   <si>
-    <t xml:space="preserve">Pcx/Igf2r/Tmem41b/Stom/Nucks1/Vapa/Apoe</t>
+    <t xml:space="preserve">Vapa/Apoe/Igf2r/Pcx/Tmem41b/Nucks1/Stom</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071353</t>
@@ -8464,7 +8464,7 @@
     <t xml:space="preserve">cellular response to interleukin-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Fasn/Alad/Hsp90ab1/Impdh2/Rpl3/Coro1a/Jak3</t>
+    <t xml:space="preserve">Jak3/Coro1a/Fasn/Rpl3/Impdh2/Hsp90ab1/Alad</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002286</t>
@@ -8473,7 +8473,7 @@
     <t xml:space="preserve">T cell activation involved in immune response</t>
   </si>
   <si>
-    <t xml:space="preserve">Tsc1/Zbtb7b/Atp7a/Shb/Rara/Psen1/Trp53/Sema4a/Havcr2/Il4/Spn/Tgfb1/Myb/Jak3/Apbb1ip/Lcp1</t>
+    <t xml:space="preserve">Jak3/Myb/Tgfb1/Spn/Apbb1ip/Tsc1/Lcp1/Trp53/Zbtb7b/Il4/Sema4a/Havcr2/Atp7a/Psen1/Rara/Shb</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046031</t>
@@ -8482,7 +8482,7 @@
     <t xml:space="preserve">ADP metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Ampd3/Pfkfb2/Eno3/Ddit4/Pkm/Nupr1/Bpgm/Mlst8/Mtch2/Psen1/Gpi1/Prkag2/Khk/Hk2/P2rx7</t>
+    <t xml:space="preserve">Ampd3/Slc4a1/Pfkfb2/P2rx7/Ddit4/Khk/Mtch2/Mlst8/Pkm/Prkag2/Eno3/Hk2/Psen1/Bpgm/Nupr1/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006103</t>
@@ -8491,7 +8491,7 @@
     <t xml:space="preserve">2-oxoglutarate metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Got1/Got2/Idh3g/Idh3a/Kyat3</t>
+    <t xml:space="preserve">Kyat3/Idh3a/Got2/Idh3g/Got1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032693</t>
@@ -8500,7 +8500,7 @@
     <t xml:space="preserve">negative regulation of interleukin-10 production</t>
   </si>
   <si>
-    <t xml:space="preserve">Vsir/Trib2/Tyrobp/Jak3/Cd84</t>
+    <t xml:space="preserve">Jak3/Trib2/Cd84/Tyrobp/Vsir</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0042492</t>
@@ -8515,7 +8515,7 @@
     <t xml:space="preserve">autophagic cell death</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamp1/Trp53inp1/Sh3glb1/Dapk1/Laptm5</t>
+    <t xml:space="preserve">Laptm5/Lamp1/Trp53inp1/Dapk1/Sh3glb1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0071404</t>
@@ -8524,7 +8524,7 @@
     <t xml:space="preserve">cellular response to low-density lipoprotein particle stimulus</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ldlr/Mylip/Itgb2/Syk</t>
+    <t xml:space="preserve">Syk/Cd36/Ldlr/Mylip/Itgb2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0072350</t>
@@ -8533,7 +8533,7 @@
     <t xml:space="preserve">tricarboxylic acid metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Aco1/Cs/Idh3g/Idh3a/Idh2</t>
+    <t xml:space="preserve">Idh2/Aco1/Idh3a/Cs/Idh3g</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901659</t>
@@ -8542,7 +8542,7 @@
     <t xml:space="preserve">glycosyl compound biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Adal/Tyw1/Mtap/Aprt/Pgm2</t>
+    <t xml:space="preserve">Pgm2/Adal/Tyw1/Aprt/Mtap</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901862</t>
@@ -8551,7 +8551,7 @@
     <t xml:space="preserve">negative regulation of muscle tissue development</t>
   </si>
   <si>
-    <t xml:space="preserve">Hdac5/Flcn/Nras/Tgfb1/Hdac7</t>
+    <t xml:space="preserve">Hdac7/Tgfb1/Hdac5/Flcn/Nras</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902004</t>
@@ -8560,7 +8560,7 @@
     <t xml:space="preserve">positive regulation of amyloid-beta formation</t>
   </si>
   <si>
-    <t xml:space="preserve">Abcg1/Picalm/Ifngr1/Abca2/Apoe</t>
+    <t xml:space="preserve">Picalm/Abcg1/Abca2/Apoe/Ifngr1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990380</t>
@@ -8578,7 +8578,7 @@
     <t xml:space="preserve">steroid biosynthetic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Dhrs11/Insig1/Abcg1/Mvd/Msmo1/Stard4/Lss/Sqle/Hmgcr/Lpcat3/Pmvk/Sc5d/Cyb5r3/Sirt1/Scp2/Igf1r/H6pd/Hsd17b11/Nr1d1/Apoe</t>
+    <t xml:space="preserve">Egr1/Abcg1/Dhrs11/Stard4/Apoe/Insig1/Sqle/Msmo1/Mvd/H6pd/Hsd17b11/Lss/Nr1d1/Hmgcr/Lpcat3/Cyb5r3/Sirt1/Sc5d/Scp2/Igf1r/Pmvk</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043467</t>
@@ -8587,7 +8587,7 @@
     <t xml:space="preserve">regulation of generation of precursor metabolites and energy</t>
   </si>
   <si>
-    <t xml:space="preserve">Slc4a1/Cd36/Rubcnl/Ddit4/Nupr1/Mlst8/Flcn/Atp7a/Ppp1r3f/Mtch2/Sorbs1/Psen1/Phb2/Ppif/Prkag2/Trp53/Khk/Ak4/Il4/Phlda2/P2rx7</t>
+    <t xml:space="preserve">Slc4a1/P2rx7/Ddit4/Cd36/Khk/Mtch2/Mlst8/Trp53/Phlda2/Il4/Prkag2/Ppif/Atp7a/Rubcnl/Flcn/Psen1/Ak4/Nupr1/Ppp1r3f/Phb2/Sorbs1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043679</t>
@@ -8596,7 +8596,7 @@
     <t xml:space="preserve">axon terminus</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Snca/Itsn1/Mylk2/Prnp/Dpysl2/Clcn3/Polg/Ap3d1/Elk1/Got1/Fkbp1a/Prkca/Unc13a/Arpc2/Slc4a8/Atp1a3/Cplx2/Kcnab2/Tspoap1/P2rx7</t>
+    <t xml:space="preserve">Atp6v0d1/Snca/Tspoap1/Prnp/Itsn1/Kcnab2/P2rx7/Arpc2/Polg/Clcn3/Dpysl2/Ap3d1/Slc4a8/Mylk2/Cplx2/Prkca/Atp1a3/Elk1/Fkbp1a/Got1/Unc13a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1901653</t>
@@ -8608,7 +8608,7 @@
     <t xml:space="preserve">271/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Appl2/Car2/Slc30a10/Agtr1a/Insig1/Prnp/Pkm/Zbtb7b/Atp2b1/Socs2/Foxo4/Sesn3/Nck1/Sorbs1/Rb1/Ncoa1/Pip4k2c/Sirt1/Rps6kb1/Uso1/Psen1/Parp1/Ctnnb1/Nucks1/Igf1r/Prkca/Snx5/Stat5a/Eif4ebp2/Pcsk9/Trp53/Stat5b/Zfp36l1/Atp1a3/Rac1/Vim/Arhgef2/Jak3</t>
+    <t xml:space="preserve">Car2/Jak3/Appl2/Arhgef2/Prnp/Slc30a10/Rac1/Vim/Atp2b1/Stat5b/Cd36/Insig1/Eif4ebp2/Pkm/Trp53/Zbtb7b/Agtr1a/Socs2/Stat5a/Zfp36l1/Ctnnb1/Rb1/Snx5/Nucks1/Prkca/Atp1a3/Psen1/Sesn3/Sirt1/Ncoa1/Pcsk9/Foxo4/Sorbs1/Igf1r/Nck1/Parp1/Rps6kb1/Pip4k2c/Uso1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000377</t>
@@ -8617,7 +8617,7 @@
     <t xml:space="preserve">regulation of reactive oxygen species metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Ctns/Slc30a10/Snca/Prdx2/Agtr1a/Pikfyve/Clcn3/Brca1/Tusc2/Sirt1/Ncf2/Hspd1/Itgb2/Trp53/Plcg2/Hk2/Aldh2/Il4/Tgfb1/Tyrobp/Syk</t>
+    <t xml:space="preserve">Prdx2/Snca/Syk/Tgfb1/Slc30a10/Ctns/Aldh2/Plcg2/Cd36/Pikfyve/Trp53/Clcn3/Agtr1a/Tyrobp/Il4/Itgb2/Hk2/Ncf2/Tusc2/Sirt1/Hspd1/Brca1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002823</t>
@@ -8626,7 +8626,7 @@
     <t xml:space="preserve">negative regulation of adaptive immune response based on somatic recombination of immune receptors built from immunoglobulin superfamily domains</t>
   </si>
   <si>
-    <t xml:space="preserve">Zbtb7b/Vsir/Ptpn6/Il27ra/Havcr2/Il4/Spn/Ptprc/Jak3/Il1rl1</t>
+    <t xml:space="preserve">Jak3/Il1rl1/Ptprc/Spn/Ptpn6/Zbtb7b/Il4/Il27ra/Havcr2/Vsir</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0008361</t>
@@ -8635,7 +8635,7 @@
     <t xml:space="preserve">regulation of cell size</t>
   </si>
   <si>
-    <t xml:space="preserve">Sema4b/Tsc1/Kel/Dpysl2/Clcn3/Cln8/Atp7a/Xk/Dip2b/Cdkl5/Golga4/Slc12a7/Lrrc8a/Arhgap35/Cttn/Rpl4/Hsp90ab1/Wdr36/Ulk2/Megf8/Srf/Abcb8/Sema4a/Ano6/Rac1/Ptprs/Apoe/P2rx7</t>
+    <t xml:space="preserve">Ptprs/Ano6/Tsc1/Rac1/P2rx7/Apoe/Megf8/Dip2b/Abcb8/Clcn3/Dpysl2/Sema4b/Xk/Sema4a/Srf/Kel/Lrrc8a/Hsp90ab1/Atp7a/Ulk2/Slc12a7/Golga4/Cdkl5/Rpl4/Wdr36/Arhgap35/Cttn/Cln8</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0002260</t>
@@ -8644,7 +8644,7 @@
     <t xml:space="preserve">lymphocyte homeostasis</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Prdx2/Bax/Bcl2l11/Tsc22d3/Stat5a/Pik3cd/Stat5b/Traf3ip2/Pmaip1/Tgfb1/Cd44/Coro1a/Jak3/P2rx7</t>
+    <t xml:space="preserve">Prdx2/Spta1/Jak3/Coro1a/Tgfb1/Cd44/P2rx7/Stat5b/Pmaip1/Pik3cd/Stat5a/Bcl2l11/Traf3ip2/Bax/Tsc22d3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0006664</t>
@@ -8653,7 +8653,7 @@
     <t xml:space="preserve">glycolipid metabolic process</t>
   </si>
   <si>
-    <t xml:space="preserve">St3gal1/St3gal6/Neu1/St3gal2/Gba/Hexa/Bax/Pigt/St6galnac4/Gla/Ugcg/Abca2/B4galnt1/Pgap2/Fut4</t>
+    <t xml:space="preserve">St3gal1/Abca2/Ugcg/Pgap2/Gba/Neu1/Fut4/B4galnt1/St3gal6/Pigt/Gla/Hexa/St3gal2/Bax/St6galnac4</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0043525</t>
@@ -8662,7 +8662,7 @@
     <t xml:space="preserve">positive regulation of neuron apoptotic process</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Optn/Grn/Prnp/Nupr1/Fbxw7/Bax/Bcl2l11/Mcl1/Ctnnb1/Ncf2/Pcsk9/Trp53/Pmaip1/Tyrobp</t>
+    <t xml:space="preserve">Egr1/Prnp/Grn/Optn/Pmaip1/Fbxw7/Trp53/Tyrobp/Ctnnb1/Mcl1/Bcl2l11/Ncf2/Pcsk9/Bax/Nupr1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0046849</t>
@@ -8671,7 +8671,7 @@
     <t xml:space="preserve">bone remodeling</t>
   </si>
   <si>
-    <t xml:space="preserve">Car2/Tfrc/Tpp1/Ubash3b/Suco/Ctnnb1/Lrp5/Def8/Prkca/Lrrk1/Snx10/Rac1/Rac2/P2rx7/Syk</t>
+    <t xml:space="preserve">Car2/Syk/Tpp1/Rac2/Rac1/P2rx7/Lrrk1/Snx10/Ctnnb1/Suco/Tfrc/Lrp5/Def8/Prkca/Ubash3b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1903509</t>
@@ -8689,7 +8689,7 @@
     <t xml:space="preserve">633/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Mid1ip1/Tmod1/Map3k1/Add2/Nfe2/Dmtn/Sptb/Snca/Dnajb2/Map1a/Tfrc/Sema4b/Mdm1/Prnp/Tsc1/Picalm/Nupr1/Ldlr/Mylip/Ssh2/Rab3ip/Gba/Trak2/Smcr8/Wasl/Fbxo5/Flcn/Cib1/Wapl/Dip2b/Ttbk2/Dyrk1a/Birc5/Camsap2/Vps35/Swap70/Twf1/Acd/Taok1/Clec16a/Scaf4/Psen1/Parp1/Was/Ubqln4/Flii/Pgrmc1/Itm2c/Syngap1/Ulk2/Sptan1/Rps6ka2/Flna/Adck1/Ptpn9/Ppif/Pcsk9/Nat10/Ankrd13b/Abca2/Arpc2/Trp53/Sema4a/Xrcc5/Kat2a/Ankrd27/Rcc2/Capg/Vim/Ptprs/Arhgef2/Mmp14/Apoe/Vill/Coro1a/Lgals1/Arhgef18/Dpp4/Rin3</t>
+    <t xml:space="preserve">Lgals1/Spta1/Add2/Sptb/Map3k1/Snca/Picalm/Arhgef2/Vill/Mid1ip1/Ptprs/Coro1a/Tmod1/Prnp/Ankrd27/Tsc1/Dmtn/Nfe2/Capg/Rcc2/Mdm1/Rin3/Abca2/Wapl/Vim/Kat2a/Arpc2/Apoe/Ldlr/Arhgef18/Dpp4/Xrcc5/Dyrk1a/Flna/Dip2b/Gba/Nat10/Trp53/Map1a/Ssh2/Sema4b/Rab3ip/Ankrd13b/Mmp14/Wasl/Sema4a/Ptpn9/Dnajb2/Mylip/Smcr8/Vps35/Flii/Ppif/Twf1/Camsap2/Ubqln4/Fbxo5/Tfrc/Sptan1/Trak2/Cib1/Swap70/Ttbk2/Rps6ka2/Flcn/Birc5/Psen1/Ulk2/Acd/Adck1/Taok1/Pgrmc1/Pcsk9/Nupr1/Syngap1/Itm2c/Scaf4/Parp1/Clec16a/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0060537</t>
@@ -8701,7 +8701,7 @@
     <t xml:space="preserve">340/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Btg2/Egr2/Cited2/Hlf/Gpcpd1/Mylk2/Sox6/Arntl/Mylpf/Tsc1/Fos/Nupr1/Pim1/Kel/Mybpc3/Epor/Hdac5/Hmgcr/Flcn/Xk/Rara/Rb1/Med20/Homer1/Sirt1/Rps6kb1/Sav1/Nras/Ctnnb1/Fkbp1a/Tnni3/Myh10/Srf/Prmt1/Fzd7/Tcf7l2/Kat2a/Popdc2/Nr1d2/Rgs2/Vamp5/Ripor2/Tenm4/Tgfb1/Hdac7/Eng</t>
+    <t xml:space="preserve">Hdac7/Egr1/Btg2/Tgfb1/Tsc1/Ripor2/Cited2/Eng/Hlf/Kat2a/Vamp5/Nr1d2/Arntl/Tenm4/Epor/Egr2/Xk/Myh10/Rgs2/Fzd7/Prmt1/Srf/Ctnnb1/Hdac5/Kel/Rb1/Gpcpd1/Hmgcr/Mylpf/Mylk2/Sox6/Flcn/Sirt1/Fkbp1a/Fos/Tnni3/Sav1/Rara/Nupr1/Nras/Popdc2/Homer1/Med20/Tcf7l2/Pim1/Rps6kb1/Mybpc3</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030427</t>
@@ -8710,7 +8710,7 @@
     <t xml:space="preserve">site of polarized growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobl/Snca/Als2/Tsc1/Dpysl2/Hdac5/Trak2/Map3k12/Usp9x/Cib1/Ppp1r9b/C9orf72/Cdkl5/Myo9a/Acap3/Cttn/Sirt1/Psen1/Iqgap1/Cbl/Hsp90ab1/Copg2/Myh10/Hcls1/Flna/Arpc2/Cxcr4</t>
+    <t xml:space="preserve">Cobl/Snca/Tsc1/Cxcr4/Als2/Arpc2/Flna/Usp9x/Dpysl2/Myh10/Ppp1r9b/Hdac5/Copg2/Hcls1/Trak2/Cib1/Hsp90ab1/Psen1/Sirt1/C9orf72/Iqgap1/Cdkl5/Map3k12/Cbl/Cttn/Acap3/Myo9a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1990266</t>
@@ -8719,7 +8719,7 @@
     <t xml:space="preserve">neutrophil migration</t>
   </si>
   <si>
-    <t xml:space="preserve">Prex1/Pikfyve/Mospd2/Mpp1/Pde4d/Wdr1/Prkca/Itgb2/Fcgr3/Vav1/Pde4b/Fut4/Rac1/Ripor2/Rac2/Dpp4/Syk</t>
+    <t xml:space="preserve">Syk/Rac2/Rac1/Ripor2/Vav1/Prex1/Pikfyve/Dpp4/Fut4/Wdr1/Mospd2/Fcgr3/Mpp1/Itgb2/Prkca/Pde4b/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032272</t>
@@ -8728,7 +8728,7 @@
     <t xml:space="preserve">negative regulation of protein polymerization</t>
   </si>
   <si>
-    <t xml:space="preserve">Spta1/Tmod1/Add2/Dmtn/Sptb/Snca/Ssh2/Dyrk1a/Twf1/Flii/Sptan1/Arpc2/Capg/Vill</t>
+    <t xml:space="preserve">Spta1/Add2/Sptb/Snca/Vill/Tmod1/Dmtn/Capg/Arpc2/Dyrk1a/Ssh2/Flii/Twf1/Sptan1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0016791</t>
@@ -8740,7 +8740,7 @@
     <t xml:space="preserve">230/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Ptp4a3/Lrrc39/Pip4p1/Pfkfb2/Dusp6/Ptpn23/Cdc25b/Ubash3b/Ssh2/Ppp2r5a/Nt5dc2/Mtmr3/Ppm1b/Mtmr12/Ppp3r1/Ptpru/Ppa2/Pfkfb3/Enoph1/Nt5m/Timm50/Ptpn9/Ssu72/Lhpp/Plpp2/Pdxp/Mtmr9/Ptpn6/Ppp2r1a/Ptpn18/Ppm1h/G6pc3/Ptprs/Ptprc</t>
+    <t xml:space="preserve">Ptprs/Ptprc/Pip4p1/Pfkfb2/Ptpn23/Ppp2r5a/Ppp2r1a/Cdc25b/Mtmr9/Ptpn6/Ptp4a3/Ssh2/Pdxp/G6pc3/Dusp6/Mtmr3/Timm50/Lhpp/Lrrc39/Ptpn18/Ptpn9/Ppm1h/Ssu72/Nt5dc2/Ubash3b/Plpp2/Ppp3r1/Mtmr12/Enoph1/Ptpru/Pfkfb3/Ppa2/Ppm1b/Nt5m</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0099024</t>
@@ -8761,7 +8761,7 @@
     <t xml:space="preserve">264/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Rph3al/Glrx/Prnp/Pfkfb2/Abcg1/Ptpn23/Arrb1/Ppard/Fbxw7/Cib1/Vps35/Brca1/Exoc1/Stom/Sirt1/Sh3glb1/Rack1/Psen1/Trim28/Ipo5/Ergic3/Tm7sf3/Hsp90ab1/Myh10/Wipf1/Hcls1/Sar1b/Flna/Ier3ip1/Tcf7l2/Ripor1/Akap5/Arpc2/Pmaip1/Rac1/Tgfb1/Sytl4/P2rx7</t>
+    <t xml:space="preserve">Prnp/Tgfb1/Rph3al/Abcg1/Rac1/Pfkfb2/Ptpn23/P2rx7/Ripor1/Glrx/Arpc2/Flna/Pmaip1/Fbxw7/Sytl4/Myh10/Ppard/Vps35/Sh3glb1/Arrb1/Hcls1/Wipf1/Sar1b/Ergic3/Cib1/Hsp90ab1/Trim28/Ier3ip1/Exoc1/Psen1/Sirt1/Tm7sf3/Brca1/Ipo5/Tcf7l2/Stom/Rack1/Akap5</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0030136</t>
@@ -8770,7 +8770,7 @@
     <t xml:space="preserve">clathrin-coated vesicle</t>
   </si>
   <si>
-    <t xml:space="preserve">Pheta2/Picalm/Cltc/Gga2/Numb/Nrgn/Syn1/Igf2r/Epn1/Myo6/Atp7a/Dvl2/Fcho1/Ap2m1/Snx3/Gopc/Ap1g1/Unc13d</t>
+    <t xml:space="preserve">Picalm/Cltc/Gga2/Pheta2/Epn1/Igf2r/Unc13d/Ap1g1/Myo6/Numb/Dvl2/Nrgn/Atp7a/Ap2m1/Fcho1/Snx3/Syn1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0032446</t>
@@ -8782,7 +8782,7 @@
     <t xml:space="preserve">653/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Map3k1/Egr2/Trim10/Trim2/Uba7/Dnajb2/Zswim8/Herc6/Ankrd9/Ube2l6/Cnot4/Vps11/Tollip/Mylip/Ticam1/Rchy1/Rnf14/Rnf115/Arrb1/Trim56/Rnf139/Fbxw7/Hace1/Rnf146/Fbxo5/Dcun1d3/Rnf38/Wsb2/Med7/Fbxo11/Pias2/Rnf10/Kdm2a/Rnf168/Gabarap/Rnf185/Pcgf3/Mkrn1/Rnf167/Brca1/Arnt/Fancm/Med20/Trip12/Nxn/Pias1/Sirt1/Fbxo38/Dcun1d1/Klhl9/Rack1/Ltn1/Fbxw11/Psen1/Ctnnb1/Prpf19/Nedd4/Trim28/Ube2e1/Trim35/Gtpbp4/Cbl/Rbck1/Hsp90ab1/Fance/Jade2/Cul7/Ube2s/Traf3/Dtx4/Dtx3l/Ifih1/Rnf138/Aktip/Pcgf2/Traf3ip2/Cbfb/Prr7/Rnf125/Trib2/Laptm5</t>
+    <t xml:space="preserve">Egr1/Map3k1/Laptm5/Trim2/Trib2/Rnf115/Uba7/Trim10/Cbfb/Tollip/Zswim8/Vps11/Cnot4/Rnf125/Rnf14/Herc6/Arnt/Fbxw7/Rnf38/Rchy1/Kdm2a/Rnf139/Gabarap/Pias2/Trim56/Hace1/Traf3/Wsb2/Egr2/Fbxo11/Ticam1/Rnf146/Ube2l6/Pcgf2/Rnf138/Cul7/Ankrd9/Ctnnb1/Dnajb2/Mylip/Rnf10/Prr7/Rnf168/Aktip/Rbck1/Arrb1/Nedd4/Fbxo5/Pcgf3/Trip12/Med7/Ltn1/Rnf167/Ube2s/Dtx3l/Dtx4/Prpf19/Hsp90ab1/Trim28/Psen1/Ifih1/Fbxo38/Sirt1/Fancm/Traf3ip2/Dcun1d1/Rnf185/Trim35/Brca1/Pias1/Gtpbp4/Dcun1d3/Ube2e1/Med20/Klhl9/Fbxw11/Fance/Nxn/Cbl/Jade2/Mkrn1/Rack1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0140657</t>
@@ -8794,7 +8794,7 @@
     <t xml:space="preserve">473/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Atp6v0d1/Abcb10/Abcg2/Atp6v1d/Abcb6/Abcg1/Chd2/Atp6v1c1/Atp6v1e1/Pikfyve/Myo6/Atp2b1/Atp6v1a/Kif13b/Atp6v1b2/Atp7a/Atp6v0b/Myo9a/Ddx6/Orc1/Fancm/Morc2a/Atp6v1g1/Srcap/Atad2b/Helq/Vps4b/Pex6/Ddx27/Rfc2/Ddx18/Recql/Cct6a/Ddx21/Ddx49/Cct2/Atad1/Hsp90ab1/Dhx35/Atad3a/Dhx33/Ruvbl2/Myh10/Mov10/Hspd1/Eif4a2/Acsf2/Tdrd9/Ifih1/Vwa8/Kif1c/Abca2/Trp53/Abcb8/Acsl5/Xrcc5/Atp1b2/Atp1a3/Kif21b/Acsbg1/Myo1g/Dnah8</t>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Myo1g/Dnah8/Abcb6/Abcb10/Abcg2/Atp6v1c1/Atp6v1e1/Abcg1/Abca2/Kif21b/Acsl5/Vwa8/Atp2b1/Pikfyve/Xrcc5/Chd2/Atp6v1b2/Kif1c/Trp53/Atp6v1a/Abcb8/Myo6/Ddx6/Myh10/Atad1/Acsbg1/Eif4a2/Atp6v0b/Morc2a/Tdrd9/Atp1b2/Ruvbl2/Cct2/Mov10/Rfc2/Hsp90ab1/Srcap/Atp1a3/Atp7a/Dhx33/Atad2b/Ifih1/Kif13b/Orc1/Ddx18/Dhx35/Recql/Fancm/Hspd1/Acsf2/Atad3a/Pex6/Ddx21/Cct6a/Helq/Vps4b/Atp6v1g1/Ddx27/Ddx49/Myo9a</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0003713</t>
@@ -8806,7 +8806,7 @@
     <t xml:space="preserve">239/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Cited2/Hipk2/Dcaf6/Nupr1/Wbp2/Actn1/Hcfc2/Arrb1/Slc30a9/Med17/Kmt2c/Dyrk1a/Npat/Taf6l/Ccar1/Med13/Brca1/Elk1/Ncoa1/Med20/Sirt1/Kat6a/Ctnnb1/Trim28/Wdr77/Nucks1/Maged1/Rbck1/Rrp1b/Rap2c/Ss18/Lmo2/Jade1/Kat2a/Cbfb</t>
+    <t xml:space="preserve">Cbfb/Cited2/Actn1/Slc30a9/Kat2a/Wbp2/Ss18/Jade1/Dyrk1a/Hipk2/Dcaf6/Rap2c/Lmo2/Med13/Med17/Maged1/Ctnnb1/Npat/Rbck1/Hcfc2/Arrb1/Ccar1/Nucks1/Trim28/Elk1/Kmt2c/Sirt1/Ncoa1/Nupr1/Brca1/Kat6a/Taf6l/Med20/Wdr77/Rrp1b</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0050853</t>
@@ -8815,7 +8815,7 @@
     <t xml:space="preserve">B cell receptor signaling pathway</t>
   </si>
   <si>
-    <t xml:space="preserve">Bax/Lpxn/Ptpn6/Plcg2/Btk/Ptprc/Rftn1/Nfam1/Syk</t>
+    <t xml:space="preserve">Btk/Nfam1/Rftn1/Syk/Ptprc/Plcg2/Ptpn6/Bax/Lpxn</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0098751</t>
@@ -8824,7 +8824,7 @@
     <t xml:space="preserve">bone cell development</t>
   </si>
   <si>
-    <t xml:space="preserve">Tal1/Fbxw7/Abi1/Flna/Srf/Ptpn6/Lrrk1/Fli1/Tyrobp</t>
+    <t xml:space="preserve">Tal1/Fli1/Ptpn6/Lrrk1/Flna/Fbxw7/Tyrobp/Srf/Abi1</t>
   </si>
   <si>
     <t xml:space="preserve">GO:2000008</t>
@@ -8833,7 +8833,7 @@
     <t xml:space="preserve">regulation of protein localization to cell surface</t>
   </si>
   <si>
-    <t xml:space="preserve">Map1a/Picalm/Ctnnb1/Gopc/Hsp90ab1/Abca2/Rangrf/Kcnab2/Tyrobp</t>
+    <t xml:space="preserve">Picalm/Kcnab2/Abca2/Map1a/Rangrf/Tyrobp/Ctnnb1/Hsp90ab1/Gopc</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070374</t>
@@ -8842,7 +8842,7 @@
     <t xml:space="preserve">positive regulation of ERK1 and ERK2 cascade</t>
   </si>
   <si>
-    <t xml:space="preserve">Cd36/Slc30a10/Mturn/Arrb1/Epor/Map3k12/Akap12/Fbxw7/Hmgcr/Cib1/Glipr2/Rara/Garem1/Rap1b/Dnajc27/Phb2/Prkca/Havcr2/Cxcr4/Apoe/Tgfb1/Cd44/Ptprc</t>
+    <t xml:space="preserve">Ptprc/Tgfb1/Slc30a10/Cd44/Cxcr4/Apoe/Cd36/Mturn/Fbxw7/Epor/Havcr2/Arrb1/Hmgcr/Cib1/Prkca/Rap1b/Garem1/Rara/Map3k12/Phb2/Akap12/Dnajc27/Glipr2</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0007265</t>
@@ -8851,7 +8851,7 @@
     <t xml:space="preserve">Ras protein signal transduction</t>
   </si>
   <si>
-    <t xml:space="preserve">Agtr1a/Als2/Rgl1/Arrb1/Arfgef2/Arhgef12/Gpsm2/Flcn/Nckap1/Rap2b/Gabarap/Rap1b/Gna13/Arhgap35/Arhgef11/Setdb1/Nras/Was/Trim28/Cbl/Dgkz/Dennd4b/Syngap1/Rap2c/Ripor1/Vangl2/Rangrf/Rgl2/Rac1/Ripor2/Rac2/Arhgdig/Csf1/Arhgef2/Dock2/Apoe/Dok2/Arhgef18/Elmo1/Arap3/Arhgdib</t>
+    <t xml:space="preserve">Arap3/Dock2/Arhgef2/Rac2/Dok2/Rac1/Ripor2/Elmo1/Ripor1/Arhgdib/Als2/Arfgef2/Rgl2/Apoe/Arhgef18/Rap2b/Arhgdig/Gabarap/Agtr1a/Rangrf/Arhgef12/Rap2c/Dgkz/Gna13/Csf1/Dennd4b/Nckap1/Arrb1/Vangl2/Gpsm2/Rgl1/Trim28/Flcn/Arhgef11/Rap1b/Nras/Setdb1/Syngap1/Arhgap35/Cbl/Was</t>
   </si>
   <si>
     <t xml:space="preserve">GO:1902532</t>
@@ -8860,7 +8860,7 @@
     <t xml:space="preserve">negative regulation of intracellular signal transduction</t>
   </si>
   <si>
-    <t xml:space="preserve">Optn/Prnp/Arntl/Dusp6/Ddit4/Tsc1/Sesn1/Arhgap12/Gba/Arrb1/Grina/Hmgcr/Flcn/Cib1/Ppp1r10/Dag1/Sesn3/Dyrk1a/Ash1l/Otud7b/Bid/Mcl1/Arhgap35/Cpne1/Sirt1/Ppm1b/Fnip1/Sh3glb1/Usp47/Qars/Rack1/Fbxw11/Nono/Pde4d/Armc10/Dgkz/Syngap1/Igf1r/Prkca/Prmt1/Ppif/Ripor1/Ptpn6/Spred2/Rgs2/Nr1d1/Ripor2/Rgs14/Rnf125/Apoe/Cd44/Spi1/Hdac7/Ptprc/Dok2/P2rx7/Tbc1d10c/Arap3/Pik3ip1</t>
+    <t xml:space="preserve">Arap3/Hdac7/Ptprc/Prnp/Dok2/Tsc1/Cd44/Ripor2/Spi1/Tbc1d10c/Pik3ip1/P2rx7/Ripor1/Ddit4/Optn/Apoe/Rnf125/Ptpn6/Dyrk1a/Sesn1/Gba/Arntl/Rgs14/Spred2/Dag1/Dusp6/Rgs2/Dgkz/Prmt1/Nono/Nr1d1/Sh3glb1/Ppif/Arhgap12/Arrb1/Mcl1/Armc10/Hmgcr/Otud7b/Ppp1r10/Cib1/Prkca/Flcn/Bid/Cpne1/Sesn3/Sirt1/Ash1l/Grina/Fnip1/Syngap1/Arhgap35/Igf1r/Fbxw11/Usp47/Qars/Rack1/Ppm1b/Pde4d</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0031058</t>
@@ -8869,7 +8869,7 @@
     <t xml:space="preserve">positive regulation of histone modification</t>
   </si>
   <si>
-    <t xml:space="preserve">Wbp2/Zbtb7b/Arrb1/Kdm2a/Brca1/Gfi1b/Asxl2/Nsd3/Sirt1/Ctnnb1/Ddx21/Ruvbl2/Glyr1/Mybbp1a/Dnmt3b/Trp53/Kat2a/Tgfb1/Myb</t>
+    <t xml:space="preserve">Myb/Tgfb1/Glyr1/Kat2a/Wbp2/Dnmt3b/Kdm2a/Trp53/Zbtb7b/Ctnnb1/Mybbp1a/Arrb1/Ruvbl2/Sirt1/Nsd3/Brca1/Gfi1b/Asxl2/Ddx21</t>
   </si>
   <si>
     <t xml:space="preserve">GO:0070647</t>
@@ -8881,7 +8881,19 @@
     <t xml:space="preserve">773/15354</t>
   </si>
   <si>
-    <t xml:space="preserve">Egr1/Map3k1/Egr2/Trim10/Trim2/Uba7/Dnajb2/Mindy2/Zswim8/Herc6/Ankrd9/Ube2l6/Cnot4/Vps11/Yod1/Tollip/Mylip/Ticam1/Rchy1/Rnf14/Rnf115/Arrb1/Trim56/Rnf139/Fbxw7/Hace1/Rnf146/Fbxo5/Dcun1d3/Rnf38/Wsb2/Med7/Usp9x/Fbxo11/Pias2/Rnf10/Kdm2a/Rnf168/Gabarap/Taf6l/Rnf185/Pcgf3/Mkrn1/Usp25/Otud7b/Rnf167/Brca1/Arnt/Fancm/Med20/Trip12/Nxn/Pias1/Sirt1/Fbxo38/Dcun1d1/Usp37/Usp15/Klhl9/Usp47/Rack1/Ltn1/Fbxw11/Otud4/Psen1/Ctnnb1/Prpf19/Nedd4/Trim28/Ube2e1/Trim35/Gtpbp4/Cbl/Rbck1/Hsp90ab1/Fance/Jade2/Sgf29/Cul7/Ube2s/Traf3/Dtx4/Dtx3l/Ifih1/Otud6b/Rnf138/Aktip/Pcgf2/Kat2a/Traf3ip2/Cbfb/Prr7/Rnf125/Trib2/Laptm5</t>
+    <t xml:space="preserve">Egr1/Map3k1/Laptm5/Trim2/Trib2/Rnf115/Uba7/Trim10/Cbfb/Mindy2/Tollip/Zswim8/Vps11/Kat2a/Cnot4/Yod1/Rnf125/Rnf14/Herc6/Arnt/Fbxw7/Rnf38/Rchy1/Kdm2a/Rnf139/Usp9x/Gabarap/Pias2/Trim56/Hace1/Traf3/Wsb2/Egr2/Fbxo11/Ticam1/Rnf146/Ube2l6/Pcgf2/Rnf138/Cul7/Ankrd9/Ctnnb1/Dnajb2/Mylip/Otud6b/Rnf10/Prr7/Rnf168/Aktip/Rbck1/Arrb1/Nedd4/Otud4/Fbxo5/Pcgf3/Trip12/Med7/Ltn1/Rnf167/Ube2s/Otud7b/Dtx3l/Dtx4/Prpf19/Usp15/Hsp90ab1/Usp25/Trim28/Psen1/Ifih1/Fbxo38/Sirt1/Sgf29/Fancm/Traf3ip2/Dcun1d1/Rnf185/Trim35/Brca1/Pias1/Gtpbp4/Dcun1d3/Taf6l/Ube2e1/Med20/Klhl9/Fbxw11/Fance/Usp47/Nxn/Cbl/Jade2/Mkrn1/Usp37/Rack1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subcategory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organismal Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excretory system</t>
   </si>
   <si>
     <t xml:space="preserve">mmu04966</t>
@@ -8890,13 +8902,79 @@
     <t xml:space="preserve">Collecting duct acid secretion - Mus musculus (house mouse)</t>
   </si>
   <si>
-    <t xml:space="preserve">11/734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/6241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slc4a1/Car2/Atp6v0d1/Atp6v1d/Atp6v1c1/Atp6v1e1/Atp6v0a1/Atp6v1a/Atp6v1b2/Slc12a7/Atp6v1g1</t>
+    <t xml:space="preserve">11/727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/6176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car2/Atp6v0d1/Atp6v1d/Slc4a1/Atp6v1c1/Atp6v1e1/Atp6v1b2/Atp6v1a/Atp6v0a1/Slc12a7/Atp6v1g1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-917977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferrin endocytosis and recycling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Atp6v1c1/Atp6v1e1/Mcoln1/Atp6v1b2/Atp6v1a/Atp6v0a1/Tfr2/Atp6v0b/Tfrc/Atp6v1g1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-9639288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amino acids regulate mTORC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Rragc/Atp6v1c1/Atp6v1e1/Fnip2/Sesn1/Atp6v1b2/Mlst8/Atp6v1a/Atp6v0b/Lamtor3/Lamtor1/Flcn/Fnip1/Atp6v1g1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-9711097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellular response to starvation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-9013149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAC1 GTPase cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arap3/Dock2/Arhgap23/Rac1/Dock8/Arhgap27/Def6/Vangl1/Vav1/Arhgdib/Als2/Prex1/Pld2/Arhgef18/Kalrn/Gmip/Arhgef6/Pkn2/Gna13/Lamtor1/Nckap1/Arhgap12/Esyt1/Tfrc/Plekhg2/Arhgap9/Swap70/Arhgef11/Ncf2/Iqgap1/Cdc42bpa/Arhgap15/Abi1/Arhgap35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-6798695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutrophil degranulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dock2/Ampd3/Ctsd/Atp6v1d/Nfam1/Ptprc/Ano6/Grn/Lamp1/Cd44/Rac1/Cd47/Adgre5/Dpp7/Kcnab2/Surf4/Tbc1d10c/Cap1/Tollip/Cd53/Vapa/Cd36/Adam10/Igf2r/Cmtm6/Atp6ap2/Ptpn6/Xrcc5/Serpinb1a/Unc13d/Gusb/Rap2b/Neu1/Txndc5/Pkm/Apeh/Prdx6/Atp6v0a1/H2-T23/Tyrobp/Ctsa/Rap2c/Pgm2/Lamtor3/Lamtor1/Impdh2/Mospd2/Creg1/Cct2/Man2b1/Arhgap9/Cyb5r3/Itgb2/Hsp90ab1/Prdx4/Rab37/Rap1b/Cpne1/Actr2/Iqgap1/Pgrmc1/Alad/Rhof/Aprt/Atad3a/P2rx1/Stom/Tom1/Snap29/Vcl/Pa2g4/Gpi1</t>
   </si>
   <si>
     <t xml:space="preserve">R-MMU-8956320</t>
@@ -8905,79 +8983,58 @@
     <t xml:space="preserve">Nucleotide biosynthesis</t>
   </si>
   <si>
-    <t xml:space="preserve">9/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adss/Impdh2/Adsl/Umps/Cad/Adssl1/Atic/Pfas/Gart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-917977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transferrin endocytosis and recycling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Tfrc/Mcoln1/Atp6v1c1/Atp6v1e1/Atp6v0a1/Atp6v1a/Atp6v1b2/Atp6v0b/Atp6v1g1/Tfr2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-9639288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amino acids regulate mTORC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Rragc/Atp6v1c1/Atp6v1e1/Fnip2/Sesn1/Lamtor1/Mlst8/Atp6v1a/Atp6v1b2/Flcn/Lamtor3/Atp6v0b/Atp6v1g1/Fnip1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-9711097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellular response to starvation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-9013149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAC1 GTPase cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pld2/Arhgap23/Vangl1/Tfrc/Kalrn/Als2/Prex1/Arhgap12/Lamtor1/Arhgap15/Plekhg2/Nckap1/Pkn2/Swap70/Gna13/Arhgap35/Arhgef11/Cdc42bpa/Abi1/Iqgap1/Ncf2/Esyt1/Arhgap9/Vav1/Arhgef6/Gmip/Rac1/Dock8/Dock2/Def6/Arhgap27/Arhgef18/Arap3/Arhgdib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-73817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purine ribonucleoside monophosphate biosynthesis</t>
-  </si>
-  <si>
     <t xml:space="preserve">7/806</t>
   </si>
   <si>
-    <t xml:space="preserve">11/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adss/Impdh2/Adsl/Adssl1/Atic/Pfas/Gart</t>
+    <t xml:space="preserve">12/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gart/Pfas/Atic/Cad/Umps/Adsl/Impdh2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-168249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innate Immune System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atp6v0d1/Btk/Dock2/Ampd3/Ctsd/Atp6v1d/Psme4/Nfam1/Syk/Ptprc/Ano6/Psmb8/Rac2/Grn/Atp6v1c1/Atp6v1e1/Lamp1/Cd44/Rac1/Cd47/Adgre5/Dpp7/Kcnab2/Surf4/Elmo1/Tbc1d10c/Cap1/Ppp2r1a/Vav1/Tollip/Cd53/P2rx7/Vapa/Plcg2/Optn/Unc93b1/Arpc2/Cd36/Adam10/Igf2r/Pld2/Cmtm6/Atp6ap2/Ptpn6/Xrcc5/Serpinb1a/Unc13d/Grap2/Gusb/Irak1/Tbk1/Rap2b/Atp6v1b2/Neu1/Txndc5/Pkm/Apeh/Atp6v1a/Prdx6/Lcp2/Atp6v0a1/H2-T23/Trim56/Traf3/Ticam1/Dusp6/Tyrobp/Ctsa/Rap2c/Pgm2/Atp6v0b/Lamtor3/Lamtor1/Ctnnb1/Impdh2/Nckap1/Mospd2/Creg1/Cct2/Psme1/Wipf1/Man2b1/Arhgap9/Dtx4/Cyb5r3/Itgb2/Psmb10/Hsp90ab1/Prdx4/Atp7a/Rps6ka2/Rab37/Ncf2/Rap1b/Cpne1/Actr2/Fos/Iqgap1/Pgrmc1/Ppp3r1/Alad/Icam2/Rhof/Aprt/Atad3a/Abi1/Nck1/Fbxw11/Atp6v1g1/P2rx1/Stom/Tom1/Snap29/Vcl/Pa2g4/Gpi1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-917937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iron uptake and transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Slc11a2/Abcg2/Atp6v1c1/Atp6v1e1/Mcoln1/Atp6v1b2/Atp6v1a/Atp6v0a1/Tfr2/Aco1/Atp6v0b/Tfrc/Atp6v1g1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-9012999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHO GTPase cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">354/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arap3/Dock2/Picalm/Arhgef2/Rac2/Cltc/Arhgap23/Arhgef1/Rac1/Dock8/Arhgap27/Itsn1/Def6/Vangl1/Vav1/Actn1/Muc13/Vim/Arhgdib/Als2/Prex1/Pld2/Arhgef18/Kalrn/Gmip/Lman1/Arhgef6/Arhgdig/Myo6/Usp9x/Pkn2/Gna13/Tex2/Lamtor1/Nckap1/Mospd2/Ubxn11/Arhgap12/Twf1/Vangl2/Esyt1/Tfrc/Cct2/Plekhg2/Cpd/Arhgap9/Hsp90ab1/Swap70/Arhgef11/Ncf2/Iqgap1/Armcx3/Rhof/Cdc42bpa/Arhgap15/Akap12/Abi1/Arhgap35/Cct6a/Nck1/Stom/Myo9a/Gopc/Daam1</t>
   </si>
   <si>
     <t xml:space="preserve">R-MMU-189451</t>
@@ -8986,40 +9043,10 @@
     <t xml:space="preserve">Heme biosynthesis</t>
   </si>
   <si>
-    <t xml:space="preserve">13/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alas2/Abcg2/Fech/Hmbs/Urod/Alad/Cox10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-917937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iron uptake and transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atp6v0d1/Abcg2/Atp6v1d/Tfrc/Mcoln1/Atp6v1c1/Atp6v1e1/Slc11a2/Atp6v0a1/Atp6v1a/Atp6v1b2/Atp6v0b/Aco1/Atp6v1g1/Tfr2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-6798695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neutrophil degranulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd36/Ampd3/Atp6v1d/Cd47/H2-T23/Ctsd/Dpp7/Grn/Neu1/Serpinb1a/Adam10/Pkm/Lamp1/Tollip/Atp6v0a1/Rhof/Lamtor1/Mospd2/Atp6ap2/Igf2r/Apeh/Alad/Creg1/Lamtor3/Tom1/Rap2b/Ctsa/Rap1b/Stom/Cpne1/Cyb5r3/Vcl/Snap29/Iqgap1/Actr2/Man2b1/Pa2g4/Gpi1/Cct2/Pgrmc1/Hsp90ab1/Atad3a/Impdh2/Aprt/Prdx4/P2rx1/Txndc5/Arhgap9/Itgb2/Rap2c/Cap1/Prdx6/Ptpn6/Xrcc5/Cmtm6/Gusb/Vapa/Unc13d/Surf4/Ano6/Rab37/Rac1/Kcnab2/Pgm2/Dock2/Adgre5/Cd44/Tyrobp/Ptprc/Tbc1d10c/Nfam1/Cd53</t>
+    <t xml:space="preserve">13/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alas2/Fech/Abcg2/Urod/Hmbs/Cox10/Alad</t>
   </si>
   <si>
     <t xml:space="preserve">R-MMU-77387</t>
@@ -9028,40 +9055,13 @@
     <t xml:space="preserve">Insulin receptor recycling</t>
   </si>
   <si>
-    <t xml:space="preserve">22/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Atp6v1c1/Atp6v1e1/Atp6v0a1/Atp6v1a/Atp6v1b2/Atp6v0b/Atp6v1g1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-9012999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHO GTPase cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pld2/Arhgap23/Itsn1/Vangl1/Tfrc/Kalrn/Als2/Picalm/Cltc/Prex1/Rhof/Actn1/Arhgap12/Lamtor1/Mospd2/Akap12/Arhgap15/Armcx3/Plekhg2/Usp9x/Tex2/Nckap1/Pkn2/Nck1/Myo9a/Cpd/Swap70/Twf1/Gna13/Stom/Arhgap35/Arhgef11/Daam1/Cdc42bpa/Abi1/Iqgap1/Cct6a/Ncf2/Gopc/Cct2/Esyt1/Hsp90ab1/Lman1/Arhgap9/Arhgef1/Vangl2/Vav1/Arhgef6/Gmip/Rac1/Ubxn11/Dock8/Rac2/Vim/Arhgdig/Arhgef2/Dock2/Def6/Arhgap27/Arhgef18/Arap3/Arhgdib/Muc13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-MMU-168249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innate Immune System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115/806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">729/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cd36/Grap2/Pld2/Ampd3/Atp6v0d1/Atp6v1d/Cd47/H2-T23/Ctsd/Dpp7/Grn/Atp6v1c1/Neu1/Dusp6/Atp6v1e1/Serpinb1a/Adam10/Psme4/Pkm/Lamp1/Fos/Tollip/Atp6v0a1/Ticam1/Rhof/Lamtor1/Mospd2/Trim56/Atp6ap2/Igf2r/Apeh/Tbk1/Alad/Atp6v1a/Atp6v1b2/Atp7a/Creg1/Lamtor3/Tom1/Nckap1/Rap2b/Atp6v0b/Nck1/Ctsa/Rap1b/Stom/Atp6v1g1/Cpne1/Cyb5r3/Vcl/Snap29/Abi1/Fbxw11/Iqgap1/Actr2/Ctnnb1/Ppp3r1/Man2b1/Ncf2/Pa2g4/Gpi1/Cct2/Pgrmc1/Hsp90ab1/Atad3a/Wipf1/Impdh2/Aprt/Prdx4/Rps6ka2/Psme1/P2rx1/Traf3/Dtx4/Txndc5/Arhgap9/Itgb2/Rap2c/Cap1/Arpc2/Irak1/Prdx6/Ptpn6/Ppp2r1a/Xrcc5/Cmtm6/Icam2/Gusb/Plcg2/Vapa/Unc13d/Vav1/Surf4/Psmb10/Ano6/Rab37/Rac1/Rac2/Kcnab2/Pgm2/Dock2/Adgre5/Lcp2/Cd44/Tyrobp/Unc93b1/Btk/Ptprc/Elmo1/P2rx7/Tbc1d10c/Psmb8/Nfam1/Syk/Cd53</t>
+    <t xml:space="preserve">10/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atp6v0d1/Ctsd/Atp6v1d/Atp6v1c1/Atp6v1e1/Atp6v1b2/Atp6v1a/Atp6v0a1/Atp6v0b/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">R-MMU-1222556</t>
@@ -9073,10 +9073,10 @@
     <t xml:space="preserve">11/806</t>
   </si>
   <si>
-    <t xml:space="preserve">32/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Atp6v1c1/Atp6v1e1/Atp6v0a1/Atp6v1a/Atp6v1b2/Atp6v0b/Atp6v1g1/Ncf2/Rac2</t>
+    <t xml:space="preserve">32/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atp6v0d1/Atp6v1d/Rac2/Atp6v1c1/Atp6v1e1/Atp6v1b2/Atp6v1a/Atp6v0a1/Atp6v0b/Ncf2/Atp6v1g1</t>
   </si>
   <si>
     <t xml:space="preserve">R-MMU-193648</t>
@@ -9088,10 +9088,25 @@
     <t xml:space="preserve">13/806</t>
   </si>
   <si>
-    <t xml:space="preserve">42/6733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Itsn1/Kalrn/Prex1/Plekhg2/Bcl2l11/Gna13/Arhgef11/Arhgef1/Vav1/Arhgef6/Rac1/Arhgef2/Arhgef18</t>
+    <t xml:space="preserve">42/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arhgef2/Arhgef1/Rac1/Itsn1/Vav1/Prex1/Arhgef18/Kalrn/Arhgef6/Gna13/Plekhg2/Bcl2l11/Arhgef11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-MMU-9013404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAC2 GTPase cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71/6803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dock2/Rac2/Def6/Vangl1/Vav1/Prex1/Pld2/Lman1/Lamtor1/Nckap1/Esyt1/Tfrc/Swap70/Ncf2/Iqgap1/Armcx3/Abi1/Arhgap35</t>
   </si>
 </sst>
 </file>
@@ -17341,7 +17356,7 @@
         <v>1030</v>
       </c>
       <c r="F248" t="n">
-        <v>0.000313199046235689</v>
+        <v>0.00031319904623569</v>
       </c>
       <c r="G248" t="n">
         <v>0.0129058487999522</v>
@@ -21309,7 +21324,7 @@
         <v>1471</v>
       </c>
       <c r="F372" t="n">
-        <v>0.000915910393040965</v>
+        <v>0.000915910393040964</v>
       </c>
       <c r="G372" t="n">
         <v>0.0249860355221575</v>
@@ -21341,7 +21356,7 @@
         <v>1471</v>
       </c>
       <c r="F373" t="n">
-        <v>0.000915910393040965</v>
+        <v>0.000915910393040964</v>
       </c>
       <c r="G373" t="n">
         <v>0.0249860355221575</v>
@@ -21373,7 +21388,7 @@
         <v>1471</v>
       </c>
       <c r="F374" t="n">
-        <v>0.000915910393040965</v>
+        <v>0.000915910393040964</v>
       </c>
       <c r="G374" t="n">
         <v>0.0249860355221575</v>
@@ -21405,7 +21420,7 @@
         <v>1471</v>
       </c>
       <c r="F375" t="n">
-        <v>0.000915910393040965</v>
+        <v>0.000915910393040964</v>
       </c>
       <c r="G375" t="n">
         <v>0.0249860355221575</v>
@@ -21437,7 +21452,7 @@
         <v>1471</v>
       </c>
       <c r="F376" t="n">
-        <v>0.000915910393040965</v>
+        <v>0.000915910393040964</v>
       </c>
       <c r="G376" t="n">
         <v>0.0249860355221575</v>
@@ -36249,59 +36264,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>2956</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2957</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2956</v>
+        <v>2958</v>
       </c>
       <c r="B2" t="s">
-        <v>2957</v>
+        <v>2959</v>
       </c>
       <c r="C2" t="s">
-        <v>2958</v>
+        <v>2960</v>
       </c>
       <c r="D2" t="s">
-        <v>2959</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.000032450282111083</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0110979964819904</v>
+        <v>2961</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2963</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0105548812340259</v>
-      </c>
-      <c r="H2" t="s">
-        <v>2960</v>
+        <v>0.0000327091539538646</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0111865306522217</v>
       </c>
       <c r="I2" t="n">
+        <v>0.0106735133954716</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2964</v>
+      </c>
+      <c r="K2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -36347,86 +36374,86 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2961</v>
+        <v>2965</v>
       </c>
       <c r="B2" t="s">
-        <v>2962</v>
+        <v>2966</v>
       </c>
       <c r="C2" t="s">
-        <v>2963</v>
+        <v>2967</v>
       </c>
       <c r="D2" t="s">
-        <v>2964</v>
+        <v>2968</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000005534362437845</v>
+        <v>0.0000224783625500777</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00639218861571097</v>
+        <v>0.0195689846895614</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00623343979841489</v>
+        <v>0.019230348085501</v>
       </c>
       <c r="H2" t="s">
-        <v>2965</v>
+        <v>2969</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2966</v>
+        <v>2970</v>
       </c>
       <c r="B3" t="s">
-        <v>2967</v>
+        <v>2971</v>
       </c>
       <c r="C3" t="s">
-        <v>2968</v>
+        <v>2972</v>
       </c>
       <c r="D3" t="s">
-        <v>2969</v>
+        <v>2973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000249795192991565</v>
+        <v>0.0000554997392672824</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0141157747244183</v>
+        <v>0.0195689846895614</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0137652120803168</v>
+        <v>0.019230348085501</v>
       </c>
       <c r="H3" t="s">
-        <v>2970</v>
+        <v>2974</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2971</v>
+        <v>2975</v>
       </c>
       <c r="B4" t="s">
+        <v>2976</v>
+      </c>
+      <c r="C4" t="s">
         <v>2972</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>2973</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="n">
+        <v>0.0000554997392672824</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0195689846895614</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.019230348085501</v>
+      </c>
+      <c r="H4" t="s">
         <v>2974</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0000629790763996717</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0141157747244183</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0137652120803168</v>
-      </c>
-      <c r="H4" t="s">
-        <v>2975</v>
       </c>
       <c r="I4" t="n">
         <v>16</v>
@@ -36434,86 +36461,86 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="B5" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="C5" t="s">
-        <v>2973</v>
+        <v>2979</v>
       </c>
       <c r="D5" t="s">
-        <v>2974</v>
+        <v>2980</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000629790763996717</v>
+        <v>0.0000666745645300219</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0141157747244183</v>
+        <v>0.0195689846895614</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0137652120803168</v>
+        <v>0.019230348085501</v>
       </c>
       <c r="H5" t="s">
-        <v>2975</v>
+        <v>2981</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2978</v>
+        <v>2982</v>
       </c>
       <c r="B6" t="s">
-        <v>2979</v>
+        <v>2983</v>
       </c>
       <c r="C6" t="s">
-        <v>2980</v>
+        <v>2984</v>
       </c>
       <c r="D6" t="s">
-        <v>2981</v>
+        <v>2985</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0000708292690018564</v>
+        <v>0.000124074381752765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0141157747244183</v>
+        <v>0.0288940986788499</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0137652120803168</v>
+        <v>0.028394093205433</v>
       </c>
       <c r="H6" t="s">
-        <v>2982</v>
+        <v>2986</v>
       </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2983</v>
+        <v>2987</v>
       </c>
       <c r="B7" t="s">
-        <v>2984</v>
+        <v>2988</v>
       </c>
       <c r="C7" t="s">
-        <v>2985</v>
+        <v>2989</v>
       </c>
       <c r="D7" t="s">
-        <v>2986</v>
+        <v>2990</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000073328699867108</v>
+        <v>0.00014767001028373</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0141157747244183</v>
+        <v>0.0288940986788499</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0137652120803168</v>
+        <v>0.028394093205433</v>
       </c>
       <c r="H7" t="s">
-        <v>2987</v>
+        <v>2991</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
@@ -36521,57 +36548,57 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2988</v>
+        <v>2992</v>
       </c>
       <c r="B8" t="s">
-        <v>2989</v>
+        <v>2993</v>
       </c>
       <c r="C8" t="s">
-        <v>2985</v>
+        <v>2994</v>
       </c>
       <c r="D8" t="s">
-        <v>2990</v>
+        <v>2995</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000306728425774634</v>
+        <v>0.000216028042215981</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0408025063684297</v>
+        <v>0.0337322921106038</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0397891836994484</v>
+        <v>0.0331485628559327</v>
       </c>
       <c r="H8" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2992</v>
+        <v>2997</v>
       </c>
       <c r="B9" t="s">
-        <v>2993</v>
+        <v>2998</v>
       </c>
       <c r="C9" t="s">
-        <v>2994</v>
+        <v>2999</v>
       </c>
       <c r="D9" t="s">
-        <v>2995</v>
+        <v>3000</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000313510299415616</v>
+        <v>0.000279781608474491</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0408025063684297</v>
+        <v>0.0337322921106038</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0397891836994484</v>
+        <v>0.0331485628559327</v>
       </c>
       <c r="H9" t="s">
-        <v>2996</v>
+        <v>3001</v>
       </c>
       <c r="I9" t="n">
         <v>15</v>
@@ -36579,176 +36606,176 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2997</v>
+        <v>3002</v>
       </c>
       <c r="B10" t="s">
-        <v>2998</v>
+        <v>3003</v>
       </c>
       <c r="C10" t="s">
-        <v>2999</v>
+        <v>3004</v>
       </c>
       <c r="D10" t="s">
-        <v>3000</v>
+        <v>3005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000317941608065686</v>
+        <v>0.000280900570036227</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0408025063684297</v>
+        <v>0.0337322921106038</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0397891836994484</v>
+        <v>0.0331485628559327</v>
       </c>
       <c r="H10" t="s">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="I10" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3002</v>
+        <v>3007</v>
       </c>
       <c r="B11" t="s">
-        <v>3003</v>
+        <v>3008</v>
       </c>
       <c r="C11" t="s">
-        <v>2963</v>
+        <v>2989</v>
       </c>
       <c r="D11" t="s">
-        <v>3004</v>
+        <v>3009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000562994303995637</v>
+        <v>0.00028732787147022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0622445242638318</v>
+        <v>0.0337322921106038</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0606986930620187</v>
+        <v>0.0331485628559327</v>
       </c>
       <c r="H11" t="s">
-        <v>3005</v>
+        <v>3010</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3006</v>
+        <v>3011</v>
       </c>
       <c r="B12" t="s">
-        <v>3007</v>
+        <v>3012</v>
       </c>
       <c r="C12" t="s">
-        <v>3008</v>
+        <v>3013</v>
       </c>
       <c r="D12" t="s">
-        <v>3009</v>
+        <v>3014</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000592804992988875</v>
+        <v>0.000316650580610472</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0622445242638318</v>
+        <v>0.0337952528760631</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0606986930620187</v>
+        <v>0.0332104341003902</v>
       </c>
       <c r="H12" t="s">
-        <v>3010</v>
+        <v>3015</v>
       </c>
       <c r="I12" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3011</v>
+        <v>3016</v>
       </c>
       <c r="B13" t="s">
-        <v>3012</v>
+        <v>3017</v>
       </c>
       <c r="C13" t="s">
-        <v>3013</v>
+        <v>3018</v>
       </c>
       <c r="D13" t="s">
-        <v>3014</v>
+        <v>3019</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000718097621617114</v>
+        <v>0.000737952358028023</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0691168960806472</v>
+        <v>0.0706761471774866</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0674003908009046</v>
+        <v>0.0694531133385863</v>
       </c>
       <c r="H13" t="s">
-        <v>3015</v>
+        <v>3020</v>
       </c>
       <c r="I13" t="n">
-        <v>115</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3016</v>
+        <v>3021</v>
       </c>
       <c r="B14" t="s">
-        <v>3017</v>
+        <v>3022</v>
       </c>
       <c r="C14" t="s">
-        <v>3018</v>
+        <v>3023</v>
       </c>
       <c r="D14" t="s">
-        <v>3019</v>
+        <v>3024</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000805887058538778</v>
+        <v>0.000782614917638267</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0712529553625675</v>
+        <v>0.0706761471774866</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0694834014472064</v>
+        <v>0.0694531133385863</v>
       </c>
       <c r="H14" t="s">
-        <v>3020</v>
+        <v>3025</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3021</v>
+        <v>3026</v>
       </c>
       <c r="B15" t="s">
-        <v>3022</v>
+        <v>3027</v>
       </c>
       <c r="C15" t="s">
-        <v>3023</v>
+        <v>3028</v>
       </c>
       <c r="D15" t="s">
-        <v>3024</v>
+        <v>3029</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000863672186212939</v>
+        <v>0.00121034372400314</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0712529553625675</v>
+        <v>0.101495966569977</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0694834014472064</v>
+        <v>0.0997396031208601</v>
       </c>
       <c r="H15" t="s">
-        <v>3025</v>
+        <v>3030</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
